--- a/infor-workflows/templates/INFOR Comps Template.xlsx
+++ b/infor-workflows/templates/INFOR Comps Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inforfg1-my.sharepoint.com/personal/twilson_inforfg_com/Documents/Desktop/Claude - INFOR/excel-templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inforfg1-my.sharepoint.com/personal/twilson_inforfg_com/Documents/Desktop/Claude Access Folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="535" documentId="8_{44689429-9083-4319-AF07-3319705600A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2435C9DB-007F-45E8-A4CF-E7A6247EF222}"/>
+  <xr:revisionPtr revIDLastSave="602" documentId="8_{44689429-9083-4319-AF07-3319705600A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72B23130-0E5C-4E73-886F-1BBB6977EEE9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="__snloffice" sheetId="2" state="veryHidden" r:id="rId1"/>
@@ -1084,7 +1084,7 @@
     <definedName name="MLNK4fd2e3ceac464726b63c904de1f9a796" hidden="1">#REF!</definedName>
     <definedName name="MLNK56b240f41d2942fcb9b403b5a476a7d8" hidden="1">#REF!</definedName>
     <definedName name="MLNK5ba01ab6b2dd4c4f94bf60093b153ee4" hidden="1">#REF!</definedName>
-    <definedName name="MLNK5e5ab4f18b104bcaa26dfc9b8edd8d3d" hidden="1">Comps!$D$6:$AL$25</definedName>
+    <definedName name="MLNK5e5ab4f18b104bcaa26dfc9b8edd8d3d" hidden="1">Comps!$D$6:$AL$39</definedName>
     <definedName name="MLNK5ec79545d49d493f93a2420475c22a3f" hidden="1">#REF!</definedName>
     <definedName name="MLNK5f342b94d77944659b1ef5a7dbaef93a" hidden="1">#REF!</definedName>
     <definedName name="MLNK601c1ef95cb34d09b82b1a6ff7d9605a" hidden="1">#REF!</definedName>
@@ -1094,7 +1094,7 @@
     <definedName name="MLNK8ad5f35a4bfd46728c3273a4d5c7a905" hidden="1">#REF!</definedName>
     <definedName name="MLNK90417d75114a48c0a1779bb363a329cd" hidden="1">#REF!</definedName>
     <definedName name="MLNK90bd4aad386a4451b6d8702c11dda57c" hidden="1">#REF!</definedName>
-    <definedName name="MLNK94d282c0cd3c43fb89fa5c845ea3d8b5" hidden="1">Comps!$D$6:$AL$28</definedName>
+    <definedName name="MLNK94d282c0cd3c43fb89fa5c845ea3d8b5" hidden="1">Comps!$D$6:$AL$42</definedName>
     <definedName name="MLNK96eba42b27654b0c96a777c2b1f2c026" hidden="1">#REF!</definedName>
     <definedName name="MLNK9c76f014126946d781f4ec0cf20e8cb4" hidden="1">#REF!</definedName>
     <definedName name="MLNK9ff9d28edd3148e7a8cba265311858fd" hidden="1">#REF!</definedName>
@@ -1140,7 +1140,7 @@
     <definedName name="noname" hidden="1">{#N/A,#N/A,FALSE,"Euromat"}</definedName>
     <definedName name="OOO" hidden="1">{"Total Credit",#N/A,FALSE,"Credit";"Appraisal",#N/A,FALSE,"Credit";"Customer Service",#N/A,FALSE,"Credit";"Home Office",#N/A,FALSE,"Credit";"Quality Control",#N/A,FALSE,"Credit";"Risk Mgmt",#N/A,FALSE,"Credit"}</definedName>
     <definedName name="PPP" hidden="1">{"Total East",#N/A,FALSE,"East";"Atlanta",#N/A,FALSE,"East";"Baltimore",#N/A,FALSE,"East";"Charlotte",#N/A,FALSE,"East";"Maitland",#N/A,FALSE,"East";"Marlton Admin",#N/A,FALSE,"East";"Marlton Sales",#N/A,FALSE,"East";"Pittsburgh",#N/A,FALSE,"East";"Plymouth Meeting",#N/A,FALSE,"East";"Raleigh",#N/A,FALSE,"East";"Richmond",#N/A,FALSE,"East";"Tampa",#N/A,FALSE,"East";"White Plains",#N/A,FALSE,"East"}</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Comps!$A$1:$CG$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Comps!$A$1:$CG$42</definedName>
     <definedName name="Q" hidden="1">{"Total East",#N/A,FALSE,"East";"Atlanta",#N/A,FALSE,"East";"Baltimore",#N/A,FALSE,"East";"Charlotte",#N/A,FALSE,"East";"Maitland",#N/A,FALSE,"East";"Marlton Admin",#N/A,FALSE,"East";"Marlton Sales",#N/A,FALSE,"East";"Pittsburgh",#N/A,FALSE,"East";"Plymouth Meeting",#N/A,FALSE,"East";"Raleigh",#N/A,FALSE,"East";"Richmond",#N/A,FALSE,"East";"Tampa",#N/A,FALSE,"East";"White Plains",#N/A,FALSE,"East"}</definedName>
     <definedName name="QQQ" hidden="1">{"NHEC",#N/A,FALSE,"NHEC"}</definedName>
     <definedName name="RO" hidden="1">{#N/A,#N/A,FALSE,"WCI - Bud - Fin. Sum. ";"Summary",#N/A,FALSE,"Summary (g)";"GM with comments",#N/A,FALSE,"GM by Client";"Program Notes",#N/A,FALSE,"Summary (g)";"Risk",#N/A,FALSE,"Summary (g)";#N/A,#N/A,FALSE,"COS by Client by CC";"GM by month",#N/A,FALSE,"GM by Client";#N/A,#N/A,FALSE,"Salaries";#N/A,#N/A,FALSE,"HO Sch 1";"Growth PL sum",#N/A,FALSE,"WCI - Bud - P&amp;L with Growth";#N/A,#N/A,FALSE,"3 CCs"}</definedName>
@@ -1307,12 +1307,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="59">
   <si>
     <t>Currency:</t>
-  </si>
-  <si>
-    <t>USD</t>
   </si>
   <si>
     <t>EV/Revenue</t>
@@ -1474,13 +1471,19 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Group 2</t>
+    <t>[Group #1]</t>
   </si>
   <si>
-    <t>Group 1</t>
+    <t>[Group #2]</t>
   </si>
   <si>
-    <t>允䅁䝁䅣䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䕁䅕兖卂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅐䅁䅁䅙䅁瑁䍁䄰䅁㉁䅁䅁杁䅁䅁䅁杒䅁䑁䅧䅁橁䕁䅫杔坂䕁䅅䅔䩂䕁䅑䅉䝂䙁䅕杔䑂䙁䅑兓偂䕁䄴䅉兂䕁䅅杕䉂䕁䄰兒啂䕁䅕杕䅁䅁䅑䅁煁䅁䅁杓兂䕁䄰睢祂䝁䅣兙畂䍁䅁睑潂䝁䅅督求䍁䅁杊杁䕁䅍睢畁䅁䅁杔䅁䕁䅯䅁䑂䙁䅫杍睁䑁䅉䅎ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䙁䅧䅁坁䅁䅁䅍㉁䍁䄸免睁䍁䄸杍睁䑁䅉兎䅁䅁䅕䅁奁䅁䅁䅋睁䑁䅅兌䭂䝁䅅杢瑁䑁䅉兎灁䅁䅁杂䅁䑁䅉䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兒噂䙁䅉䅌杁䕁䄴兑㥁䍁䄰兌䅁䑁䄸䅁捂䅁䅁杒剂䑁䅁䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰兔灂䝁䅷䅢灂䝁䄸杢穂䍁䅷䅉佂䕁䅅児瑁䍁䄰䅁兂䅁䅁杙䅁䕁䅍兗祁䑁䅁杍ㅁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁睔䅁䅁䅑䅁瑁䅁䅁䅎䅁䑁䅑䅁䑂䙁䅫杍睁䑁䅉李ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅖䅁䅁䅧䅁䑂䕁䅅䅒䅁䅁䅫䅁佁䅁䅁睑婂䑁䅉䅍祁䑁䅑䅁呁䅁䅁䅎䅁䕁䅍兗祁䑁䅁杍ぁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉佂䕁䅅児瑁䍁䄰䅁卂䅁䅁杄䅁䕁䅍兗祁䑁䅁杍㉁䅁䅁兆䅁䝁䅉䅁䑂䙁䅫杍睁䑁䅉䅎ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁兔桂䝁䅣児乂䝁䅫䅢獂䝁䅫睢畂䡁䅍䅌杁䕁䄴兑㥁䍁䄰兌䅁䙁䅅䅁浂䅁䅁睑婂䑁䅉䅍祁䑁䅑䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰兔灂䝁䅷䅢灂䝁䄸杢穂䍁䅷䅉佂䕁䅅児佂䙁䅕䅔䵂䅁䅁兖䅁䕁䅙䅁䑂䙁䅫杍睁䑁䅉䅎ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅘䅁䅁䅧䅁䝂䙁䅅䅍䅁䅁䄸䅁䭂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児卂䝁䅕䅣療䡁䅉䅤求䝁䅑䅉䑂䡁䅕杣祂䝁䅕杢橂䡁䅫䅌佂䕁䅅児瑁䍁䄰䅁㙁䅁䅁杄䅁䕁䅍兗祁䑁䅁杍ㅁ䅁䅁䅆䅁䙁䅑䅁䱂䝁䄴兡湂䝁䅧䅤瑁䙁䅍睤灂䝁䅙䅤杁䙁䅑杣桂䝁䄴督睂䝁䄸杣あ䝁䅅䅤灂䝁䄸杢杁䕁䅧睢獂䝁䅑兡畂䝁䅣督杁䕁䅫杢橂䍁䄴䅁潁䅁䅁䅎䅁䕁䅍兗祁䑁䅁杍ㅁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉佂䕁䅅児瑁䍁䄰䅁呂䅁䅁杚䅁䕁䅍兗祁䑁䅁杍ㅁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䙁䅙䅁䭂䅁䅁睑婂䑁䅉䅍祁䑁䅕䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁婂䅁䅁杈䅁䕁䄴兑呂䕁䅑兑剂䕁䅣睕㙁䕁䄰杕啂䕁䄴䅉䅁䍁䄰䅁楂䅁䅁睑婂䑁䅉䅍祁䑁䅙䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰兔灂䝁䅷䅢灂䝁䄸杢穂䍁䅷䅉佂䕁䅅児瑁䍁䄰䅁扂䅁䅁杅䅁䕁䄴兗呂䕁䅕杏䩂䕁䅉兔䅁䕁䅣䅁佁䅁䅁睑婂䑁䅉䅍祁䑁䅣䅁桂䅁䅁杚䅁䕁䅍兗祁䑁䅁杍㉁䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䙁䅣䅁䭂䅁䅁睑婂䑁䅉䅍祁䑁䅙䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁慂䅁䅁䅍䅁䕁䅧党桂䡁䅉䅤獂䝁䅅杢歂䍁䅁兒㑂䡁䅁杣求䡁䅍督獁䍁䅁兓畂䝁䅍杌䅁䍁䅷䅁䥁䅁䅁兓䍂䕁䄰䅁䩂䅁䅁杈䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䕁䄴兑䅁䅁䅍䅁捁䅁䅁兓剂䙁䄸睑䉂䙁䅍䅓時䕁䅕兕噂䕁䅫杖䅁䑁䄰䅁捁䅁䅁杔䉂䙁䅍䅒䉂䙁䅅睒呂䑁䅯䅓啂䕁䅷䅒䅁䍁䅳䅁歁䅁䅁兓剂䙁䄸睑䉂䙁䅍䅓時䙁䅍䅖時䕁䅫杔坂䕁䅕睕啂䅁䅁充䅁䅁䄴䅁䩂䙁䅅睘啂䕁䅕杖䅁䅁䅷䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅏䅁䉁䅷䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉佂䕁䅅児瑁䅁䅁睍䅁䙁䅁䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰䅖潂䝁䄸兤穂䝁䅅杢歂䡁䅍䅌杁䕁䄴兑㥁䕁䄴兑䅁䉁䄰䅁捁䅁䅁兓剂䙁䄸䅖偂䙁䅑兑䵂䙁䄸䅒䙂䕁䅉䅖䅁䙁䄴䅁杁䅁䅁兓剂䙁䄸䅖偂䙁䅑兑䵂䙁䄸兒剂䙁䅕兓啂䙁䅫䅁摂䅁䅁䅗䅁䕁䅫杢あ䝁䅕杣畂䝁䅅䅤灂䝁䄸杢桂䝁䅷䅉䍂䡁䅕督灂䝁䄴党穂䡁䅍䅉乂䝁䅅睙潂䝁䅫杢求䡁䅍䅉䑂䝁䄸杣睂䝁䄸杣桂䡁䅑兡療䝁䄴䅁䭂䅁䅁杒䅁䕁䅯杌䍂䍁䄴䅉䥂䡁䅕杢あ䍁䅁䅖祂䝁䅅杢穂䡁䅁睢祂䡁䅑䅉呂䝁䅕杣㉂䝁䅫睙求䡁䅍䅌杁䕁䅫杢橂䍁䄴䅁楁䅁䅁杂䅁䕁䄴兑䅁䉁䅣䅁䥁䅁䅁杓兂䕁䄰䅁乂䅁䅁杌䅁䕁䄰兙祂䡁䅑党畂䍁䅁䅖祂䝁䅅杢穂䡁䅁睢祂䡁䅑䅌杁䕁䅷䅤歂䍁䄴䅁畁䅁䅁䅊䅁䕁䄰兤獂䝁䅷党畂䍁䅁睒祂䝁䄸兤睂䍁䅁䅔あ䝁䅑杌䅁䍁䅁䅁兂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䙁䅑䅡療䡁䅕督桂䝁䄴䅚穂䍁䅷䅉佂䕁䅅児瑁䍁䄰䅁㝁䅁䅁杈䅁䕁䄴兑呂䕁䅑兑剂䕁䅣睕㙁䕁䅯村䥂䙁䅑䅉䅁䍁䅅䅁允䅁䅁䅖呂䙁䅧杏乂䙁䅑䅔䅁䉁䄸䅁啁䅁䅁杔婂䙁䅍兒㙁䙁䅍杔䕂䙁䅉䅁橁䅁䅁杈䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䍁䄰兌䅁䑁䅕䅁捁䅁䅁杔䉂䙁䅍䅒䉂䙁䅅睒呂䑁䅯睖䙂䙁䅉杔䅁䍁䅫䅁䭁䅁䅁杔噂䕁䅷䅔䅁䕁䅍䅁啁䅁䅁杔婂䙁䅍兒㙁䕁䅳杔奂䍁䅁䅁湁䅁䅁杅䅁䕁䄴兗呂䕁䅕杏奂䙁䅁睔䅁䍁䅕䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁䅉䑂䡁䅕杣祂䑁䄰杕求䡁䅁睢祂䡁䅑党歂䍁䅁睑ㅂ䡁䅉杣求䝁䄴睙㕂䍁䅷杔䉂䑁䄰杔䉂䅁䅁睌䅁䑁䅉䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兒噂䙁䅉䅌杁䕁䄴兑㥁䕁䄴兑䅁䉁䅳䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔䉂䅁䅁睃䅁䑁䅉䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䍁䄰兌䅁䑁䅣䅁祁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉佂䕁䅅児佂䕁䅅䅁䡁䅁䅁杉䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁䙂䅁䅁杉䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䕁䄴兤獂䝁䅷䅁㕁䅁䅁杌䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰睑䉂䕁䅑䅌佂䕁䅅児瑁䍁䄰䅁䱂䅁䅁杓䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰杕求䡁䅁睢祂䡁䅑党歂䍁䅁睑ㅂ䡁䅉杣求䝁䄴睙㕂䍁䅷杔䉂䑁䄰杔䉂䅁䅁免䅁䕁䅷䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅑䅁䙁䅁䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔噂䍁䄰兌䅁䕁䅧䅁兂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁兔桂䝁䅣児乂䝁䅫䅢獂䝁䅫睢畂䡁䅍䅌杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁䕂䅁䅁䅍䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䍁䄰兌䅁䕁䅅䅁ぁ䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䕁䅉䅁畁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䕁䄴兑㥁䍁䄰兌䅁䕁䅷䅁捁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䄴兑㥁䕁䄴兑䅁䑁䅁䅁捁䅁䅁睕兂䙁䄸睑䉂䙁䅍䅓時䕁䅕兕噂䕁䅫杖䅁䑁䄴䅁奁䅁䅁睕兂䙁䄸睑䝂䙁䅁睕時䕁䅕睕啂䅁䅁䅈䅁䍁䅁䅁呂䙁䅁睘䑂䕁䄸兔兂䕁䅅杔婂䙁䄸杔䉂䕁䄰兒䅁䅁䅁䅁慁䅁䅁睕兂䙁䄸䅒䩂䙁䅙睘婂䕁䅫兒䵂䕁䅑䅁乁䅁䅁䅈䅁䙁䅍䅕時䕁䅕村䩂䙁䅑䅒䉂䙁䄸兒呂䙁䅑䅁婁䅁䅁杆䅁䙁䅍䅕時䕁䅕䅕呂䙁䄸兒呂䙁䅑䅁慁䅁䅁䅋䅁䙁䅍䅕時䕁䅣杕偂䙁䅍睕時䕁䄰兑卂䕁䅣兓佂䙁䄸兒呂䙁䅑䅁坁䅁䅁䅍䅁䙁䅍䅕時䕁䅣杕偂䙁䅍睕時䕁䄰兑卂䕁䅣兓佂䙁䄸杔噂䕁䄰睘䙂䙁䅍䅖䅁䉁䅧䅁楁䅁䅁睕兂䙁䄸䅔䉂䙁䅍䅖呂䕁䅅䅔䙂䙁䅁杕䩂䕁䅍兒䅁䅁䅉䅁慁䅁䅁睕兂䙁䄸兔䉂䙁䅉睓䙂䙁䅑睑䉂䙁䅁䅁䭁䅁䅁杈䅁䙁䅍䅕時䙁䅁杕䩂䕁䅍兒時䕁䅍䅔偂䙁䅍兒䅁䙁䄸䅁坁䅁䅁睕兂䙁䄸杕䙂䙁䅙睘䙂䙁䅍䅖䅁䉁䅉䅁捁䅁䅁睕兂䙁䄸䅖偂䙁䅑兑䵂䙁䄸䅒䙂䕁䅉䅖䅁䉁䅁䅁杁䅁䅁睕兂䙁䄸䅖偂䙁䅑兑䵂䙁䄸兒剂䙁䅕兓啂䙁䅫䅁佁䅁䅁䅋䅁䙁䅍䅕時䙁䅑杕䉂䕁䅑兓佂䕁䅣睘䑂䙁䅕杕卂䕁䅕杔䑂䙁䅫䅁䥁䅁䅁杍䅁䙁䅍睙潂䝁䄴党灂䝁䅑党祂䍁䅁杔桂䡁䅑兡療䝁䄴兙獂䍁䅷䅉䩂䝁䄴睙畁䅁䅁䅊䅁䍁䄴䅁啂䕁䅙兓杁䕁䅫杢あ䝁䅕杣畂䝁䅅䅤灂䝁䄸杢桂䝁䅷䅉䩂䝁䄴睙畁䅁䅁允䅁䉁䅉䅁啂䙁䅍䅗㙁䙁䅑杒䩂䕁䅫䅁敁䅁䅁䅃䅁䙁䅕睕䕂䅁䅁杍䅁䑁䅉䅁塂䝁䅕杣畂䝁䅕杣杁䕁䅕杢あ䝁䅕杣睂䡁䅉兡穂䝁䅕督獁䍁䅁兓畂䝁䅍杌䅁䍁䅯䅁啁䅁䅁䅗兂䕁䄸䅌杁䕁䅫杢橂䍁䄴䅁流䅁䅁杄䅁䝁䅍入祁䑁䅁杍ㅁ䅁䅁䅙䅁䅁䄴䅁䩂䙁䅅睘卂䕁䅕杖䅁䝁䅉䅁䥁䅁䅁䅔啂䕁䄰䅁橂䅁䅁䅆䅁䙁䅍䅕時䕁䅕村䩂䙁䅑䅒䉂䅁䅁䅚䅁䉁䅉䅁啂䙁䅍䅗㙁䕁䄸䅖䙂䙁䅧䅁求䅁䅁䅌䅁䕁䄸䅣求䝁䄴䅉啂䝁䅕䅥あ䍁䅁睑療䡁䅉䅣療䡁䅉兙あ䝁䅫睢畂䅁䅁杚䅁䉁䄴䅁䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权十䅁䅁权桂䅁䅁兂䅁䅁䅁䥙浌䅑䅯䅑䅁䅁䅅䅁䉁䅁䅁兂㉁穱堵㝃か䅑杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䙁䄰䅁䭁䅁䄸䅁䙁䅁䅁䅁杂畧䅚权䅂䅁䅁允䅁䅁䅅䅁䙁䕁ㅁ牘䩲煭䄹䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯杆䅁䅁䅯兙䅁䅁䅕䅁䅁䝁䍃欵䭁䑁䅕䅁䉁䅁䅁允䅁䅁䅯李䅁䅁杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䉁䅯䅁䭁䉁䅑䅁䙁䅁䅁䅁杂畧䅚权䉂䅁䅁允䅁䅁䅅䅁䙁䙁⬳⽑瑲眶䄵䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯杇䅁䅁䅯兙䅁䅁䅕䅁䅁䝁䍃欵䭁䕁䅅䅁䉁䅁䅁允䅁䅁䅕呴㑦海煒歅䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权捁䅁䅁权噁䅁䅁兂䅁䅁䅁䥙浌䅑䅯兑䅁䅁䅅䅁䉁䅁䅁兂乄䵺䵺䵺剷䅑杷允䅁䅁䅕䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䅁䄰䅁䙁䅁䅁䅁杂畧䅚权ㅁ䅁䅁允䅁䅁䅅䅁䙁佁䱚㕺䩺硊䅎䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯杆䅁䅁䅯兆䅁䅁䅕䅁䅁䝁䍃欵䭁䑁䅕䅁䉁䅁䅁允䅁䅁䅯李䅁䅁杷允䅁䅁䅑䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䅁䅧䅁䭁䑁䅕䅁䉁䅁䅁允䅁䅁䅯元䅁䅁杷允䅁䅁䅕䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䅁䅷䅁䙁䅁䅁䅁杂畧䅚权䅂䅁䅁允䅁䅁䅅䅁䙁䝁浍单欯䵫䅖䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯兇䅁䅁䅯兆䅁䅁䅕䅁䅁䝁䍃欵䭁䕁䅁䅁䉁䅁䅁允䅁䅁䅕⭙愵牑椷䕮䵁䅉䅅䅁䙁䅁䅁睁䵁䅁䅁权求䅁䅁权時䅁䅁兂䅁䅁䅁䥙浌䅑䅯兑䅁䅁䅅䅁䉁䅁䅁兂灄爳㝢䅒㍅䅑杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䉁䅷䅁䭁䉁䅑䅁䙁䅁䅁䅁杂畧䅚权䉂䅁䅁允䅁䅁䅅䅁䙁偁橆䙺䰱䅓䅸䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯权䅁䅁䅕䅁䅁䝁䍃欵䭁䕁䅁䅁䉁䅁䅁允䅁䅁䅕楩楊煕婚歴䵁䅉䅅䅁䙁䅁䅁睁䵁䅁䅁权求䅁䅁权䍁䅁䅁兂䅁䅁䅁䥙浌䅑䅯睓䅁䅁䅅䅁䉁䅁䅁兂䅁䅁䅁䥁⽁䅑杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䙁䄴䅁䭁䅁䄸䅁䙁䅁䅁䅁杂畧䅚权䅂䅁䅁允䅁䅁䅅䅁䙁䩁契䙂佢牷䅬䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯充䅁䅁䅯睄䅁䅁䅕䅁䅁䝁䍃欵䭁䕁䅁䅁䉁䅁䅁允䅁䅁䅕䭃捷畗硔に䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权婁䅁䅁权桂䅁䅁兂䅁䅁䅁䥙浌䅑䅯䅑䅁䅁䅅䅁䉁䅁䅁兂啃䅇坒歔敃䅑杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䝁䅉䅁䭁䝁䅍䅁䙁䅁䅁䅁杂畧䅚权䅂䅁䅁允䅁䅁䅅䅁䙁䑁䩥坑䙄㝏䅒䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯杅䅁䅁䅯䅆䅁䅁䅕䅁䅁䝁䍃欵䭁䕁䅁䅁䉁䅁䅁允䅁䅁䅕報灪湊啅䕴䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权十䅁䅁权噁䅁䅁兂䅁䅁䅁䥙浌䅑䅯䅑䅁䅁䅅䅁䉁䅁䅁兂坃杳硸䙄〲䅑杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䝁䅑䅁䭁䝁䅍䅁䙁䅁䅁䅁杂畧䅚权䅂䅁䅁允䅁䅁䅅䅁䙁䱁䥔牤昶㕴䅤䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯兇䅁䅁䅯䅆䅁䅁䅕䅁䅁䝁䍃欵䭁䕁䅁䅁䉁䅁䅁允䅁䅁䅕娳䡏摨摱ね䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权坁䅁䅁权啁䅁䅁兂䅁䅁䅁䥙浌䅑䅯兎䅁䅁䅅䅁䉁䅁䅁权㉁䅁䅁䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯䅇䅁䅁䅯䅆䅁䅁䅕䅁䅁䝁䍃欵䭁䑁䅕䅁䉁䅁䅁允䅁䅁䅯李䅁䅁杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䉁䅧䅁䭁䝁䅅䅁䙁䅁䅁䅁杂畧䅚权ㅁ䅁䅁允䅁䅁䅅䅁䭁䑁䅙䅁䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权奁䅁䅁权噁䅁䅁兂䅁䅁䅁䥙浌䅑䅯兎䅁䅁䅅䅁䉁䅁䅁权㉁䅁䅁䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯杇䅁䅁䅯兆䅁䅁䅕䅁䅁䝁䍃欵䭁䕁䅅䅁䉁䅁䅁允䅁䅁䅕ㅧ䩆奮浃䕅䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权捁䅁䅁权桂䅁䅁兂䅁䅁䅁䥙浌䅑䅯兑䅁䅁䅅䅁䉁䅁䅁权㉁䅁䅁䍄䉁䅁䅁睁䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯䅁䅁䅁䅅䅁䉁䅁䅁权浂䅁䅁</t>
+    <t>[Group #3]</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>允䅁䝁䅣䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䕁䅕兖卂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅐䅁䅁䅙䅁瑁䍁䄰䅁㉁䅁䅁杁䅁䅁䅁杒䅁䑁䅧䅁橁䕁䅫杔坂䕁䅅䅔䩂䕁䅑䅉䝂䙁䅕杔䑂䙁䅑兓偂䕁䄴䅉兂䕁䅅杕䉂䕁䄰兒啂䕁䅕杕䅁䅁䅑䅁煁䅁䅁杓兂䕁䄰睢祂䝁䅣兙畂䍁䅁睑潂䝁䅅督求䍁䅁杊杁䕁䅍睢畁䅁䅁杔䅁䕁䅯䅁䑂䙁䅫杍睁䑁䅉䅎ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䙁䅧䅁坁䅁䅁䅍㉁䍁䄸免睁䍁䄸杍睁䑁䅉兎䅁䅁䅕䅁奁䅁䅁䅋睁䑁䅅兌䭂䝁䅅杢瑁䑁䅉兎灁䅁䅁杂䅁䑁䅉䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兒噂䙁䅉䅌杁䕁䄴兑㥁䍁䄰兌䅁䑁䄸䅁捂䅁䅁杒剂䑁䅁䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰兔灂䝁䅷䅢灂䝁䄸杢穂䍁䅷䅉佂䕁䅅児瑁䍁䄰䅁兂䅁䅁杙䅁䕁䅍兗祁䑁䅁杍ㅁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁睔䅁䅁䅑䅁瑁䅁䅁䅎䅁䑁䅑䅁䑂䙁䅫杍睁䑁䅉李ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅖䅁䅁䅧䅁䑂䕁䅅䅒䅁䅁䅫䅁佁䅁䅁睑婂䑁䅉䅍祁䑁䅑䅁呁䅁䅁䅎䅁䕁䅍兗祁䑁䅁杍ぁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉佂䕁䅅児瑁䍁䄰䅁卂䅁䅁杄䅁䕁䅍兗祁䑁䅁杍㉁䅁䅁兆䅁䝁䅉䅁䑂䙁䅫杍睁䑁䅉䅎ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁兔桂䝁䅣児乂䝁䅫䅢獂䝁䅫睢畂䡁䅍䅌杁䕁䄴兑㥁䍁䄰兌䅁䙁䅅䅁浂䅁䅁睑婂䑁䅉䅍祁䑁䅑䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰兔灂䝁䅷䅢灂䝁䄸杢穂䍁䅷䅉佂䕁䅅児佂䙁䅕䅔䵂䅁䅁兖䅁䕁䅙䅁䑂䙁䅫杍睁䑁䅉䅎ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅘䅁䅁䅧䅁䝂䙁䅅䅍䅁䅁䄸䅁䭂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児卂䝁䅕䅣療䡁䅉䅤求䝁䅑䅉䑂䡁䅕杣祂䝁䅕杢橂䡁䅫䅌佂䕁䅅児瑁䍁䄰䅁㙁䅁䅁杄䅁䕁䅍兗祁䑁䅁杍ㅁ䅁䅁䅆䅁䙁䅑䅁䱂䝁䄴兡湂䝁䅧䅤瑁䙁䅍睤灂䝁䅙䅤杁䙁䅑杣桂䝁䄴督睂䝁䄸杣あ䝁䅅䅤灂䝁䄸杢杁䕁䅧睢獂䝁䅑兡畂䝁䅣督杁䕁䅫杢橂䍁䄴䅁潁䅁䅁䅎䅁䕁䅍兗祁䑁䅁杍ㅁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉佂䕁䅅児瑁䍁䄰䅁呂䅁䅁杚䅁䕁䅍兗祁䑁䅁杍ㅁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䙁䅙䅁䭂䅁䅁睑婂䑁䅉䅍祁䑁䅕䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁婂䅁䅁杈䅁䕁䄴兑呂䕁䅑兑剂䕁䅣睕㙁䕁䄰杕啂䕁䄴䅉䅁䍁䄰䅁楂䅁䅁睑婂䑁䅉䅍祁䑁䅙䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰兔灂䝁䅷䅢灂䝁䄸杢穂䍁䅷䅉佂䕁䅅児瑁䍁䄰䅁扂䅁䅁杅䅁䕁䄴兗呂䕁䅕杏䩂䕁䅉兔䅁䕁䅣䅁佁䅁䅁睑婂䑁䅉䅍祁䑁䅣䅁桂䅁䅁杚䅁䕁䅍兗祁䑁䅁杍㉁䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䙁䅣䅁䭂䅁䅁睑婂䑁䅉䅍祁䑁䅙䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁慂䅁䅁䅍䅁䕁䅧党桂䡁䅉䅤獂䝁䅅杢歂䍁䅁兒㑂䡁䅁杣求䡁䅍督獁䍁䅁兓畂䝁䅍杌䅁䍁䅷䅁䥁䅁䅁兓䍂䕁䄰䅁䩂䅁䅁杈䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䕁䄴兑䅁䅁䅍䅁捁䅁䅁兓剂䙁䄸睑䉂䙁䅍䅓時䕁䅕兕噂䕁䅫杖䅁䑁䄰䅁捁䅁䅁杔䉂䙁䅍䅒䉂䙁䅅睒呂䑁䅯䅓啂䕁䅷䅒䅁䍁䅳䅁歁䅁䅁兓剂䙁䄸睑䉂䙁䅍䅓時䙁䅍䅖時䕁䅫杔坂䕁䅕睕啂䅁䅁充䅁䅁䄴䅁䩂䙁䅅睘啂䕁䅕杖䅁䅁䅷䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅏䅁䉁䅷䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉佂䕁䅅児瑁䅁䅁睍䅁䙁䅁䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰䅖潂䝁䄸兤穂䝁䅅杢歂䡁䅍䅌杁䕁䄴兑㥁䕁䄴兑䅁䉁䄰䅁捁䅁䅁兓剂䙁䄸䅖偂䙁䅑兑䵂䙁䄸䅒䙂䕁䅉䅖䅁䙁䄴䅁杁䅁䅁兓剂䙁䄸䅖偂䙁䅑兑䵂䙁䄸兒剂䙁䅕兓啂䙁䅫䅁摂䅁䅁䅗䅁䕁䅫杢あ䝁䅕杣畂䝁䅅䅤灂䝁䄸杢桂䝁䅷䅉䍂䡁䅕督灂䝁䄴党穂䡁䅍䅉乂䝁䅅睙潂䝁䅫杢求䡁䅍䅉䑂䝁䄸杣睂䝁䄸杣桂䡁䅑兡療䝁䄴䅁䭂䅁䅁杒䅁䕁䅯杌䍂䍁䄴䅉䥂䡁䅕杢あ䍁䅁䅖祂䝁䅅杢穂䡁䅁睢祂䡁䅑䅉呂䝁䅕杣㉂䝁䅫睙求䡁䅍䅌杁䕁䅫杢橂䍁䄴䅁楁䅁䅁杂䅁䕁䄴兑䅁䉁䅣䅁䥁䅁䅁杓兂䕁䄰䅁乂䅁䅁杌䅁䕁䄰兙祂䡁䅑党畂䍁䅁䅖祂䝁䅅杢穂䡁䅁睢祂䡁䅑䅌杁䕁䅷䅤歂䍁䄴䅁畁䅁䅁䅊䅁䕁䄰兤獂䝁䅷党畂䍁䅁睒祂䝁䄸兤睂䍁䅁䅔あ䝁䅑杌䅁䍁䅁䅁兂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䙁䅑䅡療䡁䅕督桂䝁䄴䅚穂䍁䅷䅉佂䕁䅅児瑁䍁䄰䅁㝁䅁䅁杈䅁䕁䄴兑呂䕁䅑兑剂䕁䅣睕㙁䕁䅯村䥂䙁䅑䅉䅁䍁䅅䅁允䅁䅁䅖呂䙁䅧杏乂䙁䅑䅔䅁䉁䄸䅁啁䅁䅁杔婂䙁䅍兒㙁䙁䅍杔䕂䙁䅉䅁橁䅁䅁杈䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䍁䄰兌䅁䑁䅕䅁捁䅁䅁杔䉂䙁䅍䅒䉂䙁䅅睒呂䑁䅯睖䙂䙁䅉杔䅁䍁䅫䅁䭁䅁䅁杔噂䕁䅷䅔䅁䕁䅍䅁啁䅁䅁杔婂䙁䅍兒㙁䕁䅳杔奂䍁䅁䅁湁䅁䅁杅䅁䕁䄴兗呂䕁䅕杏奂䙁䅁睔䅁䍁䅕䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁䅉䑂䡁䅕杣祂䑁䄰杕求䡁䅁睢祂䡁䅑党歂䍁䅁睑ㅂ䡁䅉杣求䝁䄴睙㕂䍁䅷杔䉂䑁䄰杔䉂䅁䅁睌䅁䑁䅉䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兒噂䙁䅉䅌杁䕁䄴兑㥁䕁䄴兑䅁䉁䅳䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔䉂䅁䅁睃䅁䑁䅉䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䍁䄰兌䅁䑁䅣䅁祁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉佂䕁䅅児佂䕁䅅䅁䡁䅁䅁杉䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁䙂䅁䅁杉䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䕁䄴兤獂䝁䅷䅁㕁䅁䅁杌䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰睑䉂䕁䅑䅌佂䕁䅅児瑁䍁䄰䅁䱂䅁䅁杓䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰杕求䡁䅁睢祂䡁䅑党歂䍁䅁睑ㅂ䡁䅉杣求䝁䄴睙㕂䍁䅷杔䉂䑁䄰杔䉂䅁䅁免䅁䕁䅷䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅑䅁䙁䅁䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔噂䍁䄰兌䅁䕁䅧䅁兂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁兔桂䝁䅣児乂䝁䅫䅢獂䝁䅫睢畂䡁䅍䅌杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁䕂䅁䅁䅍䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䍁䄰兌䅁䕁䅅䅁ぁ䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䕁䅉䅁畁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䕁䄴兑㥁䍁䄰兌䅁䕁䅷䅁捁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䄴兑㥁䕁䄴兑䅁䑁䅁䅁捁䅁䅁睕兂䙁䄸睑䉂䙁䅍䅓時䕁䅕兕噂䕁䅫杖䅁䑁䄴䅁奁䅁䅁睕兂䙁䄸睑䝂䙁䅁睕時䕁䅕睕啂䅁䅁䅈䅁䍁䅁䅁呂䙁䅁睘䑂䕁䄸兔兂䕁䅅杔婂䙁䄸杔䉂䕁䄰兒䅁䅁䅁䅁慁䅁䅁睕兂䙁䄸䅒䩂䙁䅙睘婂䕁䅫兒䵂䕁䅑䅁乁䅁䅁䅈䅁䙁䅍䅕時䕁䅕村䩂䙁䅑䅒䉂䙁䄸兒呂䙁䅑䅁婁䅁䅁杆䅁䙁䅍䅕時䕁䅕䅕呂䙁䄸兒呂䙁䅑䅁慁䅁䅁䅋䅁䙁䅍䅕時䕁䅣杕偂䙁䅍睕時䕁䄰兑卂䕁䅣兓佂䙁䄸兒呂䙁䅑䅁坁䅁䅁䅍䅁䙁䅍䅕時䕁䅣杕偂䙁䅍睕時䕁䄰兑卂䕁䅣兓佂䙁䄸杔噂䕁䄰睘䙂䙁䅍䅖䅁䉁䅧䅁楁䅁䅁睕兂䙁䄸䅔䉂䙁䅍䅖呂䕁䅅䅔䙂䙁䅁杕䩂䕁䅍兒䅁䅁䅉䅁慁䅁䅁睕兂䙁䄸兔䉂䙁䅉睓䙂䙁䅑睑䉂䙁䅁䅁䭁䅁䅁杈䅁䙁䅍䅕時䙁䅁杕䩂䕁䅍兒時䕁䅍䅔偂䙁䅍兒䅁䙁䄸䅁坁䅁䅁睕兂䙁䄸杕䙂䙁䅙睘䙂䙁䅍䅖䅁䉁䅉䅁捁䅁䅁睕兂䙁䄸䅖偂䙁䅑兑䵂䙁䄸䅒䙂䕁䅉䅖䅁䉁䅁䅁杁䅁䅁睕兂䙁䄸䅖偂䙁䅑兑䵂䙁䄸兒剂䙁䅕兓啂䙁䅫䅁佁䅁䅁䅋䅁䙁䅍䅕時䙁䅑杕䉂䕁䅑兓佂䕁䅣睘䑂䙁䅕杕卂䕁䅕杔䑂䙁䅫䅁䥁䅁䅁杍䅁䙁䅍睙潂䝁䄴党灂䝁䅑党祂䍁䅁杔桂䡁䅑兡療䝁䄴兙獂䍁䅷䅉䩂䝁䄴睙畁䅁䅁䅊䅁䍁䄴䅁啂䕁䅙兓杁䕁䅫杢あ䝁䅕杣畂䝁䅅䅤灂䝁䄸杢桂䝁䅷䅉䩂䝁䄴睙畁䅁䅁允䅁䉁䅉䅁啂䙁䅍䅗㙁䙁䅑杒䩂䕁䅫䅁敁䅁䅁䅃䅁䙁䅕睕䕂䅁䅁杍䅁䑁䅉䅁塂䝁䅕杣畂䝁䅕杣杁䕁䅕杢あ䝁䅕杣睂䡁䅉兡穂䝁䅕督獁䍁䅁兓畂䝁䅍杌䅁䍁䅯䅁啁䅁䅁䅗兂䕁䄸䅌杁䕁䅫杢橂䍁䄴䅁流䅁䅁杄䅁䝁䅍入祁䑁䅁杍ㅁ䅁䅁䅙䅁䅁䄴䅁䩂䙁䅅睘卂䕁䅕杖䅁䝁䅉䅁䥁䅁䅁䅔啂䕁䄰䅁橂䅁䅁䅆䅁䙁䅍䅕時䕁䅕村䩂䙁䅑䅒䉂䅁䅁䅚䅁䉁䅉䅁啂䙁䅍䅗㙁䕁䄸䅖䙂䙁䅧䅁求䅁䅁䅌䅁䕁䄸䅣求䝁䄴䅉啂䝁䅕䅥あ䍁䅁睑療䡁䅉䅣療䡁䅉兙あ䝁䅫睢畂䅁䅁杚䅁䅁䅁䅁㵁</t>
   </si>
 </sst>
 </file>
@@ -1498,7 +1501,7 @@
     <numFmt numFmtId="171" formatCode="#,##0_);\(#,##0\);&quot;--&quot;"/>
     <numFmt numFmtId="172" formatCode="#,##0.0_);\(#,##0.0\);&quot;--&quot;"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1557,14 +1560,6 @@
       <u val="singleAccounting"/>
       <sz val="9"/>
       <color theme="0"/>
-      <name val="Palatino Linotype"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="9"/>
-      <color theme="1"/>
       <name val="Palatino Linotype"/>
       <family val="1"/>
     </font>
@@ -1638,14 +1633,6 @@
       <u/>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Palatino Linotype"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
       <name val="Palatino Linotype"/>
       <family val="1"/>
     </font>
@@ -1787,10 +1774,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1817,19 +1804,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1838,28 +1825,28 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1868,13 +1855,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1883,31 +1867,31 @@
     <xf numFmtId="11" fontId="7" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -1916,22 +1900,22 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1970,43 +1954,40 @@
     <xf numFmtId="11" fontId="7" fillId="3" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="11" fontId="7" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="7" fillId="5" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2018,13 +1999,13 @@
     <xf numFmtId="170" fontId="7" fillId="5" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2041,7 +2022,19 @@
     <cellStyle name="Normal 2 3" xfId="4" xr:uid="{1DC0D5DA-9B95-4ABB-BD56-633985D4BCF5}"/>
     <cellStyle name="Note" xfId="1" builtinId="10"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
+    <dxf>
+      <numFmt numFmtId="173" formatCode="\C&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="174" formatCode="[$€-2]#,##0.00_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="173" formatCode="\C&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="174" formatCode="[$€-2]#,##0.00_)"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2071,12 +2064,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="174" formatCode="\C&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="175" formatCode="[$€-2]#,##0.00_)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2359,7 +2346,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2372,7 +2359,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:CF28"/>
+  <dimension ref="B1:CF42"/>
   <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="20.100000000000001" customHeight="1" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
@@ -2384,7 +2371,7 @@
     <col min="11" max="12" width="11.140625" style="2" customWidth="1"/>
     <col min="13" max="21" width="11.42578125" style="2" customWidth="1"/>
     <col min="22" max="38" width="11.42578125" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="39" max="39" width="50.7109375" style="2" customWidth="1" collapsed="1"/>
+    <col min="39" max="39" width="65.7109375" style="2" customWidth="1" collapsed="1"/>
     <col min="40" max="40" width="2.7109375" style="2" customWidth="1"/>
     <col min="41" max="44" width="9.5703125" style="2"/>
     <col min="45" max="45" width="1.5703125" style="2" customWidth="1"/>
@@ -2411,277 +2398,277 @@
     <row r="1" spans="2:84" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:84" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="E2" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="79">
+        <v>49</v>
+      </c>
+      <c r="F2" s="77">
         <f ca="1">TODAY()-1</f>
-        <v>46099</v>
+        <v>46133</v>
       </c>
       <c r="K2" s="10"/>
-      <c r="L2" s="81" t="s">
+      <c r="L2" s="79" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="79"/>
     </row>
     <row r="3" spans="2:84" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="E3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="80" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="39"/>
+      <c r="F3" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="38"/>
       <c r="K3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="L3" s="82">
+        <v>3</v>
+      </c>
+      <c r="L3" s="80">
         <v>0</v>
       </c>
-      <c r="M3" s="82">
+      <c r="M3" s="80">
         <v>0</v>
       </c>
-      <c r="N3" s="82">
+      <c r="N3" s="80">
         <v>0</v>
       </c>
-      <c r="O3" s="82">
+      <c r="O3" s="80">
         <v>0</v>
       </c>
-      <c r="P3" s="82">
+      <c r="P3" s="80">
         <v>0</v>
       </c>
-      <c r="Q3" s="82">
+      <c r="Q3" s="80">
         <v>0</v>
       </c>
-      <c r="R3" s="82">
+      <c r="R3" s="80">
         <v>0</v>
       </c>
-      <c r="S3" s="82">
+      <c r="S3" s="80">
         <v>0</v>
       </c>
-      <c r="AL3" s="70"/>
-      <c r="AM3" s="70"/>
+      <c r="AL3" s="69"/>
+      <c r="AM3" s="69"/>
     </row>
     <row r="4" spans="2:84" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="E4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="74" t="s">
-        <v>52</v>
-      </c>
       <c r="K4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="L4" s="83">
+        <v>4</v>
+      </c>
+      <c r="L4" s="81">
         <v>20</v>
       </c>
-      <c r="M4" s="83">
+      <c r="M4" s="81">
         <v>20</v>
       </c>
-      <c r="N4" s="83">
+      <c r="N4" s="81">
         <v>20</v>
       </c>
-      <c r="O4" s="83">
+      <c r="O4" s="81">
         <v>20</v>
       </c>
-      <c r="P4" s="83">
+      <c r="P4" s="81">
         <v>50</v>
       </c>
-      <c r="Q4" s="83">
+      <c r="Q4" s="81">
         <v>50</v>
       </c>
-      <c r="R4" s="83">
+      <c r="R4" s="81">
         <v>50</v>
       </c>
-      <c r="S4" s="83">
+      <c r="S4" s="81">
         <v>50</v>
       </c>
     </row>
     <row r="5" spans="2:84" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="BR5" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="BS5" s="65"/>
-      <c r="BT5" s="65"/>
-      <c r="BU5" s="65"/>
-      <c r="BV5" s="65"/>
-      <c r="BW5" s="65"/>
-      <c r="BX5" s="65"/>
-      <c r="BZ5" s="40" t="s">
+      <c r="BR5" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="CA5" s="40"/>
-      <c r="CB5" s="40"/>
-      <c r="CC5" s="40"/>
-      <c r="CD5" s="40"/>
-      <c r="CE5" s="40"/>
-      <c r="CF5" s="40"/>
+      <c r="BS5" s="64"/>
+      <c r="BT5" s="64"/>
+      <c r="BU5" s="64"/>
+      <c r="BV5" s="64"/>
+      <c r="BW5" s="64"/>
+      <c r="BX5" s="64"/>
+      <c r="BZ5" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="CA5" s="39"/>
+      <c r="CB5" s="39"/>
+      <c r="CC5" s="39"/>
+      <c r="CD5" s="39"/>
+      <c r="CE5" s="39"/>
+      <c r="CF5" s="39"/>
     </row>
     <row r="6" spans="2:84" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D6" s="3" t="str">
         <f>"(In "&amp;IF(F3="USD","US","C")&amp;"$MM, unless otherwise noted)"</f>
-        <v>(In US$MM, unless otherwise noted)</v>
+        <v>(In C$MM, unless otherwise noted)</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="L6" s="6" t="s">
         <v>9</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>10</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
       <c r="T6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="U6" s="32"/>
+        <v>31</v>
+      </c>
+      <c r="U6" s="31"/>
       <c r="V6" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W6" s="6"/>
       <c r="X6" s="6"/>
       <c r="Y6" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z6" s="6"/>
       <c r="AA6" s="6"/>
       <c r="AB6" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AC6" s="6"/>
       <c r="AD6" s="6"/>
       <c r="AE6" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF6" s="6"/>
       <c r="AG6" s="6"/>
       <c r="AH6" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI6" s="6"/>
       <c r="AJ6" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK6" s="6"/>
-      <c r="AL6" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="AM6" s="33"/>
+      <c r="AL6" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM6" s="32"/>
       <c r="AO6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP6" s="6"/>
       <c r="AQ6" s="6"/>
       <c r="AR6" s="6"/>
       <c r="AT6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU6" s="6"/>
       <c r="AV6" s="6"/>
       <c r="AW6" s="6"/>
       <c r="AY6" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ6" s="6"/>
       <c r="BA6" s="6"/>
       <c r="BC6" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="BD6" s="6"/>
       <c r="BE6" s="6"/>
       <c r="BG6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH6" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BI6" s="5"/>
       <c r="BJ6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="BK6" s="5"/>
       <c r="BL6" s="5"/>
-      <c r="BN6" s="44" t="s">
-        <v>39</v>
+      <c r="BN6" s="43" t="s">
+        <v>38</v>
       </c>
       <c r="BO6" s="6"/>
       <c r="BP6" s="6"/>
-      <c r="BR6" s="44" t="s">
-        <v>36</v>
+      <c r="BR6" s="43" t="s">
+        <v>35</v>
       </c>
       <c r="BS6" s="6"/>
       <c r="BT6" s="6"/>
       <c r="BU6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="BV6" s="44" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="BV6" s="43" t="s">
+        <v>36</v>
       </c>
       <c r="BW6" s="6"/>
       <c r="BX6" s="6"/>
-      <c r="BZ6" s="44" t="s">
-        <v>38</v>
+      <c r="BZ6" s="43" t="s">
+        <v>37</v>
       </c>
       <c r="CA6" s="6"/>
       <c r="CB6" s="6"/>
       <c r="CD6" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CE6" s="6"/>
       <c r="CF6" s="6"/>
     </row>
     <row r="7" spans="2:84" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D7" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="8" t="str">
         <f ca="1">CONCATENATE("(",TEXT($F$2,"dd-mmm-yy"),")")</f>
-        <v>(18-Mar-26)</v>
+        <v>(21-Apr-26)</v>
       </c>
       <c r="H7" s="8" t="str">
         <f>"("&amp;F3&amp;")"</f>
-        <v>(USD)</v>
+        <v>(CAD)</v>
       </c>
       <c r="I7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="K7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="L7" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M7" s="5" t="str">
         <f>AP7&amp;"A"</f>
@@ -2696,7 +2683,7 @@
         <v>CY2027E</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q7" s="5" t="str">
         <f>$M$7</f>
@@ -2710,11 +2697,11 @@
         <f>$O$7</f>
         <v>CY2027E</v>
       </c>
-      <c r="T7" s="62" t="str">
+      <c r="T7" s="61" t="str">
         <f>RIGHT(Y7,3)&amp;"-"&amp;RIGHT(Z7,3)</f>
         <v>25A-26E</v>
       </c>
-      <c r="U7" s="62" t="str">
+      <c r="U7" s="61" t="str">
         <f>RIGHT(Z7,3)&amp;"-"&amp;RIGHT(AA7,3)</f>
         <v>26E-27E</v>
       </c>
@@ -2775,19 +2762,19 @@
         <v>CY2026E</v>
       </c>
       <c r="AJ7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="AK7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL7" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AM7" s="71" t="s">
-        <v>54</v>
+      <c r="AL7" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM7" s="70" t="s">
+        <v>53</v>
       </c>
       <c r="AO7" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AP7" s="5" t="str">
         <f>$F$4</f>
@@ -2802,7 +2789,7 @@
         <v>CY2027</v>
       </c>
       <c r="AT7" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AU7" s="5" t="str">
         <f>$AP$7</f>
@@ -2841,22 +2828,22 @@
         <v>CY2027</v>
       </c>
       <c r="BG7" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="BI7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="BJ7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="BK7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="BL7" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="BI7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="BJ7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="BK7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="BL7" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="BN7" s="5" t="str">
         <f>$AP$7</f>
@@ -2998,17 +2985,14 @@
       <c r="CE8" s="1"/>
       <c r="CF8" s="1"/>
     </row>
-    <row r="9" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="72" t="str">
-        <f>+B9</f>
-        <v>Group 1</v>
+    <row r="9" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="1"/>
+      <c r="D9" s="71" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="35"/>
+      <c r="B10" s="34"/>
       <c r="D10" s="10" t="str" cm="1">
         <f t="array" ref="D10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10, "SP_COMPANY_NAME"))</f>
         <v/>
@@ -3021,7 +3005,7 @@
         <f t="array" ref="H10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="I10" s="41" t="str" cm="1">
+      <c r="I10" s="40" t="str" cm="1">
         <f t="array" ref="I10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
         <v/>
       </c>
@@ -3034,42 +3018,42 @@
         <v/>
       </c>
       <c r="L10" s="16" t="str">
-        <f>IFERROR(IF(OR($K10/AO10&gt;L$4,$K10/AO10&lt;L$3),"nmf ",$K10/AO10),"n/a ")</f>
+        <f t="shared" ref="L10:O15" si="0">IFERROR(IF(OR($K10/AO10&gt;L$4,$K10/AO10&lt;L$3),"nmf ",$K10/AO10),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M10" s="16" t="str">
-        <f>IFERROR(IF(OR($K10/AP10&gt;M$4,$K10/AP10&lt;M$3),"nmf ",$K10/AP10),"n/a ")</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N10" s="16" t="str">
-        <f>IFERROR(IF(OR($K10/AQ10&gt;N$4,$K10/AQ10&lt;N$3),"nmf ",$K10/AQ10),"n/a ")</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O10" s="16" t="str">
-        <f>IFERROR(IF(OR($K10/AR10&gt;O$4,$K10/AR10&lt;O$3),"nmf ",$K10/AR10),"n/a ")</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P10" s="16" t="str">
-        <f>IFERROR(IF(OR($K10/AT10&gt;P$4,$K10/AT10&lt;P$3),"nmf ",$K10/AT10),"n/a ")</f>
+        <f t="shared" ref="P10:S15" si="1">IFERROR(IF(OR($K10/AT10&gt;P$4,$K10/AT10&lt;P$3),"nmf ",$K10/AT10),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q10" s="16" t="str">
-        <f>IFERROR(IF(OR($K10/AU10&gt;Q$4,$K10/AU10&lt;Q$3),"nmf ",$K10/AU10),"n/a ")</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R10" s="16" t="str">
-        <f>IFERROR(IF(OR($K10/AV10&gt;R$4,$K10/AV10&lt;R$3),"nmf ",$K10/AV10),"n/a ")</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S10" s="16" t="str">
-        <f>IFERROR(IF(OR($K10/AW10&gt;S$4,$K10/AW10&lt;S$3),"nmf ",$K10/AW10),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T10" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T10" s="33" t="str">
         <f>IFERROR((AQ10/AP10)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="U10" s="34" t="str">
+      <c r="U10" s="33" t="str">
         <f>IFERROR((AR10/AQ10)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
@@ -3097,51 +3081,51 @@
         <f>IFERROR(IF(OR($H10/BE10&gt;#REF!,$H10/BE10&lt;#REF!),"nmf ",$H10/BE10),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="AB10" s="34" t="str">
-        <f t="shared" ref="AB10:AF13" si="0">IFERROR((AS10/AR10)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AC10" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AD10" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AE10" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AF10" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AG10" s="34" t="str">
+      <c r="AB10" s="33" t="str">
+        <f t="shared" ref="AB10:AF15" si="2">IFERROR((AS10/AR10)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC10" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD10" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE10" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF10" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG10" s="33" t="str">
         <f>IFERROR((BM10/AW10)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="AH10" s="34" t="str">
-        <f>IFERROR((BN10/BM10)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AI10" s="34" t="str">
-        <f>IFERROR((BO10/BN10)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ10" s="34" t="str">
-        <f>IFERROR((BP10/BO10)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK10" s="34" t="str">
-        <f>IFERROR((BQ10/BP10)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL10" s="34" t="str">
-        <f>IFERROR((BR10/BQ10)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM10" s="73"/>
+      <c r="AH10" s="33" t="str">
+        <f t="shared" ref="AH10:AL15" si="3">IFERROR((BN10/BM10)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI10" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ10" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK10" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL10" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM10" s="72"/>
       <c r="AO10" s="20" t="str" cm="1">
         <f t="array" ref="AO10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
@@ -3198,7 +3182,7 @@
         <f t="array" ref="BE10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BG10" s="66" t="str" cm="1">
+      <c r="BG10" s="65" t="str" cm="1">
         <f t="array" ref="BG10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
         <v/>
       </c>
@@ -3214,7 +3198,7 @@
         <f t="array" ref="BJ10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="BK10" s="38" t="e">
+      <c r="BK10" s="37" t="e">
         <f>+BI10-BJ10</f>
         <v>#VALUE!</v>
       </c>
@@ -3234,58 +3218,58 @@
         <f>IFERROR($AR10*$BT10,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BR10" s="45" t="str">
+      <c r="BR10" s="44" t="str">
         <f>IF($B10="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BS10" s="45" t="str">
+      <c r="BS10" s="44" t="str">
         <f>IF($B10="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BT10" s="45" t="str">
+      <c r="BT10" s="44" t="str">
         <f>IF($B10="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BU10" s="46"/>
-      <c r="BV10" s="48" t="str" cm="1">
+      <c r="BU10" s="45"/>
+      <c r="BV10" s="47" t="str" cm="1">
         <f t="array" ref="BV10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BW10" s="48" t="str" cm="1">
+      <c r="BW10" s="47" t="str" cm="1">
         <f t="array" ref="BW10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BX10" s="48" t="str" cm="1">
+      <c r="BX10" s="47" t="str" cm="1">
         <f t="array" ref="BX10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BZ10" s="63" t="str">
-        <f>IFERROR(IF(CD10/AP10&lt;0,"nmf ",CD10/AP10),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CA10" s="63" t="str">
-        <f>IFERROR(IF(CE10/AQ10&lt;0,"nmf ",CE10/AQ10),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CB10" s="63" t="str">
-        <f>IFERROR(IF(CF10/AR10&lt;0,"nmf ",CF10/AR10),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CD10" s="69" t="str">
-        <f>IFERROR(BR10*AP10,"--")</f>
+      <c r="BZ10" s="62" t="str">
+        <f t="shared" ref="BZ10:CB15" si="4">IFERROR(IF(CD10/AP10&lt;0,"nmf ",CD10/AP10),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA10" s="62" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB10" s="62" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD10" s="68" t="str">
+        <f t="shared" ref="CD10:CF15" si="5">IFERROR(BR10*AP10,"--")</f>
         <v>--</v>
       </c>
       <c r="CE10" s="20" t="str">
-        <f>IFERROR(BS10*AQ10,"--")</f>
+        <f t="shared" si="5"/>
         <v>--</v>
       </c>
       <c r="CF10" s="20" t="str">
-        <f>IFERROR(BT10*AR10,"--")</f>
+        <f t="shared" si="5"/>
         <v>--</v>
       </c>
     </row>
     <row r="11" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="35"/>
+      <c r="B11" s="34"/>
       <c r="D11" s="10" t="str" cm="1">
         <f t="array" ref="D11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11, "SP_COMPANY_NAME"))</f>
         <v/>
@@ -3298,7 +3282,7 @@
         <f t="array" ref="H11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="I11" s="41" t="str" cm="1">
+      <c r="I11" s="40" t="str" cm="1">
         <f t="array" ref="I11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
         <v/>
       </c>
@@ -3311,43 +3295,43 @@
         <v/>
       </c>
       <c r="L11" s="16" t="str">
-        <f>IFERROR(IF(OR($K11/AO11&gt;L$4,$K11/AO11&lt;L$3),"nmf ",$K11/AO11),"n/a ")</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M11" s="16" t="str">
-        <f>IFERROR(IF(OR($K11/AP11&gt;M$4,$K11/AP11&lt;M$3),"nmf ",$K11/AP11),"n/a ")</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N11" s="16" t="str">
-        <f>IFERROR(IF(OR($K11/AQ11&gt;N$4,$K11/AQ11&lt;N$3),"nmf ",$K11/AQ11),"n/a ")</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O11" s="16" t="str">
-        <f>IFERROR(IF(OR($K11/AR11&gt;O$4,$K11/AR11&lt;O$3),"nmf ",$K11/AR11),"n/a ")</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P11" s="16" t="str">
-        <f>IFERROR(IF(OR($K11/AT11&gt;P$4,$K11/AT11&lt;P$3),"nmf ",$K11/AT11),"n/a ")</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q11" s="16" t="str">
-        <f>IFERROR(IF(OR($K11/AU11&gt;Q$4,$K11/AU11&lt;Q$3),"nmf ",$K11/AU11),"n/a ")</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R11" s="16" t="str">
-        <f>IFERROR(IF(OR($K11/AV11&gt;R$4,$K11/AV11&lt;R$3),"nmf ",$K11/AV11),"n/a ")</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S11" s="16" t="str">
-        <f>IFERROR(IF(OR($K11/AW11&gt;S$4,$K11/AW11&lt;S$3),"nmf ",$K11/AW11),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T11" s="34" t="str">
-        <f t="shared" ref="T11" si="1">IFERROR((AQ11/AP11)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="U11" s="34" t="str">
-        <f t="shared" ref="U11" si="2">IFERROR((AR11/AQ11)-1,"n/a ")</f>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T11" s="33" t="str">
+        <f t="shared" ref="T11" si="6">IFERROR((AQ11/AP11)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U11" s="33" t="str">
+        <f t="shared" ref="U11" si="7">IFERROR((AR11/AQ11)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V11" s="16" t="str">
@@ -3374,51 +3358,51 @@
         <f>IFERROR(IF(OR($H11/BE11&gt;#REF!,$H11/BE11&lt;#REF!),"nmf ",$H11/BE11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="AB11" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AC11" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AD11" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AE11" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AF11" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AG11" s="34" t="str">
+      <c r="AB11" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC11" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD11" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE11" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF11" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG11" s="33" t="str">
         <f>IFERROR((BM11/AW11)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="AH11" s="34" t="str">
-        <f>IFERROR((BN11/BM11)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AI11" s="34" t="str">
-        <f>IFERROR((BO11/BN11)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ11" s="34" t="str">
-        <f>IFERROR((BP11/BO11)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK11" s="34" t="str">
-        <f>IFERROR((BQ11/BP11)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL11" s="34" t="str">
-        <f>IFERROR((BR11/BQ11)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM11" s="73"/>
+      <c r="AH11" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI11" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ11" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK11" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL11" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM11" s="72"/>
       <c r="AO11" s="20" t="str" cm="1">
         <f t="array" ref="AO11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
@@ -3475,7 +3459,7 @@
         <f t="array" ref="BE11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BG11" s="66" t="str" cm="1">
+      <c r="BG11" s="65" t="str" cm="1">
         <f t="array" ref="BG11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
         <v/>
       </c>
@@ -3491,8 +3475,8 @@
         <f t="array" ref="BJ11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="BK11" s="38" t="e">
-        <f t="shared" ref="BK11" si="3">+BI11-BJ11</f>
+      <c r="BK11" s="37" t="e">
+        <f t="shared" ref="BK11" si="8">+BI11-BJ11</f>
         <v>#VALUE!</v>
       </c>
       <c r="BL11" s="19" t="str" cm="1">
@@ -3504,65 +3488,65 @@
         <v>n/a</v>
       </c>
       <c r="BO11" s="20" t="str">
-        <f t="shared" ref="BO11" si="4">IFERROR($AQ11*BS11,"n/a")</f>
+        <f t="shared" ref="BO11" si="9">IFERROR($AQ11*BS11,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BP11" s="20" t="str">
         <f>IFERROR($AR11*$BT11,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BR11" s="45" t="str">
+      <c r="BR11" s="44" t="str">
         <f>IF($B11="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BS11" s="45" t="str">
+      <c r="BS11" s="44" t="str">
         <f>IF($B11="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BT11" s="45" t="str">
+      <c r="BT11" s="44" t="str">
         <f>IF($B11="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BU11" s="46"/>
-      <c r="BV11" s="48" t="str" cm="1">
+      <c r="BU11" s="45"/>
+      <c r="BV11" s="47" t="str" cm="1">
         <f t="array" ref="BV11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BW11" s="48" t="str" cm="1">
+      <c r="BW11" s="47" t="str" cm="1">
         <f t="array" ref="BW11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BX11" s="48" t="str" cm="1">
+      <c r="BX11" s="47" t="str" cm="1">
         <f t="array" ref="BX11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BZ11" s="63" t="str">
-        <f>IFERROR(IF(CD11/AP11&lt;0,"nmf ",CD11/AP11),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CA11" s="63" t="str">
-        <f>IFERROR(IF(CE11/AQ11&lt;0,"nmf ",CE11/AQ11),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CB11" s="63" t="str">
-        <f>IFERROR(IF(CF11/AR11&lt;0,"nmf ",CF11/AR11),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CD11" s="69" t="str">
-        <f>IFERROR(BR11*AP11,"--")</f>
+      <c r="BZ11" s="62" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA11" s="62" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB11" s="62" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD11" s="68" t="str">
+        <f t="shared" si="5"/>
         <v>--</v>
       </c>
       <c r="CE11" s="20" t="str">
-        <f>IFERROR(BS11*AQ11,"--")</f>
+        <f t="shared" si="5"/>
         <v>--</v>
       </c>
       <c r="CF11" s="20" t="str">
-        <f>IFERROR(BT11*AR11,"--")</f>
+        <f t="shared" si="5"/>
         <v>--</v>
       </c>
     </row>
     <row r="12" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="35"/>
+      <c r="B12" s="34"/>
       <c r="D12" s="10" t="str" cm="1">
         <f t="array" ref="D12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12, "SP_COMPANY_NAME"))</f>
         <v/>
@@ -3575,7 +3559,7 @@
         <f t="array" ref="H12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="I12" s="41" t="str" cm="1">
+      <c r="I12" s="40" t="str" cm="1">
         <f t="array" ref="I12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
         <v/>
       </c>
@@ -3588,43 +3572,43 @@
         <v/>
       </c>
       <c r="L12" s="16" t="str">
-        <f>IFERROR(IF(OR($K12/AO12&gt;L$4,$K12/AO12&lt;L$3),"nmf ",$K12/AO12),"n/a ")</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M12" s="16" t="str">
-        <f>IFERROR(IF(OR($K12/AP12&gt;M$4,$K12/AP12&lt;M$3),"nmf ",$K12/AP12),"n/a ")</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N12" s="16" t="str">
-        <f>IFERROR(IF(OR($K12/AQ12&gt;N$4,$K12/AQ12&lt;N$3),"nmf ",$K12/AQ12),"n/a ")</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O12" s="16" t="str">
-        <f>IFERROR(IF(OR($K12/AR12&gt;O$4,$K12/AR12&lt;O$3),"nmf ",$K12/AR12),"n/a ")</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P12" s="16" t="str">
-        <f>IFERROR(IF(OR($K12/AT12&gt;P$4,$K12/AT12&lt;P$3),"nmf ",$K12/AT12),"n/a ")</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q12" s="16" t="str">
-        <f>IFERROR(IF(OR($K12/AU12&gt;Q$4,$K12/AU12&lt;Q$3),"nmf ",$K12/AU12),"n/a ")</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R12" s="16" t="str">
-        <f>IFERROR(IF(OR($K12/AV12&gt;R$4,$K12/AV12&lt;R$3),"nmf ",$K12/AV12),"n/a ")</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S12" s="16" t="str">
-        <f>IFERROR(IF(OR($K12/AW12&gt;S$4,$K12/AW12&lt;S$3),"nmf ",$K12/AW12),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T12" s="34" t="str">
-        <f t="shared" ref="T12" si="5">IFERROR((AQ12/AP12)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="U12" s="34" t="str">
-        <f t="shared" ref="U12" si="6">IFERROR((AR12/AQ12)-1,"n/a ")</f>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T12" s="33" t="str">
+        <f t="shared" ref="T12" si="10">IFERROR((AQ12/AP12)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U12" s="33" t="str">
+        <f t="shared" ref="U12" si="11">IFERROR((AR12/AQ12)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V12" s="16" t="str">
@@ -3651,51 +3635,51 @@
         <f>IFERROR(IF(OR($H12/BE12&gt;#REF!,$H12/BE12&lt;#REF!),"nmf ",$H12/BE12),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="AB12" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AC12" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AD12" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AE12" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AF12" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AG12" s="34" t="str">
+      <c r="AB12" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC12" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD12" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE12" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF12" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG12" s="33" t="str">
         <f>IFERROR((BM12/AW12)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="AH12" s="34" t="str">
-        <f>IFERROR((BN12/BM12)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AI12" s="34" t="str">
-        <f>IFERROR((BO12/BN12)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ12" s="34" t="str">
-        <f>IFERROR((BP12/BO12)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK12" s="34" t="str">
-        <f>IFERROR((BQ12/BP12)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL12" s="34" t="str">
-        <f>IFERROR((BR12/BQ12)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM12" s="73"/>
+      <c r="AH12" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI12" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ12" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK12" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL12" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM12" s="72"/>
       <c r="AO12" s="20" t="str" cm="1">
         <f t="array" ref="AO12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
@@ -3752,7 +3736,7 @@
         <f t="array" ref="BE12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BG12" s="66" t="str" cm="1">
+      <c r="BG12" s="65" t="str" cm="1">
         <f t="array" ref="BG12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
         <v/>
       </c>
@@ -3768,8 +3752,8 @@
         <f t="array" ref="BJ12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="BK12" s="38" t="e">
-        <f t="shared" ref="BK12" si="7">+BI12-BJ12</f>
+      <c r="BK12" s="37" t="e">
+        <f t="shared" ref="BK12" si="12">+BI12-BJ12</f>
         <v>#VALUE!</v>
       </c>
       <c r="BL12" s="19" t="str" cm="1">
@@ -3781,70 +3765,70 @@
         <v>n/a</v>
       </c>
       <c r="BO12" s="20" t="str">
-        <f t="shared" ref="BO12" si="8">IFERROR($AQ12*BS12,"n/a")</f>
+        <f t="shared" ref="BO12" si="13">IFERROR($AQ12*BS12,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BP12" s="20" t="str">
         <f>IFERROR($AR12*$BT12,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BR12" s="45" t="str">
+      <c r="BR12" s="44" t="str">
         <f>IF($B12="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BS12" s="45" t="str">
+      <c r="BS12" s="44" t="str">
         <f>IF($B12="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BT12" s="45" t="str">
+      <c r="BT12" s="44" t="str">
         <f>IF($B12="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BU12" s="46"/>
-      <c r="BV12" s="48" t="str" cm="1">
+      <c r="BU12" s="45"/>
+      <c r="BV12" s="47" t="str" cm="1">
         <f t="array" ref="BV12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BW12" s="48" t="str" cm="1">
+      <c r="BW12" s="47" t="str" cm="1">
         <f t="array" ref="BW12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BX12" s="48" t="str" cm="1">
+      <c r="BX12" s="47" t="str" cm="1">
         <f t="array" ref="BX12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BZ12" s="63" t="str">
-        <f>IFERROR(IF(CD12/AP12&lt;0,"nmf ",CD12/AP12),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CA12" s="63" t="str">
-        <f>IFERROR(IF(CE12/AQ12&lt;0,"nmf ",CE12/AQ12),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CB12" s="63" t="str">
-        <f>IFERROR(IF(CF12/AR12&lt;0,"nmf ",CF12/AR12),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CD12" s="69" t="str">
-        <f>IFERROR(BR12*AP12,"--")</f>
+      <c r="BZ12" s="62" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA12" s="62" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB12" s="62" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD12" s="68" t="str">
+        <f t="shared" si="5"/>
         <v>--</v>
       </c>
       <c r="CE12" s="20" t="str">
-        <f>IFERROR(BS12*AQ12,"--")</f>
+        <f t="shared" si="5"/>
         <v>--</v>
       </c>
       <c r="CF12" s="20" t="str">
-        <f>IFERROR(BT12*AR12,"--")</f>
+        <f t="shared" si="5"/>
         <v>--</v>
       </c>
     </row>
     <row r="13" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="35"/>
+      <c r="B13" s="34"/>
       <c r="D13" s="10" t="str" cm="1">
         <f t="array" ref="D13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13, "SP_COMPANY_NAME"))</f>
         <v/>
       </c>
-      <c r="G13" s="21" t="str" cm="1">
+      <c r="G13" s="12" t="str" cm="1">
         <f t="array" ref="G13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I13&amp;",NA=--"))</f>
         <v/>
       </c>
@@ -3852,7 +3836,7 @@
         <f t="array" ref="H13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="I13" s="41" t="str" cm="1">
+      <c r="I13" s="40" t="str" cm="1">
         <f t="array" ref="I13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
         <v/>
       </c>
@@ -3865,43 +3849,43 @@
         <v/>
       </c>
       <c r="L13" s="16" t="str">
-        <f>IFERROR(IF(OR($K13/AO13&gt;L$4,$K13/AO13&lt;L$3),"nmf ",$K13/AO13),"n/a ")</f>
+        <f t="shared" ref="L13:L14" si="14">IFERROR(IF(OR($K13/AO13&gt;L$4,$K13/AO13&lt;L$3),"nmf ",$K13/AO13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M13" s="16" t="str">
-        <f>IFERROR(IF(OR($K13/AP13&gt;M$4,$K13/AP13&lt;M$3),"nmf ",$K13/AP13),"n/a ")</f>
+        <f t="shared" ref="M13:M14" si="15">IFERROR(IF(OR($K13/AP13&gt;M$4,$K13/AP13&lt;M$3),"nmf ",$K13/AP13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N13" s="16" t="str">
-        <f>IFERROR(IF(OR($K13/AQ13&gt;N$4,$K13/AQ13&lt;N$3),"nmf ",$K13/AQ13),"n/a ")</f>
+        <f t="shared" ref="N13:N14" si="16">IFERROR(IF(OR($K13/AQ13&gt;N$4,$K13/AQ13&lt;N$3),"nmf ",$K13/AQ13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O13" s="16" t="str">
-        <f>IFERROR(IF(OR($K13/AR13&gt;O$4,$K13/AR13&lt;O$3),"nmf ",$K13/AR13),"n/a ")</f>
+        <f t="shared" ref="O13:O14" si="17">IFERROR(IF(OR($K13/AR13&gt;O$4,$K13/AR13&lt;O$3),"nmf ",$K13/AR13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P13" s="16" t="str">
-        <f>IFERROR(IF(OR($K13/AT13&gt;P$4,$K13/AT13&lt;P$3),"nmf ",$K13/AT13),"n/a ")</f>
+        <f t="shared" ref="P13:P14" si="18">IFERROR(IF(OR($K13/AT13&gt;P$4,$K13/AT13&lt;P$3),"nmf ",$K13/AT13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q13" s="16" t="str">
-        <f>IFERROR(IF(OR($K13/AU13&gt;Q$4,$K13/AU13&lt;Q$3),"nmf ",$K13/AU13),"n/a ")</f>
+        <f t="shared" ref="Q13:Q14" si="19">IFERROR(IF(OR($K13/AU13&gt;Q$4,$K13/AU13&lt;Q$3),"nmf ",$K13/AU13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R13" s="16" t="str">
-        <f>IFERROR(IF(OR($K13/AV13&gt;R$4,$K13/AV13&lt;R$3),"nmf ",$K13/AV13),"n/a ")</f>
+        <f t="shared" ref="R13:R14" si="20">IFERROR(IF(OR($K13/AV13&gt;R$4,$K13/AV13&lt;R$3),"nmf ",$K13/AV13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S13" s="16" t="str">
-        <f>IFERROR(IF(OR($K13/AW13&gt;S$4,$K13/AW13&lt;S$3),"nmf ",$K13/AW13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T13" s="34" t="str">
-        <f>IFERROR((AQ13/AP13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="U13" s="34" t="str">
-        <f>IFERROR((AR13/AQ13)-1,"n/a ")</f>
+        <f t="shared" ref="S13:S14" si="21">IFERROR(IF(OR($K13/AW13&gt;S$4,$K13/AW13&lt;S$3),"nmf ",$K13/AW13),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T13" s="33" t="str">
+        <f t="shared" ref="T13:T14" si="22">IFERROR((AQ13/AP13)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U13" s="33" t="str">
+        <f t="shared" ref="U13:U14" si="23">IFERROR((AR13/AQ13)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V13" s="16" t="str">
@@ -3928,51 +3912,51 @@
         <f>IFERROR(IF(OR($H13/BE13&gt;#REF!,$H13/BE13&lt;#REF!),"nmf ",$H13/BE13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="AB13" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AC13" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AD13" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AE13" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AF13" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AG13" s="34" t="str">
-        <f>IFERROR((BM13/AW13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AH13" s="34" t="str">
-        <f>IFERROR((BN13/BM13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AI13" s="34" t="str">
-        <f>IFERROR((BO13/BN13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ13" s="34" t="str">
-        <f>IFERROR((BP13/BO13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK13" s="34" t="str">
-        <f>IFERROR((BQ13/BP13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL13" s="34" t="str">
-        <f>IFERROR((BR13/BQ13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM13" s="73"/>
+      <c r="AB13" s="33" t="str">
+        <f t="shared" ref="AB13:AB14" si="24">IFERROR((AS13/AR13)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC13" s="33" t="str">
+        <f t="shared" ref="AC13:AC14" si="25">IFERROR((AT13/AS13)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD13" s="33" t="str">
+        <f t="shared" ref="AD13:AD14" si="26">IFERROR((AU13/AT13)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE13" s="33" t="str">
+        <f t="shared" ref="AE13:AE14" si="27">IFERROR((AV13/AU13)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF13" s="33" t="str">
+        <f t="shared" ref="AF13:AF14" si="28">IFERROR((AW13/AV13)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG13" s="33" t="str">
+        <f t="shared" ref="AG13:AG14" si="29">IFERROR((BM13/AW13)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH13" s="33" t="str">
+        <f t="shared" ref="AH13:AH14" si="30">IFERROR((BN13/BM13)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI13" s="33" t="str">
+        <f t="shared" ref="AI13:AI14" si="31">IFERROR((BO13/BN13)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ13" s="33" t="str">
+        <f t="shared" ref="AJ13:AJ14" si="32">IFERROR((BP13/BO13)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK13" s="33" t="str">
+        <f t="shared" ref="AK13:AK14" si="33">IFERROR((BQ13/BP13)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL13" s="33" t="str">
+        <f t="shared" ref="AL13:AL14" si="34">IFERROR((BR13/BQ13)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM13" s="72"/>
       <c r="AO13" s="20" t="str" cm="1">
         <f t="array" ref="AO13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
@@ -4029,7 +4013,7 @@
         <f t="array" ref="BE13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BG13" s="67" t="str" cm="1">
+      <c r="BG13" s="65" t="str" cm="1">
         <f t="array" ref="BG13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
         <v/>
       </c>
@@ -4045,8 +4029,8 @@
         <f t="array" ref="BJ13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="BK13" s="38" t="e">
-        <f>+BI13-BJ13</f>
+      <c r="BK13" s="37" t="e">
+        <f t="shared" ref="BK13:BK14" si="35">+BI13-BJ13</f>
         <v>#VALUE!</v>
       </c>
       <c r="BL13" s="19" t="str" cm="1">
@@ -4054,910 +4038,907 @@
         <v/>
       </c>
       <c r="BN13" s="20" t="str">
-        <f>IFERROR($AP13*$BR13,"n/a")</f>
+        <f t="shared" ref="BN13:BN14" si="36">IFERROR($AP13*$BR13,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO13" s="20" t="str">
-        <f>IFERROR($AQ13*BS13,"n/a")</f>
+        <f t="shared" ref="BO13:BO14" si="37">IFERROR($AQ13*BS13,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BP13" s="20" t="str">
-        <f>IFERROR($AR13*$BT13,"n/a")</f>
+        <f t="shared" ref="BP13:BP14" si="38">IFERROR($AR13*$BT13,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BR13" s="45" t="str">
+      <c r="BR13" s="44" t="str">
         <f>IF($B13="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BS13" s="45" t="str">
+      <c r="BS13" s="44" t="str">
         <f>IF($B13="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BT13" s="45" t="str">
+      <c r="BT13" s="44" t="str">
         <f>IF($B13="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BU13" s="46"/>
-      <c r="BV13" s="48" t="str" cm="1">
+      <c r="BU13" s="45"/>
+      <c r="BV13" s="47" t="str" cm="1">
         <f t="array" ref="BV13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BW13" s="48" t="str" cm="1">
+      <c r="BW13" s="47" t="str" cm="1">
         <f t="array" ref="BW13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BX13" s="48" t="str" cm="1">
+      <c r="BX13" s="47" t="str" cm="1">
         <f t="array" ref="BX13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BZ13" s="63" t="str">
-        <f>IFERROR(IF(CD13/AP13&lt;0,"nmf ",CD13/AP13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CA13" s="63" t="str">
-        <f>IFERROR(IF(CE13/AQ13&lt;0,"nmf ",CE13/AQ13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CB13" s="63" t="str">
-        <f>IFERROR(IF(CF13/AR13&lt;0,"nmf ",CF13/AR13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CD13" s="20" t="str">
-        <f>IFERROR(BR13*AP13,"--")</f>
+      <c r="BZ13" s="62" t="str">
+        <f t="shared" ref="BZ13:BZ14" si="39">IFERROR(IF(CD13/AP13&lt;0,"nmf ",CD13/AP13),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA13" s="62" t="str">
+        <f t="shared" ref="CA13:CA14" si="40">IFERROR(IF(CE13/AQ13&lt;0,"nmf ",CE13/AQ13),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB13" s="62" t="str">
+        <f t="shared" ref="CB13:CB14" si="41">IFERROR(IF(CF13/AR13&lt;0,"nmf ",CF13/AR13),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD13" s="68" t="str">
+        <f t="shared" ref="CD13:CD14" si="42">IFERROR(BR13*AP13,"--")</f>
         <v>--</v>
       </c>
       <c r="CE13" s="20" t="str">
-        <f>IFERROR(BS13*AQ13,"--")</f>
+        <f t="shared" ref="CE13:CE14" si="43">IFERROR(BS13*AQ13,"--")</f>
         <v>--</v>
       </c>
       <c r="CF13" s="20" t="str">
-        <f>IFERROR(BT13*AR13,"--")</f>
+        <f t="shared" ref="CF13:CF14" si="44">IFERROR(BT13*AR13,"--")</f>
         <v>--</v>
       </c>
     </row>
-    <row r="14" spans="2:84" s="10" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="11"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="16"/>
-      <c r="Y14" s="16"/>
-      <c r="Z14" s="16"/>
-      <c r="AA14" s="16"/>
-      <c r="AB14" s="17"/>
-      <c r="AC14" s="17"/>
-      <c r="AD14" s="17"/>
-      <c r="AE14" s="17"/>
-      <c r="AF14" s="17"/>
-      <c r="AG14" s="17"/>
-      <c r="AH14" s="17"/>
-      <c r="AI14" s="17"/>
-      <c r="AJ14" s="17"/>
-      <c r="AK14" s="17"/>
-      <c r="AL14" s="17"/>
-      <c r="AM14" s="17"/>
-      <c r="AO14" s="13"/>
-      <c r="AP14" s="13"/>
-      <c r="AQ14" s="13"/>
-      <c r="AR14" s="13"/>
-      <c r="AU14" s="20"/>
-      <c r="AV14" s="20"/>
-      <c r="AW14" s="20"/>
-      <c r="AY14" s="13"/>
-      <c r="AZ14" s="13"/>
-      <c r="BA14" s="13"/>
-      <c r="BG14" s="67"/>
-      <c r="BH14" s="19"/>
-      <c r="BI14" s="19"/>
-      <c r="BJ14" s="19"/>
-      <c r="BK14" s="19"/>
-      <c r="BL14" s="19"/>
-      <c r="BR14" s="46"/>
-      <c r="BS14" s="46"/>
-      <c r="BT14" s="46"/>
-      <c r="BU14" s="46"/>
-      <c r="BV14" s="49"/>
-      <c r="BW14" s="49"/>
-      <c r="BX14" s="49"/>
-      <c r="BZ14" s="64"/>
-      <c r="CA14" s="64"/>
-      <c r="CB14" s="64"/>
+    <row r="14" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="34"/>
+      <c r="D14" s="10" t="str" cm="1">
+        <f t="array" ref="D14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14, "SP_COMPANY_NAME"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="12" t="str" cm="1">
+        <f t="array" ref="G14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I14&amp;",NA=--"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="13" t="str" cm="1">
+        <f t="array" ref="H14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="I14" s="40" t="str" cm="1">
+        <f t="array" ref="I14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="J14" s="15" t="str" cm="1">
+        <f t="array" ref="J14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="K14" s="15" t="str" cm="1">
+        <f t="array" ref="K14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="L14" s="16" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M14" s="16" t="str">
+        <f t="shared" si="15"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N14" s="16" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O14" s="16" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P14" s="16" t="str">
+        <f t="shared" si="18"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q14" s="16" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R14" s="16" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S14" s="16" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T14" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U14" s="33" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V14" s="16" t="str">
+        <f>IFERROR(IF(OR($H14/AY14&gt;#REF!,$H14/AY14&lt;#REF!),"nmf ",$H14/AY14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W14" s="16" t="str">
+        <f>IFERROR(IF(OR($H14/AZ14&gt;#REF!,$H14/AZ14&lt;#REF!),"nmf ",$H14/AZ14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X14" s="16" t="str">
+        <f>IFERROR(IF(OR($H14/BA14&gt;#REF!,$H14/BA14&lt;#REF!),"nmf ",$H14/BA14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y14" s="16" t="str">
+        <f>IFERROR(IF(OR($H14/BC14&gt;#REF!,$H14/BC14&lt;#REF!),"nmf ",$H14/BC14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z14" s="16" t="str">
+        <f>IFERROR(IF(OR($H14/BD14&gt;#REF!,$H14/BD14&lt;#REF!),"nmf ",$H14/BD14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA14" s="16" t="str">
+        <f>IFERROR(IF(OR($H14/BE14&gt;#REF!,$H14/BE14&lt;#REF!),"nmf ",$H14/BE14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB14" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC14" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD14" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE14" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF14" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG14" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH14" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI14" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ14" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK14" s="33" t="str">
+        <f t="shared" si="33"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL14" s="33" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM14" s="72"/>
+      <c r="AO14" s="20" t="str" cm="1">
+        <f t="array" ref="AO14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AP14" s="20" t="str" cm="1">
+        <f t="array" ref="AP14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AQ14" s="20" t="str" cm="1">
+        <f t="array" ref="AQ14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AR14" s="20" t="str" cm="1">
+        <f t="array" ref="AR14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AT14" s="20" t="str" cm="1">
+        <f t="array" ref="AT14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AU14" s="20" t="str" cm="1">
+        <f t="array" ref="AU14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AV14" s="20" t="str" cm="1">
+        <f t="array" ref="AV14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AW14" s="20" t="str" cm="1">
+        <f t="array" ref="AW14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AY14" s="13" t="str" cm="1">
+        <f t="array" ref="AY14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AZ14" s="13" t="str" cm="1">
+        <f t="array" ref="AZ14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BA14" s="13" t="str" cm="1">
+        <f t="array" ref="BA14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BC14" s="13" t="str" cm="1">
+        <f t="array" ref="BC14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BD14" s="13" t="str" cm="1">
+        <f t="array" ref="BD14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BE14" s="13" t="str" cm="1">
+        <f t="array" ref="BE14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG14" s="65" t="str" cm="1">
+        <f t="array" ref="BG14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BH14" s="19" t="str" cm="1">
+        <f t="array" ref="BH14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BI14" s="19" t="str" cm="1">
+        <f t="array" ref="BI14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ14" s="19" t="str" cm="1">
+        <f t="array" ref="BJ14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BK14" s="37" t="e">
+        <f t="shared" si="35"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL14" s="19" t="str" cm="1">
+        <f t="array" ref="BL14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BN14" s="20" t="str">
+        <f t="shared" si="36"/>
+        <v>n/a</v>
+      </c>
+      <c r="BO14" s="20" t="str">
+        <f t="shared" si="37"/>
+        <v>n/a</v>
+      </c>
+      <c r="BP14" s="20" t="str">
+        <f t="shared" si="38"/>
+        <v>n/a</v>
+      </c>
+      <c r="BR14" s="44" t="str">
+        <f>IF($B14="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BS14" s="44" t="str">
+        <f>IF($B14="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BT14" s="44" t="str">
+        <f>IF($B14="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BU14" s="45"/>
+      <c r="BV14" s="47" t="str" cm="1">
+        <f t="array" ref="BV14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BW14" s="47" t="str" cm="1">
+        <f t="array" ref="BW14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BX14" s="47" t="str" cm="1">
+        <f t="array" ref="BX14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BZ14" s="62" t="str">
+        <f t="shared" si="39"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA14" s="62" t="str">
+        <f t="shared" si="40"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB14" s="62" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD14" s="68" t="str">
+        <f t="shared" si="42"/>
+        <v>--</v>
+      </c>
+      <c r="CE14" s="20" t="str">
+        <f t="shared" si="43"/>
+        <v>--</v>
+      </c>
+      <c r="CF14" s="20" t="str">
+        <f t="shared" si="44"/>
+        <v>--</v>
+      </c>
     </row>
     <row r="15" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="11"/>
-      <c r="D15" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="36" t="str">
-        <f>IFERROR(AVERAGE(L10:L13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="M15" s="36" t="str">
-        <f>IFERROR(AVERAGE(M10:M13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="N15" s="26" t="str">
-        <f>IFERROR(AVERAGE(N10:N13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="O15" s="36" t="str">
-        <f>IFERROR(AVERAGE(O10:O13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="P15" s="36" t="str">
-        <f>IFERROR(AVERAGE(P10:P13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Q15" s="26" t="str">
-        <f>IFERROR(AVERAGE(Q10:Q13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="R15" s="26" t="str">
-        <f>IFERROR(AVERAGE(R10:R13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="S15" s="26" t="str">
-        <f>IFERROR(AVERAGE(S10:S13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T15" s="37" t="str">
-        <f>IFERROR(AVERAGE(T10:T13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="U15" s="37" t="str">
-        <f>IFERROR(AVERAGE(U10:U13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="V15" s="26" t="str">
-        <f>IFERROR(AVERAGE(V10:V13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="W15" s="26" t="str">
-        <f>IFERROR(AVERAGE(W10:W13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="X15" s="26" t="str">
-        <f>IFERROR(AVERAGE(X10:X13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Y15" s="26" t="str">
-        <f>IFERROR(AVERAGE(Y10:Y13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Z15" s="26" t="str">
-        <f>IFERROR(AVERAGE(Z10:Z13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AA15" s="26" t="str">
-        <f>IFERROR(AVERAGE(AA10:AA13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AB15" s="37" t="str">
-        <f>IFERROR(AVERAGE(AB10:AB13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AC15" s="37" t="str">
-        <f>IFERROR(AVERAGE(AC10:AC13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AD15" s="37" t="str">
-        <f>IFERROR(AVERAGE(AD10:AD13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AE15" s="37" t="str">
-        <f>IFERROR(AVERAGE(AE10:AE13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AF15" s="37" t="str">
-        <f>IFERROR(AVERAGE(AF10:AF13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AG15" s="37" t="str">
-        <f>IFERROR(AVERAGE(AG10:AG13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AH15" s="37" t="str">
-        <f>IFERROR(AVERAGE(AH10:AH13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AI15" s="37" t="str">
-        <f>IFERROR(AVERAGE(AI10:AI13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ15" s="37" t="str">
-        <f>IFERROR(AVERAGE(AJ10:AJ13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK15" s="37" t="str">
-        <f>IFERROR(AVERAGE(AK10:AK13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL15" s="37" t="str">
-        <f>IFERROR(AVERAGE(AL10:AL13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM15" s="37"/>
-      <c r="AU15" s="27"/>
-      <c r="AV15" s="27"/>
-      <c r="AW15" s="27"/>
-      <c r="BG15" s="68"/>
-      <c r="BR15" s="46"/>
-      <c r="BS15" s="46"/>
-      <c r="BT15" s="46"/>
-      <c r="BU15" s="46"/>
-      <c r="BV15" s="49"/>
-      <c r="BW15" s="49"/>
-      <c r="BX15" s="49"/>
-      <c r="BZ15" s="64"/>
-      <c r="CA15" s="64"/>
-      <c r="CB15" s="64"/>
+      <c r="B15" s="34"/>
+      <c r="D15" s="10" t="str" cm="1">
+        <f t="array" ref="D15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15, "SP_COMPANY_NAME"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="21" t="str" cm="1">
+        <f t="array" ref="G15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I15&amp;",NA=--"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="13" t="str" cm="1">
+        <f t="array" ref="H15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="I15" s="40" t="str" cm="1">
+        <f t="array" ref="I15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="J15" s="15" t="str" cm="1">
+        <f t="array" ref="J15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="K15" s="15" t="str" cm="1">
+        <f t="array" ref="K15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="L15" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M15" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N15" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O15" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P15" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q15" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R15" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S15" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T15" s="33" t="str">
+        <f>IFERROR((AQ15/AP15)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U15" s="33" t="str">
+        <f>IFERROR((AR15/AQ15)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V15" s="16" t="str">
+        <f>IFERROR(IF(OR($H15/AY15&gt;#REF!,$H15/AY15&lt;#REF!),"nmf ",$H15/AY15),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W15" s="16" t="str">
+        <f>IFERROR(IF(OR($H15/AZ15&gt;#REF!,$H15/AZ15&lt;#REF!),"nmf ",$H15/AZ15),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X15" s="16" t="str">
+        <f>IFERROR(IF(OR($H15/BA15&gt;#REF!,$H15/BA15&lt;#REF!),"nmf ",$H15/BA15),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y15" s="16" t="str">
+        <f>IFERROR(IF(OR($H15/BC15&gt;#REF!,$H15/BC15&lt;#REF!),"nmf ",$H15/BC15),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z15" s="16" t="str">
+        <f>IFERROR(IF(OR($H15/BD15&gt;#REF!,$H15/BD15&lt;#REF!),"nmf ",$H15/BD15),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA15" s="16" t="str">
+        <f>IFERROR(IF(OR($H15/BE15&gt;#REF!,$H15/BE15&lt;#REF!),"nmf ",$H15/BE15),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB15" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC15" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD15" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE15" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF15" s="33" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG15" s="33" t="str">
+        <f>IFERROR((BM15/AW15)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH15" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI15" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ15" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK15" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL15" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM15" s="72"/>
+      <c r="AO15" s="20" t="str" cm="1">
+        <f t="array" ref="AO15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AP15" s="20" t="str" cm="1">
+        <f t="array" ref="AP15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AQ15" s="20" t="str" cm="1">
+        <f t="array" ref="AQ15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AR15" s="20" t="str" cm="1">
+        <f t="array" ref="AR15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AT15" s="20" t="str" cm="1">
+        <f t="array" ref="AT15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AU15" s="20" t="str" cm="1">
+        <f t="array" ref="AU15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AV15" s="20" t="str" cm="1">
+        <f t="array" ref="AV15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AW15" s="20" t="str" cm="1">
+        <f t="array" ref="AW15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AY15" s="13" t="str" cm="1">
+        <f t="array" ref="AY15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AZ15" s="13" t="str" cm="1">
+        <f t="array" ref="AZ15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BA15" s="13" t="str" cm="1">
+        <f t="array" ref="BA15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BC15" s="13" t="str" cm="1">
+        <f t="array" ref="BC15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BD15" s="13" t="str" cm="1">
+        <f t="array" ref="BD15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BE15" s="13" t="str" cm="1">
+        <f t="array" ref="BE15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG15" s="66" t="str" cm="1">
+        <f t="array" ref="BG15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BH15" s="19" t="str" cm="1">
+        <f t="array" ref="BH15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BI15" s="19" t="str" cm="1">
+        <f t="array" ref="BI15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ15" s="19" t="str" cm="1">
+        <f t="array" ref="BJ15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BK15" s="37" t="e">
+        <f>+BI15-BJ15</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL15" s="19" t="str" cm="1">
+        <f t="array" ref="BL15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BN15" s="20" t="str">
+        <f>IFERROR($AP15*$BR15,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BO15" s="20" t="str">
+        <f>IFERROR($AQ15*BS15,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BP15" s="20" t="str">
+        <f>IFERROR($AR15*$BT15,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BR15" s="44" t="str">
+        <f>IF($B15="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BS15" s="44" t="str">
+        <f>IF($B15="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BT15" s="44" t="str">
+        <f>IF($B15="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BU15" s="45"/>
+      <c r="BV15" s="47" t="str" cm="1">
+        <f t="array" ref="BV15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BW15" s="47" t="str" cm="1">
+        <f t="array" ref="BW15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BX15" s="47" t="str" cm="1">
+        <f t="array" ref="BX15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BZ15" s="62" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA15" s="62" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB15" s="62" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD15" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>--</v>
+      </c>
+      <c r="CE15" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>--</v>
+      </c>
+      <c r="CF15" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>--</v>
+      </c>
     </row>
     <row r="16" spans="2:84" s="10" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
-      <c r="AU16" s="27"/>
-      <c r="AV16" s="27"/>
-      <c r="AW16" s="27"/>
-      <c r="BG16" s="68"/>
-      <c r="BR16" s="46"/>
-      <c r="BS16" s="46"/>
-      <c r="BT16" s="46"/>
-      <c r="BU16" s="46"/>
-      <c r="BV16" s="49"/>
-      <c r="BW16" s="49"/>
-      <c r="BX16" s="49"/>
-      <c r="BZ16" s="64"/>
-      <c r="CA16" s="64"/>
-      <c r="CB16" s="64"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="16"/>
+      <c r="Y16" s="16"/>
+      <c r="Z16" s="16"/>
+      <c r="AA16" s="16"/>
+      <c r="AB16" s="17"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="17"/>
+      <c r="AF16" s="17"/>
+      <c r="AG16" s="17"/>
+      <c r="AH16" s="17"/>
+      <c r="AI16" s="17"/>
+      <c r="AJ16" s="17"/>
+      <c r="AK16" s="17"/>
+      <c r="AL16" s="17"/>
+      <c r="AM16" s="17"/>
+      <c r="AO16" s="13"/>
+      <c r="AP16" s="13"/>
+      <c r="AQ16" s="13"/>
+      <c r="AR16" s="13"/>
+      <c r="AU16" s="20"/>
+      <c r="AV16" s="20"/>
+      <c r="AW16" s="20"/>
+      <c r="AY16" s="13"/>
+      <c r="AZ16" s="13"/>
+      <c r="BA16" s="13"/>
+      <c r="BG16" s="66"/>
+      <c r="BH16" s="19"/>
+      <c r="BI16" s="19"/>
+      <c r="BJ16" s="19"/>
+      <c r="BK16" s="19"/>
+      <c r="BL16" s="19"/>
+      <c r="BR16" s="45"/>
+      <c r="BS16" s="45"/>
+      <c r="BT16" s="45"/>
+      <c r="BU16" s="45"/>
+      <c r="BV16" s="48"/>
+      <c r="BW16" s="48"/>
+      <c r="BX16" s="48"/>
+      <c r="BZ16" s="63"/>
+      <c r="CA16" s="63"/>
+      <c r="CB16" s="63"/>
     </row>
     <row r="17" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="75" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="29" t="str">
-        <f>+B17</f>
-        <v>Group 2</v>
-      </c>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="B17" s="11"/>
+      <c r="D17" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
       <c r="I17" s="41"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="18"/>
-      <c r="R17" s="18"/>
-      <c r="S17" s="18"/>
-      <c r="T17" s="17"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="18"/>
-      <c r="W17" s="18"/>
-      <c r="X17" s="18"/>
-      <c r="Y17" s="18"/>
-      <c r="Z17" s="18"/>
-      <c r="AA17" s="18"/>
-      <c r="AB17" s="17"/>
-      <c r="AC17" s="17"/>
-      <c r="AD17" s="17"/>
-      <c r="AE17" s="17"/>
-      <c r="AF17" s="17"/>
-      <c r="AG17" s="17"/>
-      <c r="AH17" s="17"/>
-      <c r="AI17" s="17"/>
-      <c r="AJ17" s="17"/>
-      <c r="AK17" s="17"/>
-      <c r="AL17" s="17"/>
-      <c r="AM17" s="17"/>
-      <c r="AO17" s="13"/>
-      <c r="AP17" s="13"/>
-      <c r="AQ17" s="13"/>
-      <c r="AR17" s="13"/>
-      <c r="AU17" s="20"/>
-      <c r="AV17" s="20"/>
-      <c r="AW17" s="20"/>
-      <c r="AY17" s="13"/>
-      <c r="AZ17" s="13"/>
-      <c r="BA17" s="13"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="35" t="str">
+        <f t="shared" ref="L17:AL17" si="45">IFERROR(AVERAGE(L10:L15),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M17" s="35" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N17" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O17" s="35" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P17" s="35" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q17" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R17" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S17" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T17" s="36" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U17" s="36" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V17" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W17" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X17" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y17" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z17" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA17" s="26" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB17" s="36" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC17" s="36" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD17" s="36" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE17" s="36" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF17" s="36" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG17" s="36" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH17" s="36" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI17" s="36" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ17" s="36" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK17" s="36" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL17" s="36" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM17" s="36"/>
+      <c r="AU17" s="27"/>
+      <c r="AV17" s="27"/>
+      <c r="AW17" s="27"/>
       <c r="BG17" s="67"/>
-      <c r="BH17" s="19"/>
-      <c r="BI17" s="19"/>
-      <c r="BJ17" s="19"/>
-      <c r="BK17" s="19"/>
-      <c r="BL17" s="19"/>
-      <c r="BR17" s="46"/>
-      <c r="BS17" s="46"/>
-      <c r="BT17" s="46"/>
-      <c r="BU17" s="46"/>
-      <c r="BV17" s="49"/>
-      <c r="BW17" s="49"/>
-      <c r="BX17" s="49"/>
-      <c r="BZ17" s="64"/>
-      <c r="CA17" s="64"/>
-      <c r="CB17" s="64"/>
+      <c r="BR17" s="45"/>
+      <c r="BS17" s="45"/>
+      <c r="BT17" s="45"/>
+      <c r="BU17" s="45"/>
+      <c r="BV17" s="48"/>
+      <c r="BW17" s="48"/>
+      <c r="BX17" s="48"/>
+      <c r="BZ17" s="63"/>
+      <c r="CA17" s="63"/>
+      <c r="CB17" s="63"/>
     </row>
-    <row r="18" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="35"/>
-      <c r="D18" s="10" t="str" cm="1">
-        <f t="array" ref="D18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18, "SP_COMPANY_NAME"))</f>
-        <v/>
-      </c>
-      <c r="G18" s="21" t="str" cm="1">
-        <f t="array" ref="G18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I18&amp;",NA=--"))</f>
-        <v/>
-      </c>
-      <c r="H18" s="13" t="str" cm="1">
-        <f t="array" ref="H18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="I18" s="41" t="str" cm="1">
-        <f t="array" ref="I18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str" cm="1">
-        <f t="array" ref="J18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="K18" s="15" t="str" cm="1">
-        <f t="array" ref="K18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="L18" s="16" t="str">
-        <f>IFERROR(IF(OR($K18/AO18&gt;L$4,$K18/AO18&lt;L$3),"nmf ",$K18/AO18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="M18" s="16" t="str">
-        <f>IFERROR(IF(OR($K18/AP18&gt;M$4,$K18/AP18&lt;M$3),"nmf ",$K18/AP18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="N18" s="16" t="str">
-        <f>IFERROR(IF(OR($K18/AQ18&gt;N$4,$K18/AQ18&lt;N$3),"nmf ",$K18/AQ18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="O18" s="16" t="str">
-        <f>IFERROR(IF(OR($K18/AR18&gt;O$4,$K18/AR18&lt;O$3),"nmf ",$K18/AR18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="P18" s="16" t="str">
-        <f>IFERROR(IF(OR($K18/AT18&gt;P$4,$K18/AT18&lt;P$3),"nmf ",$K18/AT18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Q18" s="16" t="str">
-        <f>IFERROR(IF(OR($K18/AU18&gt;Q$4,$K18/AU18&lt;Q$3),"nmf ",$K18/AU18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="R18" s="16" t="str">
-        <f>IFERROR(IF(OR($K18/AV18&gt;R$4,$K18/AV18&lt;R$3),"nmf ",$K18/AV18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="S18" s="16" t="str">
-        <f>IFERROR(IF(OR($K18/AW18&gt;S$4,$K18/AW18&lt;S$3),"nmf ",$K18/AW18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T18" s="34" t="str">
-        <f t="shared" ref="T18:U21" si="9">IFERROR((AQ18/AP18)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="U18" s="34" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="V18" s="16" t="str">
-        <f>IFERROR(IF(OR($H18/AY18&gt;#REF!,$H18/AY18&lt;#REF!),"nmf ",$H18/AY18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="W18" s="16" t="str">
-        <f>IFERROR(IF(OR($H18/AZ18&gt;#REF!,$H18/AZ18&lt;#REF!),"nmf ",$H18/AZ18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="X18" s="16" t="str">
-        <f>IFERROR(IF(OR($H18/BA18&gt;#REF!,$H18/BA18&lt;#REF!),"nmf ",$H18/BA18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Y18" s="16" t="str">
-        <f>IFERROR(IF(OR($H18/BC18&gt;#REF!,$H18/BC18&lt;#REF!),"nmf ",$H18/BC18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Z18" s="16" t="str">
-        <f>IFERROR(IF(OR($H18/BD18&gt;#REF!,$H18/BD18&lt;#REF!),"nmf ",$H18/BD18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AA18" s="16" t="str">
-        <f>IFERROR(IF(OR($H18/BE18&gt;#REF!,$H18/BE18&lt;#REF!),"nmf ",$H18/BE18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AB18" s="34" t="str">
-        <f t="shared" ref="AB18:AB21" si="10">IFERROR((AS18/AR18)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AC18" s="34" t="str">
-        <f t="shared" ref="AC18:AC21" si="11">IFERROR((AT18/AS18)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AD18" s="34" t="str">
-        <f t="shared" ref="AD18:AD21" si="12">IFERROR((AU18/AT18)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AE18" s="34" t="str">
-        <f t="shared" ref="AE18:AE21" si="13">IFERROR((AV18/AU18)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AF18" s="34" t="str">
-        <f t="shared" ref="AF18:AF21" si="14">IFERROR((AW18/AV18)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AG18" s="34" t="str">
-        <f>IFERROR((BM18/AW18)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AH18" s="34" t="str">
-        <f t="shared" ref="AH18:AH21" si="15">IFERROR((BN18/BM18)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AI18" s="34" t="str">
-        <f t="shared" ref="AI18:AI21" si="16">IFERROR((BO18/BN18)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ18" s="34" t="str">
-        <f t="shared" ref="AJ18:AJ21" si="17">IFERROR((BP18/BO18)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK18" s="34" t="str">
-        <f t="shared" ref="AK18:AK21" si="18">IFERROR((BQ18/BP18)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL18" s="34" t="str">
-        <f t="shared" ref="AL18:AL21" si="19">IFERROR((BR18/BQ18)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM18" s="73"/>
-      <c r="AO18" s="20" t="str" cm="1">
-        <f t="array" ref="AO18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AP18" s="20" t="str" cm="1">
-        <f t="array" ref="AP18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AQ18" s="20" t="str" cm="1">
-        <f t="array" ref="AQ18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AR18" s="20" t="str" cm="1">
-        <f t="array" ref="AR18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AT18" s="20" t="str" cm="1">
-        <f t="array" ref="AT18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AU18" s="20" t="str" cm="1">
-        <f t="array" ref="AU18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AV18" s="20" t="str" cm="1">
-        <f t="array" ref="AV18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AW18" s="20" t="str" cm="1">
-        <f t="array" ref="AW18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AY18" s="13" t="str" cm="1">
-        <f t="array" ref="AY18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AZ18" s="13" t="str" cm="1">
-        <f t="array" ref="AZ18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BA18" s="13" t="str" cm="1">
-        <f t="array" ref="BA18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BC18" s="13" t="str" cm="1">
-        <f t="array" ref="BC18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BD18" s="13" t="str" cm="1">
-        <f t="array" ref="BD18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BE18" s="13" t="str" cm="1">
-        <f t="array" ref="BE18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG18" s="67" t="str" cm="1">
-        <f t="array" ref="BG18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BH18" s="19" t="str" cm="1">
-        <f t="array" ref="BH18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BI18" s="19" t="str" cm="1">
-        <f t="array" ref="BI18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ18" s="19" t="str" cm="1">
-        <f t="array" ref="BJ18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK18" s="38" t="e">
-        <f t="shared" ref="BK18:BK20" si="20">+BI18-BJ18</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BL18" s="19" t="str" cm="1">
-        <f t="array" ref="BL18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BN18" s="20" t="str">
-        <f>IFERROR($AP18*$BR18,"n/a")</f>
-        <v>n/a</v>
-      </c>
-      <c r="BO18" s="20" t="str">
-        <f t="shared" ref="BO18:BO21" si="21">IFERROR($AQ18*BS18,"n/a")</f>
-        <v>n/a</v>
-      </c>
-      <c r="BP18" s="20" t="str">
-        <f>IFERROR($AR18*$BT18,"n/a")</f>
-        <v>n/a</v>
-      </c>
-      <c r="BR18" s="45" t="str">
-        <f>IF($B18="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
-        <v/>
-      </c>
-      <c r="BS18" s="45" t="str">
-        <f>IF($B18="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
-        <v/>
-      </c>
-      <c r="BT18" s="45" t="str">
-        <f>IF($B18="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
-        <v/>
-      </c>
-      <c r="BU18" s="46"/>
-      <c r="BV18" s="48" t="str" cm="1">
-        <f t="array" ref="BV18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BW18" s="48" t="str" cm="1">
-        <f t="array" ref="BW18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BX18" s="48" t="str" cm="1">
-        <f t="array" ref="BX18">IF($B18="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B18,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BZ18" s="63" t="str">
-        <f>IFERROR(IF(CD18/AP18&lt;0,"nmf ",CD18/AP18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CA18" s="63" t="str">
-        <f>IFERROR(IF(CE18/AQ18&lt;0,"nmf ",CE18/AQ18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CB18" s="63" t="str">
-        <f>IFERROR(IF(CF18/AR18&lt;0,"nmf ",CF18/AR18),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CD18" s="20" t="str">
-        <f>IFERROR(BR18*AP18,"--")</f>
-        <v>--</v>
-      </c>
-      <c r="CE18" s="20" t="str">
-        <f>IFERROR(BS18*AQ18,"--")</f>
-        <v>--</v>
-      </c>
-      <c r="CF18" s="20" t="str">
-        <f>IFERROR(BT18*AR18,"--")</f>
-        <v>--</v>
-      </c>
+    <row r="18" spans="2:84" s="10" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="AU18" s="27"/>
+      <c r="AV18" s="27"/>
+      <c r="AW18" s="27"/>
+      <c r="BG18" s="67"/>
+      <c r="BR18" s="45"/>
+      <c r="BS18" s="45"/>
+      <c r="BT18" s="45"/>
+      <c r="BU18" s="45"/>
+      <c r="BV18" s="48"/>
+      <c r="BW18" s="48"/>
+      <c r="BX18" s="48"/>
+      <c r="BZ18" s="63"/>
+      <c r="CA18" s="63"/>
+      <c r="CB18" s="63"/>
     </row>
     <row r="19" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="35"/>
-      <c r="D19" s="10" t="str" cm="1">
-        <f t="array" ref="D19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19, "SP_COMPANY_NAME"))</f>
-        <v/>
-      </c>
-      <c r="G19" s="21" t="str" cm="1">
-        <f t="array" ref="G19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I19&amp;",NA=--"))</f>
-        <v/>
-      </c>
-      <c r="H19" s="13" t="str" cm="1">
-        <f t="array" ref="H19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="I19" s="41" t="str" cm="1">
-        <f t="array" ref="I19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str" cm="1">
-        <f t="array" ref="J19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="K19" s="15" t="str" cm="1">
-        <f t="array" ref="K19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="L19" s="16" t="str">
-        <f>IFERROR(IF(OR($K19/AO19&gt;L$4,$K19/AO19&lt;L$3),"nmf ",$K19/AO19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="M19" s="16" t="str">
-        <f>IFERROR(IF(OR($K19/AP19&gt;M$4,$K19/AP19&lt;M$3),"nmf ",$K19/AP19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="N19" s="16" t="str">
-        <f>IFERROR(IF(OR($K19/AQ19&gt;N$4,$K19/AQ19&lt;N$3),"nmf ",$K19/AQ19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="O19" s="16" t="str">
-        <f>IFERROR(IF(OR($K19/AR19&gt;O$4,$K19/AR19&lt;O$3),"nmf ",$K19/AR19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="P19" s="16" t="str">
-        <f>IFERROR(IF(OR($K19/AT19&gt;P$4,$K19/AT19&lt;P$3),"nmf ",$K19/AT19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Q19" s="16" t="str">
-        <f>IFERROR(IF(OR($K19/AU19&gt;Q$4,$K19/AU19&lt;Q$3),"nmf ",$K19/AU19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="R19" s="16" t="str">
-        <f>IFERROR(IF(OR($K19/AV19&gt;R$4,$K19/AV19&lt;R$3),"nmf ",$K19/AV19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="S19" s="16" t="str">
-        <f>IFERROR(IF(OR($K19/AW19&gt;S$4,$K19/AW19&lt;S$3),"nmf ",$K19/AW19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T19" s="34" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="U19" s="34" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="V19" s="16" t="str">
-        <f>IFERROR(IF(OR($H19/AY19&gt;#REF!,$H19/AY19&lt;#REF!),"nmf ",$H19/AY19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="W19" s="16" t="str">
-        <f>IFERROR(IF(OR($H19/AZ19&gt;#REF!,$H19/AZ19&lt;#REF!),"nmf ",$H19/AZ19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="X19" s="16" t="str">
-        <f>IFERROR(IF(OR($H19/BA19&gt;#REF!,$H19/BA19&lt;#REF!),"nmf ",$H19/BA19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Y19" s="16" t="str">
-        <f>IFERROR(IF(OR($H19/BC19&gt;#REF!,$H19/BC19&lt;#REF!),"nmf ",$H19/BC19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Z19" s="16" t="str">
-        <f>IFERROR(IF(OR($H19/BD19&gt;#REF!,$H19/BD19&lt;#REF!),"nmf ",$H19/BD19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AA19" s="16" t="str">
-        <f>IFERROR(IF(OR($H19/BE19&gt;#REF!,$H19/BE19&lt;#REF!),"nmf ",$H19/BE19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AB19" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AC19" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AD19" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AE19" s="34" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AF19" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AG19" s="34" t="str">
-        <f>IFERROR((BM19/AW19)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AH19" s="34" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AI19" s="34" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ19" s="34" t="str">
-        <f t="shared" si="17"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK19" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL19" s="34" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM19" s="73"/>
-      <c r="AO19" s="20" t="str" cm="1">
-        <f t="array" ref="AO19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AP19" s="20" t="str" cm="1">
-        <f t="array" ref="AP19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AQ19" s="20" t="str" cm="1">
-        <f t="array" ref="AQ19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AR19" s="20" t="str" cm="1">
-        <f t="array" ref="AR19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AT19" s="20" t="str" cm="1">
-        <f t="array" ref="AT19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AU19" s="20" t="str" cm="1">
-        <f t="array" ref="AU19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AV19" s="20" t="str" cm="1">
-        <f t="array" ref="AV19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AW19" s="20" t="str" cm="1">
-        <f t="array" ref="AW19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AY19" s="13" t="str" cm="1">
-        <f t="array" ref="AY19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="AZ19" s="13" t="str" cm="1">
-        <f t="array" ref="AZ19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BA19" s="13" t="str" cm="1">
-        <f t="array" ref="BA19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BC19" s="13" t="str" cm="1">
-        <f t="array" ref="BC19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BD19" s="13" t="str" cm="1">
-        <f t="array" ref="BD19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BE19" s="13" t="str" cm="1">
-        <f t="array" ref="BE19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG19" s="67" t="str" cm="1">
-        <f t="array" ref="BG19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BH19" s="19" t="str" cm="1">
-        <f t="array" ref="BH19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BI19" s="19" t="str" cm="1">
-        <f t="array" ref="BI19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ19" s="19" t="str" cm="1">
-        <f t="array" ref="BJ19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK19" s="38" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BL19" s="19" t="str" cm="1">
-        <f t="array" ref="BL19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BN19" s="20" t="str">
-        <f>IFERROR($AP19*$BR19,"n/a")</f>
-        <v>n/a</v>
-      </c>
-      <c r="BO19" s="20" t="str">
-        <f t="shared" si="21"/>
-        <v>n/a</v>
-      </c>
-      <c r="BP19" s="20" t="str">
-        <f>IFERROR($AR19*$BT19,"n/a")</f>
-        <v>n/a</v>
-      </c>
-      <c r="BR19" s="45" t="str">
-        <f>IF($B19="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
-        <v/>
-      </c>
-      <c r="BS19" s="45" t="str">
-        <f>IF($B19="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
-        <v/>
-      </c>
-      <c r="BT19" s="45" t="str">
-        <f>IF($B19="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
-        <v/>
-      </c>
-      <c r="BU19" s="46"/>
-      <c r="BV19" s="48" t="str" cm="1">
-        <f t="array" ref="BV19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BW19" s="48" t="str" cm="1">
-        <f t="array" ref="BW19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BX19" s="48" t="str" cm="1">
-        <f t="array" ref="BX19">IF($B19="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B19,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BZ19" s="63" t="str">
-        <f>IFERROR(IF(CD19/AP19&lt;0,"nmf ",CD19/AP19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CA19" s="63" t="str">
-        <f>IFERROR(IF(CE19/AQ19&lt;0,"nmf ",CE19/AQ19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CB19" s="63" t="str">
-        <f>IFERROR(IF(CF19/AR19&lt;0,"nmf ",CF19/AR19),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CD19" s="20" t="str">
-        <f>IFERROR(BR19*AP19,"--")</f>
-        <v>--</v>
-      </c>
-      <c r="CE19" s="20" t="str">
-        <f>IFERROR(BS19*AQ19,"--")</f>
-        <v>--</v>
-      </c>
-      <c r="CF19" s="20" t="str">
-        <f>IFERROR(BT19*AR19,"--")</f>
-        <v>--</v>
-      </c>
+      <c r="B19" s="11"/>
+      <c r="D19" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="18"/>
+      <c r="X19" s="18"/>
+      <c r="Y19" s="18"/>
+      <c r="Z19" s="18"/>
+      <c r="AA19" s="18"/>
+      <c r="AB19" s="17"/>
+      <c r="AC19" s="17"/>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
+      <c r="AF19" s="17"/>
+      <c r="AG19" s="17"/>
+      <c r="AH19" s="17"/>
+      <c r="AI19" s="17"/>
+      <c r="AJ19" s="17"/>
+      <c r="AK19" s="17"/>
+      <c r="AL19" s="17"/>
+      <c r="AM19" s="17"/>
+      <c r="AO19" s="13"/>
+      <c r="AP19" s="13"/>
+      <c r="AQ19" s="13"/>
+      <c r="AR19" s="13"/>
+      <c r="AU19" s="20"/>
+      <c r="AV19" s="20"/>
+      <c r="AW19" s="20"/>
+      <c r="AY19" s="13"/>
+      <c r="AZ19" s="13"/>
+      <c r="BA19" s="13"/>
+      <c r="BG19" s="66"/>
+      <c r="BH19" s="19"/>
+      <c r="BI19" s="19"/>
+      <c r="BJ19" s="19"/>
+      <c r="BK19" s="19"/>
+      <c r="BL19" s="19"/>
+      <c r="BR19" s="45"/>
+      <c r="BS19" s="45"/>
+      <c r="BT19" s="45"/>
+      <c r="BU19" s="45"/>
+      <c r="BV19" s="48"/>
+      <c r="BW19" s="48"/>
+      <c r="BX19" s="48"/>
+      <c r="BZ19" s="63"/>
+      <c r="CA19" s="63"/>
+      <c r="CB19" s="63"/>
     </row>
     <row r="20" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="35"/>
+      <c r="B20" s="34"/>
       <c r="D20" s="10" t="str" cm="1">
         <f t="array" ref="D20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20, "SP_COMPANY_NAME"))</f>
         <v/>
@@ -4970,7 +4951,7 @@
         <f t="array" ref="H20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="I20" s="41" t="str" cm="1">
+      <c r="I20" s="40" t="str" cm="1">
         <f t="array" ref="I20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
         <v/>
       </c>
@@ -4983,43 +4964,43 @@
         <v/>
       </c>
       <c r="L20" s="16" t="str">
-        <f>IFERROR(IF(OR($K20/AO20&gt;L$4,$K20/AO20&lt;L$3),"nmf ",$K20/AO20),"n/a ")</f>
+        <f t="shared" ref="L20:O25" si="46">IFERROR(IF(OR($K20/AO20&gt;L$4,$K20/AO20&lt;L$3),"nmf ",$K20/AO20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M20" s="16" t="str">
-        <f>IFERROR(IF(OR($K20/AP20&gt;M$4,$K20/AP20&lt;M$3),"nmf ",$K20/AP20),"n/a ")</f>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N20" s="16" t="str">
-        <f>IFERROR(IF(OR($K20/AQ20&gt;N$4,$K20/AQ20&lt;N$3),"nmf ",$K20/AQ20),"n/a ")</f>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O20" s="16" t="str">
-        <f>IFERROR(IF(OR($K20/AR20&gt;O$4,$K20/AR20&lt;O$3),"nmf ",$K20/AR20),"n/a ")</f>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P20" s="16" t="str">
-        <f>IFERROR(IF(OR($K20/AT20&gt;P$4,$K20/AT20&lt;P$3),"nmf ",$K20/AT20),"n/a ")</f>
+        <f t="shared" ref="P20:S25" si="47">IFERROR(IF(OR($K20/AT20&gt;P$4,$K20/AT20&lt;P$3),"nmf ",$K20/AT20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q20" s="16" t="str">
-        <f>IFERROR(IF(OR($K20/AU20&gt;Q$4,$K20/AU20&lt;Q$3),"nmf ",$K20/AU20),"n/a ")</f>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R20" s="16" t="str">
-        <f>IFERROR(IF(OR($K20/AV20&gt;R$4,$K20/AV20&lt;R$3),"nmf ",$K20/AV20),"n/a ")</f>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S20" s="16" t="str">
-        <f>IFERROR(IF(OR($K20/AW20&gt;S$4,$K20/AW20&lt;S$3),"nmf ",$K20/AW20),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T20" s="34" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="U20" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T20" s="33" t="str">
+        <f t="shared" ref="T20:U25" si="48">IFERROR((AQ20/AP20)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U20" s="33" t="str">
+        <f t="shared" si="48"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V20" s="16" t="str">
@@ -5046,51 +5027,51 @@
         <f>IFERROR(IF(OR($H20/BE20&gt;#REF!,$H20/BE20&lt;#REF!),"nmf ",$H20/BE20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="AB20" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AC20" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AD20" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AE20" s="34" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AF20" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AG20" s="34" t="str">
+      <c r="AB20" s="33" t="str">
+        <f t="shared" ref="AB20:AB25" si="49">IFERROR((AS20/AR20)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC20" s="33" t="str">
+        <f t="shared" ref="AC20:AC25" si="50">IFERROR((AT20/AS20)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD20" s="33" t="str">
+        <f t="shared" ref="AD20:AD25" si="51">IFERROR((AU20/AT20)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE20" s="33" t="str">
+        <f t="shared" ref="AE20:AE25" si="52">IFERROR((AV20/AU20)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF20" s="33" t="str">
+        <f t="shared" ref="AF20:AF25" si="53">IFERROR((AW20/AV20)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG20" s="33" t="str">
         <f>IFERROR((BM20/AW20)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="AH20" s="34" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AI20" s="34" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ20" s="34" t="str">
-        <f t="shared" si="17"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK20" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL20" s="34" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM20" s="73"/>
+      <c r="AH20" s="33" t="str">
+        <f t="shared" ref="AH20:AH25" si="54">IFERROR((BN20/BM20)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI20" s="33" t="str">
+        <f t="shared" ref="AI20:AI25" si="55">IFERROR((BO20/BN20)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ20" s="33" t="str">
+        <f t="shared" ref="AJ20:AJ25" si="56">IFERROR((BP20/BO20)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK20" s="33" t="str">
+        <f t="shared" ref="AK20:AK25" si="57">IFERROR((BQ20/BP20)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL20" s="33" t="str">
+        <f t="shared" ref="AL20:AL25" si="58">IFERROR((BR20/BQ20)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM20" s="72"/>
       <c r="AO20" s="20" t="str" cm="1">
         <f t="array" ref="AO20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
@@ -5147,7 +5128,7 @@
         <f t="array" ref="BE20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BG20" s="67" t="str" cm="1">
+      <c r="BG20" s="66" t="str" cm="1">
         <f t="array" ref="BG20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
         <v/>
       </c>
@@ -5163,8 +5144,8 @@
         <f t="array" ref="BJ20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="BK20" s="38" t="e">
-        <f t="shared" si="20"/>
+      <c r="BK20" s="37" t="e">
+        <f t="shared" ref="BK20:BK22" si="59">+BI20-BJ20</f>
         <v>#VALUE!</v>
       </c>
       <c r="BL20" s="19" t="str" cm="1">
@@ -5176,65 +5157,65 @@
         <v>n/a</v>
       </c>
       <c r="BO20" s="20" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="BO20:BO25" si="60">IFERROR($AQ20*BS20,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BP20" s="20" t="str">
         <f>IFERROR($AR20*$BT20,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BR20" s="45" t="str">
+      <c r="BR20" s="44" t="str">
         <f>IF($B20="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BS20" s="45" t="str">
+      <c r="BS20" s="44" t="str">
         <f>IF($B20="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BT20" s="45" t="str">
+      <c r="BT20" s="44" t="str">
         <f>IF($B20="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BU20" s="46"/>
-      <c r="BV20" s="48" t="str" cm="1">
+      <c r="BU20" s="45"/>
+      <c r="BV20" s="47" t="str" cm="1">
         <f t="array" ref="BV20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BW20" s="48" t="str" cm="1">
+      <c r="BW20" s="47" t="str" cm="1">
         <f t="array" ref="BW20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BX20" s="48" t="str" cm="1">
+      <c r="BX20" s="47" t="str" cm="1">
         <f t="array" ref="BX20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BZ20" s="63" t="str">
-        <f>IFERROR(IF(CD20/AP20&lt;0,"nmf ",CD20/AP20),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CA20" s="63" t="str">
-        <f>IFERROR(IF(CE20/AQ20&lt;0,"nmf ",CE20/AQ20),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CB20" s="63" t="str">
-        <f>IFERROR(IF(CF20/AR20&lt;0,"nmf ",CF20/AR20),"n/a ")</f>
+      <c r="BZ20" s="62" t="str">
+        <f t="shared" ref="BZ20:CB25" si="61">IFERROR(IF(CD20/AP20&lt;0,"nmf ",CD20/AP20),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA20" s="62" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB20" s="62" t="str">
+        <f t="shared" si="61"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD20" s="20" t="str">
-        <f>IFERROR(BR20*AP20,"--")</f>
+        <f t="shared" ref="CD20:CF25" si="62">IFERROR(BR20*AP20,"--")</f>
         <v>--</v>
       </c>
       <c r="CE20" s="20" t="str">
-        <f>IFERROR(BS20*AQ20,"--")</f>
+        <f t="shared" si="62"/>
         <v>--</v>
       </c>
       <c r="CF20" s="20" t="str">
-        <f>IFERROR(BT20*AR20,"--")</f>
+        <f t="shared" si="62"/>
         <v>--</v>
       </c>
     </row>
     <row r="21" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="35"/>
+      <c r="B21" s="34"/>
       <c r="D21" s="10" t="str" cm="1">
         <f t="array" ref="D21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21, "SP_COMPANY_NAME"))</f>
         <v/>
@@ -5247,7 +5228,7 @@
         <f t="array" ref="H21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="I21" s="41" t="str" cm="1">
+      <c r="I21" s="40" t="str" cm="1">
         <f t="array" ref="I21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
         <v/>
       </c>
@@ -5260,43 +5241,43 @@
         <v/>
       </c>
       <c r="L21" s="16" t="str">
-        <f>IFERROR(IF(OR($K21/AO21&gt;L$4,$K21/AO21&lt;L$3),"nmf ",$K21/AO21),"n/a ")</f>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M21" s="16" t="str">
-        <f>IFERROR(IF(OR($K21/AP21&gt;M$4,$K21/AP21&lt;M$3),"nmf ",$K21/AP21),"n/a ")</f>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N21" s="16" t="str">
-        <f>IFERROR(IF(OR($K21/AQ21&gt;N$4,$K21/AQ21&lt;N$3),"nmf ",$K21/AQ21),"n/a ")</f>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O21" s="16" t="str">
-        <f>IFERROR(IF(OR($K21/AR21&gt;O$4,$K21/AR21&lt;O$3),"nmf ",$K21/AR21),"n/a ")</f>
+        <f t="shared" si="46"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P21" s="16" t="str">
-        <f>IFERROR(IF(OR($K21/AT21&gt;P$4,$K21/AT21&lt;P$3),"nmf ",$K21/AT21),"n/a ")</f>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q21" s="16" t="str">
-        <f>IFERROR(IF(OR($K21/AU21&gt;Q$4,$K21/AU21&lt;Q$3),"nmf ",$K21/AU21),"n/a ")</f>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R21" s="16" t="str">
-        <f>IFERROR(IF(OR($K21/AV21&gt;R$4,$K21/AV21&lt;R$3),"nmf ",$K21/AV21),"n/a ")</f>
+        <f t="shared" si="47"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S21" s="16" t="str">
-        <f>IFERROR(IF(OR($K21/AW21&gt;S$4,$K21/AW21&lt;S$3),"nmf ",$K21/AW21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T21" s="34" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="U21" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T21" s="33" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U21" s="33" t="str">
+        <f t="shared" si="48"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V21" s="16" t="str">
@@ -5323,51 +5304,51 @@
         <f>IFERROR(IF(OR($H21/BE21&gt;#REF!,$H21/BE21&lt;#REF!),"nmf ",$H21/BE21),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="AB21" s="34" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AC21" s="34" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AD21" s="34" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AE21" s="34" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AF21" s="34" t="str">
-        <f t="shared" si="14"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AG21" s="34" t="str">
+      <c r="AB21" s="33" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC21" s="33" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD21" s="33" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE21" s="33" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF21" s="33" t="str">
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG21" s="33" t="str">
         <f>IFERROR((BM21/AW21)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="AH21" s="34" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AI21" s="34" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ21" s="34" t="str">
-        <f t="shared" si="17"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK21" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL21" s="34" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM21" s="73"/>
+      <c r="AH21" s="33" t="str">
+        <f t="shared" si="54"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI21" s="33" t="str">
+        <f t="shared" si="55"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ21" s="33" t="str">
+        <f t="shared" si="56"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK21" s="33" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL21" s="33" t="str">
+        <f t="shared" si="58"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM21" s="72"/>
       <c r="AO21" s="20" t="str" cm="1">
         <f t="array" ref="AO21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
@@ -5424,7 +5405,7 @@
         <f t="array" ref="BE21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BG21" s="67" t="str" cm="1">
+      <c r="BG21" s="66" t="str" cm="1">
         <f t="array" ref="BG21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
         <v/>
       </c>
@@ -5440,8 +5421,8 @@
         <f t="array" ref="BJ21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="BK21" s="38" t="e">
-        <f>+BI21-BJ21</f>
+      <c r="BK21" s="37" t="e">
+        <f t="shared" si="59"/>
         <v>#VALUE!</v>
       </c>
       <c r="BL21" s="19" t="str" cm="1">
@@ -5453,740 +5434,3798 @@
         <v>n/a</v>
       </c>
       <c r="BO21" s="20" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="60"/>
         <v>n/a</v>
       </c>
       <c r="BP21" s="20" t="str">
         <f>IFERROR($AR21*$BT21,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BR21" s="45" t="str">
+      <c r="BR21" s="44" t="str">
         <f>IF($B21="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BS21" s="45" t="str">
+      <c r="BS21" s="44" t="str">
         <f>IF($B21="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BT21" s="45" t="str">
+      <c r="BT21" s="44" t="str">
         <f>IF($B21="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
         <v/>
       </c>
-      <c r="BU21" s="46"/>
-      <c r="BV21" s="48" t="str" cm="1">
+      <c r="BU21" s="45"/>
+      <c r="BV21" s="47" t="str" cm="1">
         <f t="array" ref="BV21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BW21" s="48" t="str" cm="1">
+      <c r="BW21" s="47" t="str" cm="1">
         <f t="array" ref="BW21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BX21" s="48" t="str" cm="1">
+      <c r="BX21" s="47" t="str" cm="1">
         <f t="array" ref="BX21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
         <v/>
       </c>
-      <c r="BZ21" s="63" t="str">
-        <f>IFERROR(IF(CD21/AP21&lt;0,"nmf ",CD21/AP21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CA21" s="63" t="str">
-        <f>IFERROR(IF(CE21/AQ21&lt;0,"nmf ",CE21/AQ21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="CB21" s="63" t="str">
-        <f>IFERROR(IF(CF21/AR21&lt;0,"nmf ",CF21/AR21),"n/a ")</f>
+      <c r="BZ21" s="62" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA21" s="62" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB21" s="62" t="str">
+        <f t="shared" si="61"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD21" s="20" t="str">
-        <f>IFERROR(BR21*AP21,"--")</f>
+        <f t="shared" si="62"/>
         <v>--</v>
       </c>
       <c r="CE21" s="20" t="str">
-        <f>IFERROR(BS21*AQ21,"--")</f>
+        <f t="shared" si="62"/>
         <v>--</v>
       </c>
       <c r="CF21" s="20" t="str">
-        <f>IFERROR(BT21*AR21,"--")</f>
+        <f t="shared" si="62"/>
         <v>--</v>
       </c>
     </row>
-    <row r="22" spans="2:84" s="10" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="11"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="16"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="16"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="16"/>
-      <c r="Y22" s="16"/>
-      <c r="Z22" s="16"/>
-      <c r="AA22" s="16"/>
-      <c r="AB22" s="17"/>
-      <c r="AC22" s="17"/>
-      <c r="AD22" s="17"/>
-      <c r="AE22" s="17"/>
-      <c r="AF22" s="17"/>
-      <c r="AG22" s="17"/>
-      <c r="AH22" s="17"/>
-      <c r="AI22" s="17"/>
-      <c r="AJ22" s="17"/>
-      <c r="AK22" s="17"/>
-      <c r="AL22" s="17"/>
-      <c r="AM22" s="17"/>
-      <c r="AO22" s="19"/>
-      <c r="AP22" s="13"/>
-      <c r="AQ22" s="13"/>
-      <c r="AR22" s="13"/>
-      <c r="AU22" s="20"/>
-      <c r="AV22" s="20"/>
-      <c r="AW22" s="20"/>
-      <c r="AY22" s="13"/>
-      <c r="AZ22" s="13"/>
-      <c r="BA22" s="13"/>
-      <c r="BG22" s="19"/>
-      <c r="BH22" s="19"/>
-      <c r="BI22" s="19"/>
-      <c r="BJ22" s="19"/>
-      <c r="BK22" s="19"/>
-      <c r="BL22" s="19"/>
-      <c r="BR22" s="46"/>
-      <c r="BS22" s="46"/>
-      <c r="BT22" s="46"/>
-      <c r="BU22" s="46"/>
-      <c r="BV22" s="49"/>
-      <c r="BW22" s="49"/>
-      <c r="BX22" s="49"/>
-      <c r="BZ22" s="46"/>
-      <c r="CA22" s="46"/>
-      <c r="CB22" s="46"/>
+    <row r="22" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="34"/>
+      <c r="D22" s="10" t="str" cm="1">
+        <f t="array" ref="D22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22, "SP_COMPANY_NAME"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="21" t="str" cm="1">
+        <f t="array" ref="G22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I22&amp;",NA=--"))</f>
+        <v/>
+      </c>
+      <c r="H22" s="13" t="str" cm="1">
+        <f t="array" ref="H22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="I22" s="40" t="str" cm="1">
+        <f t="array" ref="I22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="J22" s="15" t="str" cm="1">
+        <f t="array" ref="J22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="K22" s="15" t="str" cm="1">
+        <f t="array" ref="K22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="L22" s="16" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M22" s="16" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N22" s="16" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O22" s="16" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P22" s="16" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q22" s="16" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R22" s="16" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S22" s="16" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T22" s="33" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U22" s="33" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V22" s="16" t="str">
+        <f>IFERROR(IF(OR($H22/AY22&gt;#REF!,$H22/AY22&lt;#REF!),"nmf ",$H22/AY22),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W22" s="16" t="str">
+        <f>IFERROR(IF(OR($H22/AZ22&gt;#REF!,$H22/AZ22&lt;#REF!),"nmf ",$H22/AZ22),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X22" s="16" t="str">
+        <f>IFERROR(IF(OR($H22/BA22&gt;#REF!,$H22/BA22&lt;#REF!),"nmf ",$H22/BA22),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y22" s="16" t="str">
+        <f>IFERROR(IF(OR($H22/BC22&gt;#REF!,$H22/BC22&lt;#REF!),"nmf ",$H22/BC22),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z22" s="16" t="str">
+        <f>IFERROR(IF(OR($H22/BD22&gt;#REF!,$H22/BD22&lt;#REF!),"nmf ",$H22/BD22),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA22" s="16" t="str">
+        <f>IFERROR(IF(OR($H22/BE22&gt;#REF!,$H22/BE22&lt;#REF!),"nmf ",$H22/BE22),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB22" s="33" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC22" s="33" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD22" s="33" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE22" s="33" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF22" s="33" t="str">
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG22" s="33" t="str">
+        <f>IFERROR((BM22/AW22)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH22" s="33" t="str">
+        <f t="shared" si="54"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI22" s="33" t="str">
+        <f t="shared" si="55"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ22" s="33" t="str">
+        <f t="shared" si="56"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK22" s="33" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL22" s="33" t="str">
+        <f t="shared" si="58"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM22" s="72"/>
+      <c r="AO22" s="20" t="str" cm="1">
+        <f t="array" ref="AO22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AP22" s="20" t="str" cm="1">
+        <f t="array" ref="AP22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AQ22" s="20" t="str" cm="1">
+        <f t="array" ref="AQ22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AR22" s="20" t="str" cm="1">
+        <f t="array" ref="AR22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AT22" s="20" t="str" cm="1">
+        <f t="array" ref="AT22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AU22" s="20" t="str" cm="1">
+        <f t="array" ref="AU22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AV22" s="20" t="str" cm="1">
+        <f t="array" ref="AV22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AW22" s="20" t="str" cm="1">
+        <f t="array" ref="AW22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AY22" s="13" t="str" cm="1">
+        <f t="array" ref="AY22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AZ22" s="13" t="str" cm="1">
+        <f t="array" ref="AZ22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BA22" s="13" t="str" cm="1">
+        <f t="array" ref="BA22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BC22" s="13" t="str" cm="1">
+        <f t="array" ref="BC22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BD22" s="13" t="str" cm="1">
+        <f t="array" ref="BD22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BE22" s="13" t="str" cm="1">
+        <f t="array" ref="BE22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG22" s="66" t="str" cm="1">
+        <f t="array" ref="BG22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BH22" s="19" t="str" cm="1">
+        <f t="array" ref="BH22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BI22" s="19" t="str" cm="1">
+        <f t="array" ref="BI22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ22" s="19" t="str" cm="1">
+        <f t="array" ref="BJ22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BK22" s="37" t="e">
+        <f t="shared" si="59"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL22" s="19" t="str" cm="1">
+        <f t="array" ref="BL22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BN22" s="20" t="str">
+        <f>IFERROR($AP22*$BR22,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BO22" s="20" t="str">
+        <f t="shared" si="60"/>
+        <v>n/a</v>
+      </c>
+      <c r="BP22" s="20" t="str">
+        <f>IFERROR($AR22*$BT22,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BR22" s="44" t="str">
+        <f>IF($B22="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BS22" s="44" t="str">
+        <f>IF($B22="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BT22" s="44" t="str">
+        <f>IF($B22="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BU22" s="45"/>
+      <c r="BV22" s="47" t="str" cm="1">
+        <f t="array" ref="BV22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BW22" s="47" t="str" cm="1">
+        <f t="array" ref="BW22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BX22" s="47" t="str" cm="1">
+        <f t="array" ref="BX22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BZ22" s="62" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA22" s="62" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB22" s="62" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD22" s="20" t="str">
+        <f t="shared" si="62"/>
+        <v>--</v>
+      </c>
+      <c r="CE22" s="20" t="str">
+        <f t="shared" si="62"/>
+        <v>--</v>
+      </c>
+      <c r="CF22" s="20" t="str">
+        <f t="shared" si="62"/>
+        <v>--</v>
+      </c>
     </row>
     <row r="23" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="9"/>
-      <c r="D23" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="36" t="str">
-        <f>IFERROR(AVERAGE(L18:L21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="M23" s="36" t="str">
-        <f>IFERROR(AVERAGE(M18:M21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="N23" s="26" t="str">
-        <f>IFERROR(AVERAGE(N18:N21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="O23" s="26" t="str">
-        <f>IFERROR(AVERAGE(O18:O21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="P23" s="26" t="str">
-        <f t="shared" ref="P23" si="22">IFERROR(AVERAGE(P18:P21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Q23" s="26" t="str">
-        <f>IFERROR(AVERAGE(Q18:Q21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="R23" s="26" t="str">
-        <f>IFERROR(AVERAGE(R18:R21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="S23" s="26" t="str">
-        <f>IFERROR(AVERAGE(S18:S21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T23" s="37" t="str">
-        <f>IFERROR(AVERAGE(T18:T21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="U23" s="37" t="str">
-        <f>IFERROR(AVERAGE(U18:U21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="V23" s="26" t="str">
-        <f>IFERROR(AVERAGE(V18:V21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="W23" s="26" t="str">
-        <f>IFERROR(AVERAGE(W18:W21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="X23" s="26" t="str">
-        <f>IFERROR(AVERAGE(X18:X21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Y23" s="26" t="str">
-        <f>IFERROR(AVERAGE(Y18:Y21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Z23" s="26" t="str">
-        <f>IFERROR(AVERAGE(Z18:Z21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AA23" s="26" t="str">
-        <f>IFERROR(AVERAGE(AA18:AA21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AB23" s="37" t="str">
-        <f>IFERROR(AVERAGE(AB18:AB21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AC23" s="37" t="str">
-        <f>IFERROR(AVERAGE(AC18:AC21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AD23" s="37" t="str">
-        <f>IFERROR(AVERAGE(AD18:AD21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AE23" s="37" t="str">
-        <f>IFERROR(AVERAGE(AE18:AE21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AF23" s="37" t="str">
-        <f>IFERROR(AVERAGE(AF18:AF21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AG23" s="37" t="str">
-        <f>IFERROR(AVERAGE(AG18:AG21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AH23" s="37" t="str">
-        <f>IFERROR(AVERAGE(AH18:AH21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AI23" s="37" t="str">
-        <f>IFERROR(AVERAGE(AI18:AI21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ23" s="37" t="str">
-        <f>IFERROR(AVERAGE(AJ18:AJ21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK23" s="37" t="str">
-        <f>IFERROR(AVERAGE(AK18:AK21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL23" s="37" t="str">
-        <f>IFERROR(AVERAGE(AL18:AL21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM23" s="37"/>
-      <c r="BR23" s="46"/>
-      <c r="BS23" s="46"/>
-      <c r="BT23" s="46"/>
-      <c r="BU23" s="46"/>
-      <c r="BV23" s="49"/>
-      <c r="BW23" s="49"/>
-      <c r="BX23" s="49"/>
-      <c r="BZ23" s="46"/>
-      <c r="CA23" s="46"/>
-      <c r="CB23" s="46"/>
+      <c r="B23" s="34"/>
+      <c r="D23" s="10" t="str" cm="1">
+        <f t="array" ref="D23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23, "SP_COMPANY_NAME"))</f>
+        <v/>
+      </c>
+      <c r="G23" s="21" t="str" cm="1">
+        <f t="array" ref="G23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I23&amp;",NA=--"))</f>
+        <v/>
+      </c>
+      <c r="H23" s="13" t="str" cm="1">
+        <f t="array" ref="H23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="I23" s="40" t="str" cm="1">
+        <f t="array" ref="I23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="J23" s="15" t="str" cm="1">
+        <f t="array" ref="J23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="K23" s="15" t="str" cm="1">
+        <f t="array" ref="K23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="L23" s="16" t="str">
+        <f t="shared" ref="L23:L24" si="63">IFERROR(IF(OR($K23/AO23&gt;L$4,$K23/AO23&lt;L$3),"nmf ",$K23/AO23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M23" s="16" t="str">
+        <f t="shared" ref="M23:M24" si="64">IFERROR(IF(OR($K23/AP23&gt;M$4,$K23/AP23&lt;M$3),"nmf ",$K23/AP23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N23" s="16" t="str">
+        <f t="shared" ref="N23:N24" si="65">IFERROR(IF(OR($K23/AQ23&gt;N$4,$K23/AQ23&lt;N$3),"nmf ",$K23/AQ23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O23" s="16" t="str">
+        <f t="shared" ref="O23:O24" si="66">IFERROR(IF(OR($K23/AR23&gt;O$4,$K23/AR23&lt;O$3),"nmf ",$K23/AR23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P23" s="16" t="str">
+        <f t="shared" ref="P23:P24" si="67">IFERROR(IF(OR($K23/AT23&gt;P$4,$K23/AT23&lt;P$3),"nmf ",$K23/AT23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q23" s="16" t="str">
+        <f t="shared" ref="Q23:Q24" si="68">IFERROR(IF(OR($K23/AU23&gt;Q$4,$K23/AU23&lt;Q$3),"nmf ",$K23/AU23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R23" s="16" t="str">
+        <f t="shared" ref="R23:R24" si="69">IFERROR(IF(OR($K23/AV23&gt;R$4,$K23/AV23&lt;R$3),"nmf ",$K23/AV23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S23" s="16" t="str">
+        <f t="shared" ref="S23:S24" si="70">IFERROR(IF(OR($K23/AW23&gt;S$4,$K23/AW23&lt;S$3),"nmf ",$K23/AW23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T23" s="33" t="str">
+        <f t="shared" ref="T23:T24" si="71">IFERROR((AQ23/AP23)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U23" s="33" t="str">
+        <f t="shared" ref="U23:U24" si="72">IFERROR((AR23/AQ23)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V23" s="16" t="str">
+        <f>IFERROR(IF(OR($H23/AY23&gt;#REF!,$H23/AY23&lt;#REF!),"nmf ",$H23/AY23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W23" s="16" t="str">
+        <f>IFERROR(IF(OR($H23/AZ23&gt;#REF!,$H23/AZ23&lt;#REF!),"nmf ",$H23/AZ23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X23" s="16" t="str">
+        <f>IFERROR(IF(OR($H23/BA23&gt;#REF!,$H23/BA23&lt;#REF!),"nmf ",$H23/BA23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y23" s="16" t="str">
+        <f>IFERROR(IF(OR($H23/BC23&gt;#REF!,$H23/BC23&lt;#REF!),"nmf ",$H23/BC23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z23" s="16" t="str">
+        <f>IFERROR(IF(OR($H23/BD23&gt;#REF!,$H23/BD23&lt;#REF!),"nmf ",$H23/BD23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA23" s="16" t="str">
+        <f>IFERROR(IF(OR($H23/BE23&gt;#REF!,$H23/BE23&lt;#REF!),"nmf ",$H23/BE23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB23" s="33" t="str">
+        <f t="shared" ref="AB23:AB24" si="73">IFERROR((AS23/AR23)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC23" s="33" t="str">
+        <f t="shared" ref="AC23:AC24" si="74">IFERROR((AT23/AS23)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD23" s="33" t="str">
+        <f t="shared" ref="AD23:AD24" si="75">IFERROR((AU23/AT23)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE23" s="33" t="str">
+        <f t="shared" ref="AE23:AE24" si="76">IFERROR((AV23/AU23)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF23" s="33" t="str">
+        <f t="shared" ref="AF23:AF24" si="77">IFERROR((AW23/AV23)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG23" s="33" t="str">
+        <f t="shared" ref="AG23:AG24" si="78">IFERROR((BM23/AW23)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH23" s="33" t="str">
+        <f t="shared" ref="AH23:AH24" si="79">IFERROR((BN23/BM23)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI23" s="33" t="str">
+        <f t="shared" ref="AI23:AI24" si="80">IFERROR((BO23/BN23)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ23" s="33" t="str">
+        <f t="shared" ref="AJ23:AJ24" si="81">IFERROR((BP23/BO23)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK23" s="33" t="str">
+        <f t="shared" ref="AK23:AK24" si="82">IFERROR((BQ23/BP23)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL23" s="33" t="str">
+        <f t="shared" ref="AL23:AL24" si="83">IFERROR((BR23/BQ23)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM23" s="72"/>
+      <c r="AO23" s="20" t="str" cm="1">
+        <f t="array" ref="AO23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AP23" s="20" t="str" cm="1">
+        <f t="array" ref="AP23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AQ23" s="20" t="str" cm="1">
+        <f t="array" ref="AQ23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AR23" s="20" t="str" cm="1">
+        <f t="array" ref="AR23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AT23" s="20" t="str" cm="1">
+        <f t="array" ref="AT23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AU23" s="20" t="str" cm="1">
+        <f t="array" ref="AU23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AV23" s="20" t="str" cm="1">
+        <f t="array" ref="AV23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AW23" s="20" t="str" cm="1">
+        <f t="array" ref="AW23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AY23" s="13" t="str" cm="1">
+        <f t="array" ref="AY23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AZ23" s="13" t="str" cm="1">
+        <f t="array" ref="AZ23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BA23" s="13" t="str" cm="1">
+        <f t="array" ref="BA23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BC23" s="13" t="str" cm="1">
+        <f t="array" ref="BC23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BD23" s="13" t="str" cm="1">
+        <f t="array" ref="BD23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BE23" s="13" t="str" cm="1">
+        <f t="array" ref="BE23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG23" s="66" t="str" cm="1">
+        <f t="array" ref="BG23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BH23" s="19" t="str" cm="1">
+        <f t="array" ref="BH23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BI23" s="19" t="str" cm="1">
+        <f t="array" ref="BI23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ23" s="19" t="str" cm="1">
+        <f t="array" ref="BJ23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BK23" s="37" t="e">
+        <f t="shared" ref="BK23:BK24" si="84">+BI23-BJ23</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL23" s="19" t="str" cm="1">
+        <f t="array" ref="BL23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BN23" s="20" t="str">
+        <f t="shared" ref="BN23:BN24" si="85">IFERROR($AP23*$BR23,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BO23" s="20" t="str">
+        <f t="shared" ref="BO23:BO24" si="86">IFERROR($AQ23*BS23,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BP23" s="20" t="str">
+        <f t="shared" ref="BP23:BP24" si="87">IFERROR($AR23*$BT23,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BR23" s="44" t="str">
+        <f>IF($B23="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BS23" s="44" t="str">
+        <f>IF($B23="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BT23" s="44" t="str">
+        <f>IF($B23="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BU23" s="45"/>
+      <c r="BV23" s="47" t="str" cm="1">
+        <f t="array" ref="BV23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BW23" s="47" t="str" cm="1">
+        <f t="array" ref="BW23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BX23" s="47" t="str" cm="1">
+        <f t="array" ref="BX23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BZ23" s="62" t="str">
+        <f t="shared" ref="BZ23:BZ24" si="88">IFERROR(IF(CD23/AP23&lt;0,"nmf ",CD23/AP23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA23" s="62" t="str">
+        <f t="shared" ref="CA23:CA24" si="89">IFERROR(IF(CE23/AQ23&lt;0,"nmf ",CE23/AQ23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB23" s="62" t="str">
+        <f t="shared" ref="CB23:CB24" si="90">IFERROR(IF(CF23/AR23&lt;0,"nmf ",CF23/AR23),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD23" s="20" t="str">
+        <f t="shared" ref="CD23:CD24" si="91">IFERROR(BR23*AP23,"--")</f>
+        <v>--</v>
+      </c>
+      <c r="CE23" s="20" t="str">
+        <f t="shared" ref="CE23:CE24" si="92">IFERROR(BS23*AQ23,"--")</f>
+        <v>--</v>
+      </c>
+      <c r="CF23" s="20" t="str">
+        <f t="shared" ref="CF23:CF24" si="93">IFERROR(BT23*AR23,"--")</f>
+        <v>--</v>
+      </c>
     </row>
-    <row r="24" spans="2:84" s="10" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="9"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="55"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="54"/>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="54"/>
-      <c r="R24" s="54"/>
-      <c r="S24" s="54"/>
-      <c r="T24" s="54"/>
-      <c r="U24" s="54"/>
-      <c r="V24" s="54"/>
-      <c r="W24" s="54"/>
-      <c r="X24" s="54"/>
-      <c r="Y24" s="54"/>
-      <c r="Z24" s="54"/>
-      <c r="AA24" s="54"/>
-      <c r="AB24" s="54"/>
-      <c r="AC24" s="54"/>
-      <c r="AD24" s="54"/>
-      <c r="AE24" s="54"/>
-      <c r="AF24" s="54"/>
-      <c r="AG24" s="54"/>
-      <c r="AH24" s="54"/>
-      <c r="AI24" s="54"/>
-      <c r="AJ24" s="54"/>
-      <c r="AK24" s="54"/>
-      <c r="AL24" s="54"/>
-      <c r="AM24" s="54"/>
-      <c r="BR24" s="46"/>
-      <c r="BS24" s="46"/>
-      <c r="BT24" s="46"/>
-      <c r="BU24" s="46"/>
-      <c r="BV24" s="49"/>
-      <c r="BW24" s="49"/>
-      <c r="BX24" s="49"/>
-      <c r="BZ24" s="46"/>
-      <c r="CA24" s="46"/>
-      <c r="CB24" s="46"/>
+    <row r="24" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="34"/>
+      <c r="D24" s="10" t="str" cm="1">
+        <f t="array" ref="D24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24, "SP_COMPANY_NAME"))</f>
+        <v/>
+      </c>
+      <c r="G24" s="21" t="str" cm="1">
+        <f t="array" ref="G24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I24&amp;",NA=--"))</f>
+        <v/>
+      </c>
+      <c r="H24" s="13" t="str" cm="1">
+        <f t="array" ref="H24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="I24" s="40" t="str" cm="1">
+        <f t="array" ref="I24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="J24" s="15" t="str" cm="1">
+        <f t="array" ref="J24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="K24" s="15" t="str" cm="1">
+        <f t="array" ref="K24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="L24" s="16" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M24" s="16" t="str">
+        <f t="shared" si="64"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N24" s="16" t="str">
+        <f t="shared" si="65"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O24" s="16" t="str">
+        <f t="shared" si="66"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P24" s="16" t="str">
+        <f t="shared" si="67"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q24" s="16" t="str">
+        <f t="shared" si="68"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R24" s="16" t="str">
+        <f t="shared" si="69"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S24" s="16" t="str">
+        <f t="shared" si="70"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T24" s="33" t="str">
+        <f t="shared" si="71"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U24" s="33" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V24" s="16" t="str">
+        <f>IFERROR(IF(OR($H24/AY24&gt;#REF!,$H24/AY24&lt;#REF!),"nmf ",$H24/AY24),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W24" s="16" t="str">
+        <f>IFERROR(IF(OR($H24/AZ24&gt;#REF!,$H24/AZ24&lt;#REF!),"nmf ",$H24/AZ24),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X24" s="16" t="str">
+        <f>IFERROR(IF(OR($H24/BA24&gt;#REF!,$H24/BA24&lt;#REF!),"nmf ",$H24/BA24),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y24" s="16" t="str">
+        <f>IFERROR(IF(OR($H24/BC24&gt;#REF!,$H24/BC24&lt;#REF!),"nmf ",$H24/BC24),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z24" s="16" t="str">
+        <f>IFERROR(IF(OR($H24/BD24&gt;#REF!,$H24/BD24&lt;#REF!),"nmf ",$H24/BD24),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA24" s="16" t="str">
+        <f>IFERROR(IF(OR($H24/BE24&gt;#REF!,$H24/BE24&lt;#REF!),"nmf ",$H24/BE24),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB24" s="33" t="str">
+        <f t="shared" si="73"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC24" s="33" t="str">
+        <f t="shared" si="74"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD24" s="33" t="str">
+        <f t="shared" si="75"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE24" s="33" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF24" s="33" t="str">
+        <f t="shared" si="77"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG24" s="33" t="str">
+        <f t="shared" si="78"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH24" s="33" t="str">
+        <f t="shared" si="79"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI24" s="33" t="str">
+        <f t="shared" si="80"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ24" s="33" t="str">
+        <f t="shared" si="81"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK24" s="33" t="str">
+        <f t="shared" si="82"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL24" s="33" t="str">
+        <f t="shared" si="83"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM24" s="72"/>
+      <c r="AO24" s="20" t="str" cm="1">
+        <f t="array" ref="AO24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AP24" s="20" t="str" cm="1">
+        <f t="array" ref="AP24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AQ24" s="20" t="str" cm="1">
+        <f t="array" ref="AQ24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AR24" s="20" t="str" cm="1">
+        <f t="array" ref="AR24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AT24" s="20" t="str" cm="1">
+        <f t="array" ref="AT24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AU24" s="20" t="str" cm="1">
+        <f t="array" ref="AU24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AV24" s="20" t="str" cm="1">
+        <f t="array" ref="AV24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AW24" s="20" t="str" cm="1">
+        <f t="array" ref="AW24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AY24" s="13" t="str" cm="1">
+        <f t="array" ref="AY24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AZ24" s="13" t="str" cm="1">
+        <f t="array" ref="AZ24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BA24" s="13" t="str" cm="1">
+        <f t="array" ref="BA24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BC24" s="13" t="str" cm="1">
+        <f t="array" ref="BC24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BD24" s="13" t="str" cm="1">
+        <f t="array" ref="BD24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BE24" s="13" t="str" cm="1">
+        <f t="array" ref="BE24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG24" s="66" t="str" cm="1">
+        <f t="array" ref="BG24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BH24" s="19" t="str" cm="1">
+        <f t="array" ref="BH24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BI24" s="19" t="str" cm="1">
+        <f t="array" ref="BI24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ24" s="19" t="str" cm="1">
+        <f t="array" ref="BJ24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BK24" s="37" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL24" s="19" t="str" cm="1">
+        <f t="array" ref="BL24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BN24" s="20" t="str">
+        <f t="shared" si="85"/>
+        <v>n/a</v>
+      </c>
+      <c r="BO24" s="20" t="str">
+        <f t="shared" si="86"/>
+        <v>n/a</v>
+      </c>
+      <c r="BP24" s="20" t="str">
+        <f t="shared" si="87"/>
+        <v>n/a</v>
+      </c>
+      <c r="BR24" s="44" t="str">
+        <f>IF($B24="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BS24" s="44" t="str">
+        <f>IF($B24="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BT24" s="44" t="str">
+        <f>IF($B24="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BU24" s="45"/>
+      <c r="BV24" s="47" t="str" cm="1">
+        <f t="array" ref="BV24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BW24" s="47" t="str" cm="1">
+        <f t="array" ref="BW24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BX24" s="47" t="str" cm="1">
+        <f t="array" ref="BX24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BZ24" s="62" t="str">
+        <f t="shared" si="88"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA24" s="62" t="str">
+        <f t="shared" si="89"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB24" s="62" t="str">
+        <f t="shared" si="90"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD24" s="20" t="str">
+        <f t="shared" si="91"/>
+        <v>--</v>
+      </c>
+      <c r="CE24" s="20" t="str">
+        <f t="shared" si="92"/>
+        <v>--</v>
+      </c>
+      <c r="CF24" s="20" t="str">
+        <f t="shared" si="93"/>
+        <v>--</v>
+      </c>
     </row>
-    <row r="25" spans="2:84" s="31" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="30"/>
-      <c r="D25" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="56"/>
-      <c r="K25" s="56"/>
-      <c r="L25" s="57" t="str">
-        <f>IFERROR(AVERAGE(L10:L13,L18:L21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="M25" s="57" t="str">
-        <f>IFERROR(AVERAGE(M10:M13,M18:M21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="N25" s="57" t="str">
-        <f>IFERROR(AVERAGE(N10:N13,N18:N21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="O25" s="57" t="str">
-        <f>IFERROR(AVERAGE(O10:O13,O18:O21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="P25" s="57" t="str">
-        <f>IFERROR(AVERAGE(P10:P13,P18:P21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Q25" s="57" t="str">
-        <f>IFERROR(AVERAGE(Q10:Q13,Q18:Q21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="R25" s="57" t="str">
-        <f>IFERROR(AVERAGE(R10:R13,R18:R21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="S25" s="57" t="str">
-        <f>IFERROR(AVERAGE(S10:S13,S18:S21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T25" s="76" t="str">
-        <f>IFERROR(AVERAGE(T10:T13,T18:T21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="U25" s="76" t="str">
-        <f>IFERROR(AVERAGE(U10:U13,U18:U21),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="V25" s="57" t="e">
-        <f>AVERAGE(V10:V13,V18:V21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W25" s="57" t="e">
-        <f>AVERAGE(W10:W13,W18:W21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X25" s="57" t="e">
-        <f>AVERAGE(X10:X13,X18:X21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y25" s="57" t="e">
-        <f>AVERAGE(Y10:Y13,Y18:Y21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z25" s="57" t="e">
-        <f>AVERAGE(Z10:Z13,Z18:Z21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA25" s="57" t="e">
-        <f>AVERAGE(AA10:AA13,AA18:AA21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB25" s="58" t="e">
-        <f>AVERAGE(AB10:AB13,AB18:AB21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC25" s="58" t="e">
-        <f>AVERAGE(AC10:AC13,AC18:AC21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD25" s="58" t="e">
-        <f>AVERAGE(AD10:AD13,AD18:AD21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE25" s="58" t="e">
-        <f>AVERAGE(AE10:AE13,AE18:AE21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF25" s="58" t="e">
-        <f>AVERAGE(AF10:AF13,AF18:AF21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG25" s="58" t="e">
-        <f>AVERAGE(AG10:AG13,AG18:AG21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH25" s="58" t="e">
-        <f>AVERAGE(AH10:AH13,AH18:AH21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI25" s="58" t="e">
-        <f>AVERAGE(AI10:AI13,AI18:AI21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ25" s="58" t="e">
-        <f>AVERAGE(AJ10:AJ13,AJ18:AJ21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK25" s="58" t="e">
-        <f>AVERAGE(AK10:AK13,AK18:AK21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL25" s="58" t="e">
-        <f>AVERAGE(AL10:AL13,AL18:AL21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM25" s="58"/>
-      <c r="BR25" s="47"/>
-      <c r="BS25" s="47"/>
-      <c r="BT25" s="47"/>
-      <c r="BU25" s="47"/>
-      <c r="BV25" s="50"/>
-      <c r="BW25" s="50"/>
-      <c r="BX25" s="50"/>
-      <c r="BZ25" s="47"/>
-      <c r="CA25" s="47"/>
-      <c r="CB25" s="47"/>
+    <row r="25" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="34"/>
+      <c r="D25" s="10" t="str" cm="1">
+        <f t="array" ref="D25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25, "SP_COMPANY_NAME"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="21" t="str" cm="1">
+        <f t="array" ref="G25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I25&amp;",NA=--"))</f>
+        <v/>
+      </c>
+      <c r="H25" s="13" t="str" cm="1">
+        <f t="array" ref="H25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="I25" s="40" t="str" cm="1">
+        <f t="array" ref="I25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="J25" s="15" t="str" cm="1">
+        <f t="array" ref="J25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="K25" s="15" t="str" cm="1">
+        <f t="array" ref="K25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="L25" s="16" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M25" s="16" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N25" s="16" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O25" s="16" t="str">
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P25" s="16" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q25" s="16" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R25" s="16" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S25" s="16" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T25" s="33" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U25" s="33" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V25" s="16" t="str">
+        <f>IFERROR(IF(OR($H25/AY25&gt;#REF!,$H25/AY25&lt;#REF!),"nmf ",$H25/AY25),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W25" s="16" t="str">
+        <f>IFERROR(IF(OR($H25/AZ25&gt;#REF!,$H25/AZ25&lt;#REF!),"nmf ",$H25/AZ25),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X25" s="16" t="str">
+        <f>IFERROR(IF(OR($H25/BA25&gt;#REF!,$H25/BA25&lt;#REF!),"nmf ",$H25/BA25),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y25" s="16" t="str">
+        <f>IFERROR(IF(OR($H25/BC25&gt;#REF!,$H25/BC25&lt;#REF!),"nmf ",$H25/BC25),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z25" s="16" t="str">
+        <f>IFERROR(IF(OR($H25/BD25&gt;#REF!,$H25/BD25&lt;#REF!),"nmf ",$H25/BD25),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA25" s="16" t="str">
+        <f>IFERROR(IF(OR($H25/BE25&gt;#REF!,$H25/BE25&lt;#REF!),"nmf ",$H25/BE25),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB25" s="33" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC25" s="33" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD25" s="33" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE25" s="33" t="str">
+        <f t="shared" si="52"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF25" s="33" t="str">
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG25" s="33" t="str">
+        <f>IFERROR((BM25/AW25)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH25" s="33" t="str">
+        <f t="shared" si="54"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI25" s="33" t="str">
+        <f t="shared" si="55"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ25" s="33" t="str">
+        <f t="shared" si="56"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK25" s="33" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL25" s="33" t="str">
+        <f t="shared" si="58"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM25" s="72"/>
+      <c r="AO25" s="20" t="str" cm="1">
+        <f t="array" ref="AO25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AP25" s="20" t="str" cm="1">
+        <f t="array" ref="AP25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AQ25" s="20" t="str" cm="1">
+        <f t="array" ref="AQ25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AR25" s="20" t="str" cm="1">
+        <f t="array" ref="AR25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AT25" s="20" t="str" cm="1">
+        <f t="array" ref="AT25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AU25" s="20" t="str" cm="1">
+        <f t="array" ref="AU25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AV25" s="20" t="str" cm="1">
+        <f t="array" ref="AV25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AW25" s="20" t="str" cm="1">
+        <f t="array" ref="AW25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AY25" s="13" t="str" cm="1">
+        <f t="array" ref="AY25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AZ25" s="13" t="str" cm="1">
+        <f t="array" ref="AZ25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BA25" s="13" t="str" cm="1">
+        <f t="array" ref="BA25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BC25" s="13" t="str" cm="1">
+        <f t="array" ref="BC25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BD25" s="13" t="str" cm="1">
+        <f t="array" ref="BD25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BE25" s="13" t="str" cm="1">
+        <f t="array" ref="BE25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG25" s="66" t="str" cm="1">
+        <f t="array" ref="BG25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BH25" s="19" t="str" cm="1">
+        <f t="array" ref="BH25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BI25" s="19" t="str" cm="1">
+        <f t="array" ref="BI25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ25" s="19" t="str" cm="1">
+        <f t="array" ref="BJ25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BK25" s="37" t="e">
+        <f>+BI25-BJ25</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL25" s="19" t="str" cm="1">
+        <f t="array" ref="BL25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BN25" s="20" t="str">
+        <f>IFERROR($AP25*$BR25,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BO25" s="20" t="str">
+        <f t="shared" si="60"/>
+        <v>n/a</v>
+      </c>
+      <c r="BP25" s="20" t="str">
+        <f>IFERROR($AR25*$BT25,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BR25" s="44" t="str">
+        <f>IF($B25="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BS25" s="44" t="str">
+        <f>IF($B25="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BT25" s="44" t="str">
+        <f>IF($B25="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BU25" s="45"/>
+      <c r="BV25" s="47" t="str" cm="1">
+        <f t="array" ref="BV25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BW25" s="47" t="str" cm="1">
+        <f t="array" ref="BW25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BX25" s="47" t="str" cm="1">
+        <f t="array" ref="BX25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BZ25" s="62" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA25" s="62" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB25" s="62" t="str">
+        <f t="shared" si="61"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD25" s="20" t="str">
+        <f t="shared" si="62"/>
+        <v>--</v>
+      </c>
+      <c r="CE25" s="20" t="str">
+        <f t="shared" si="62"/>
+        <v>--</v>
+      </c>
+      <c r="CF25" s="20" t="str">
+        <f t="shared" si="62"/>
+        <v>--</v>
+      </c>
     </row>
-    <row r="26" spans="2:84" s="31" customFormat="1" ht="18" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="30"/>
-      <c r="D26" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="51"/>
-      <c r="L26" s="52">
-        <f>+IFERROR((SUM(L18:L21,L10:L13)-MAX(L10:L13,L18:L21)-MIN(L10:L13,L18:L21))/(COUNT(L18:L21,L10:L13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="M26" s="52">
-        <f>+IFERROR((SUM(M18:M21,M10:M13)-MAX(M10:M13,M18:M21)-MIN(M10:M13,M18:M21))/(COUNT(M18:M21,M10:M13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="N26" s="52">
-        <f>+IFERROR((SUM(N18:N21,N10:N13)-MAX(N10:N13,N18:N21)-MIN(N10:N13,N18:N21))/(COUNT(N18:N21,N10:N13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="O26" s="52">
-        <f>+IFERROR((SUM(O18:O21,O10:O13)-MAX(O10:O13,O18:O21)-MIN(O10:O13,O18:O21))/(COUNT(O18:O21,O10:O13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="P26" s="52">
-        <f>+IFERROR((SUM(P18:P21,P10:P13)-MAX(P10:P13,P18:P21)-MIN(P10:P13,P18:P21))/(COUNT(P18:P21,P10:P13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="52">
-        <f>+IFERROR((SUM(Q18:Q21,Q10:Q13)-MAX(Q10:Q13,Q18:Q21)-MIN(Q10:Q13,Q18:Q21))/(COUNT(Q18:Q21,Q10:Q13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="R26" s="52">
-        <f>+IFERROR((SUM(R18:R21,R10:R13)-MAX(R10:R13,R18:R21)-MIN(R10:R13,R18:R21))/(COUNT(R18:R21,R10:R13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="S26" s="52">
-        <f>+IFERROR((SUM(S18:S21,S10:S13)-MAX(S10:S13,S18:S21)-MIN(S10:S13,S18:S21))/(COUNT(S18:S21,S10:S13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="T26" s="77">
-        <f>+IFERROR((SUM(T18:T21,T10:T13)-MAX(T10:T13,T18:T21)-MIN(T10:T13,T18:T21))/(COUNT(T18:T21,T10:T13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="U26" s="77">
-        <f>+IFERROR((SUM(U18:U21,U10:U13)-MAX(U10:U13,U18:U21)-MIN(U10:U13,U18:U21))/(COUNT(U18:U21,U10:U13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="V26" s="52">
-        <f>+IFERROR((SUM(V18:V21,V10:V13)-MAX(V10:V13,V18:V21)-MIN(V10:V13,V18:V21))/(COUNT(V18:V21,V10:V13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="W26" s="52">
-        <f>+IFERROR((SUM(W18:W21,W10:W13)-MAX(W10:W13,W18:W21)-MIN(W10:W13,W18:W21))/(COUNT(W18:W21,W10:W13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="X26" s="52">
-        <f>+IFERROR((SUM(X18:X21,X10:X13)-MAX(X10:X13,X18:X21)-MIN(X10:X13,X18:X21))/(COUNT(X18:X21,X10:X13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="52">
-        <f>+IFERROR((SUM(Y18:Y21,Y10:Y13)-MAX(Y10:Y13,Y18:Y21)-MIN(Y10:Y13,Y18:Y21))/(COUNT(Y18:Y21,Y10:Y13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="Z26" s="52">
-        <f>+IFERROR((SUM(Z18:Z21,Z10:Z13)-MAX(Z10:Z13,Z18:Z21)-MIN(Z10:Z13,Z18:Z21))/(COUNT(Z18:Z21,Z10:Z13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="AA26" s="52">
-        <f>+IFERROR((SUM(AA18:AA21,AA10:AA13)-MAX(AA10:AA13,AA18:AA21)-MIN(AA10:AA13,AA18:AA21))/(COUNT(AA18:AA21,AA10:AA13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="AB26" s="53">
-        <f>+IFERROR((SUM(AB18:AB21,AB10:AB13)-MAX(AB10:AB13,AB18:AB21)-MIN(AB10:AB13,AB18:AB21))/(COUNT(AB18:AB21,AB10:AB13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="AC26" s="53">
-        <f>+IFERROR((SUM(AC18:AC21,AC10:AC13)-MAX(AC10:AC13,AC18:AC21)-MIN(AC10:AC13,AC18:AC21))/(COUNT(AC18:AC21,AC10:AC13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="AD26" s="53">
-        <f>+IFERROR((SUM(AD18:AD21,AD10:AD13)-MAX(AD10:AD13,AD18:AD21)-MIN(AD10:AD13,AD18:AD21))/(COUNT(AD18:AD21,AD10:AD13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="AE26" s="53">
-        <f>+IFERROR((SUM(AE18:AE21,AE10:AE13)-MAX(AE10:AE13,AE18:AE21)-MIN(AE10:AE13,AE18:AE21))/(COUNT(AE18:AE21,AE10:AE13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="AF26" s="53">
-        <f>+IFERROR((SUM(AF18:AF21,AF10:AF13)-MAX(AF10:AF13,AF18:AF21)-MIN(AF10:AF13,AF18:AF21))/(COUNT(AF18:AF21,AF10:AF13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="AG26" s="53">
-        <f>+IFERROR((SUM(AG18:AG21,AG10:AG13)-MAX(AG10:AG13,AG18:AG21)-MIN(AG10:AG13,AG18:AG21))/(COUNT(AG18:AG21,AG10:AG13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="AH26" s="53">
-        <f>+IFERROR((SUM(AH18:AH21,AH10:AH13)-MAX(AH10:AH13,AH18:AH21)-MIN(AH10:AH13,AH18:AH21))/(COUNT(AH18:AH21,AH10:AH13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="AI26" s="53">
-        <f>+IFERROR((SUM(AI18:AI21,AI10:AI13)-MAX(AI10:AI13,AI18:AI21)-MIN(AI10:AI13,AI18:AI21))/(COUNT(AI18:AI21,AI10:AI13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="53">
-        <f>+IFERROR((SUM(AJ18:AJ21,AJ10:AJ13)-MAX(AJ10:AJ13,AJ18:AJ21)-MIN(AJ10:AJ13,AJ18:AJ21))/(COUNT(AJ18:AJ21,AJ10:AJ13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="AK26" s="53">
-        <f>+IFERROR((SUM(AK18:AK21,AK10:AK13)-MAX(AK10:AK13,AK18:AK21)-MIN(AK10:AK13,AK18:AK21))/(COUNT(AK18:AK21,AK10:AK13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="AL26" s="53">
-        <f>+IFERROR((SUM(AL18:AL21,AL10:AL13)-MAX(AL10:AL13,AL18:AL21)-MIN(AL10:AL13,AL18:AL21))/(COUNT(AL18:AL21,AL10:AL13)-2),"n/a ")</f>
-        <v>0</v>
-      </c>
-      <c r="AM26" s="53"/>
-      <c r="BR26" s="47"/>
-      <c r="BS26" s="47"/>
-      <c r="BT26" s="47"/>
-      <c r="BU26" s="47"/>
-      <c r="BV26" s="50"/>
-      <c r="BW26" s="50"/>
-      <c r="BX26" s="50"/>
-      <c r="BZ26" s="47"/>
-      <c r="CA26" s="47"/>
-      <c r="CB26" s="47"/>
+    <row r="26" spans="2:84" s="10" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="11"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="17"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="16"/>
+      <c r="X26" s="16"/>
+      <c r="Y26" s="16"/>
+      <c r="Z26" s="16"/>
+      <c r="AA26" s="16"/>
+      <c r="AB26" s="17"/>
+      <c r="AC26" s="17"/>
+      <c r="AD26" s="17"/>
+      <c r="AE26" s="17"/>
+      <c r="AF26" s="17"/>
+      <c r="AG26" s="17"/>
+      <c r="AH26" s="17"/>
+      <c r="AI26" s="17"/>
+      <c r="AJ26" s="17"/>
+      <c r="AK26" s="17"/>
+      <c r="AL26" s="17"/>
+      <c r="AM26" s="17"/>
+      <c r="AO26" s="19"/>
+      <c r="AP26" s="13"/>
+      <c r="AQ26" s="13"/>
+      <c r="AR26" s="13"/>
+      <c r="AU26" s="20"/>
+      <c r="AV26" s="20"/>
+      <c r="AW26" s="20"/>
+      <c r="AY26" s="13"/>
+      <c r="AZ26" s="13"/>
+      <c r="BA26" s="13"/>
+      <c r="BG26" s="19"/>
+      <c r="BH26" s="19"/>
+      <c r="BI26" s="19"/>
+      <c r="BJ26" s="19"/>
+      <c r="BK26" s="19"/>
+      <c r="BL26" s="19"/>
+      <c r="BR26" s="45"/>
+      <c r="BS26" s="45"/>
+      <c r="BT26" s="45"/>
+      <c r="BU26" s="45"/>
+      <c r="BV26" s="48"/>
+      <c r="BW26" s="48"/>
+      <c r="BX26" s="48"/>
+      <c r="BZ26" s="45"/>
+      <c r="CA26" s="45"/>
+      <c r="CB26" s="45"/>
     </row>
-    <row r="27" spans="2:84" s="31" customFormat="1" ht="16.350000000000001" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="30"/>
-      <c r="D27" s="59" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="59"/>
-      <c r="J27" s="59"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="60" t="str">
-        <f>IFERROR(MEDIAN(L18:L21,L10:L13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="M27" s="60" t="str">
-        <f>IFERROR(MEDIAN(M18:M21,M10:M13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="N27" s="60" t="str">
-        <f>IFERROR(MEDIAN(N18:N21,N10:N13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="O27" s="60" t="str">
-        <f>IFERROR(MEDIAN(O18:O21,O10:O13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="P27" s="60" t="str">
-        <f>IFERROR(MEDIAN(P18:P21,P10:P13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Q27" s="60" t="str">
-        <f>IFERROR(MEDIAN(Q18:Q21,Q10:Q13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="R27" s="60" t="str">
-        <f>IFERROR(MEDIAN(R18:R21,R10:R13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="S27" s="60" t="str">
-        <f>IFERROR(MEDIAN(S18:S21,S10:S13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T27" s="78" t="str">
-        <f>IFERROR(MEDIAN(T18:T21,T10:T13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="U27" s="78" t="str">
-        <f>IFERROR(MEDIAN(U18:U21,U10:U13),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="V27" s="60" t="e">
-        <f>+MEDIAN(V18:V21,V10:V13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W27" s="60" t="e">
-        <f>+MEDIAN(W18:W21,W10:W13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X27" s="60" t="e">
-        <f>+MEDIAN(X18:X21,X10:X13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y27" s="60" t="e">
-        <f>+MEDIAN(Y18:Y21,Y10:Y13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z27" s="60" t="e">
-        <f>+MEDIAN(Z18:Z21,Z10:Z13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA27" s="60" t="e">
-        <f>+MEDIAN(AA18:AA21,AA10:AA13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB27" s="61" t="e">
-        <f>+MEDIAN(AB18:AB21,AB10:AB13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC27" s="61" t="e">
-        <f>+MEDIAN(AC18:AC21,AC10:AC13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD27" s="61" t="e">
-        <f>+MEDIAN(AD18:AD21,AD10:AD13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE27" s="61" t="e">
-        <f>+MEDIAN(AE18:AE21,AE10:AE13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF27" s="61" t="e">
-        <f>+MEDIAN(AF18:AF21,AF10:AF13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG27" s="61" t="e">
-        <f>+MEDIAN(AG18:AG21,AG10:AG13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH27" s="61" t="e">
-        <f>+MEDIAN(AH18:AH21,AH10:AH13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI27" s="61" t="e">
-        <f>+MEDIAN(AI18:AI21,AI10:AI13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ27" s="61" t="e">
-        <f>+MEDIAN(AJ18:AJ21,AJ10:AJ13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AK27" s="61" t="e">
-        <f>+MEDIAN(AK18:AK21,AK10:AK13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AL27" s="61" t="e">
-        <f>+MEDIAN(AL18:AL21,AL10:AL13)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AM27" s="61"/>
-      <c r="BR27" s="47"/>
-      <c r="BS27" s="47"/>
-      <c r="BT27" s="47"/>
-      <c r="BU27" s="47"/>
-      <c r="BV27" s="50"/>
-      <c r="BW27" s="50"/>
-      <c r="BX27" s="50"/>
-      <c r="BZ27" s="47"/>
-      <c r="CA27" s="47"/>
-      <c r="CB27" s="47"/>
+    <row r="27" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="9"/>
+      <c r="D27" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="35" t="str">
+        <f>IFERROR(AVERAGE(L20:L25),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M27" s="35" t="str">
+        <f>IFERROR(AVERAGE(M20:M25),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N27" s="26" t="str">
+        <f>IFERROR(AVERAGE(N20:N25),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O27" s="26" t="str">
+        <f>IFERROR(AVERAGE(O20:O25),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P27" s="26" t="str">
+        <f t="shared" ref="P27" si="94">IFERROR(AVERAGE(P20:P25),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q27" s="26" t="str">
+        <f t="shared" ref="Q27:AL27" si="95">IFERROR(AVERAGE(Q20:Q25),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R27" s="26" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S27" s="26" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T27" s="36" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U27" s="36" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V27" s="26" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W27" s="26" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X27" s="26" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y27" s="26" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z27" s="26" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA27" s="26" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB27" s="36" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC27" s="36" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD27" s="36" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE27" s="36" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF27" s="36" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG27" s="36" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH27" s="36" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI27" s="36" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ27" s="36" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK27" s="36" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL27" s="36" t="str">
+        <f t="shared" si="95"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM27" s="36"/>
+      <c r="BR27" s="45"/>
+      <c r="BS27" s="45"/>
+      <c r="BT27" s="45"/>
+      <c r="BU27" s="45"/>
+      <c r="BV27" s="48"/>
+      <c r="BW27" s="48"/>
+      <c r="BX27" s="48"/>
+      <c r="BZ27" s="45"/>
+      <c r="CA27" s="45"/>
+      <c r="CB27" s="45"/>
     </row>
     <row r="28" spans="2:84" s="10" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="9"/>
+      <c r="B28" s="11"/>
+      <c r="I28" s="42"/>
       <c r="J28" s="28"/>
       <c r="K28" s="28"/>
       <c r="L28" s="28"/>
-      <c r="BR28" s="46"/>
-      <c r="BS28" s="46"/>
-      <c r="BT28" s="46"/>
-      <c r="BU28" s="46"/>
-      <c r="BV28" s="49"/>
-      <c r="BW28" s="49"/>
-      <c r="BX28" s="49"/>
-      <c r="BZ28" s="46"/>
-      <c r="CA28" s="46"/>
-      <c r="CB28" s="46"/>
+      <c r="AU28" s="27"/>
+      <c r="AV28" s="27"/>
+      <c r="AW28" s="27"/>
+      <c r="BG28" s="67"/>
+      <c r="BR28" s="45"/>
+      <c r="BS28" s="45"/>
+      <c r="BT28" s="45"/>
+      <c r="BU28" s="45"/>
+      <c r="BV28" s="48"/>
+      <c r="BW28" s="48"/>
+      <c r="BX28" s="48"/>
+      <c r="BZ28" s="63"/>
+      <c r="CA28" s="63"/>
+      <c r="CB28" s="63"/>
+    </row>
+    <row r="29" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="11"/>
+      <c r="D29" s="71" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="17"/>
+      <c r="U29" s="17"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="18"/>
+      <c r="X29" s="18"/>
+      <c r="Y29" s="18"/>
+      <c r="Z29" s="18"/>
+      <c r="AA29" s="18"/>
+      <c r="AB29" s="17"/>
+      <c r="AC29" s="17"/>
+      <c r="AD29" s="17"/>
+      <c r="AE29" s="17"/>
+      <c r="AF29" s="17"/>
+      <c r="AG29" s="17"/>
+      <c r="AH29" s="17"/>
+      <c r="AI29" s="17"/>
+      <c r="AJ29" s="17"/>
+      <c r="AK29" s="17"/>
+      <c r="AL29" s="17"/>
+      <c r="AM29" s="17"/>
+      <c r="AO29" s="13"/>
+      <c r="AP29" s="13"/>
+      <c r="AQ29" s="13"/>
+      <c r="AR29" s="13"/>
+      <c r="AU29" s="20"/>
+      <c r="AV29" s="20"/>
+      <c r="AW29" s="20"/>
+      <c r="AY29" s="13"/>
+      <c r="AZ29" s="13"/>
+      <c r="BA29" s="13"/>
+      <c r="BG29" s="66"/>
+      <c r="BH29" s="19"/>
+      <c r="BI29" s="19"/>
+      <c r="BJ29" s="19"/>
+      <c r="BK29" s="19"/>
+      <c r="BL29" s="19"/>
+      <c r="BR29" s="45"/>
+      <c r="BS29" s="45"/>
+      <c r="BT29" s="45"/>
+      <c r="BU29" s="45"/>
+      <c r="BV29" s="48"/>
+      <c r="BW29" s="48"/>
+      <c r="BX29" s="48"/>
+      <c r="BZ29" s="63"/>
+      <c r="CA29" s="63"/>
+      <c r="CB29" s="63"/>
+    </row>
+    <row r="30" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="34"/>
+      <c r="D30" s="10" t="str" cm="1">
+        <f t="array" ref="D30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30, "SP_COMPANY_NAME"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="21" t="str" cm="1">
+        <f t="array" ref="G30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I30&amp;",NA=--"))</f>
+        <v/>
+      </c>
+      <c r="H30" s="13" t="str" cm="1">
+        <f t="array" ref="H30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="I30" s="40" t="str" cm="1">
+        <f t="array" ref="I30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="J30" s="15" t="str" cm="1">
+        <f t="array" ref="J30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="K30" s="15" t="str" cm="1">
+        <f t="array" ref="K30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="L30" s="16" t="str">
+        <f t="shared" ref="L30:L35" si="96">IFERROR(IF(OR($K30/AO30&gt;L$4,$K30/AO30&lt;L$3),"nmf ",$K30/AO30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M30" s="16" t="str">
+        <f t="shared" ref="M30:M35" si="97">IFERROR(IF(OR($K30/AP30&gt;M$4,$K30/AP30&lt;M$3),"nmf ",$K30/AP30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N30" s="16" t="str">
+        <f t="shared" ref="N30:N35" si="98">IFERROR(IF(OR($K30/AQ30&gt;N$4,$K30/AQ30&lt;N$3),"nmf ",$K30/AQ30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O30" s="16" t="str">
+        <f t="shared" ref="O30:O35" si="99">IFERROR(IF(OR($K30/AR30&gt;O$4,$K30/AR30&lt;O$3),"nmf ",$K30/AR30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P30" s="16" t="str">
+        <f t="shared" ref="P30:P35" si="100">IFERROR(IF(OR($K30/AT30&gt;P$4,$K30/AT30&lt;P$3),"nmf ",$K30/AT30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q30" s="16" t="str">
+        <f t="shared" ref="Q30:Q35" si="101">IFERROR(IF(OR($K30/AU30&gt;Q$4,$K30/AU30&lt;Q$3),"nmf ",$K30/AU30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R30" s="16" t="str">
+        <f t="shared" ref="R30:R35" si="102">IFERROR(IF(OR($K30/AV30&gt;R$4,$K30/AV30&lt;R$3),"nmf ",$K30/AV30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S30" s="16" t="str">
+        <f t="shared" ref="S30:S35" si="103">IFERROR(IF(OR($K30/AW30&gt;S$4,$K30/AW30&lt;S$3),"nmf ",$K30/AW30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T30" s="33" t="str">
+        <f t="shared" ref="T30:T35" si="104">IFERROR((AQ30/AP30)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U30" s="33" t="str">
+        <f t="shared" ref="U30:U35" si="105">IFERROR((AR30/AQ30)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V30" s="16" t="str">
+        <f>IFERROR(IF(OR($H30/AY30&gt;#REF!,$H30/AY30&lt;#REF!),"nmf ",$H30/AY30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W30" s="16" t="str">
+        <f>IFERROR(IF(OR($H30/AZ30&gt;#REF!,$H30/AZ30&lt;#REF!),"nmf ",$H30/AZ30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X30" s="16" t="str">
+        <f>IFERROR(IF(OR($H30/BA30&gt;#REF!,$H30/BA30&lt;#REF!),"nmf ",$H30/BA30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y30" s="16" t="str">
+        <f>IFERROR(IF(OR($H30/BC30&gt;#REF!,$H30/BC30&lt;#REF!),"nmf ",$H30/BC30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z30" s="16" t="str">
+        <f>IFERROR(IF(OR($H30/BD30&gt;#REF!,$H30/BD30&lt;#REF!),"nmf ",$H30/BD30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA30" s="16" t="str">
+        <f>IFERROR(IF(OR($H30/BE30&gt;#REF!,$H30/BE30&lt;#REF!),"nmf ",$H30/BE30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB30" s="33" t="str">
+        <f t="shared" ref="AB30:AB35" si="106">IFERROR((AS30/AR30)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC30" s="33" t="str">
+        <f t="shared" ref="AC30:AC35" si="107">IFERROR((AT30/AS30)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD30" s="33" t="str">
+        <f t="shared" ref="AD30:AD35" si="108">IFERROR((AU30/AT30)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE30" s="33" t="str">
+        <f t="shared" ref="AE30:AE35" si="109">IFERROR((AV30/AU30)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF30" s="33" t="str">
+        <f t="shared" ref="AF30:AF35" si="110">IFERROR((AW30/AV30)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG30" s="33" t="str">
+        <f>IFERROR((BM30/AW30)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH30" s="33" t="str">
+        <f t="shared" ref="AH30:AH35" si="111">IFERROR((BN30/BM30)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI30" s="33" t="str">
+        <f t="shared" ref="AI30:AI35" si="112">IFERROR((BO30/BN30)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ30" s="33" t="str">
+        <f t="shared" ref="AJ30:AJ35" si="113">IFERROR((BP30/BO30)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK30" s="33" t="str">
+        <f t="shared" ref="AK30:AK35" si="114">IFERROR((BQ30/BP30)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL30" s="33" t="str">
+        <f t="shared" ref="AL30:AL35" si="115">IFERROR((BR30/BQ30)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM30" s="72"/>
+      <c r="AO30" s="20" t="str" cm="1">
+        <f t="array" ref="AO30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AP30" s="20" t="str" cm="1">
+        <f t="array" ref="AP30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AQ30" s="20" t="str" cm="1">
+        <f t="array" ref="AQ30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AR30" s="20" t="str" cm="1">
+        <f t="array" ref="AR30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AT30" s="20" t="str" cm="1">
+        <f t="array" ref="AT30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AU30" s="20" t="str" cm="1">
+        <f t="array" ref="AU30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AV30" s="20" t="str" cm="1">
+        <f t="array" ref="AV30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AW30" s="20" t="str" cm="1">
+        <f t="array" ref="AW30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AY30" s="13" t="str" cm="1">
+        <f t="array" ref="AY30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AZ30" s="13" t="str" cm="1">
+        <f t="array" ref="AZ30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BA30" s="13" t="str" cm="1">
+        <f t="array" ref="BA30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BC30" s="13" t="str" cm="1">
+        <f t="array" ref="BC30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BD30" s="13" t="str" cm="1">
+        <f t="array" ref="BD30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BE30" s="13" t="str" cm="1">
+        <f t="array" ref="BE30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG30" s="66" t="str" cm="1">
+        <f t="array" ref="BG30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BH30" s="19" t="str" cm="1">
+        <f t="array" ref="BH30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BI30" s="19" t="str" cm="1">
+        <f t="array" ref="BI30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ30" s="19" t="str" cm="1">
+        <f t="array" ref="BJ30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BK30" s="37" t="e">
+        <f t="shared" ref="BK30:BK34" si="116">+BI30-BJ30</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL30" s="19" t="str" cm="1">
+        <f t="array" ref="BL30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BN30" s="20" t="str">
+        <f>IFERROR($AP30*$BR30,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BO30" s="20" t="str">
+        <f t="shared" ref="BO30:BO35" si="117">IFERROR($AQ30*BS30,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BP30" s="20" t="str">
+        <f>IFERROR($AR30*$BT30,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BR30" s="44" t="str">
+        <f>IF($B30="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BS30" s="44" t="str">
+        <f>IF($B30="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BT30" s="44" t="str">
+        <f>IF($B30="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BU30" s="45"/>
+      <c r="BV30" s="47" t="str" cm="1">
+        <f t="array" ref="BV30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BW30" s="47" t="str" cm="1">
+        <f t="array" ref="BW30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BX30" s="47" t="str" cm="1">
+        <f t="array" ref="BX30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BZ30" s="62" t="str">
+        <f t="shared" ref="BZ30:BZ35" si="118">IFERROR(IF(CD30/AP30&lt;0,"nmf ",CD30/AP30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA30" s="62" t="str">
+        <f t="shared" ref="CA30:CA35" si="119">IFERROR(IF(CE30/AQ30&lt;0,"nmf ",CE30/AQ30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB30" s="62" t="str">
+        <f t="shared" ref="CB30:CB35" si="120">IFERROR(IF(CF30/AR30&lt;0,"nmf ",CF30/AR30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD30" s="20" t="str">
+        <f t="shared" ref="CD30:CD35" si="121">IFERROR(BR30*AP30,"--")</f>
+        <v>--</v>
+      </c>
+      <c r="CE30" s="20" t="str">
+        <f t="shared" ref="CE30:CE35" si="122">IFERROR(BS30*AQ30,"--")</f>
+        <v>--</v>
+      </c>
+      <c r="CF30" s="20" t="str">
+        <f t="shared" ref="CF30:CF35" si="123">IFERROR(BT30*AR30,"--")</f>
+        <v>--</v>
+      </c>
+    </row>
+    <row r="31" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="34"/>
+      <c r="D31" s="10" t="str" cm="1">
+        <f t="array" ref="D31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31, "SP_COMPANY_NAME"))</f>
+        <v/>
+      </c>
+      <c r="G31" s="21" t="str" cm="1">
+        <f t="array" ref="G31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I31&amp;",NA=--"))</f>
+        <v/>
+      </c>
+      <c r="H31" s="13" t="str" cm="1">
+        <f t="array" ref="H31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="I31" s="40" t="str" cm="1">
+        <f t="array" ref="I31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="J31" s="15" t="str" cm="1">
+        <f t="array" ref="J31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="K31" s="15" t="str" cm="1">
+        <f t="array" ref="K31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="L31" s="16" t="str">
+        <f t="shared" si="96"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M31" s="16" t="str">
+        <f t="shared" si="97"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N31" s="16" t="str">
+        <f t="shared" si="98"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O31" s="16" t="str">
+        <f t="shared" si="99"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P31" s="16" t="str">
+        <f t="shared" si="100"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q31" s="16" t="str">
+        <f t="shared" si="101"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R31" s="16" t="str">
+        <f t="shared" si="102"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S31" s="16" t="str">
+        <f t="shared" si="103"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T31" s="33" t="str">
+        <f t="shared" si="104"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U31" s="33" t="str">
+        <f t="shared" si="105"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V31" s="16" t="str">
+        <f>IFERROR(IF(OR($H31/AY31&gt;#REF!,$H31/AY31&lt;#REF!),"nmf ",$H31/AY31),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W31" s="16" t="str">
+        <f>IFERROR(IF(OR($H31/AZ31&gt;#REF!,$H31/AZ31&lt;#REF!),"nmf ",$H31/AZ31),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X31" s="16" t="str">
+        <f>IFERROR(IF(OR($H31/BA31&gt;#REF!,$H31/BA31&lt;#REF!),"nmf ",$H31/BA31),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y31" s="16" t="str">
+        <f>IFERROR(IF(OR($H31/BC31&gt;#REF!,$H31/BC31&lt;#REF!),"nmf ",$H31/BC31),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z31" s="16" t="str">
+        <f>IFERROR(IF(OR($H31/BD31&gt;#REF!,$H31/BD31&lt;#REF!),"nmf ",$H31/BD31),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA31" s="16" t="str">
+        <f>IFERROR(IF(OR($H31/BE31&gt;#REF!,$H31/BE31&lt;#REF!),"nmf ",$H31/BE31),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB31" s="33" t="str">
+        <f t="shared" si="106"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC31" s="33" t="str">
+        <f t="shared" si="107"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD31" s="33" t="str">
+        <f t="shared" si="108"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE31" s="33" t="str">
+        <f t="shared" si="109"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF31" s="33" t="str">
+        <f t="shared" si="110"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG31" s="33" t="str">
+        <f>IFERROR((BM31/AW31)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH31" s="33" t="str">
+        <f t="shared" si="111"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI31" s="33" t="str">
+        <f t="shared" si="112"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ31" s="33" t="str">
+        <f t="shared" si="113"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK31" s="33" t="str">
+        <f t="shared" si="114"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL31" s="33" t="str">
+        <f t="shared" si="115"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM31" s="72"/>
+      <c r="AO31" s="20" t="str" cm="1">
+        <f t="array" ref="AO31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AP31" s="20" t="str" cm="1">
+        <f t="array" ref="AP31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AQ31" s="20" t="str" cm="1">
+        <f t="array" ref="AQ31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AR31" s="20" t="str" cm="1">
+        <f t="array" ref="AR31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AT31" s="20" t="str" cm="1">
+        <f t="array" ref="AT31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AU31" s="20" t="str" cm="1">
+        <f t="array" ref="AU31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AV31" s="20" t="str" cm="1">
+        <f t="array" ref="AV31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AW31" s="20" t="str" cm="1">
+        <f t="array" ref="AW31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AY31" s="13" t="str" cm="1">
+        <f t="array" ref="AY31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AZ31" s="13" t="str" cm="1">
+        <f t="array" ref="AZ31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BA31" s="13" t="str" cm="1">
+        <f t="array" ref="BA31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BC31" s="13" t="str" cm="1">
+        <f t="array" ref="BC31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BD31" s="13" t="str" cm="1">
+        <f t="array" ref="BD31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BE31" s="13" t="str" cm="1">
+        <f t="array" ref="BE31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG31" s="66" t="str" cm="1">
+        <f t="array" ref="BG31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BH31" s="19" t="str" cm="1">
+        <f t="array" ref="BH31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BI31" s="19" t="str" cm="1">
+        <f t="array" ref="BI31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ31" s="19" t="str" cm="1">
+        <f t="array" ref="BJ31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BK31" s="37" t="e">
+        <f t="shared" si="116"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL31" s="19" t="str" cm="1">
+        <f t="array" ref="BL31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BN31" s="20" t="str">
+        <f>IFERROR($AP31*$BR31,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BO31" s="20" t="str">
+        <f t="shared" si="117"/>
+        <v>n/a</v>
+      </c>
+      <c r="BP31" s="20" t="str">
+        <f>IFERROR($AR31*$BT31,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BR31" s="44" t="str">
+        <f>IF($B31="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BS31" s="44" t="str">
+        <f>IF($B31="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BT31" s="44" t="str">
+        <f>IF($B31="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BU31" s="45"/>
+      <c r="BV31" s="47" t="str" cm="1">
+        <f t="array" ref="BV31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BW31" s="47" t="str" cm="1">
+        <f t="array" ref="BW31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BX31" s="47" t="str" cm="1">
+        <f t="array" ref="BX31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BZ31" s="62" t="str">
+        <f t="shared" si="118"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA31" s="62" t="str">
+        <f t="shared" si="119"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB31" s="62" t="str">
+        <f t="shared" si="120"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD31" s="20" t="str">
+        <f t="shared" si="121"/>
+        <v>--</v>
+      </c>
+      <c r="CE31" s="20" t="str">
+        <f t="shared" si="122"/>
+        <v>--</v>
+      </c>
+      <c r="CF31" s="20" t="str">
+        <f t="shared" si="123"/>
+        <v>--</v>
+      </c>
+    </row>
+    <row r="32" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="34"/>
+      <c r="D32" s="10" t="str" cm="1">
+        <f t="array" ref="D32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32, "SP_COMPANY_NAME"))</f>
+        <v/>
+      </c>
+      <c r="G32" s="21" t="str" cm="1">
+        <f t="array" ref="G32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I32&amp;",NA=--"))</f>
+        <v/>
+      </c>
+      <c r="H32" s="13" t="str" cm="1">
+        <f t="array" ref="H32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="I32" s="40" t="str" cm="1">
+        <f t="array" ref="I32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="J32" s="15" t="str" cm="1">
+        <f t="array" ref="J32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="K32" s="15" t="str" cm="1">
+        <f t="array" ref="K32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="L32" s="16" t="str">
+        <f t="shared" si="96"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M32" s="16" t="str">
+        <f t="shared" si="97"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N32" s="16" t="str">
+        <f t="shared" si="98"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O32" s="16" t="str">
+        <f t="shared" si="99"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P32" s="16" t="str">
+        <f t="shared" si="100"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q32" s="16" t="str">
+        <f t="shared" si="101"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R32" s="16" t="str">
+        <f t="shared" si="102"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S32" s="16" t="str">
+        <f t="shared" si="103"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T32" s="33" t="str">
+        <f t="shared" si="104"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U32" s="33" t="str">
+        <f t="shared" si="105"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V32" s="16" t="str">
+        <f>IFERROR(IF(OR($H32/AY32&gt;#REF!,$H32/AY32&lt;#REF!),"nmf ",$H32/AY32),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W32" s="16" t="str">
+        <f>IFERROR(IF(OR($H32/AZ32&gt;#REF!,$H32/AZ32&lt;#REF!),"nmf ",$H32/AZ32),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X32" s="16" t="str">
+        <f>IFERROR(IF(OR($H32/BA32&gt;#REF!,$H32/BA32&lt;#REF!),"nmf ",$H32/BA32),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y32" s="16" t="str">
+        <f>IFERROR(IF(OR($H32/BC32&gt;#REF!,$H32/BC32&lt;#REF!),"nmf ",$H32/BC32),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z32" s="16" t="str">
+        <f>IFERROR(IF(OR($H32/BD32&gt;#REF!,$H32/BD32&lt;#REF!),"nmf ",$H32/BD32),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA32" s="16" t="str">
+        <f>IFERROR(IF(OR($H32/BE32&gt;#REF!,$H32/BE32&lt;#REF!),"nmf ",$H32/BE32),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB32" s="33" t="str">
+        <f t="shared" si="106"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC32" s="33" t="str">
+        <f t="shared" si="107"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD32" s="33" t="str">
+        <f t="shared" si="108"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE32" s="33" t="str">
+        <f t="shared" si="109"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF32" s="33" t="str">
+        <f t="shared" si="110"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG32" s="33" t="str">
+        <f>IFERROR((BM32/AW32)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH32" s="33" t="str">
+        <f t="shared" si="111"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI32" s="33" t="str">
+        <f t="shared" si="112"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ32" s="33" t="str">
+        <f t="shared" si="113"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK32" s="33" t="str">
+        <f t="shared" si="114"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL32" s="33" t="str">
+        <f t="shared" si="115"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM32" s="72"/>
+      <c r="AO32" s="20" t="str" cm="1">
+        <f t="array" ref="AO32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AP32" s="20" t="str" cm="1">
+        <f t="array" ref="AP32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AQ32" s="20" t="str" cm="1">
+        <f t="array" ref="AQ32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AR32" s="20" t="str" cm="1">
+        <f t="array" ref="AR32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AT32" s="20" t="str" cm="1">
+        <f t="array" ref="AT32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AU32" s="20" t="str" cm="1">
+        <f t="array" ref="AU32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AV32" s="20" t="str" cm="1">
+        <f t="array" ref="AV32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AW32" s="20" t="str" cm="1">
+        <f t="array" ref="AW32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AY32" s="13" t="str" cm="1">
+        <f t="array" ref="AY32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AZ32" s="13" t="str" cm="1">
+        <f t="array" ref="AZ32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BA32" s="13" t="str" cm="1">
+        <f t="array" ref="BA32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BC32" s="13" t="str" cm="1">
+        <f t="array" ref="BC32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BD32" s="13" t="str" cm="1">
+        <f t="array" ref="BD32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BE32" s="13" t="str" cm="1">
+        <f t="array" ref="BE32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG32" s="66" t="str" cm="1">
+        <f t="array" ref="BG32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BH32" s="19" t="str" cm="1">
+        <f t="array" ref="BH32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BI32" s="19" t="str" cm="1">
+        <f t="array" ref="BI32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ32" s="19" t="str" cm="1">
+        <f t="array" ref="BJ32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BK32" s="37" t="e">
+        <f t="shared" si="116"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL32" s="19" t="str" cm="1">
+        <f t="array" ref="BL32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BN32" s="20" t="str">
+        <f>IFERROR($AP32*$BR32,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BO32" s="20" t="str">
+        <f t="shared" si="117"/>
+        <v>n/a</v>
+      </c>
+      <c r="BP32" s="20" t="str">
+        <f>IFERROR($AR32*$BT32,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BR32" s="44" t="str">
+        <f>IF($B32="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BS32" s="44" t="str">
+        <f>IF($B32="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BT32" s="44" t="str">
+        <f>IF($B32="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BU32" s="45"/>
+      <c r="BV32" s="47" t="str" cm="1">
+        <f t="array" ref="BV32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BW32" s="47" t="str" cm="1">
+        <f t="array" ref="BW32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BX32" s="47" t="str" cm="1">
+        <f t="array" ref="BX32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BZ32" s="62" t="str">
+        <f t="shared" si="118"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA32" s="62" t="str">
+        <f t="shared" si="119"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB32" s="62" t="str">
+        <f t="shared" si="120"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD32" s="20" t="str">
+        <f t="shared" si="121"/>
+        <v>--</v>
+      </c>
+      <c r="CE32" s="20" t="str">
+        <f t="shared" si="122"/>
+        <v>--</v>
+      </c>
+      <c r="CF32" s="20" t="str">
+        <f t="shared" si="123"/>
+        <v>--</v>
+      </c>
+    </row>
+    <row r="33" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="34"/>
+      <c r="D33" s="10" t="str" cm="1">
+        <f t="array" ref="D33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33, "SP_COMPANY_NAME"))</f>
+        <v/>
+      </c>
+      <c r="G33" s="21" t="str" cm="1">
+        <f t="array" ref="G33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I33&amp;",NA=--"))</f>
+        <v/>
+      </c>
+      <c r="H33" s="13" t="str" cm="1">
+        <f t="array" ref="H33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="I33" s="40" t="str" cm="1">
+        <f t="array" ref="I33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="J33" s="15" t="str" cm="1">
+        <f t="array" ref="J33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="K33" s="15" t="str" cm="1">
+        <f t="array" ref="K33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="L33" s="16" t="str">
+        <f t="shared" si="96"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M33" s="16" t="str">
+        <f t="shared" si="97"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N33" s="16" t="str">
+        <f t="shared" si="98"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O33" s="16" t="str">
+        <f t="shared" si="99"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P33" s="16" t="str">
+        <f t="shared" si="100"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q33" s="16" t="str">
+        <f t="shared" si="101"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R33" s="16" t="str">
+        <f t="shared" si="102"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S33" s="16" t="str">
+        <f t="shared" si="103"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T33" s="33" t="str">
+        <f t="shared" si="104"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U33" s="33" t="str">
+        <f t="shared" si="105"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V33" s="16" t="str">
+        <f>IFERROR(IF(OR($H33/AY33&gt;#REF!,$H33/AY33&lt;#REF!),"nmf ",$H33/AY33),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W33" s="16" t="str">
+        <f>IFERROR(IF(OR($H33/AZ33&gt;#REF!,$H33/AZ33&lt;#REF!),"nmf ",$H33/AZ33),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X33" s="16" t="str">
+        <f>IFERROR(IF(OR($H33/BA33&gt;#REF!,$H33/BA33&lt;#REF!),"nmf ",$H33/BA33),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y33" s="16" t="str">
+        <f>IFERROR(IF(OR($H33/BC33&gt;#REF!,$H33/BC33&lt;#REF!),"nmf ",$H33/BC33),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z33" s="16" t="str">
+        <f>IFERROR(IF(OR($H33/BD33&gt;#REF!,$H33/BD33&lt;#REF!),"nmf ",$H33/BD33),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA33" s="16" t="str">
+        <f>IFERROR(IF(OR($H33/BE33&gt;#REF!,$H33/BE33&lt;#REF!),"nmf ",$H33/BE33),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB33" s="33" t="str">
+        <f t="shared" si="106"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC33" s="33" t="str">
+        <f t="shared" si="107"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD33" s="33" t="str">
+        <f t="shared" si="108"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE33" s="33" t="str">
+        <f t="shared" si="109"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF33" s="33" t="str">
+        <f t="shared" si="110"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG33" s="33" t="str">
+        <f t="shared" ref="AG33:AG34" si="124">IFERROR((BM33/AW33)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH33" s="33" t="str">
+        <f t="shared" si="111"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI33" s="33" t="str">
+        <f t="shared" si="112"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ33" s="33" t="str">
+        <f t="shared" si="113"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK33" s="33" t="str">
+        <f t="shared" si="114"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL33" s="33" t="str">
+        <f t="shared" si="115"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM33" s="72"/>
+      <c r="AO33" s="20" t="str" cm="1">
+        <f t="array" ref="AO33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AP33" s="20" t="str" cm="1">
+        <f t="array" ref="AP33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AQ33" s="20" t="str" cm="1">
+        <f t="array" ref="AQ33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AR33" s="20" t="str" cm="1">
+        <f t="array" ref="AR33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AT33" s="20" t="str" cm="1">
+        <f t="array" ref="AT33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AU33" s="20" t="str" cm="1">
+        <f t="array" ref="AU33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AV33" s="20" t="str" cm="1">
+        <f t="array" ref="AV33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AW33" s="20" t="str" cm="1">
+        <f t="array" ref="AW33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AY33" s="13" t="str" cm="1">
+        <f t="array" ref="AY33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AZ33" s="13" t="str" cm="1">
+        <f t="array" ref="AZ33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BA33" s="13" t="str" cm="1">
+        <f t="array" ref="BA33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BC33" s="13" t="str" cm="1">
+        <f t="array" ref="BC33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BD33" s="13" t="str" cm="1">
+        <f t="array" ref="BD33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BE33" s="13" t="str" cm="1">
+        <f t="array" ref="BE33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG33" s="66" t="str" cm="1">
+        <f t="array" ref="BG33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BH33" s="19" t="str" cm="1">
+        <f t="array" ref="BH33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BI33" s="19" t="str" cm="1">
+        <f t="array" ref="BI33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ33" s="19" t="str" cm="1">
+        <f t="array" ref="BJ33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BK33" s="37" t="e">
+        <f t="shared" si="116"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL33" s="19" t="str" cm="1">
+        <f t="array" ref="BL33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BN33" s="20" t="str">
+        <f t="shared" ref="BN33:BN34" si="125">IFERROR($AP33*$BR33,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BO33" s="20" t="str">
+        <f t="shared" si="117"/>
+        <v>n/a</v>
+      </c>
+      <c r="BP33" s="20" t="str">
+        <f t="shared" ref="BP33:BP34" si="126">IFERROR($AR33*$BT33,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BR33" s="44" t="str">
+        <f>IF($B33="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BS33" s="44" t="str">
+        <f>IF($B33="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BT33" s="44" t="str">
+        <f>IF($B33="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BU33" s="45"/>
+      <c r="BV33" s="47" t="str" cm="1">
+        <f t="array" ref="BV33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BW33" s="47" t="str" cm="1">
+        <f t="array" ref="BW33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BX33" s="47" t="str" cm="1">
+        <f t="array" ref="BX33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BZ33" s="62" t="str">
+        <f t="shared" si="118"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA33" s="62" t="str">
+        <f t="shared" si="119"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB33" s="62" t="str">
+        <f t="shared" si="120"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD33" s="20" t="str">
+        <f t="shared" si="121"/>
+        <v>--</v>
+      </c>
+      <c r="CE33" s="20" t="str">
+        <f t="shared" si="122"/>
+        <v>--</v>
+      </c>
+      <c r="CF33" s="20" t="str">
+        <f t="shared" si="123"/>
+        <v>--</v>
+      </c>
+    </row>
+    <row r="34" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="34"/>
+      <c r="D34" s="10" t="str" cm="1">
+        <f t="array" ref="D34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34, "SP_COMPANY_NAME"))</f>
+        <v/>
+      </c>
+      <c r="G34" s="21" t="str" cm="1">
+        <f t="array" ref="G34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I34&amp;",NA=--"))</f>
+        <v/>
+      </c>
+      <c r="H34" s="13" t="str" cm="1">
+        <f t="array" ref="H34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="I34" s="40" t="str" cm="1">
+        <f t="array" ref="I34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="J34" s="15" t="str" cm="1">
+        <f t="array" ref="J34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="K34" s="15" t="str" cm="1">
+        <f t="array" ref="K34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="L34" s="16" t="str">
+        <f t="shared" si="96"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M34" s="16" t="str">
+        <f t="shared" si="97"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N34" s="16" t="str">
+        <f t="shared" si="98"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O34" s="16" t="str">
+        <f t="shared" si="99"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P34" s="16" t="str">
+        <f t="shared" si="100"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q34" s="16" t="str">
+        <f t="shared" si="101"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R34" s="16" t="str">
+        <f t="shared" si="102"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S34" s="16" t="str">
+        <f t="shared" si="103"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T34" s="33" t="str">
+        <f t="shared" si="104"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U34" s="33" t="str">
+        <f t="shared" si="105"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V34" s="16" t="str">
+        <f>IFERROR(IF(OR($H34/AY34&gt;#REF!,$H34/AY34&lt;#REF!),"nmf ",$H34/AY34),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W34" s="16" t="str">
+        <f>IFERROR(IF(OR($H34/AZ34&gt;#REF!,$H34/AZ34&lt;#REF!),"nmf ",$H34/AZ34),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X34" s="16" t="str">
+        <f>IFERROR(IF(OR($H34/BA34&gt;#REF!,$H34/BA34&lt;#REF!),"nmf ",$H34/BA34),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y34" s="16" t="str">
+        <f>IFERROR(IF(OR($H34/BC34&gt;#REF!,$H34/BC34&lt;#REF!),"nmf ",$H34/BC34),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z34" s="16" t="str">
+        <f>IFERROR(IF(OR($H34/BD34&gt;#REF!,$H34/BD34&lt;#REF!),"nmf ",$H34/BD34),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA34" s="16" t="str">
+        <f>IFERROR(IF(OR($H34/BE34&gt;#REF!,$H34/BE34&lt;#REF!),"nmf ",$H34/BE34),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB34" s="33" t="str">
+        <f t="shared" si="106"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC34" s="33" t="str">
+        <f t="shared" si="107"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD34" s="33" t="str">
+        <f t="shared" si="108"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE34" s="33" t="str">
+        <f t="shared" si="109"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF34" s="33" t="str">
+        <f t="shared" si="110"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG34" s="33" t="str">
+        <f t="shared" si="124"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH34" s="33" t="str">
+        <f t="shared" si="111"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI34" s="33" t="str">
+        <f t="shared" si="112"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ34" s="33" t="str">
+        <f t="shared" si="113"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK34" s="33" t="str">
+        <f t="shared" si="114"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL34" s="33" t="str">
+        <f t="shared" si="115"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM34" s="72"/>
+      <c r="AO34" s="20" t="str" cm="1">
+        <f t="array" ref="AO34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AP34" s="20" t="str" cm="1">
+        <f t="array" ref="AP34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AQ34" s="20" t="str" cm="1">
+        <f t="array" ref="AQ34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AR34" s="20" t="str" cm="1">
+        <f t="array" ref="AR34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AT34" s="20" t="str" cm="1">
+        <f t="array" ref="AT34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AU34" s="20" t="str" cm="1">
+        <f t="array" ref="AU34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AV34" s="20" t="str" cm="1">
+        <f t="array" ref="AV34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AW34" s="20" t="str" cm="1">
+        <f t="array" ref="AW34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AY34" s="13" t="str" cm="1">
+        <f t="array" ref="AY34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AZ34" s="13" t="str" cm="1">
+        <f t="array" ref="AZ34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BA34" s="13" t="str" cm="1">
+        <f t="array" ref="BA34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BC34" s="13" t="str" cm="1">
+        <f t="array" ref="BC34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BD34" s="13" t="str" cm="1">
+        <f t="array" ref="BD34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BE34" s="13" t="str" cm="1">
+        <f t="array" ref="BE34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG34" s="66" t="str" cm="1">
+        <f t="array" ref="BG34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BH34" s="19" t="str" cm="1">
+        <f t="array" ref="BH34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BI34" s="19" t="str" cm="1">
+        <f t="array" ref="BI34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ34" s="19" t="str" cm="1">
+        <f t="array" ref="BJ34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BK34" s="37" t="e">
+        <f t="shared" si="116"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL34" s="19" t="str" cm="1">
+        <f t="array" ref="BL34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BN34" s="20" t="str">
+        <f t="shared" si="125"/>
+        <v>n/a</v>
+      </c>
+      <c r="BO34" s="20" t="str">
+        <f t="shared" si="117"/>
+        <v>n/a</v>
+      </c>
+      <c r="BP34" s="20" t="str">
+        <f t="shared" si="126"/>
+        <v>n/a</v>
+      </c>
+      <c r="BR34" s="44" t="str">
+        <f>IF($B34="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BS34" s="44" t="str">
+        <f>IF($B34="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BT34" s="44" t="str">
+        <f>IF($B34="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BU34" s="45"/>
+      <c r="BV34" s="47" t="str" cm="1">
+        <f t="array" ref="BV34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BW34" s="47" t="str" cm="1">
+        <f t="array" ref="BW34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BX34" s="47" t="str" cm="1">
+        <f t="array" ref="BX34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BZ34" s="62" t="str">
+        <f t="shared" si="118"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA34" s="62" t="str">
+        <f t="shared" si="119"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB34" s="62" t="str">
+        <f t="shared" si="120"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD34" s="20" t="str">
+        <f t="shared" si="121"/>
+        <v>--</v>
+      </c>
+      <c r="CE34" s="20" t="str">
+        <f t="shared" si="122"/>
+        <v>--</v>
+      </c>
+      <c r="CF34" s="20" t="str">
+        <f t="shared" si="123"/>
+        <v>--</v>
+      </c>
+    </row>
+    <row r="35" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="34"/>
+      <c r="D35" s="10" t="str" cm="1">
+        <f t="array" ref="D35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35, "SP_COMPANY_NAME"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="21" t="str" cm="1">
+        <f t="array" ref="G35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_LASTSALEPRICE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;I35&amp;",NA=--"))</f>
+        <v/>
+      </c>
+      <c r="H35" s="13" t="str" cm="1">
+        <f t="array" ref="H35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_PRICE_CLOSE",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="I35" s="40" t="str" cm="1">
+        <f t="array" ref="I35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_TRADING_CURRENCY","Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="J35" s="15" t="str" cm="1">
+        <f t="array" ref="J35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_MARKETCAP",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="K35" s="15" t="str" cm="1">
+        <f t="array" ref="K35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_TEV",WORKDAY($F$2+1,-1),"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="L35" s="16" t="str">
+        <f t="shared" si="96"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M35" s="16" t="str">
+        <f t="shared" si="97"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N35" s="16" t="str">
+        <f t="shared" si="98"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O35" s="16" t="str">
+        <f t="shared" si="99"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P35" s="16" t="str">
+        <f t="shared" si="100"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q35" s="16" t="str">
+        <f t="shared" si="101"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R35" s="16" t="str">
+        <f t="shared" si="102"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S35" s="16" t="str">
+        <f t="shared" si="103"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T35" s="33" t="str">
+        <f t="shared" si="104"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U35" s="33" t="str">
+        <f t="shared" si="105"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V35" s="16" t="str">
+        <f>IFERROR(IF(OR($H35/AY35&gt;#REF!,$H35/AY35&lt;#REF!),"nmf ",$H35/AY35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W35" s="16" t="str">
+        <f>IFERROR(IF(OR($H35/AZ35&gt;#REF!,$H35/AZ35&lt;#REF!),"nmf ",$H35/AZ35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X35" s="16" t="str">
+        <f>IFERROR(IF(OR($H35/BA35&gt;#REF!,$H35/BA35&lt;#REF!),"nmf ",$H35/BA35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y35" s="16" t="str">
+        <f>IFERROR(IF(OR($H35/BC35&gt;#REF!,$H35/BC35&lt;#REF!),"nmf ",$H35/BC35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z35" s="16" t="str">
+        <f>IFERROR(IF(OR($H35/BD35&gt;#REF!,$H35/BD35&lt;#REF!),"nmf ",$H35/BD35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA35" s="16" t="str">
+        <f>IFERROR(IF(OR($H35/BE35&gt;#REF!,$H35/BE35&lt;#REF!),"nmf ",$H35/BE35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB35" s="33" t="str">
+        <f t="shared" si="106"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC35" s="33" t="str">
+        <f t="shared" si="107"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD35" s="33" t="str">
+        <f t="shared" si="108"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE35" s="33" t="str">
+        <f t="shared" si="109"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF35" s="33" t="str">
+        <f t="shared" si="110"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG35" s="33" t="str">
+        <f>IFERROR((BM35/AW35)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH35" s="33" t="str">
+        <f t="shared" si="111"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI35" s="33" t="str">
+        <f t="shared" si="112"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ35" s="33" t="str">
+        <f t="shared" si="113"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK35" s="33" t="str">
+        <f t="shared" si="114"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL35" s="33" t="str">
+        <f t="shared" si="115"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM35" s="72"/>
+      <c r="AO35" s="20" t="str" cm="1">
+        <f t="array" ref="AO35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AP35" s="20" t="str" cm="1">
+        <f t="array" ref="AP35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_REV_EST",AP$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AQ35" s="20" t="str" cm="1">
+        <f t="array" ref="AQ35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AR35" s="20" t="str" cm="1">
+        <f t="array" ref="AR35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AT35" s="20" t="str" cm="1">
+        <f t="array" ref="AT35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AU35" s="20" t="str" cm="1">
+        <f t="array" ref="AU35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EBITDA_EST",AU$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AV35" s="20" t="str" cm="1">
+        <f t="array" ref="AV35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AW35" s="20" t="str" cm="1">
+        <f t="array" ref="AW35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AY35" s="13" t="str" cm="1">
+        <f t="array" ref="AY35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EPS_EST",AY$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="AZ35" s="13" t="str" cm="1">
+        <f t="array" ref="AZ35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BA35" s="13" t="str" cm="1">
+        <f t="array" ref="BA35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BC35" s="13" t="str" cm="1">
+        <f t="array" ref="BC35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_CFPS_EST",BC$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BD35" s="13" t="str" cm="1">
+        <f t="array" ref="BD35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BE35" s="13" t="str" cm="1">
+        <f t="array" ref="BE35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG35" s="66" t="str" cm="1">
+        <f t="array" ref="BG35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BH35" s="19" t="str" cm="1">
+        <f t="array" ref="BH35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BI35" s="19" t="str" cm="1">
+        <f t="array" ref="BI35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ35" s="19" t="str" cm="1">
+        <f t="array" ref="BJ35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BK35" s="37" t="e">
+        <f>+BI35-BJ35</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL35" s="19" t="str" cm="1">
+        <f t="array" ref="BL35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BN35" s="20" t="str">
+        <f>IFERROR($AP35*$BR35,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BO35" s="20" t="str">
+        <f t="shared" si="117"/>
+        <v>n/a</v>
+      </c>
+      <c r="BP35" s="20" t="str">
+        <f>IFERROR($AR35*$BT35,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="BR35" s="44" t="str">
+        <f>IF($B35="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BS35" s="44" t="str">
+        <f>IF($B35="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_GROSS_MARGIN_EST",BS$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BT35" s="44" t="str">
+        <f>IF($B35="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_GROSS_MARGIN_EST",BT$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
+      </c>
+      <c r="BU35" s="45"/>
+      <c r="BV35" s="47" t="str" cm="1">
+        <f t="array" ref="BV35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_GROSS_MARGIN_NUM_EST",BV$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BW35" s="47" t="str" cm="1">
+        <f t="array" ref="BW35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_GROSS_MARGIN_NUM_EST",BW$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BX35" s="47" t="str" cm="1">
+        <f t="array" ref="BX35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_GROSS_MARGIN_NUM_EST",BX$7,$F$2,"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BZ35" s="62" t="str">
+        <f t="shared" si="118"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CA35" s="62" t="str">
+        <f t="shared" si="119"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CB35" s="62" t="str">
+        <f t="shared" si="120"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="CD35" s="20" t="str">
+        <f t="shared" si="121"/>
+        <v>--</v>
+      </c>
+      <c r="CE35" s="20" t="str">
+        <f t="shared" si="122"/>
+        <v>--</v>
+      </c>
+      <c r="CF35" s="20" t="str">
+        <f t="shared" si="123"/>
+        <v>--</v>
+      </c>
+    </row>
+    <row r="36" spans="2:84" s="10" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="11"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="23"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="16"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16"/>
+      <c r="S36" s="16"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
+      <c r="V36" s="16"/>
+      <c r="W36" s="16"/>
+      <c r="X36" s="16"/>
+      <c r="Y36" s="16"/>
+      <c r="Z36" s="16"/>
+      <c r="AA36" s="16"/>
+      <c r="AB36" s="17"/>
+      <c r="AC36" s="17"/>
+      <c r="AD36" s="17"/>
+      <c r="AE36" s="17"/>
+      <c r="AF36" s="17"/>
+      <c r="AG36" s="17"/>
+      <c r="AH36" s="17"/>
+      <c r="AI36" s="17"/>
+      <c r="AJ36" s="17"/>
+      <c r="AK36" s="17"/>
+      <c r="AL36" s="17"/>
+      <c r="AM36" s="17"/>
+      <c r="AO36" s="19"/>
+      <c r="AP36" s="13"/>
+      <c r="AQ36" s="13"/>
+      <c r="AR36" s="13"/>
+      <c r="AU36" s="20"/>
+      <c r="AV36" s="20"/>
+      <c r="AW36" s="20"/>
+      <c r="AY36" s="13"/>
+      <c r="AZ36" s="13"/>
+      <c r="BA36" s="13"/>
+      <c r="BG36" s="19"/>
+      <c r="BH36" s="19"/>
+      <c r="BI36" s="19"/>
+      <c r="BJ36" s="19"/>
+      <c r="BK36" s="19"/>
+      <c r="BL36" s="19"/>
+      <c r="BR36" s="45"/>
+      <c r="BS36" s="45"/>
+      <c r="BT36" s="45"/>
+      <c r="BU36" s="45"/>
+      <c r="BV36" s="48"/>
+      <c r="BW36" s="48"/>
+      <c r="BX36" s="48"/>
+      <c r="BZ36" s="45"/>
+      <c r="CA36" s="45"/>
+      <c r="CB36" s="45"/>
+    </row>
+    <row r="37" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="9"/>
+      <c r="D37" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="35" t="str">
+        <f>IFERROR(AVERAGE(L30:L35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M37" s="35" t="str">
+        <f>IFERROR(AVERAGE(M30:M35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N37" s="26" t="str">
+        <f>IFERROR(AVERAGE(N30:N35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O37" s="26" t="str">
+        <f>IFERROR(AVERAGE(O30:O35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P37" s="26" t="str">
+        <f t="shared" ref="P37:AL37" si="127">IFERROR(AVERAGE(P30:P35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q37" s="26" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R37" s="26" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S37" s="26" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T37" s="36" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U37" s="36" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V37" s="26" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W37" s="26" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X37" s="26" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y37" s="26" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z37" s="26" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA37" s="26" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB37" s="36" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC37" s="36" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD37" s="36" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE37" s="36" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF37" s="36" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG37" s="36" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH37" s="36" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI37" s="36" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ37" s="36" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK37" s="36" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL37" s="36" t="str">
+        <f t="shared" si="127"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AM37" s="36"/>
+      <c r="BR37" s="45"/>
+      <c r="BS37" s="45"/>
+      <c r="BT37" s="45"/>
+      <c r="BU37" s="45"/>
+      <c r="BV37" s="48"/>
+      <c r="BW37" s="48"/>
+      <c r="BX37" s="48"/>
+      <c r="BZ37" s="45"/>
+      <c r="CA37" s="45"/>
+      <c r="CB37" s="45"/>
+    </row>
+    <row r="38" spans="2:84" s="10" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="9"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="54"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="53"/>
+      <c r="N38" s="53"/>
+      <c r="O38" s="53"/>
+      <c r="P38" s="53"/>
+      <c r="Q38" s="53"/>
+      <c r="R38" s="53"/>
+      <c r="S38" s="53"/>
+      <c r="T38" s="53"/>
+      <c r="U38" s="53"/>
+      <c r="V38" s="53"/>
+      <c r="W38" s="53"/>
+      <c r="X38" s="53"/>
+      <c r="Y38" s="53"/>
+      <c r="Z38" s="53"/>
+      <c r="AA38" s="53"/>
+      <c r="AB38" s="53"/>
+      <c r="AC38" s="53"/>
+      <c r="AD38" s="53"/>
+      <c r="AE38" s="53"/>
+      <c r="AF38" s="53"/>
+      <c r="AG38" s="53"/>
+      <c r="AH38" s="53"/>
+      <c r="AI38" s="53"/>
+      <c r="AJ38" s="53"/>
+      <c r="AK38" s="53"/>
+      <c r="AL38" s="53"/>
+      <c r="AM38" s="53"/>
+      <c r="BR38" s="45"/>
+      <c r="BS38" s="45"/>
+      <c r="BT38" s="45"/>
+      <c r="BU38" s="45"/>
+      <c r="BV38" s="48"/>
+      <c r="BW38" s="48"/>
+      <c r="BX38" s="48"/>
+      <c r="BZ38" s="45"/>
+      <c r="CA38" s="45"/>
+      <c r="CB38" s="45"/>
+    </row>
+    <row r="39" spans="2:84" s="30" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="29"/>
+      <c r="D39" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="55"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="56" t="str">
+        <f>IFERROR(AVERAGE(L10:L15,L20:L25,L30:L35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M39" s="56" t="str">
+        <f t="shared" ref="M39:U39" si="128">IFERROR(AVERAGE(M10:M15,M20:M25,M30:M35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N39" s="56" t="str">
+        <f t="shared" si="128"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O39" s="56" t="str">
+        <f t="shared" si="128"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P39" s="56" t="str">
+        <f t="shared" si="128"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q39" s="56" t="str">
+        <f t="shared" si="128"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R39" s="56" t="str">
+        <f t="shared" si="128"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S39" s="56" t="str">
+        <f t="shared" si="128"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T39" s="74" t="str">
+        <f t="shared" si="128"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U39" s="74" t="str">
+        <f t="shared" si="128"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V39" s="56" t="e">
+        <f t="shared" ref="V39:AL39" si="129">AVERAGE(V10:V15,V20:V25)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W39" s="56" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X39" s="56" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y39" s="56" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z39" s="56" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA39" s="56" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB39" s="57" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC39" s="57" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD39" s="57" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE39" s="57" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF39" s="57" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG39" s="57" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH39" s="57" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AI39" s="57" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AJ39" s="57" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AK39" s="57" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL39" s="57" t="e">
+        <f t="shared" si="129"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AM39" s="57"/>
+      <c r="BR39" s="46"/>
+      <c r="BS39" s="46"/>
+      <c r="BT39" s="46"/>
+      <c r="BU39" s="46"/>
+      <c r="BV39" s="49"/>
+      <c r="BW39" s="49"/>
+      <c r="BX39" s="49"/>
+      <c r="BZ39" s="46"/>
+      <c r="CA39" s="46"/>
+      <c r="CB39" s="46"/>
+    </row>
+    <row r="40" spans="2:84" s="30" customFormat="1" ht="18" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="29"/>
+      <c r="D40" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="50"/>
+      <c r="F40" s="50"/>
+      <c r="G40" s="50"/>
+      <c r="H40" s="50"/>
+      <c r="I40" s="50"/>
+      <c r="J40" s="50"/>
+      <c r="K40" s="50"/>
+      <c r="L40" s="51">
+        <f t="shared" ref="L40:AL40" si="130">+IFERROR((SUM(L20:L25,L10:L15)-MAX(L10:L15,L20:L25)-MIN(L10:L15,L20:L25))/(COUNT(L20:L25,L10:L15)-2),"n/a ")</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="51">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="N40" s="51">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="O40" s="51">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="P40" s="51">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="51">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="R40" s="51">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="51">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="75">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="75">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="51">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="51">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="51">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="51">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="51">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AA40" s="51">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AB40" s="52">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AC40" s="52">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AD40" s="52">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AE40" s="52">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AF40" s="52">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AG40" s="52">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AH40" s="52">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AI40" s="52">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="52">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AK40" s="52">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AL40" s="52">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="AM40" s="52"/>
+      <c r="BR40" s="46"/>
+      <c r="BS40" s="46"/>
+      <c r="BT40" s="46"/>
+      <c r="BU40" s="46"/>
+      <c r="BV40" s="49"/>
+      <c r="BW40" s="49"/>
+      <c r="BX40" s="49"/>
+      <c r="BZ40" s="46"/>
+      <c r="CA40" s="46"/>
+      <c r="CB40" s="46"/>
+    </row>
+    <row r="41" spans="2:84" s="30" customFormat="1" ht="16.350000000000001" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="29"/>
+      <c r="D41" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="59" t="str">
+        <f>IFERROR(MEDIAN(L20:L25,L10:L15,L30:L35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="M41" s="59" t="str">
+        <f t="shared" ref="M41:U41" si="131">IFERROR(MEDIAN(M20:M25,M10:M15,M30:M35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N41" s="59" t="str">
+        <f t="shared" si="131"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O41" s="59" t="str">
+        <f t="shared" si="131"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P41" s="59" t="str">
+        <f t="shared" si="131"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q41" s="59" t="str">
+        <f t="shared" si="131"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R41" s="59" t="str">
+        <f t="shared" si="131"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S41" s="59" t="str">
+        <f t="shared" si="131"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T41" s="76" t="str">
+        <f t="shared" si="131"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U41" s="76" t="str">
+        <f t="shared" si="131"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V41" s="59" t="e">
+        <f t="shared" ref="V41:AL41" si="132">+MEDIAN(V20:V25,V10:V15)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W41" s="59" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="X41" s="59" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y41" s="59" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z41" s="59" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA41" s="59" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB41" s="60" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC41" s="60" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD41" s="60" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE41" s="60" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF41" s="60" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG41" s="60" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH41" s="60" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI41" s="60" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ41" s="60" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="AK41" s="60" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="AL41" s="60" t="e">
+        <f t="shared" si="132"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="AM41" s="60"/>
+      <c r="BR41" s="46"/>
+      <c r="BS41" s="46"/>
+      <c r="BT41" s="46"/>
+      <c r="BU41" s="46"/>
+      <c r="BV41" s="49"/>
+      <c r="BW41" s="49"/>
+      <c r="BX41" s="49"/>
+      <c r="BZ41" s="46"/>
+      <c r="CA41" s="46"/>
+      <c r="CB41" s="46"/>
+    </row>
+    <row r="42" spans="2:84" s="10" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="9"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="BR42" s="45"/>
+      <c r="BS42" s="45"/>
+      <c r="BT42" s="45"/>
+      <c r="BU42" s="45"/>
+      <c r="BV42" s="48"/>
+      <c r="BW42" s="48"/>
+      <c r="BX42" s="48"/>
+      <c r="BZ42" s="45"/>
+      <c r="CA42" s="45"/>
+      <c r="CB42" s="45"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:CF13">
-    <sortCondition descending="1" ref="K10:K13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:CF15">
+    <sortCondition descending="1" ref="K10:K15"/>
   </sortState>
-  <conditionalFormatting sqref="G10:G13 G18:G21">
-    <cfRule type="expression" dxfId="4" priority="41">
+  <conditionalFormatting sqref="B10:B15">
+    <cfRule type="duplicateValues" dxfId="6" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20:B25">
+    <cfRule type="duplicateValues" dxfId="5" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30:B35">
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G10:G15 G20:G25">
+    <cfRule type="expression" dxfId="3" priority="44">
       <formula>I10="EUR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="42">
+    <cfRule type="expression" dxfId="2" priority="45">
       <formula>I10="CAD"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:B13">
-    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18:B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+  <conditionalFormatting sqref="G30:G35">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>I30="EUR"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>I30="CAD"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="20" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="19" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/infor-workflows/templates/INFOR Comps Template.xlsx
+++ b/infor-workflows/templates/INFOR Comps Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inforfg1-my.sharepoint.com/personal/twilson_inforfg_com/Documents/Desktop/Claude Access Folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="602" documentId="8_{44689429-9083-4319-AF07-3319705600A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72B23130-0E5C-4E73-886F-1BBB6977EEE9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE767EBD-4B0B-423A-B47B-5C8D3B5800E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="__snloffice" sheetId="2" state="veryHidden" r:id="rId1"/>
@@ -1084,7 +1084,7 @@
     <definedName name="MLNK4fd2e3ceac464726b63c904de1f9a796" hidden="1">#REF!</definedName>
     <definedName name="MLNK56b240f41d2942fcb9b403b5a476a7d8" hidden="1">#REF!</definedName>
     <definedName name="MLNK5ba01ab6b2dd4c4f94bf60093b153ee4" hidden="1">#REF!</definedName>
-    <definedName name="MLNK5e5ab4f18b104bcaa26dfc9b8edd8d3d" hidden="1">Comps!$D$6:$AL$39</definedName>
+    <definedName name="MLNK5e5ab4f18b104bcaa26dfc9b8edd8d3d" hidden="1">Comps!$D$6:$AK$39</definedName>
     <definedName name="MLNK5ec79545d49d493f93a2420475c22a3f" hidden="1">#REF!</definedName>
     <definedName name="MLNK5f342b94d77944659b1ef5a7dbaef93a" hidden="1">#REF!</definedName>
     <definedName name="MLNK601c1ef95cb34d09b82b1a6ff7d9605a" hidden="1">#REF!</definedName>
@@ -1094,7 +1094,7 @@
     <definedName name="MLNK8ad5f35a4bfd46728c3273a4d5c7a905" hidden="1">#REF!</definedName>
     <definedName name="MLNK90417d75114a48c0a1779bb363a329cd" hidden="1">#REF!</definedName>
     <definedName name="MLNK90bd4aad386a4451b6d8702c11dda57c" hidden="1">#REF!</definedName>
-    <definedName name="MLNK94d282c0cd3c43fb89fa5c845ea3d8b5" hidden="1">Comps!$D$6:$AL$42</definedName>
+    <definedName name="MLNK94d282c0cd3c43fb89fa5c845ea3d8b5" hidden="1">Comps!$D$6:$AK$42</definedName>
     <definedName name="MLNK96eba42b27654b0c96a777c2b1f2c026" hidden="1">#REF!</definedName>
     <definedName name="MLNK9c76f014126946d781f4ec0cf20e8cb4" hidden="1">#REF!</definedName>
     <definedName name="MLNK9ff9d28edd3148e7a8cba265311858fd" hidden="1">#REF!</definedName>
@@ -1307,7 +1307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
   <si>
     <t>Currency:</t>
   </si>
@@ -1390,9 +1390,6 @@
     <t>Yield</t>
   </si>
   <si>
-    <t>Dividend</t>
-  </si>
-  <si>
     <t>Net Debt</t>
   </si>
   <si>
@@ -1444,15 +1441,6 @@
     <t>Net Debt / Adj. EBITDA</t>
   </si>
   <si>
-    <t>Net Debt / Equity</t>
-  </si>
-  <si>
-    <t>Book Value</t>
-  </si>
-  <si>
-    <t>Market Cap</t>
-  </si>
-  <si>
     <t>CFPS</t>
   </si>
   <si>
@@ -1483,14 +1471,17 @@
     <t>CAD</t>
   </si>
   <si>
-    <t>允䅁䝁䅣䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䕁䅕兖卂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅐䅁䅁䅙䅁瑁䍁䄰䅁㉁䅁䅁杁䅁䅁䅁杒䅁䑁䅧䅁橁䕁䅫杔坂䕁䅅䅔䩂䕁䅑䅉䝂䙁䅕杔䑂䙁䅑兓偂䕁䄴䅉兂䕁䅅杕䉂䕁䄰兒啂䕁䅕杕䅁䅁䅑䅁煁䅁䅁杓兂䕁䄰睢祂䝁䅣兙畂䍁䅁睑潂䝁䅅督求䍁䅁杊杁䕁䅍睢畁䅁䅁杔䅁䕁䅯䅁䑂䙁䅫杍睁䑁䅉䅎ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䙁䅧䅁坁䅁䅁䅍㉁䍁䄸免睁䍁䄸杍睁䑁䅉兎䅁䅁䅕䅁奁䅁䅁䅋睁䑁䅅兌䭂䝁䅅杢瑁䑁䅉兎灁䅁䅁杂䅁䑁䅉䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兒噂䙁䅉䅌杁䕁䄴兑㥁䍁䄰兌䅁䑁䄸䅁捂䅁䅁杒剂䑁䅁䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰兔灂䝁䅷䅢灂䝁䄸杢穂䍁䅷䅉佂䕁䅅児瑁䍁䄰䅁兂䅁䅁杙䅁䕁䅍兗祁䑁䅁杍ㅁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁睔䅁䅁䅑䅁瑁䅁䅁䅎䅁䑁䅑䅁䑂䙁䅫杍睁䑁䅉李ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅖䅁䅁䅧䅁䑂䕁䅅䅒䅁䅁䅫䅁佁䅁䅁睑婂䑁䅉䅍祁䑁䅑䅁呁䅁䅁䅎䅁䕁䅍兗祁䑁䅁杍ぁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉佂䕁䅅児瑁䍁䄰䅁卂䅁䅁杄䅁䕁䅍兗祁䑁䅁杍㉁䅁䅁兆䅁䝁䅉䅁䑂䙁䅫杍睁䑁䅉䅎ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁兔桂䝁䅣児乂䝁䅫䅢獂䝁䅫睢畂䡁䅍䅌杁䕁䄴兑㥁䍁䄰兌䅁䙁䅅䅁浂䅁䅁睑婂䑁䅉䅍祁䑁䅑䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰兔灂䝁䅷䅢灂䝁䄸杢穂䍁䅷䅉佂䕁䅅児佂䙁䅕䅔䵂䅁䅁兖䅁䕁䅙䅁䑂䙁䅫杍睁䑁䅉䅎ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅘䅁䅁䅧䅁䝂䙁䅅䅍䅁䅁䄸䅁䭂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児卂䝁䅕䅣療䡁䅉䅤求䝁䅑䅉䑂䡁䅕杣祂䝁䅕杢橂䡁䅫䅌佂䕁䅅児瑁䍁䄰䅁㙁䅁䅁杄䅁䕁䅍兗祁䑁䅁杍ㅁ䅁䅁䅆䅁䙁䅑䅁䱂䝁䄴兡湂䝁䅧䅤瑁䙁䅍睤灂䝁䅙䅤杁䙁䅑杣桂䝁䄴督睂䝁䄸杣あ䝁䅅䅤灂䝁䄸杢杁䕁䅧睢獂䝁䅑兡畂䝁䅣督杁䕁䅫杢橂䍁䄴䅁潁䅁䅁䅎䅁䕁䅍兗祁䑁䅁杍ㅁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉佂䕁䅅児瑁䍁䄰䅁呂䅁䅁杚䅁䕁䅍兗祁䑁䅁杍ㅁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䙁䅙䅁䭂䅁䅁睑婂䑁䅉䅍祁䑁䅕䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁婂䅁䅁杈䅁䕁䄴兑呂䕁䅑兑剂䕁䅣睕㙁䕁䄰杕啂䕁䄴䅉䅁䍁䄰䅁楂䅁䅁睑婂䑁䅉䅍祁䑁䅙䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰兔灂䝁䅷䅢灂䝁䄸杢穂䍁䅷䅉佂䕁䅅児瑁䍁䄰䅁扂䅁䅁杅䅁䕁䄴兗呂䕁䅕杏䩂䕁䅉兔䅁䕁䅣䅁佁䅁䅁睑婂䑁䅉䅍祁䑁䅣䅁桂䅁䅁杚䅁䕁䅍兗祁䑁䅁杍㉁䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䙁䅣䅁䭂䅁䅁睑婂䑁䅉䅍祁䑁䅙䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁慂䅁䅁䅍䅁䕁䅧党桂䡁䅉䅤獂䝁䅅杢歂䍁䅁兒㑂䡁䅁杣求䡁䅍督獁䍁䅁兓畂䝁䅍杌䅁䍁䅷䅁䥁䅁䅁兓䍂䕁䄰䅁䩂䅁䅁杈䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䕁䄴兑䅁䅁䅍䅁捁䅁䅁兓剂䙁䄸睑䉂䙁䅍䅓時䕁䅕兕噂䕁䅫杖䅁䑁䄰䅁捁䅁䅁杔䉂䙁䅍䅒䉂䙁䅅睒呂䑁䅯䅓啂䕁䅷䅒䅁䍁䅳䅁歁䅁䅁兓剂䙁䄸睑䉂䙁䅍䅓時䙁䅍䅖時䕁䅫杔坂䕁䅕睕啂䅁䅁充䅁䅁䄴䅁䩂䙁䅅睘啂䕁䅕杖䅁䅁䅷䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅏䅁䉁䅷䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉佂䕁䅅児瑁䅁䅁睍䅁䙁䅁䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰䅖潂䝁䄸兤穂䝁䅅杢歂䡁䅍䅌杁䕁䄴兑㥁䕁䄴兑䅁䉁䄰䅁捁䅁䅁兓剂䙁䄸䅖偂䙁䅑兑䵂䙁䄸䅒䙂䕁䅉䅖䅁䙁䄴䅁杁䅁䅁兓剂䙁䄸䅖偂䙁䅑兑䵂䙁䄸兒剂䙁䅕兓啂䙁䅫䅁摂䅁䅁䅗䅁䕁䅫杢あ䝁䅕杣畂䝁䅅䅤灂䝁䄸杢桂䝁䅷䅉䍂䡁䅕督灂䝁䄴党穂䡁䅍䅉乂䝁䅅睙潂䝁䅫杢求䡁䅍䅉䑂䝁䄸杣睂䝁䄸杣桂䡁䅑兡療䝁䄴䅁䭂䅁䅁杒䅁䕁䅯杌䍂䍁䄴䅉䥂䡁䅕杢あ䍁䅁䅖祂䝁䅅杢穂䡁䅁睢祂䡁䅑䅉呂䝁䅕杣㉂䝁䅫睙求䡁䅍䅌杁䕁䅫杢橂䍁䄴䅁楁䅁䅁杂䅁䕁䄴兑䅁䉁䅣䅁䥁䅁䅁杓兂䕁䄰䅁乂䅁䅁杌䅁䕁䄰兙祂䡁䅑党畂䍁䅁䅖祂䝁䅅杢穂䡁䅁睢祂䡁䅑䅌杁䕁䅷䅤歂䍁䄴䅁畁䅁䅁䅊䅁䕁䄰兤獂䝁䅷党畂䍁䅁睒祂䝁䄸兤睂䍁䅁䅔あ䝁䅑杌䅁䍁䅁䅁兂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䙁䅑䅡療䡁䅕督桂䝁䄴䅚穂䍁䅷䅉佂䕁䅅児瑁䍁䄰䅁㝁䅁䅁杈䅁䕁䄴兑呂䕁䅑兑剂䕁䅣睕㙁䕁䅯村䥂䙁䅑䅉䅁䍁䅅䅁允䅁䅁䅖呂䙁䅧杏乂䙁䅑䅔䅁䉁䄸䅁啁䅁䅁杔婂䙁䅍兒㙁䙁䅍杔䕂䙁䅉䅁橁䅁䅁杈䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䍁䄰兌䅁䑁䅕䅁捁䅁䅁杔䉂䙁䅍䅒䉂䙁䅅睒呂䑁䅯睖䙂䙁䅉杔䅁䍁䅫䅁䭁䅁䅁杔噂䕁䅷䅔䅁䕁䅍䅁啁䅁䅁杔婂䙁䅍兒㙁䕁䅳杔奂䍁䅁䅁湁䅁䅁杅䅁䕁䄴兗呂䕁䅕杏奂䙁䅁睔䅁䍁䅕䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁䅉䑂䡁䅕杣祂䑁䄰杕求䡁䅁睢祂䡁䅑党歂䍁䅁睑ㅂ䡁䅉杣求䝁䄴睙㕂䍁䅷杔䉂䑁䄰杔䉂䅁䅁睌䅁䑁䅉䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兒噂䙁䅉䅌杁䕁䄴兑㥁䕁䄴兑䅁䉁䅳䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔䉂䅁䅁睃䅁䑁䅉䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䍁䄰兌䅁䑁䅣䅁祁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉佂䕁䅅児佂䕁䅅䅁䡁䅁䅁杉䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁䙂䅁䅁杉䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䕁䄴兤獂䝁䅷䅁㕁䅁䅁杌䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰睑䉂䕁䅑䅌佂䕁䅅児瑁䍁䄰䅁䱂䅁䅁杓䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰杕求䡁䅁睢祂䡁䅑党歂䍁䅁睑ㅂ䡁䅉杣求䝁䄴睙㕂䍁䅷杔䉂䑁䄰杔䉂䅁䅁免䅁䕁䅷䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅑䅁䙁䅁䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔噂䍁䄰兌䅁䕁䅧䅁兂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁兔桂䝁䅣児乂䝁䅫䅢獂䝁䅫睢畂䡁䅍䅌杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁䕂䅁䅁䅍䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䍁䄰兌䅁䕁䅅䅁ぁ䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䕁䅉䅁畁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䕁䄴兑㥁䍁䄰兌䅁䕁䅷䅁捁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䄴兑㥁䕁䄴兑䅁䑁䅁䅁捁䅁䅁睕兂䙁䄸睑䉂䙁䅍䅓時䕁䅕兕噂䕁䅫杖䅁䑁䄴䅁奁䅁䅁睕兂䙁䄸睑䝂䙁䅁睕時䕁䅕睕啂䅁䅁䅈䅁䍁䅁䅁呂䙁䅁睘䑂䕁䄸兔兂䕁䅅杔婂䙁䄸杔䉂䕁䄰兒䅁䅁䅁䅁慁䅁䅁睕兂䙁䄸䅒䩂䙁䅙睘婂䕁䅫兒䵂䕁䅑䅁乁䅁䅁䅈䅁䙁䅍䅕時䕁䅕村䩂䙁䅑䅒䉂䙁䄸兒呂䙁䅑䅁婁䅁䅁杆䅁䙁䅍䅕時䕁䅕䅕呂䙁䄸兒呂䙁䅑䅁慁䅁䅁䅋䅁䙁䅍䅕時䕁䅣杕偂䙁䅍睕時䕁䄰兑卂䕁䅣兓佂䙁䄸兒呂䙁䅑䅁坁䅁䅁䅍䅁䙁䅍䅕時䕁䅣杕偂䙁䅍睕時䕁䄰兑卂䕁䅣兓佂䙁䄸杔噂䕁䄰睘䙂䙁䅍䅖䅁䉁䅧䅁楁䅁䅁睕兂䙁䄸䅔䉂䙁䅍䅖呂䕁䅅䅔䙂䙁䅁杕䩂䕁䅍兒䅁䅁䅉䅁慁䅁䅁睕兂䙁䄸兔䉂䙁䅉睓䙂䙁䅑睑䉂䙁䅁䅁䭁䅁䅁杈䅁䙁䅍䅕時䙁䅁杕䩂䕁䅍兒時䕁䅍䅔偂䙁䅍兒䅁䙁䄸䅁坁䅁䅁睕兂䙁䄸杕䙂䙁䅙睘䙂䙁䅍䅖䅁䉁䅉䅁捁䅁䅁睕兂䙁䄸䅖偂䙁䅑兑䵂䙁䄸䅒䙂䕁䅉䅖䅁䉁䅁䅁杁䅁䅁睕兂䙁䄸䅖偂䙁䅑兑䵂䙁䄸兒剂䙁䅕兓啂䙁䅫䅁佁䅁䅁䅋䅁䙁䅍䅕時䙁䅑杕䉂䕁䅑兓佂䕁䅣睘䑂䙁䅕杕卂䕁䅕杔䑂䙁䅫䅁䥁䅁䅁杍䅁䙁䅍睙潂䝁䄴党灂䝁䅑党祂䍁䅁杔桂䡁䅑兡療䝁䄴兙獂䍁䅷䅉䩂䝁䄴睙畁䅁䅁䅊䅁䍁䄴䅁啂䕁䅙兓杁䕁䅫杢あ䝁䅕杣畂䝁䅅䅤灂䝁䄸杢桂䝁䅷䅉䩂䝁䄴睙畁䅁䅁允䅁䉁䅉䅁啂䙁䅍䅗㙁䙁䅑杒䩂䕁䅫䅁敁䅁䅁䅃䅁䙁䅕睕䕂䅁䅁杍䅁䑁䅉䅁塂䝁䅕杣畂䝁䅕杣杁䕁䅕杢あ䝁䅕杣睂䡁䅉兡穂䝁䅕督獁䍁䅁兓畂䝁䅍杌䅁䍁䅯䅁啁䅁䅁䅗兂䕁䄸䅌杁䕁䅫杢橂䍁䄴䅁流䅁䅁杄䅁䝁䅍入祁䑁䅁杍ㅁ䅁䅁䅙䅁䅁䄴䅁䩂䙁䅅睘卂䕁䅕杖䅁䝁䅉䅁䥁䅁䅁䅔啂䕁䄰䅁橂䅁䅁䅆䅁䙁䅍䅕時䕁䅕村䩂䙁䅑䅒䉂䅁䅁䅚䅁䉁䅉䅁啂䙁䅍䅗㙁䕁䄸䅖䙂䙁䅧䅁求䅁䅁䅌䅁䕁䄸䅣求䝁䄴䅉啂䝁䅕䅥あ䍁䅁睑療䡁䅉䅣療䡁䅉兙あ䝁䅫睢畂䅁䅁杚䅁䅁䅁䅁㵁</t>
+    <t>\</t>
+  </si>
+  <si>
+    <t>允䅁䝁䅫䅁䍁䅁䅁䅁䝂䅁䅁杔䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䅍兤祂䡁䅉児䙂䙁䅕杕獁䍁䅁兔桂䝁䅣児乂䝁䅫䅢獂䝁䅫睢畂䡁䅍䅌杁䕁䄴兑㥁䍁䄰兌䅁䑁䅷䅁䝁䅁䅁兌瑁䅁䅁李䅁䑁䅧䅁橁䕁䅫杔坂䕁䅅䅔䩂䕁䅑䅉䝂䙁䅕杔䑂䙁䅑兓偂䕁䄴䅉兂䕁䅅杕䉂䕁䄰兒啂䕁䅕杕䅁䅁䅑䅁奁䅁䅁䅋睁䑁䅅兌䭂䝁䅅杢瑁䑁䅉兎灁䅁䅁杂䅁䍁䅯䅁䭂䙁䅁兔療䡁䅉睚桂䝁䄴䅉䑂䝁䅧兙穂䝁䅕䅉流䍁䅁睑療䍁䄴䅁佂䅁䅁杓䅁䕁䅍兗祁䑁䅁杍ぁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉佂䕁䅅児佂䙁䅕䅔䵂䅁䅁䅗䅁䉁䅙䅁睁䑁䅙睌硁䑁䅁睌祁䑁䅁杍ㅁ䅁䅁兂䅁䅁䅑䅁瑁䅁䅁䅎䅁䝁䅉䅁䑂䙁䅫杍睁䑁䅉兎ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁兔桂䝁䅣児乂䝁䅫䅢獂䝁䅫睢畂䡁䅍䅌杁䕁䄴兑㥁䍁䄰兌䅁䕁䄸䅁捂䅁䅁杒剂䑁䅁䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰兔灂䝁䅷䅢灂䝁䄸杢穂䍁䅷䅉佂䕁䅅児瑁䍁䄰䅁兂䅁䅁杍䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䅍兤祂䡁䅉児䙂䙁䅕杕獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁睐䅁䅁䄴䅁䑂䙁䅫杍睁䑁䅉䅎䅁䉁䅍䅁䥁䅁䅁睑䉂䕁䅑䅁䩁䅁䅁䅎䅁䕁䅍兗祁䑁䅁杍㉁䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉佂䕁䅅児瑁䍁䄰䅁啂䅁䅁䅎䅁䕁䅍兗祁䑁䅁杍ぁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉佂䕁䅅児瑁䍁䄰䅁卂䅁䅁杙䅁䕁䅍兗祁䑁䅁杍ぁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁兕䅁䅁䄴䅁䑂䙁䅫杍睁䑁䅉李䅁䉁䅕䅁浂䅁䅁睑婂䑁䅉䅍祁䑁䅑䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰兔灂䝁䅷䅢灂䝁䄸杢穂䍁䅷䅉佂䕁䅅児佂䙁䅕䅔䵂䅁䅁兖䅁䕁䅙䅁䑂䙁䅫杍睁䑁䅉䅎ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅘䅁䕁䅯䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅉党睂䝁䄸杣あ䝁䅕䅚杁䕁䅍兤祂䡁䅉党畂䝁䅍入獁䕁䄴兑㥁䍁䄰兌䅁䑁䅯䅁佁䅁䅁睑婂䑁䅉䅍祁䑁䅕䅁啁䅁䅁䅃䅁䕁䅙兕睁䅁䅁睄䅁䑁䅑䅁䑂䙁䅫杍睁䑁䅉兎ぁ䑁䅕李ㅁ䑁䅧睔睂䡁䅑兡療䝁䄴督㙁䍁䅁杔䉂䑁䄰兌瑁䅁䅁睕䅁䙁䅑䅁䱂䝁䄴兡湂䝁䅧䅤瑁䙁䅍睤灂䝁䅙䅤杁䙁䅑杣桂䝁䄴督睂䝁䄸杣あ䝁䅅䅤灂䝁䄸杢杁䕁䅧睢獂䝁䅑兡畂䝁䅣督杁䕁䅫杢橂䍁䄴䅁潁䅁䅁杚䅁䕁䅍兗祁䑁䅁杍ㅁ䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䙁䅙䅁䭂䅁䅁睑婂䑁䅉䅍祁䑁䅕䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁婂䅁䅁杈䅁䕁䄴兑呂䕁䅑兑剂䕁䅣睕㙁䕁䄰杕啂䕁䄴䅉䅁䍁䄰䅁楂䅁䅁睑婂䑁䅉䅍祁䑁䅙䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰兔灂䝁䅷䅢灂䝁䄸杢穂䍁䅷䅉佂䕁䅅児瑁䍁䄰䅁扂䅁䅁杚䅁䕁䅍兗祁䑁䅁杍㉁䑁䅑兎㉁䑁䅕䅏偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䙁䅣䅁佁䅁䅁睑婂䑁䅉䅍祁䑁䅣䅁桂䅁䅁杅䅁䕁䄴兗呂䕁䅕杏䩂䕁䅉兔䅁䕁䅣䅁䭂䅁䅁睑婂䑁䅉䅍祁䑁䅙䅎ㅁ䑁䅙兎㑁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁慂䅁䅁䅍䅁䕁䅧党桂䡁䅉䅤獂䝁䅅杢歂䍁䅁兒㑂䡁䅁杣求䡁䅍督獁䍁䅁兓畂䝁䅍杌䅁䍁䅷䅁䥁䅁䅁兓䍂䕁䄰䅁䩂䅁䅁䅈䅁䕁䅫兕時䕁䅍兑呂䕁䅧睘䙂䙁䅅兖䩂䙁䅙䅁㥁䅁䅁杈䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䕁䄴兑䅁䅁䅍䅁歁䅁䅁兓剂䙁䄸睑䉂䙁䅍䅓時䙁䅍䅖時䕁䅫杔坂䕁䅕睕啂䅁䅁充䅁䉁䅷䅁佂䕁䅅睕䕂䕁䅅兕䡂䙁䅍杏䥂䙁䅑䅔䕂䅁䅁睋䅁䅁䄴䅁䩂䙁䅅睘啂䕁䅕杖䅁䅁䅷䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅏䅁䉁䅷䅁䩂䙁䅅睘啂䕁䄸䅖䉂䕁䅷睘䕂䕁䅕村啂䅁䅁杘䅁䙁䅁䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰䅖潂䝁䄸兤穂䝁䅅杢歂䡁䅍䅌杁䕁䄴兑㥁䕁䄴兑䅁䉁䄰䅁捁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁杔䉂䑁䄰兌䅁䑁䅍䅁杁䅁䅁兓剂䙁䄸䅖偂䙁䅑兑䵂䙁䄸兒剂䙁䅕兓啂䙁䅫䅁摂䅁䅁䅗䅁䕁䅫杢あ䝁䅕杣畂䝁䅅䅤灂䝁䄸杢桂䝁䅷䅉䍂䡁䅕督灂䝁䄴党穂䡁䅍䅉乂䝁䅅睙潂䝁䅫杢求䡁䅍䅉䑂䝁䄸杣睂䝁䄸杣桂䡁䅑兡療䝁䄴䅁䭂䅁䅁杒䅁䕁䅯杌䍂䍁䄴䅉䥂䡁䅕杢あ䍁䅁䅖祂䝁䅅杢穂䡁䅁睢祂䡁䅑䅉呂䝁䅕杣㉂䝁䅫睙求䡁䅍䅌杁䕁䅫杢橂䍁䄴䅁楁䅁䅁䅃䅁䕁䅯䅕乂䅁䅁兔䅁䅁䅙䅁佂䕁䅅䅁塁䅁䅁杌䅁䕁䄰兙祂䡁䅑党畂䍁䅁䅖祂䝁䅅杢穂䡁䅁睢祂䡁䅑䅌杁䕁䅷䅤歂䍁䄴䅁畁䅁䅁䅊䅁䕁䄰兤獂䝁䅷党畂䍁䅁睒祂䝁䄸兤睂䍁䅁䅔あ䝁䅑杌䅁䍁䅁䅁敁䅁䅁杔䉂䙁䅍䅒䉂䙁䅅睒呂䑁䅯杓䍂䕁䅧䅖杁䅁䅁光䅁䙁䅁䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄰兙湂䑁䄰䅖潂䝁䄸兤穂䝁䅅杢歂䡁䅍䅌杁䕁䄴兑㥁䍁䄰兌䅁䑁䅳䅁捁䅁䅁杔䉂䙁䅍䅒䉂䙁䅅睒呂䑁䅯睖䙂䙁䅉杔䅁䍁䅫䅁允䅁䅁䅖呂䙁䅧杏乂䙁䅑䅔䅁䉁䄸䅁啁䅁䅁杔婂䙁䅍兒㙁䙁䅍杔䕂䙁䅉䅁橁䅁䅁杈䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䍁䄰兌䅁䑁䅕䅁䭁䅁䅁杔噂䕁䅷䅔䅁䕁䅍䅁啁䅁䅁杔婂䙁䅍兒㙁䕁䅳杔奂䍁䅁䅁湁䅁䅁杅䅁䕁䄴兗呂䕁䅕杏奂䙁䅁睔䅁䍁䅕䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁䅉䑂䡁䅕杣祂䑁䄰杕求䡁䅁睢祂䡁䅑党歂䍁䅁睑ㅂ䡁䅉杣求䝁䄴睙㕂䍁䅷杔䉂䑁䄰杔䉂䅁䅁睌䅁䑁䅉䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兒噂䙁䅉䅌杁䕁䄴兑㥁䕁䄴兑䅁䉁䅳䅁佂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔䉂䅁䅁睃䅁䑁䅉䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯䅉䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䍁䄰兌䅁䑁䅣䅁祁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䍁䅁睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉佂䕁䅅児佂䕁䅅䅁䡁䅁䅁杉䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁䙂䅁䅁杉䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏杁䕁䄴兑㥁䕁䄴兤獂䝁䅷䅁㕁䅁䅁杌䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰睑䉂䕁䅑䅌佂䕁䅅児瑁䍁䄰䅁䱂䅁䅁杓䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰杕求䡁䅁睢祂䡁䅑党歂䍁䅁睑ㅂ䡁䅉杣求䝁䄴睙㕂䍁䅷杔䉂䑁䄰杔䉂䅁䅁免䅁䕁䅷䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰兌瑁䅁䅁䅑䅁䙁䅁䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䙁䅕睕䕂䍁䅷䅉乂䝁䅅睚㥁䕁䄰兡獂䝁䅷兡療䝁䄴督獁䍁䅁杔䉂䑁䄰杔噂䍁䄰兌䅁䕁䅧䅁兂䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁兔桂䝁䅣児乂䝁䅫䅢獂䝁䅫睢畂䡁䅍䅌杁䕁䄴兑㥁䕁䄴兖䵂䕁䅷䅁䕂䅁䅁䅍䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰兖呂䕁䅑䅌杁䕁䄴兑㥁䍁䄰兌䅁䕁䅅䅁ぁ䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䍁䅁杔䉂䑁䄰杔噂䕁䅷䅔䅁䕁䅉䅁畁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䅍兤祂䡁䅉児噂䙁䅍䅒獁䕁䄴兑㥁䍁䄰兌䅁䕁䅷䅁捁䅁䅁睔睂䡁䅑兡療䝁䄴督㙁䕁䄴兑㥁䕁䄴兑䅁䑁䅁䅁捁䅁䅁睕兂䙁䄸睑䉂䙁䅍䅓時䕁䅕兕噂䕁䅫杖䅁䑁䄴䅁奁䅁䅁睕兂䙁䄸睑䝂䙁䅁睕時䕁䅕睕啂䅁䅁䅈䅁䍁䅁䅁呂䙁䅁睘䑂䕁䄸兔兂䕁䅅杔婂䙁䄸杔䉂䕁䄰兒䅁䅁䅁䅁慁䅁䅁睕兂䙁䄸䅒䩂䙁䅙睘婂䕁䅫兒䵂䕁䅑䅁乁䅁䅁䅈䅁䙁䅍䅕時䕁䅕村䩂䙁䅑䅒䉂䙁䄸兒呂䙁䅑䅁婁䅁䅁杆䅁䙁䅍䅕時䕁䅕䅕呂䙁䄸兒呂䙁䅑䅁慁䅁䅁䅋䅁䙁䅍䅕時䕁䅣杕偂䙁䅍睕時䕁䄰兑卂䕁䅣兓佂䙁䄸兒呂䙁䅑䅁坁䅁䅁䅍䅁䙁䅍䅕時䕁䅣杕偂䙁䅍睕時䕁䄰兑卂䕁䅣兓佂䙁䄸杔噂䕁䄰睘䙂䙁䅍䅖䅁䉁䅧䅁楁䅁䅁睕兂䙁䄸䅔䉂䙁䅍䅖呂䕁䅅䅔䙂䙁䅁杕䩂䕁䅍兒䅁䅁䅉䅁慁䅁䅁睕兂䙁䄸兔䉂䙁䅉睓䙂䙁䅑睑䉂䙁䅁䅁䭁䅁䅁杈䅁䙁䅍䅕時䙁䅁杕䩂䕁䅍兒時䕁䅍䅔偂䙁䅍兒䅁䙁䄸䅁坁䅁䅁睕兂䙁䄸杕䙂䙁䅙睘䙂䙁䅍䅖䅁䉁䅉䅁捁䅁䅁睕兂䙁䄸䅖偂䙁䅑兑䵂䙁䄸䅒䙂䕁䅉䅖䅁䉁䅁䅁杁䅁䅁睕兂䙁䄸䅖偂䙁䅑兑䵂䙁䄸兒剂䙁䅕兓啂䙁䅫䅁佁䅁䅁䅋䅁䙁䅍䅕時䙁䅑杕䉂䕁䅑兓佂䕁䅣睘䑂䙁䅕杕卂䕁䅕杔䑂䙁䅫䅁䥁䅁䅁杍䅁䙁䅍睙潂䝁䄴党灂䝁䅑党祂䍁䅁杔桂䡁䅑兡療䝁䄴兙獂䍁䅷䅉䩂䝁䄴睙畁䅁䅁䅊䅁䍁䄴䅁啂䕁䅙兓杁䕁䅫杢あ䝁䅕杣畂䝁䅅䅤灂䝁䄸杢桂䝁䅷䅉䩂䝁䄴睙畁䅁䅁允䅁䉁䅉䅁啂䙁䅍䅗㙁䙁䅑杒䩂䕁䅫䅁敁䅁䅁䅃䅁䙁䅕睕䕂䅁䅁杍䅁䑁䅉䅁塂䝁䅕杣畂䝁䅕杣杁䕁䅕杢あ䝁䅕杣睂䡁䅉兡穂䝁䅕督獁䍁䅁兓畂䝁䅍杌䅁䍁䅯䅁啁䅁䅁䅗兂䕁䄸䅌杁䕁䅫杢橂䍁䄴䅁流䅁䅁杄䅁䝁䅍入祁䑁䅁杍ㅁ䅁䅁䅙䅁䅁䄴䅁䩂䙁䅅睘卂䕁䅕杖䅁䝁䅉䅁䥁䅁䅁䅔啂䕁䄰䅁橂䅁䅁䅆䅁䙁䅍䅕時䕁䅕村䩂䙁䅑䅒䉂䅁䅁䅚䅁䉁䅉䅁啂䙁䅍䅗㙁䕁䄸䅖䙂䙁䅧䅁求䅁䅁䅌䅁䕁䄸䅣求䝁䄴䅉啂䝁䅕䅥あ䍁䅁睑療䡁䅉䅣療䡁䅉兙あ䝁䅫睢畂䅁䅁杚䅁䑁䅁䅁偂䡁䅁䅤灂䝁䄸杢穂䑁䅯睑ㅂ䡁䅉杣㥁䕁䅍兑䕂䍁䅷䅉佂䕁䅅児瑁䍁䄰䅁湂䅁䅁䅔䅁䕁䄸䅣あ䝁䅫睢畂䡁䅍杏䑂䡁䅕杣祂䑁䄰睑䉂䕁䅑䅌杁䕁䄰兙湂䑁䄰兔灂䝁䅷䅢灂䝁䄸杢穂䍁䅷䅉佂䕁䅅児瑁䍁䄰䅁潂䅁䅁杈䅁䅁杷允䅁䅁䅑䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䅁䅧䅁䭁䑁䅕䅁䉁䅁䅁允䅁䅁䅯元䅁䅁杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䉁䅯䅁䭁䉁䅕䅁䙁䅁䅁䅁杄畨䅚权湂䅁䅁允䅁䅁䅅䅁䙁䉁䅍㉷灬䈴䅚䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯权䅁䅁䅕䅁䅁佁䝃欵䭁䝁䅧䅁䉁䅁䅁允䅁䅁䅕䕈㡺䝵獏啶䵁䅉䅅䅁䙁䅁䅁睁䵁䅁䅁权求䅁䅁权䵁䅁䅁兂䅁䅁䅁䤴浢䅑䅯䅡䅁䅁䅅䅁䉁䅁䅁兂婂⭉楬睬丳䅑杷允䅁䅁䅕䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䙁䄸䅁䙁䅁䅁䅁杄畨䅚权湂䅁䅁允䅁䅁䅅䅁䙁䥁牘払敧周䄵䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯䅈䅁䅁䅯兆䅁䅁䅕䅁䅁佁䝃欵䭁䝁䅣䅁䉁䅁䅁允䅁䅁䅕㝑慲捡硂䕇䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权婁䅁䅁权啁䅁䅁兂䅁䅁䅁䤴浢䅑䅯䅡䅁䅁䅅䅁䉁䅁䅁兂穃㑄㈸の橵䅑杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䝁䅉䅁䭁䝁䅍䅁䙁䅁䅁䅁杄畨䅚权潂䅁䅁允䅁䅁䅅䅁䙁偁潣塤坣牒䅸䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯杅䅁䅁䅯䅆䅁䅁䅕䅁䅁佁䝃欵䭁䝁䅧䅁䉁䅁䅁允䅁䅁䅕慘き祘偅䕶䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权婁䅁䅁权噁䅁䅁兂䅁䅁䅁䤴浢䅑䅯䅡䅁䅁䅅䅁䉁䅁䅁兂䙃畇䅘丵橥䅑杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䉁䅉䅁䭁䉁䅕䅁䙁䅁䅁䅁杄畨䅚权潂䅁䅁允䅁䅁䅅䅁䙁偁㑳扂浴爫䅴䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯杅䅁䅁䅯兙䅁䅁䅕䅁䅁佁䝃欵䭁䝁䅧䅁䉁䅁䅁允䅁䅁䅕決共婧兊䕶䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权歂䅁䅁权橂䅁䅁兂䅁䅁䅁䤴浢䅑䅯䅡䅁䅁䅅䅁䉁䅁䅁兂䱃漱⭓㕋杋䅑杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䉁䅙䅁䭁䉁䅑䅁䙁䅁䅁䅁杄畨䅚权ㅁ䅁䅁允䅁䅁䅅䅁䭁䑁䅙䅁䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权慁䅁䅁权啁䅁䅁兂䅁䅁䅁䤴浢䅑䅯睚䅁䅁䅅䅁䉁䅁䅁兂䡄䙬据㕷噯䅑杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䉁䅫䅁䭁䝁䅅䅁䙁䅁䅁䅁杄畨䅚权潂䅁䅁允䅁䅁䅅䅁䙁䍁䕩㑱㔫慳䅒䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯杆䅁䅁䅯兙䅁䅁䅕䅁䅁佁䝃欵䭁䑁䅕䅁䉁䅁䅁允䅁䅁䅯李䅁䅁杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䉁䅯䅁䭁䝁䅅䅁䙁䅁䅁䅁杄畨䅚权湂䅁䅁允䅁䅁䅅䅁䙁䡁愴㍬䱑桍䅬䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯兄䅁䅁䅕䅁䅁佁䝃欵䭁䑁䅕䅁䉁䅁䅁允䅁䅁䅕呋䕇坈㥏ぅ䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权捁䅁䅁权啁䅁䅁兂䅁䅁䅁䤴浢䅑䅯睚䅁䅁䅅䅁䉁䅁䅁兂慃坵ㅈ䵴呉䅑杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䉁䅧䅁䭁䝁䅅䅁䙁䅁䅁䅁杄畨䅚权ㅁ䅁䅁允䅁䅁䅅䅁䭁䑁䅙䅁䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权摂䅁䅁权偁䅁䅁兂䅁䅁䅁䤴浢䅑䅯䅡䅁䅁䅅䅁䉁䅁䅁兂湂焳㙊䭵ㅱ䅑杷允䅁䅁䅕䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䅁䅉䅁䙁䅁䅁䅁杄畨䅚权䱂䅁䅁允䅁䅁䅅䅁䙁䥁牘払敧周䄵䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯䅈䅁䅁䅯兙䅁䅁䅕䅁䅁佁䝃欵䭁䝁䅣䅁䉁䅁䅁允䅁䅁䅯李䅁䅁杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䙁䄴䅁䭁䅁䄸䅁䙁䅁䅁䅁杄畨䅚权潂䅁䅁允䅁䅁䅅䅁䙁䩁牎灪楷捱䅆䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯充䅁䅁䅯睄䅁䅁䅕䅁䅁佁䝃欵䭁䝁䅧䅁䉁䅁䅁允䅁䅁䅕癶剎㡚奰ね䵁䅉䅅䅁䝁䅁䅁睁䵁䅁䅁权求䅁䅁权坁䅁䅁权噁䅁䅁兂䅁䅁䅁䤴浢䅑䅯兎䅁䅁䅅䅁䉁䅁䅁权㉁䅁䅁䍄䉁䅁䅁杂䅁䅁䅍䅄䅁䅁䅯党䅁䅁䅯䅇䅁䅁䅯䅆䅁䅁䅕䅁䅁佁䝃欵䭁䑁䅕䅁䉁䅁䅁允䅁䅁䅯李䅁䅁杷允䅁䅁䅙䅁䑁䅁䅷䅁䭁䝁䅕䅁䭁䉁䅧䅁䭁䉁䅕䅁䙁䅁䅁䅁杄畨䅚权ㅁ䅁䅁允䅁䅁䅅䅁䭁䑁䅙䅁䵁䅉䅅䅁䑁䅁䅁睁䵁䅁䅁权求䅁䅁权䅁䅁䅁允䅁䅁䅅䅁䭁䝁䅙䅁㵁</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="mmm\.\ d\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0\x_);\(0.0\x\);&quot;-- &quot;"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\);&quot;-- &quot;"/>
@@ -1500,6 +1491,7 @@
     <numFmt numFmtId="170" formatCode="#,##0.0%_);\(#,##0.0%\);&quot;--&quot;"/>
     <numFmt numFmtId="171" formatCode="#,##0_);\(#,##0\);&quot;--&quot;"/>
     <numFmt numFmtId="172" formatCode="#,##0.0_);\(#,##0.0\);&quot;--&quot;"/>
+    <numFmt numFmtId="180" formatCode="#,##0.0\x_);\(#,##0.0\x\);&quot;--&quot;"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -1777,7 +1769,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2014,6 +2006,22 @@
     <xf numFmtId="165" fontId="3" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="13" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="7" fillId="5" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="7" fillId="5" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="7" fillId="5" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2022,7 +2030,27 @@
     <cellStyle name="Normal 2 3" xfId="4" xr:uid="{1DC0D5DA-9B95-4ABB-BD56-633985D4BCF5}"/>
     <cellStyle name="Note" xfId="1" builtinId="10"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="173" formatCode="\C&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     </dxf>
@@ -2346,7 +2374,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2370,22 +2398,22 @@
     <col min="10" max="10" width="11.42578125" style="2" customWidth="1" collapsed="1"/>
     <col min="11" max="12" width="11.140625" style="2" customWidth="1"/>
     <col min="13" max="21" width="11.42578125" style="2" customWidth="1"/>
-    <col min="22" max="38" width="11.42578125" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="39" max="39" width="65.7109375" style="2" customWidth="1" collapsed="1"/>
-    <col min="40" max="40" width="2.7109375" style="2" customWidth="1"/>
-    <col min="41" max="44" width="9.5703125" style="2"/>
-    <col min="45" max="45" width="1.5703125" style="2" customWidth="1"/>
-    <col min="46" max="49" width="9.5703125" style="2"/>
-    <col min="50" max="50" width="1.5703125" style="2" customWidth="1"/>
-    <col min="51" max="53" width="9.5703125" style="2"/>
-    <col min="54" max="54" width="1.5703125" style="2" customWidth="1"/>
-    <col min="55" max="57" width="9.5703125" style="2"/>
-    <col min="58" max="58" width="1.5703125" style="2" customWidth="1"/>
-    <col min="59" max="64" width="9.5703125" style="2"/>
-    <col min="65" max="65" width="1.5703125" style="2" customWidth="1"/>
-    <col min="66" max="68" width="9.5703125" style="2" customWidth="1"/>
-    <col min="69" max="69" width="1.5703125" style="2" customWidth="1"/>
-    <col min="70" max="72" width="9.5703125" style="2" customWidth="1"/>
+    <col min="22" max="37" width="11.42578125" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="38" max="38" width="65.7109375" style="2" customWidth="1" collapsed="1"/>
+    <col min="39" max="39" width="2.7109375" style="2" customWidth="1"/>
+    <col min="40" max="43" width="9.5703125" style="2"/>
+    <col min="44" max="44" width="1.5703125" style="2" customWidth="1"/>
+    <col min="45" max="48" width="9.5703125" style="2"/>
+    <col min="49" max="49" width="1.5703125" style="2" customWidth="1"/>
+    <col min="50" max="52" width="9.5703125" style="2"/>
+    <col min="53" max="53" width="1.5703125" style="2" customWidth="1"/>
+    <col min="54" max="56" width="9.5703125" style="2"/>
+    <col min="57" max="57" width="1.5703125" style="2" customWidth="1"/>
+    <col min="58" max="63" width="9.5703125" style="2"/>
+    <col min="64" max="64" width="1.5703125" style="2" customWidth="1"/>
+    <col min="65" max="67" width="9.5703125" style="2" customWidth="1"/>
+    <col min="68" max="68" width="1.5703125" style="2" customWidth="1"/>
+    <col min="69" max="72" width="9.5703125" style="2" customWidth="1"/>
     <col min="73" max="73" width="1.5703125" style="2" customWidth="1"/>
     <col min="74" max="76" width="9.5703125" style="2" customWidth="1"/>
     <col min="77" max="77" width="1.5703125" style="2" customWidth="1"/>
@@ -2398,11 +2426,11 @@
     <row r="1" spans="2:84" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:84" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="E2" s="10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F2" s="77">
         <f ca="1">TODAY()-1</f>
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="K2" s="10"/>
       <c r="L2" s="79" t="s">
@@ -2423,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="78" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G3" s="38"/>
       <c r="K3" s="10" t="s">
@@ -2454,14 +2482,13 @@
         <v>0</v>
       </c>
       <c r="AL3" s="69"/>
-      <c r="AM3" s="69"/>
     </row>
     <row r="4" spans="2:84" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="E4" s="10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F4" s="73" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>4</v>
@@ -2490,10 +2517,11 @@
       <c r="S4" s="81">
         <v>50</v>
       </c>
+      <c r="AC4" s="82"/>
     </row>
     <row r="5" spans="2:84" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="BR5" s="39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="BS5" s="64"/>
       <c r="BT5" s="64"/>
@@ -2502,7 +2530,7 @@
       <c r="BW5" s="64"/>
       <c r="BX5" s="64"/>
       <c r="BZ5" s="39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CA5" s="39"/>
       <c r="CB5" s="39"/>
@@ -2546,7 +2574,7 @@
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
       <c r="T6" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U6" s="31"/>
       <c r="V6" s="6" t="s">
@@ -2555,91 +2583,87 @@
       <c r="W6" s="6"/>
       <c r="X6" s="6"/>
       <c r="Y6" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z6" s="6"/>
       <c r="AA6" s="6"/>
       <c r="AB6" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC6" s="6"/>
       <c r="AD6" s="6"/>
-      <c r="AE6" s="6" t="s">
+      <c r="AE6" s="6"/>
+      <c r="AF6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AF6" s="6"/>
       <c r="AG6" s="6"/>
-      <c r="AH6" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="AH6" s="6"/>
       <c r="AI6" s="6"/>
       <c r="AJ6" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK6" s="6"/>
-      <c r="AL6" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="AM6" s="32"/>
-      <c r="AO6" s="6" t="s">
+      <c r="AL6" s="32"/>
+      <c r="AN6" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="AO6" s="6"/>
       <c r="AP6" s="6"/>
       <c r="AQ6" s="6"/>
-      <c r="AR6" s="6"/>
-      <c r="AT6" s="6" t="s">
+      <c r="AS6" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="AT6" s="6"/>
       <c r="AU6" s="6"/>
       <c r="AV6" s="6"/>
-      <c r="AW6" s="6"/>
-      <c r="AY6" s="6" t="s">
+      <c r="AX6" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="AY6" s="6"/>
       <c r="AZ6" s="6"/>
-      <c r="BA6" s="6"/>
-      <c r="BC6" s="6" t="s">
-        <v>48</v>
-      </c>
+      <c r="BB6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="BC6" s="6"/>
       <c r="BD6" s="6"/>
-      <c r="BE6" s="6"/>
+      <c r="BF6" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="BG6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="BH6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="BI6" s="5"/>
-      <c r="BJ6" s="5" t="s">
-        <v>33</v>
-      </c>
+      <c r="BH6" s="5"/>
+      <c r="BI6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="BJ6" s="5"/>
       <c r="BK6" s="5"/>
-      <c r="BL6" s="5"/>
-      <c r="BN6" s="43" t="s">
-        <v>38</v>
-      </c>
+      <c r="BM6" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="BN6" s="6"/>
       <c r="BO6" s="6"/>
-      <c r="BP6" s="6"/>
-      <c r="BR6" s="43" t="s">
-        <v>35</v>
-      </c>
+      <c r="BQ6" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="BR6" s="43"/>
       <c r="BS6" s="6"/>
       <c r="BT6" s="6"/>
       <c r="BU6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BV6" s="43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="BW6" s="6"/>
       <c r="BX6" s="6"/>
       <c r="BZ6" s="43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="CA6" s="6"/>
       <c r="CB6" s="6"/>
       <c r="CD6" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CE6" s="6"/>
       <c r="CF6" s="6"/>
@@ -2652,7 +2676,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="8" t="str">
         <f ca="1">CONCATENATE("(",TEXT($F$2,"dd-mmm-yy"),")")</f>
-        <v>(21-Apr-26)</v>
+        <v>(23-Apr-26)</v>
       </c>
       <c r="H7" s="8" t="str">
         <f>"("&amp;F3&amp;")"</f>
@@ -2668,22 +2692,22 @@
         <v>19</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="M7" s="5" t="str">
-        <f>AP7&amp;"A"</f>
+        <f>AO7&amp;"A"</f>
         <v>CY2025A</v>
       </c>
       <c r="N7" s="5" t="str">
+        <f>AP7&amp;"E"</f>
+        <v>CY2026E</v>
+      </c>
+      <c r="O7" s="5" t="str">
         <f>AQ7&amp;"E"</f>
-        <v>CY2026E</v>
-      </c>
-      <c r="O7" s="5" t="str">
-        <f>AR7&amp;"E"</f>
         <v>CY2027E</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="Q7" s="5" t="str">
         <f>$M$7</f>
@@ -2729,180 +2753,180 @@
         <f>$O$7</f>
         <v>CY2027E</v>
       </c>
-      <c r="AB7" s="5" t="str">
+      <c r="AB7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC7" s="5" t="str">
         <f>$M$7</f>
         <v>CY2025A</v>
       </c>
-      <c r="AC7" s="5" t="str">
+      <c r="AD7" s="5" t="str">
         <f>$N$7</f>
         <v>CY2026E</v>
       </c>
-      <c r="AD7" s="5" t="str">
+      <c r="AE7" s="5" t="str">
         <f>$O$7</f>
         <v>CY2027E</v>
       </c>
-      <c r="AE7" s="5" t="str">
+      <c r="AF7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG7" s="5" t="str">
         <f>$M$7</f>
         <v>CY2025A</v>
       </c>
-      <c r="AF7" s="5" t="str">
+      <c r="AH7" s="5" t="str">
         <f>$N$7</f>
         <v>CY2026E</v>
       </c>
-      <c r="AG7" s="5" t="str">
+      <c r="AI7" s="5" t="str">
         <f>$O$7</f>
         <v>CY2027E</v>
       </c>
-      <c r="AH7" s="5" t="str">
+      <c r="AJ7" s="5" t="str">
         <f>$M$7</f>
         <v>CY2025A</v>
       </c>
-      <c r="AI7" s="5" t="str">
+      <c r="AK7" s="5" t="str">
         <f>$N$7</f>
         <v>CY2026E</v>
       </c>
-      <c r="AJ7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="AK7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL7" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="AM7" s="70" t="s">
-        <v>53</v>
-      </c>
-      <c r="AO7" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AP7" s="5" t="str">
+      <c r="AL7" s="70" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO7" s="5" t="str">
         <f>$F$4</f>
         <v>CY2025</v>
       </c>
+      <c r="AP7" s="5" t="str">
+        <f>"CY"&amp;RIGHT(AO7,4)+1</f>
+        <v>CY2026</v>
+      </c>
       <c r="AQ7" s="5" t="str">
         <f>"CY"&amp;RIGHT(AP7,4)+1</f>
-        <v>CY2026</v>
-      </c>
-      <c r="AR7" s="5" t="str">
-        <f>"CY"&amp;RIGHT(AQ7,4)+1</f>
         <v>CY2027</v>
       </c>
-      <c r="AT7" s="5" t="s">
-        <v>52</v>
+      <c r="AS7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AT7" s="5" t="str">
+        <f>$AO$7</f>
+        <v>CY2025</v>
       </c>
       <c r="AU7" s="5" t="str">
         <f>$AP$7</f>
-        <v>CY2025</v>
+        <v>CY2026</v>
       </c>
       <c r="AV7" s="5" t="str">
         <f>$AQ$7</f>
-        <v>CY2026</v>
-      </c>
-      <c r="AW7" s="5" t="str">
-        <f>$AR$7</f>
         <v>CY2027</v>
+      </c>
+      <c r="AX7" s="5" t="str">
+        <f>$AO$7</f>
+        <v>CY2025</v>
       </c>
       <c r="AY7" s="5" t="str">
         <f>$AP$7</f>
-        <v>CY2025</v>
+        <v>CY2026</v>
       </c>
       <c r="AZ7" s="5" t="str">
         <f>$AQ$7</f>
-        <v>CY2026</v>
-      </c>
-      <c r="BA7" s="5" t="str">
-        <f>$AR$7</f>
         <v>CY2027</v>
+      </c>
+      <c r="BB7" s="5" t="str">
+        <f>$AO$7</f>
+        <v>CY2025</v>
       </c>
       <c r="BC7" s="5" t="str">
         <f>$AP$7</f>
-        <v>CY2025</v>
+        <v>CY2026</v>
       </c>
       <c r="BD7" s="5" t="str">
         <f>$AQ$7</f>
-        <v>CY2026</v>
-      </c>
-      <c r="BE7" s="5" t="str">
-        <f>$AR$7</f>
         <v>CY2027</v>
       </c>
+      <c r="BF7" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="BG7" s="5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BH7" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BI7" s="5" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="BJ7" s="5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BK7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="BL7" s="5" t="s">
         <v>20</v>
+      </c>
+      <c r="BM7" s="5" t="str">
+        <f>$AO$7</f>
+        <v>CY2025</v>
       </c>
       <c r="BN7" s="5" t="str">
         <f>$AP$7</f>
-        <v>CY2025</v>
+        <v>CY2026</v>
       </c>
       <c r="BO7" s="5" t="str">
         <f>$AQ$7</f>
+        <v>CY2027</v>
+      </c>
+      <c r="BQ7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="BR7" s="5" t="str">
+        <f>$AO$7</f>
+        <v>CY2025</v>
+      </c>
+      <c r="BS7" s="5" t="str">
+        <f>$AP$7</f>
         <v>CY2026</v>
       </c>
-      <c r="BP7" s="5" t="str">
-        <f>$AR$7</f>
+      <c r="BT7" s="5" t="str">
+        <f>$AQ$7</f>
         <v>CY2027</v>
       </c>
-      <c r="BR7" s="5" t="str">
+      <c r="BV7" s="5" t="str">
+        <f>$AO$7</f>
+        <v>CY2025</v>
+      </c>
+      <c r="BW7" s="5" t="str">
         <f>$AP$7</f>
+        <v>CY2026</v>
+      </c>
+      <c r="BX7" s="5" t="str">
+        <f>$AQ$7</f>
+        <v>CY2027</v>
+      </c>
+      <c r="BZ7" s="5" t="str">
+        <f>$AO$7</f>
         <v>CY2025</v>
       </c>
-      <c r="BS7" s="5" t="str">
+      <c r="CA7" s="5" t="str">
+        <f>$AP$7</f>
+        <v>CY2026</v>
+      </c>
+      <c r="CB7" s="5" t="str">
         <f>$AQ$7</f>
+        <v>CY2027</v>
+      </c>
+      <c r="CD7" s="5" t="str">
+        <f>$AO$7</f>
+        <v>CY2025</v>
+      </c>
+      <c r="CE7" s="5" t="str">
+        <f>$AP$7</f>
         <v>CY2026</v>
       </c>
-      <c r="BT7" s="5" t="str">
-        <f>$AR$7</f>
-        <v>CY2027</v>
-      </c>
-      <c r="BV7" s="5" t="str">
-        <f>$AP$7</f>
-        <v>CY2025</v>
-      </c>
-      <c r="BW7" s="5" t="str">
+      <c r="CF7" s="5" t="str">
         <f>$AQ$7</f>
-        <v>CY2026</v>
-      </c>
-      <c r="BX7" s="5" t="str">
-        <f>$AR$7</f>
-        <v>CY2027</v>
-      </c>
-      <c r="BZ7" s="5" t="str">
-        <f>$AP$7</f>
-        <v>CY2025</v>
-      </c>
-      <c r="CA7" s="5" t="str">
-        <f>$AQ$7</f>
-        <v>CY2026</v>
-      </c>
-      <c r="CB7" s="5" t="str">
-        <f>$AR$7</f>
-        <v>CY2027</v>
-      </c>
-      <c r="CD7" s="5" t="str">
-        <f>$AP$7</f>
-        <v>CY2025</v>
-      </c>
-      <c r="CE7" s="5" t="str">
-        <f>$AQ$7</f>
-        <v>CY2026</v>
-      </c>
-      <c r="CF7" s="5" t="str">
-        <f>$AR$7</f>
         <v>CY2027</v>
       </c>
     </row>
@@ -2956,7 +2980,7 @@
       <c r="AX8" s="1"/>
       <c r="AY8" s="1"/>
       <c r="AZ8" s="1"/>
-      <c r="BA8" s="1"/>
+      <c r="BE8" s="1"/>
       <c r="BF8" s="1"/>
       <c r="BG8" s="1"/>
       <c r="BH8" s="1"/>
@@ -2968,7 +2992,9 @@
       <c r="BN8" s="1"/>
       <c r="BO8" s="1"/>
       <c r="BP8" s="1"/>
-      <c r="BQ8" s="1"/>
+      <c r="BQ8" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="BR8" s="1"/>
       <c r="BS8" s="1"/>
       <c r="BT8" s="1"/>
@@ -2988,7 +3014,7 @@
     <row r="9" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1"/>
       <c r="D9" s="71" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3018,116 +3044,116 @@
         <v/>
       </c>
       <c r="L10" s="16" t="str">
-        <f t="shared" ref="L10:O15" si="0">IFERROR(IF(OR($K10/AO10&gt;L$4,$K10/AO10&lt;L$3),"nmf ",$K10/AO10),"n/a ")</f>
+        <f>IFERROR(IF(OR($K10/AN10&gt;L$4,$K10/AN10&lt;L$3),"nmf ",$K10/AN10),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M10" s="16" t="str">
+        <f>IFERROR(IF(OR($K10/AO10&gt;M$4,$K10/AO10&lt;M$3),"nmf ",$K10/AO10),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="N10" s="16" t="str">
+        <f>IFERROR(IF(OR($K10/AP10&gt;N$4,$K10/AP10&lt;N$3),"nmf ",$K10/AP10),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O10" s="16" t="str">
+        <f>IFERROR(IF(OR($K10/AQ10&gt;O$4,$K10/AQ10&lt;O$3),"nmf ",$K10/AQ10),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P10" s="16" t="str">
+        <f>IFERROR(IF(OR($K10/AS10&gt;P$4,$K10/AS10&lt;P$3),"nmf ",$K10/AS10),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q10" s="16" t="str">
+        <f>IFERROR(IF(OR($K10/AT10&gt;Q$4,$K10/AT10&lt;Q$3),"nmf ",$K10/AT10),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R10" s="16" t="str">
+        <f>IFERROR(IF(OR($K10/AU10&gt;R$4,$K10/AU10&lt;R$3),"nmf ",$K10/AU10),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S10" s="16" t="str">
+        <f>IFERROR(IF(OR($K10/AV10&gt;S$4,$K10/AV10&lt;S$3),"nmf ",$K10/AV10),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T10" s="33" t="str">
+        <f>IFERROR((AP10/AO10)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U10" s="33" t="str">
+        <f>IFERROR((AQ10/AP10)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V10" s="16" t="str">
+        <f>IFERROR($H10/AX10,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W10" s="16" t="str">
+        <f>IFERROR($H10/AY10,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X10" s="16" t="str">
+        <f>IFERROR($H10/AZ10,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y10" s="16" t="str">
+        <f>IFERROR($H10/BB10,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z10" s="16" t="str">
+        <f>IFERROR($H10/BC10,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA10" s="16" t="str">
+        <f>IFERROR($H10/BD10,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB10" s="33" t="str">
+        <f>IFERROR(IF(BQ10="--","n/a ",BQ10),"n/a ")</f>
+        <v/>
+      </c>
+      <c r="AC10" s="33" t="str">
+        <f>IFERROR(IF(BR10="--","n/a ",BR10),"n/a ")</f>
+        <v/>
+      </c>
+      <c r="AD10" s="33" t="str">
+        <f t="shared" ref="AD10:AE10" si="0">IFERROR(IF(BS10="--","n/a ",BS10),"n/a ")</f>
+        <v/>
+      </c>
+      <c r="AE10" s="33" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="N10" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="O10" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="P10" s="16" t="str">
-        <f t="shared" ref="P10:S15" si="1">IFERROR(IF(OR($K10/AT10&gt;P$4,$K10/AT10&lt;P$3),"nmf ",$K10/AT10),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Q10" s="16" t="str">
+        <v/>
+      </c>
+      <c r="AF10" s="33" t="str">
+        <f>IFERROR((AS10/AN10),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG10" s="33" t="str">
+        <f>IFERROR((AT10/AO10),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH10" s="33" t="str">
+        <f t="shared" ref="AH10:AI10" si="1">IFERROR((AU10/AP10),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI10" s="33" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="R10" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="S10" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T10" s="33" t="str">
-        <f>IFERROR((AQ10/AP10)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="U10" s="33" t="str">
-        <f>IFERROR((AR10/AQ10)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="V10" s="16" t="str">
-        <f>IFERROR(IF(OR($H10/AY10&gt;#REF!,$H10/AY10&lt;#REF!),"nmf ",$H10/AY10),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="W10" s="16" t="str">
-        <f>IFERROR(IF(OR($H10/AZ10&gt;#REF!,$H10/AZ10&lt;#REF!),"nmf ",$H10/AZ10),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="X10" s="16" t="str">
-        <f>IFERROR(IF(OR($H10/BA10&gt;#REF!,$H10/BA10&lt;#REF!),"nmf ",$H10/BA10),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Y10" s="16" t="str">
-        <f>IFERROR(IF(OR($H10/BC10&gt;#REF!,$H10/BC10&lt;#REF!),"nmf ",$H10/BC10),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Z10" s="16" t="str">
-        <f>IFERROR(IF(OR($H10/BD10&gt;#REF!,$H10/BD10&lt;#REF!),"nmf ",$H10/BD10),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AA10" s="16" t="str">
-        <f>IFERROR(IF(OR($H10/BE10&gt;#REF!,$H10/BE10&lt;#REF!),"nmf ",$H10/BE10),"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AB10" s="33" t="str">
-        <f t="shared" ref="AB10:AF15" si="2">IFERROR((AS10/AR10)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AC10" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AD10" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AE10" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AF10" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AG10" s="33" t="str">
-        <f>IFERROR((BM10/AW10)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AH10" s="33" t="str">
-        <f t="shared" ref="AH10:AL15" si="3">IFERROR((BN10/BM10)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AI10" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ10" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK10" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL10" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM10" s="72"/>
+      <c r="AJ10" s="83" t="str">
+        <f>IFERROR((BJ10/AT10),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK10" s="83" t="str">
+        <f>IFERROR((BJ10/AU10),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL10" s="72"/>
+      <c r="AN10" s="20" t="str" cm="1">
+        <f t="array" ref="AN10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO10" s="20" t="str" cm="1">
-        <f t="array" ref="AO10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP10" s="20" t="str" cm="1">
@@ -3138,12 +3164,12 @@
         <f t="array" ref="AQ10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR10" s="20" t="str" cm="1">
-        <f t="array" ref="AR10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS10" s="20" t="str" cm="1">
+        <f t="array" ref="AS10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT10" s="20" t="str" cm="1">
-        <f t="array" ref="AT10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU10" s="20" t="str" cm="1">
@@ -3154,8 +3180,8 @@
         <f t="array" ref="AV10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW10" s="20" t="str" cm="1">
-        <f t="array" ref="AW10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX10" s="13" t="str" cm="1">
+        <f t="array" ref="AX10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY10" s="13" t="str" cm="1">
@@ -3166,8 +3192,8 @@
         <f t="array" ref="AZ10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA10" s="13" t="str" cm="1">
-        <f t="array" ref="BA10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB10" s="13" t="str" cm="1">
+        <f t="array" ref="BB10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC10" s="13" t="str" cm="1">
@@ -3178,45 +3204,45 @@
         <f t="array" ref="BD10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE10" s="13" t="str" cm="1">
-        <f t="array" ref="BE10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG10" s="65" t="str" cm="1">
-        <f t="array" ref="BG10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF10" s="65" t="str" cm="1">
+        <f t="array" ref="BF10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG10" s="19" t="str" cm="1">
+        <f t="array" ref="BG10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH10" s="19" t="str" cm="1">
-        <f t="array" ref="BH10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI10" s="19" t="str" cm="1">
-        <f t="array" ref="BI10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ10" s="19" t="str" cm="1">
-        <f t="array" ref="BJ10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK10" s="37" t="e">
-        <f>+BI10-BJ10</f>
+        <f t="array" ref="BI10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ10" s="37" t="e">
+        <f>+BH10-BI10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BL10" s="19" t="str" cm="1">
-        <f t="array" ref="BL10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK10" s="19" t="str" cm="1">
+        <f t="array" ref="BK10">IF($B10="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM10" s="20" t="str">
+        <f>IFERROR($AO10*$BR10,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN10" s="20" t="str">
-        <f>IFERROR($AP10*$BR10,"n/a")</f>
+        <f>IFERROR($AP10*BS10,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO10" s="20" t="str">
-        <f>IFERROR($AQ10*BS10,"n/a")</f>
+        <f>IFERROR($AQ10*$BT10,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP10" s="20" t="str">
-        <f>IFERROR($AR10*$BT10,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ10" s="44" t="str">
+        <f>IF($B10="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR10" s="44" t="str">
         <f>IF($B10="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B10,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -3244,27 +3270,27 @@
         <v/>
       </c>
       <c r="BZ10" s="62" t="str">
-        <f t="shared" ref="BZ10:CB15" si="4">IFERROR(IF(CD10/AP10&lt;0,"nmf ",CD10/AP10),"n/a ")</f>
+        <f>IFERROR(IF(CD10/AO10&lt;0,"nmf ",CD10/AO10),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA10" s="62" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(IF(CE10/AP10&lt;0,"nmf ",CE10/AP10),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB10" s="62" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(IF(CF10/AQ10&lt;0,"nmf ",CF10/AQ10),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD10" s="68" t="str">
-        <f t="shared" ref="CD10:CF15" si="5">IFERROR(BR10*AP10,"--")</f>
+        <f>IFERROR(BR10*AO10,"--")</f>
         <v>--</v>
       </c>
       <c r="CE10" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f>IFERROR(BS10*AP10,"--")</f>
         <v>--</v>
       </c>
       <c r="CF10" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f>IFERROR(BT10*AQ10,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -3295,116 +3321,116 @@
         <v/>
       </c>
       <c r="L11" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(OR($K11/AN11&gt;L$4,$K11/AN11&lt;L$3),"nmf ",$K11/AN11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M11" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(OR($K11/AO11&gt;M$4,$K11/AO11&lt;M$3),"nmf ",$K11/AO11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N11" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(OR($K11/AP11&gt;N$4,$K11/AP11&lt;N$3),"nmf ",$K11/AP11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O11" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(OR($K11/AQ11&gt;O$4,$K11/AQ11&lt;O$3),"nmf ",$K11/AQ11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P11" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(IF(OR($K11/AS11&gt;P$4,$K11/AS11&lt;P$3),"nmf ",$K11/AS11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q11" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(IF(OR($K11/AT11&gt;Q$4,$K11/AT11&lt;Q$3),"nmf ",$K11/AT11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R11" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(IF(OR($K11/AU11&gt;R$4,$K11/AU11&lt;R$3),"nmf ",$K11/AU11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S11" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(IF(OR($K11/AV11&gt;S$4,$K11/AV11&lt;S$3),"nmf ",$K11/AV11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T11" s="33" t="str">
-        <f t="shared" ref="T11" si="6">IFERROR((AQ11/AP11)-1,"n/a ")</f>
+        <f t="shared" ref="T11" si="2">IFERROR((AP11/AO11)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U11" s="33" t="str">
-        <f t="shared" ref="U11" si="7">IFERROR((AR11/AQ11)-1,"n/a ")</f>
+        <f t="shared" ref="U11" si="3">IFERROR((AQ11/AP11)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V11" s="16" t="str">
-        <f>IFERROR(IF(OR($H11/AY11&gt;#REF!,$H11/AY11&lt;#REF!),"nmf ",$H11/AY11),"n/a ")</f>
+        <f>IFERROR($H11/AX11,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W11" s="16" t="str">
-        <f>IFERROR(IF(OR($H11/AZ11&gt;#REF!,$H11/AZ11&lt;#REF!),"nmf ",$H11/AZ11),"n/a ")</f>
+        <f>IFERROR($H11/AY11,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X11" s="16" t="str">
-        <f>IFERROR(IF(OR($H11/BA11&gt;#REF!,$H11/BA11&lt;#REF!),"nmf ",$H11/BA11),"n/a ")</f>
+        <f>IFERROR($H11/AZ11,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y11" s="16" t="str">
-        <f>IFERROR(IF(OR($H11/BC11&gt;#REF!,$H11/BC11&lt;#REF!),"nmf ",$H11/BC11),"n/a ")</f>
+        <f>IFERROR($H11/BB11,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z11" s="16" t="str">
-        <f>IFERROR(IF(OR($H11/BD11&gt;#REF!,$H11/BD11&lt;#REF!),"nmf ",$H11/BD11),"n/a ")</f>
+        <f>IFERROR($H11/BC11,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA11" s="16" t="str">
-        <f>IFERROR(IF(OR($H11/BE11&gt;#REF!,$H11/BE11&lt;#REF!),"nmf ",$H11/BE11),"n/a ")</f>
+        <f>IFERROR($H11/BD11,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB11" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" ref="AB11:AC15" si="4">IFERROR(IF(BQ11="--","n/a ",BQ11),"n/a ")</f>
+        <v/>
       </c>
       <c r="AC11" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="AD11" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" ref="AD11:AD15" si="5">IFERROR(IF(BS11="--","n/a ",BS11),"n/a ")</f>
+        <v/>
       </c>
       <c r="AE11" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" ref="AE11:AE15" si="6">IFERROR(IF(BT11="--","n/a ",BT11),"n/a ")</f>
+        <v/>
       </c>
       <c r="AF11" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AF11:AG15" si="7">IFERROR((AS11/AN11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG11" s="33" t="str">
-        <f>IFERROR((BM11/AW11)-1,"n/a ")</f>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH11" s="33" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="AH11:AH15" si="8">IFERROR((AU11/AP11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI11" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ11" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK11" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL11" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM11" s="72"/>
+        <f t="shared" ref="AI11:AI15" si="9">IFERROR((AV11/AQ11),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ11" s="83" t="str">
+        <f t="shared" ref="AJ11:AJ15" si="10">IFERROR((BJ11/AT11),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK11" s="83" t="str">
+        <f t="shared" ref="AK11:AK15" si="11">IFERROR((BJ11/AU11),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL11" s="72"/>
+      <c r="AN11" s="20" t="str" cm="1">
+        <f t="array" ref="AN11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO11" s="20" t="str" cm="1">
-        <f t="array" ref="AO11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP11" s="20" t="str" cm="1">
@@ -3415,12 +3441,12 @@
         <f t="array" ref="AQ11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR11" s="20" t="str" cm="1">
-        <f t="array" ref="AR11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS11" s="20" t="str" cm="1">
+        <f t="array" ref="AS11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT11" s="20" t="str" cm="1">
-        <f t="array" ref="AT11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU11" s="20" t="str" cm="1">
@@ -3431,8 +3457,8 @@
         <f t="array" ref="AV11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW11" s="20" t="str" cm="1">
-        <f t="array" ref="AW11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX11" s="13" t="str" cm="1">
+        <f t="array" ref="AX11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY11" s="13" t="str" cm="1">
@@ -3443,8 +3469,8 @@
         <f t="array" ref="AZ11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA11" s="13" t="str" cm="1">
-        <f t="array" ref="BA11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB11" s="13" t="str" cm="1">
+        <f t="array" ref="BB11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC11" s="13" t="str" cm="1">
@@ -3455,45 +3481,45 @@
         <f t="array" ref="BD11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE11" s="13" t="str" cm="1">
-        <f t="array" ref="BE11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG11" s="65" t="str" cm="1">
-        <f t="array" ref="BG11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF11" s="65" t="str" cm="1">
+        <f t="array" ref="BF11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG11" s="19" t="str" cm="1">
+        <f t="array" ref="BG11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH11" s="19" t="str" cm="1">
-        <f t="array" ref="BH11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI11" s="19" t="str" cm="1">
-        <f t="array" ref="BI11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ11" s="19" t="str" cm="1">
-        <f t="array" ref="BJ11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK11" s="37" t="e">
-        <f t="shared" ref="BK11" si="8">+BI11-BJ11</f>
+        <f t="array" ref="BI11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ11" s="37" t="e">
+        <f t="shared" ref="BJ11" si="12">+BH11-BI11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BL11" s="19" t="str" cm="1">
-        <f t="array" ref="BL11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK11" s="19" t="str" cm="1">
+        <f t="array" ref="BK11">IF($B11="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM11" s="20" t="str">
+        <f>IFERROR($AO11*$BR11,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN11" s="20" t="str">
-        <f>IFERROR($AP11*$BR11,"n/a")</f>
+        <f>IFERROR($AP11*BS11,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO11" s="20" t="str">
-        <f t="shared" ref="BO11" si="9">IFERROR($AQ11*BS11,"n/a")</f>
+        <f>IFERROR($AQ11*$BT11,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP11" s="20" t="str">
-        <f>IFERROR($AR11*$BT11,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ11" s="44" t="str">
+        <f>IF($B11="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR11" s="44" t="str">
         <f>IF($B11="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B11,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -3521,27 +3547,27 @@
         <v/>
       </c>
       <c r="BZ11" s="62" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(IF(CD11/AO11&lt;0,"nmf ",CD11/AO11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA11" s="62" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(IF(CE11/AP11&lt;0,"nmf ",CE11/AP11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB11" s="62" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(IF(CF11/AQ11&lt;0,"nmf ",CF11/AQ11),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD11" s="68" t="str">
-        <f t="shared" si="5"/>
+        <f>IFERROR(BR11*AO11,"--")</f>
         <v>--</v>
       </c>
       <c r="CE11" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f>IFERROR(BS11*AP11,"--")</f>
         <v>--</v>
       </c>
       <c r="CF11" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f>IFERROR(BT11*AQ11,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -3572,116 +3598,116 @@
         <v/>
       </c>
       <c r="L12" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(OR($K12/AN12&gt;L$4,$K12/AN12&lt;L$3),"nmf ",$K12/AN12),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M12" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(OR($K12/AO12&gt;M$4,$K12/AO12&lt;M$3),"nmf ",$K12/AO12),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N12" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(OR($K12/AP12&gt;N$4,$K12/AP12&lt;N$3),"nmf ",$K12/AP12),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O12" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(OR($K12/AQ12&gt;O$4,$K12/AQ12&lt;O$3),"nmf ",$K12/AQ12),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P12" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(IF(OR($K12/AS12&gt;P$4,$K12/AS12&lt;P$3),"nmf ",$K12/AS12),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q12" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(IF(OR($K12/AT12&gt;Q$4,$K12/AT12&lt;Q$3),"nmf ",$K12/AT12),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R12" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(IF(OR($K12/AU12&gt;R$4,$K12/AU12&lt;R$3),"nmf ",$K12/AU12),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S12" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(IF(OR($K12/AV12&gt;S$4,$K12/AV12&lt;S$3),"nmf ",$K12/AV12),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T12" s="33" t="str">
-        <f t="shared" ref="T12" si="10">IFERROR((AQ12/AP12)-1,"n/a ")</f>
+        <f t="shared" ref="T12" si="13">IFERROR((AP12/AO12)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U12" s="33" t="str">
-        <f t="shared" ref="U12" si="11">IFERROR((AR12/AQ12)-1,"n/a ")</f>
+        <f t="shared" ref="U12" si="14">IFERROR((AQ12/AP12)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V12" s="16" t="str">
-        <f>IFERROR(IF(OR($H12/AY12&gt;#REF!,$H12/AY12&lt;#REF!),"nmf ",$H12/AY12),"n/a ")</f>
+        <f>IFERROR($H12/AX12,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W12" s="16" t="str">
-        <f>IFERROR(IF(OR($H12/AZ12&gt;#REF!,$H12/AZ12&lt;#REF!),"nmf ",$H12/AZ12),"n/a ")</f>
+        <f>IFERROR($H12/AY12,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X12" s="16" t="str">
-        <f>IFERROR(IF(OR($H12/BA12&gt;#REF!,$H12/BA12&lt;#REF!),"nmf ",$H12/BA12),"n/a ")</f>
+        <f>IFERROR($H12/AZ12,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y12" s="16" t="str">
-        <f>IFERROR(IF(OR($H12/BC12&gt;#REF!,$H12/BC12&lt;#REF!),"nmf ",$H12/BC12),"n/a ")</f>
+        <f>IFERROR($H12/BB12,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z12" s="16" t="str">
-        <f>IFERROR(IF(OR($H12/BD12&gt;#REF!,$H12/BD12&lt;#REF!),"nmf ",$H12/BD12),"n/a ")</f>
+        <f>IFERROR($H12/BC12,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA12" s="16" t="str">
-        <f>IFERROR(IF(OR($H12/BE12&gt;#REF!,$H12/BE12&lt;#REF!),"nmf ",$H12/BE12),"n/a ")</f>
+        <f>IFERROR($H12/BD12,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB12" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="AC12" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="AD12" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="AE12" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AF12" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG12" s="33" t="str">
-        <f>IFERROR((BM12/AW12)-1,"n/a ")</f>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH12" s="33" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI12" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ12" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK12" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL12" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM12" s="72"/>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ12" s="83" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK12" s="83" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL12" s="72"/>
+      <c r="AN12" s="20" t="str" cm="1">
+        <f t="array" ref="AN12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO12" s="20" t="str" cm="1">
-        <f t="array" ref="AO12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP12" s="20" t="str" cm="1">
@@ -3692,12 +3718,12 @@
         <f t="array" ref="AQ12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR12" s="20" t="str" cm="1">
-        <f t="array" ref="AR12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS12" s="20" t="str" cm="1">
+        <f t="array" ref="AS12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT12" s="20" t="str" cm="1">
-        <f t="array" ref="AT12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU12" s="20" t="str" cm="1">
@@ -3708,8 +3734,8 @@
         <f t="array" ref="AV12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW12" s="20" t="str" cm="1">
-        <f t="array" ref="AW12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX12" s="13" t="str" cm="1">
+        <f t="array" ref="AX12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY12" s="13" t="str" cm="1">
@@ -3720,8 +3746,8 @@
         <f t="array" ref="AZ12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA12" s="13" t="str" cm="1">
-        <f t="array" ref="BA12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB12" s="13" t="str" cm="1">
+        <f t="array" ref="BB12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC12" s="13" t="str" cm="1">
@@ -3732,45 +3758,45 @@
         <f t="array" ref="BD12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE12" s="13" t="str" cm="1">
-        <f t="array" ref="BE12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG12" s="65" t="str" cm="1">
-        <f t="array" ref="BG12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF12" s="65" t="str" cm="1">
+        <f t="array" ref="BF12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG12" s="19" t="str" cm="1">
+        <f t="array" ref="BG12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH12" s="19" t="str" cm="1">
-        <f t="array" ref="BH12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI12" s="19" t="str" cm="1">
-        <f t="array" ref="BI12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ12" s="19" t="str" cm="1">
-        <f t="array" ref="BJ12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK12" s="37" t="e">
-        <f t="shared" ref="BK12" si="12">+BI12-BJ12</f>
+        <f t="array" ref="BI12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ12" s="37" t="e">
+        <f t="shared" ref="BJ12" si="15">+BH12-BI12</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BL12" s="19" t="str" cm="1">
-        <f t="array" ref="BL12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK12" s="19" t="str" cm="1">
+        <f t="array" ref="BK12">IF($B12="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM12" s="20" t="str">
+        <f>IFERROR($AO12*$BR12,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN12" s="20" t="str">
-        <f>IFERROR($AP12*$BR12,"n/a")</f>
+        <f>IFERROR($AP12*BS12,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO12" s="20" t="str">
-        <f t="shared" ref="BO12" si="13">IFERROR($AQ12*BS12,"n/a")</f>
+        <f>IFERROR($AQ12*$BT12,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP12" s="20" t="str">
-        <f>IFERROR($AR12*$BT12,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ12" s="44" t="str">
+        <f>IF($B12="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR12" s="44" t="str">
         <f>IF($B12="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B12,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -3798,27 +3824,27 @@
         <v/>
       </c>
       <c r="BZ12" s="62" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(IF(CD12/AO12&lt;0,"nmf ",CD12/AO12),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA12" s="62" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(IF(CE12/AP12&lt;0,"nmf ",CE12/AP12),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB12" s="62" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(IF(CF12/AQ12&lt;0,"nmf ",CF12/AQ12),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD12" s="68" t="str">
-        <f t="shared" si="5"/>
+        <f>IFERROR(BR12*AO12,"--")</f>
         <v>--</v>
       </c>
       <c r="CE12" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f>IFERROR(BS12*AP12,"--")</f>
         <v>--</v>
       </c>
       <c r="CF12" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f>IFERROR(BT12*AQ12,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -3849,116 +3875,116 @@
         <v/>
       </c>
       <c r="L13" s="16" t="str">
-        <f t="shared" ref="L13:L14" si="14">IFERROR(IF(OR($K13/AO13&gt;L$4,$K13/AO13&lt;L$3),"nmf ",$K13/AO13),"n/a ")</f>
+        <f>IFERROR(IF(OR($K13/AN13&gt;L$4,$K13/AN13&lt;L$3),"nmf ",$K13/AN13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M13" s="16" t="str">
-        <f t="shared" ref="M13:M14" si="15">IFERROR(IF(OR($K13/AP13&gt;M$4,$K13/AP13&lt;M$3),"nmf ",$K13/AP13),"n/a ")</f>
+        <f>IFERROR(IF(OR($K13/AO13&gt;M$4,$K13/AO13&lt;M$3),"nmf ",$K13/AO13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N13" s="16" t="str">
-        <f t="shared" ref="N13:N14" si="16">IFERROR(IF(OR($K13/AQ13&gt;N$4,$K13/AQ13&lt;N$3),"nmf ",$K13/AQ13),"n/a ")</f>
+        <f>IFERROR(IF(OR($K13/AP13&gt;N$4,$K13/AP13&lt;N$3),"nmf ",$K13/AP13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O13" s="16" t="str">
-        <f t="shared" ref="O13:O14" si="17">IFERROR(IF(OR($K13/AR13&gt;O$4,$K13/AR13&lt;O$3),"nmf ",$K13/AR13),"n/a ")</f>
+        <f>IFERROR(IF(OR($K13/AQ13&gt;O$4,$K13/AQ13&lt;O$3),"nmf ",$K13/AQ13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P13" s="16" t="str">
-        <f t="shared" ref="P13:P14" si="18">IFERROR(IF(OR($K13/AT13&gt;P$4,$K13/AT13&lt;P$3),"nmf ",$K13/AT13),"n/a ")</f>
+        <f>IFERROR(IF(OR($K13/AS13&gt;P$4,$K13/AS13&lt;P$3),"nmf ",$K13/AS13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q13" s="16" t="str">
-        <f t="shared" ref="Q13:Q14" si="19">IFERROR(IF(OR($K13/AU13&gt;Q$4,$K13/AU13&lt;Q$3),"nmf ",$K13/AU13),"n/a ")</f>
+        <f>IFERROR(IF(OR($K13/AT13&gt;Q$4,$K13/AT13&lt;Q$3),"nmf ",$K13/AT13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R13" s="16" t="str">
-        <f t="shared" ref="R13:R14" si="20">IFERROR(IF(OR($K13/AV13&gt;R$4,$K13/AV13&lt;R$3),"nmf ",$K13/AV13),"n/a ")</f>
+        <f>IFERROR(IF(OR($K13/AU13&gt;R$4,$K13/AU13&lt;R$3),"nmf ",$K13/AU13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S13" s="16" t="str">
-        <f t="shared" ref="S13:S14" si="21">IFERROR(IF(OR($K13/AW13&gt;S$4,$K13/AW13&lt;S$3),"nmf ",$K13/AW13),"n/a ")</f>
+        <f>IFERROR(IF(OR($K13/AV13&gt;S$4,$K13/AV13&lt;S$3),"nmf ",$K13/AV13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T13" s="33" t="str">
-        <f t="shared" ref="T13:T14" si="22">IFERROR((AQ13/AP13)-1,"n/a ")</f>
+        <f t="shared" ref="T13:T14" si="16">IFERROR((AP13/AO13)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U13" s="33" t="str">
-        <f t="shared" ref="U13:U14" si="23">IFERROR((AR13/AQ13)-1,"n/a ")</f>
+        <f t="shared" ref="U13:U14" si="17">IFERROR((AQ13/AP13)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V13" s="16" t="str">
-        <f>IFERROR(IF(OR($H13/AY13&gt;#REF!,$H13/AY13&lt;#REF!),"nmf ",$H13/AY13),"n/a ")</f>
+        <f>IFERROR($H13/AX13,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W13" s="16" t="str">
-        <f>IFERROR(IF(OR($H13/AZ13&gt;#REF!,$H13/AZ13&lt;#REF!),"nmf ",$H13/AZ13),"n/a ")</f>
+        <f>IFERROR($H13/AY13,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X13" s="16" t="str">
-        <f>IFERROR(IF(OR($H13/BA13&gt;#REF!,$H13/BA13&lt;#REF!),"nmf ",$H13/BA13),"n/a ")</f>
+        <f>IFERROR($H13/AZ13,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y13" s="16" t="str">
-        <f>IFERROR(IF(OR($H13/BC13&gt;#REF!,$H13/BC13&lt;#REF!),"nmf ",$H13/BC13),"n/a ")</f>
+        <f>IFERROR($H13/BB13,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z13" s="16" t="str">
-        <f>IFERROR(IF(OR($H13/BD13&gt;#REF!,$H13/BD13&lt;#REF!),"nmf ",$H13/BD13),"n/a ")</f>
+        <f>IFERROR($H13/BC13,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA13" s="16" t="str">
-        <f>IFERROR(IF(OR($H13/BE13&gt;#REF!,$H13/BE13&lt;#REF!),"nmf ",$H13/BE13),"n/a ")</f>
+        <f>IFERROR($H13/BD13,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB13" s="33" t="str">
-        <f t="shared" ref="AB13:AB14" si="24">IFERROR((AS13/AR13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="AC13" s="33" t="str">
-        <f t="shared" ref="AC13:AC14" si="25">IFERROR((AT13/AS13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="AD13" s="33" t="str">
-        <f t="shared" ref="AD13:AD14" si="26">IFERROR((AU13/AT13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="AE13" s="33" t="str">
-        <f t="shared" ref="AE13:AE14" si="27">IFERROR((AV13/AU13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AF13" s="33" t="str">
-        <f t="shared" ref="AF13:AF14" si="28">IFERROR((AW13/AV13)-1,"n/a ")</f>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG13" s="33" t="str">
-        <f t="shared" ref="AG13:AG14" si="29">IFERROR((BM13/AW13)-1,"n/a ")</f>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH13" s="33" t="str">
-        <f t="shared" ref="AH13:AH14" si="30">IFERROR((BN13/BM13)-1,"n/a ")</f>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI13" s="33" t="str">
-        <f t="shared" ref="AI13:AI14" si="31">IFERROR((BO13/BN13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ13" s="33" t="str">
-        <f t="shared" ref="AJ13:AJ14" si="32">IFERROR((BP13/BO13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK13" s="33" t="str">
-        <f t="shared" ref="AK13:AK14" si="33">IFERROR((BQ13/BP13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL13" s="33" t="str">
-        <f t="shared" ref="AL13:AL14" si="34">IFERROR((BR13/BQ13)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM13" s="72"/>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ13" s="83" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK13" s="83" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL13" s="72"/>
+      <c r="AN13" s="20" t="str" cm="1">
+        <f t="array" ref="AN13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO13" s="20" t="str" cm="1">
-        <f t="array" ref="AO13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP13" s="20" t="str" cm="1">
@@ -3969,12 +3995,12 @@
         <f t="array" ref="AQ13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR13" s="20" t="str" cm="1">
-        <f t="array" ref="AR13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS13" s="20" t="str" cm="1">
+        <f t="array" ref="AS13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT13" s="20" t="str" cm="1">
-        <f t="array" ref="AT13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU13" s="20" t="str" cm="1">
@@ -3985,8 +4011,8 @@
         <f t="array" ref="AV13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW13" s="20" t="str" cm="1">
-        <f t="array" ref="AW13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX13" s="13" t="str" cm="1">
+        <f t="array" ref="AX13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY13" s="13" t="str" cm="1">
@@ -3997,8 +4023,8 @@
         <f t="array" ref="AZ13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA13" s="13" t="str" cm="1">
-        <f t="array" ref="BA13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB13" s="13" t="str" cm="1">
+        <f t="array" ref="BB13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC13" s="13" t="str" cm="1">
@@ -4009,45 +4035,45 @@
         <f t="array" ref="BD13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE13" s="13" t="str" cm="1">
-        <f t="array" ref="BE13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG13" s="65" t="str" cm="1">
-        <f t="array" ref="BG13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF13" s="65" t="str" cm="1">
+        <f t="array" ref="BF13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG13" s="19" t="str" cm="1">
+        <f t="array" ref="BG13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH13" s="19" t="str" cm="1">
-        <f t="array" ref="BH13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI13" s="19" t="str" cm="1">
-        <f t="array" ref="BI13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ13" s="19" t="str" cm="1">
-        <f t="array" ref="BJ13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK13" s="37" t="e">
-        <f t="shared" ref="BK13:BK14" si="35">+BI13-BJ13</f>
+        <f t="array" ref="BI13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ13" s="37" t="e">
+        <f t="shared" ref="BJ13:BJ14" si="18">+BH13-BI13</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BL13" s="19" t="str" cm="1">
-        <f t="array" ref="BL13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK13" s="19" t="str" cm="1">
+        <f t="array" ref="BK13">IF($B13="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM13" s="20" t="str">
+        <f t="shared" ref="BM13:BM14" si="19">IFERROR($AO13*$BR13,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN13" s="20" t="str">
-        <f t="shared" ref="BN13:BN14" si="36">IFERROR($AP13*$BR13,"n/a")</f>
+        <f>IFERROR($AP13*BS13,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO13" s="20" t="str">
-        <f t="shared" ref="BO13:BO14" si="37">IFERROR($AQ13*BS13,"n/a")</f>
+        <f>IFERROR($AQ13*$BT13,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP13" s="20" t="str">
-        <f t="shared" ref="BP13:BP14" si="38">IFERROR($AR13*$BT13,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ13" s="44" t="str">
+        <f>IF($B13="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR13" s="44" t="str">
         <f>IF($B13="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B13,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -4075,27 +4101,27 @@
         <v/>
       </c>
       <c r="BZ13" s="62" t="str">
-        <f t="shared" ref="BZ13:BZ14" si="39">IFERROR(IF(CD13/AP13&lt;0,"nmf ",CD13/AP13),"n/a ")</f>
+        <f>IFERROR(IF(CD13/AO13&lt;0,"nmf ",CD13/AO13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA13" s="62" t="str">
-        <f t="shared" ref="CA13:CA14" si="40">IFERROR(IF(CE13/AQ13&lt;0,"nmf ",CE13/AQ13),"n/a ")</f>
+        <f>IFERROR(IF(CE13/AP13&lt;0,"nmf ",CE13/AP13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB13" s="62" t="str">
-        <f t="shared" ref="CB13:CB14" si="41">IFERROR(IF(CF13/AR13&lt;0,"nmf ",CF13/AR13),"n/a ")</f>
+        <f>IFERROR(IF(CF13/AQ13&lt;0,"nmf ",CF13/AQ13),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD13" s="68" t="str">
-        <f t="shared" ref="CD13:CD14" si="42">IFERROR(BR13*AP13,"--")</f>
+        <f>IFERROR(BR13*AO13,"--")</f>
         <v>--</v>
       </c>
       <c r="CE13" s="20" t="str">
-        <f t="shared" ref="CE13:CE14" si="43">IFERROR(BS13*AQ13,"--")</f>
+        <f>IFERROR(BS13*AP13,"--")</f>
         <v>--</v>
       </c>
       <c r="CF13" s="20" t="str">
-        <f t="shared" ref="CF13:CF14" si="44">IFERROR(BT13*AR13,"--")</f>
+        <f>IFERROR(BT13*AQ13,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -4126,116 +4152,116 @@
         <v/>
       </c>
       <c r="L14" s="16" t="str">
-        <f t="shared" si="14"/>
+        <f>IFERROR(IF(OR($K14/AN14&gt;L$4,$K14/AN14&lt;L$3),"nmf ",$K14/AN14),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M14" s="16" t="str">
-        <f t="shared" si="15"/>
+        <f>IFERROR(IF(OR($K14/AO14&gt;M$4,$K14/AO14&lt;M$3),"nmf ",$K14/AO14),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N14" s="16" t="str">
+        <f>IFERROR(IF(OR($K14/AP14&gt;N$4,$K14/AP14&lt;N$3),"nmf ",$K14/AP14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="O14" s="16" t="str">
+        <f>IFERROR(IF(OR($K14/AQ14&gt;O$4,$K14/AQ14&lt;O$3),"nmf ",$K14/AQ14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="P14" s="16" t="str">
+        <f>IFERROR(IF(OR($K14/AS14&gt;P$4,$K14/AS14&lt;P$3),"nmf ",$K14/AS14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Q14" s="16" t="str">
+        <f>IFERROR(IF(OR($K14/AT14&gt;Q$4,$K14/AT14&lt;Q$3),"nmf ",$K14/AT14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="R14" s="16" t="str">
+        <f>IFERROR(IF(OR($K14/AU14&gt;R$4,$K14/AU14&lt;R$3),"nmf ",$K14/AU14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="S14" s="16" t="str">
+        <f>IFERROR(IF(OR($K14/AV14&gt;S$4,$K14/AV14&lt;S$3),"nmf ",$K14/AV14),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="T14" s="33" t="str">
         <f t="shared" si="16"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="O14" s="16" t="str">
+      <c r="U14" s="33" t="str">
         <f t="shared" si="17"/>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="P14" s="16" t="str">
-        <f t="shared" si="18"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="Q14" s="16" t="str">
-        <f t="shared" si="19"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="R14" s="16" t="str">
-        <f t="shared" si="20"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="S14" s="16" t="str">
-        <f t="shared" si="21"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="T14" s="33" t="str">
-        <f t="shared" si="22"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="U14" s="33" t="str">
-        <f t="shared" si="23"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
       <c r="V14" s="16" t="str">
-        <f>IFERROR(IF(OR($H14/AY14&gt;#REF!,$H14/AY14&lt;#REF!),"nmf ",$H14/AY14),"n/a ")</f>
+        <f>IFERROR($H14/AX14,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W14" s="16" t="str">
-        <f>IFERROR(IF(OR($H14/AZ14&gt;#REF!,$H14/AZ14&lt;#REF!),"nmf ",$H14/AZ14),"n/a ")</f>
+        <f>IFERROR($H14/AY14,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X14" s="16" t="str">
-        <f>IFERROR(IF(OR($H14/BA14&gt;#REF!,$H14/BA14&lt;#REF!),"nmf ",$H14/BA14),"n/a ")</f>
+        <f>IFERROR($H14/AZ14,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y14" s="16" t="str">
-        <f>IFERROR(IF(OR($H14/BC14&gt;#REF!,$H14/BC14&lt;#REF!),"nmf ",$H14/BC14),"n/a ")</f>
+        <f>IFERROR($H14/BB14,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z14" s="16" t="str">
-        <f>IFERROR(IF(OR($H14/BD14&gt;#REF!,$H14/BD14&lt;#REF!),"nmf ",$H14/BD14),"n/a ")</f>
+        <f>IFERROR($H14/BC14,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA14" s="16" t="str">
-        <f>IFERROR(IF(OR($H14/BE14&gt;#REF!,$H14/BE14&lt;#REF!),"nmf ",$H14/BE14),"n/a ")</f>
+        <f>IFERROR($H14/BD14,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB14" s="33" t="str">
-        <f t="shared" si="24"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="AC14" s="33" t="str">
-        <f t="shared" si="25"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="AD14" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="AE14" s="33" t="str">
-        <f t="shared" si="27"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AF14" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG14" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH14" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI14" s="33" t="str">
-        <f t="shared" si="31"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ14" s="33" t="str">
-        <f t="shared" si="32"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK14" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL14" s="33" t="str">
-        <f t="shared" si="34"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM14" s="72"/>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ14" s="83" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK14" s="83" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL14" s="72"/>
+      <c r="AN14" s="20" t="str" cm="1">
+        <f t="array" ref="AN14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO14" s="20" t="str" cm="1">
-        <f t="array" ref="AO14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP14" s="20" t="str" cm="1">
@@ -4246,12 +4272,12 @@
         <f t="array" ref="AQ14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR14" s="20" t="str" cm="1">
-        <f t="array" ref="AR14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS14" s="20" t="str" cm="1">
+        <f t="array" ref="AS14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT14" s="20" t="str" cm="1">
-        <f t="array" ref="AT14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU14" s="20" t="str" cm="1">
@@ -4262,8 +4288,8 @@
         <f t="array" ref="AV14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW14" s="20" t="str" cm="1">
-        <f t="array" ref="AW14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX14" s="13" t="str" cm="1">
+        <f t="array" ref="AX14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY14" s="13" t="str" cm="1">
@@ -4274,8 +4300,8 @@
         <f t="array" ref="AZ14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA14" s="13" t="str" cm="1">
-        <f t="array" ref="BA14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB14" s="13" t="str" cm="1">
+        <f t="array" ref="BB14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC14" s="13" t="str" cm="1">
@@ -4286,45 +4312,45 @@
         <f t="array" ref="BD14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE14" s="13" t="str" cm="1">
-        <f t="array" ref="BE14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG14" s="65" t="str" cm="1">
-        <f t="array" ref="BG14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF14" s="65" t="str" cm="1">
+        <f t="array" ref="BF14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG14" s="19" t="str" cm="1">
+        <f t="array" ref="BG14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH14" s="19" t="str" cm="1">
-        <f t="array" ref="BH14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI14" s="19" t="str" cm="1">
-        <f t="array" ref="BI14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ14" s="19" t="str" cm="1">
-        <f t="array" ref="BJ14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK14" s="37" t="e">
-        <f t="shared" si="35"/>
+        <f t="array" ref="BI14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ14" s="37" t="e">
+        <f t="shared" si="18"/>
         <v>#VALUE!</v>
       </c>
-      <c r="BL14" s="19" t="str" cm="1">
-        <f t="array" ref="BL14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK14" s="19" t="str" cm="1">
+        <f t="array" ref="BK14">IF($B14="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM14" s="20" t="str">
+        <f t="shared" si="19"/>
+        <v>n/a</v>
       </c>
       <c r="BN14" s="20" t="str">
-        <f t="shared" si="36"/>
+        <f>IFERROR($AP14*BS14,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO14" s="20" t="str">
-        <f t="shared" si="37"/>
+        <f>IFERROR($AQ14*$BT14,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP14" s="20" t="str">
-        <f t="shared" si="38"/>
-        <v>n/a</v>
+      <c r="BQ14" s="44" t="str">
+        <f>IF($B14="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR14" s="44" t="str">
         <f>IF($B14="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B14,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -4352,27 +4378,27 @@
         <v/>
       </c>
       <c r="BZ14" s="62" t="str">
-        <f t="shared" si="39"/>
+        <f>IFERROR(IF(CD14/AO14&lt;0,"nmf ",CD14/AO14),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA14" s="62" t="str">
-        <f t="shared" si="40"/>
+        <f>IFERROR(IF(CE14/AP14&lt;0,"nmf ",CE14/AP14),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB14" s="62" t="str">
-        <f t="shared" si="41"/>
+        <f>IFERROR(IF(CF14/AQ14&lt;0,"nmf ",CF14/AQ14),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD14" s="68" t="str">
-        <f t="shared" si="42"/>
+        <f>IFERROR(BR14*AO14,"--")</f>
         <v>--</v>
       </c>
       <c r="CE14" s="20" t="str">
-        <f t="shared" si="43"/>
+        <f>IFERROR(BS14*AP14,"--")</f>
         <v>--</v>
       </c>
       <c r="CF14" s="20" t="str">
-        <f t="shared" si="44"/>
+        <f>IFERROR(BT14*AQ14,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -4403,116 +4429,116 @@
         <v/>
       </c>
       <c r="L15" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(OR($K15/AN15&gt;L$4,$K15/AN15&lt;L$3),"nmf ",$K15/AN15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M15" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(OR($K15/AO15&gt;M$4,$K15/AO15&lt;M$3),"nmf ",$K15/AO15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N15" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(OR($K15/AP15&gt;N$4,$K15/AP15&lt;N$3),"nmf ",$K15/AP15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O15" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(OR($K15/AQ15&gt;O$4,$K15/AQ15&lt;O$3),"nmf ",$K15/AQ15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P15" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(IF(OR($K15/AS15&gt;P$4,$K15/AS15&lt;P$3),"nmf ",$K15/AS15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q15" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(IF(OR($K15/AT15&gt;Q$4,$K15/AT15&lt;Q$3),"nmf ",$K15/AT15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R15" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(IF(OR($K15/AU15&gt;R$4,$K15/AU15&lt;R$3),"nmf ",$K15/AU15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S15" s="16" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(IF(OR($K15/AV15&gt;S$4,$K15/AV15&lt;S$3),"nmf ",$K15/AV15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T15" s="33" t="str">
+        <f>IFERROR((AP15/AO15)-1,"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="U15" s="33" t="str">
         <f>IFERROR((AQ15/AP15)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
-      <c r="U15" s="33" t="str">
-        <f>IFERROR((AR15/AQ15)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
       <c r="V15" s="16" t="str">
-        <f>IFERROR(IF(OR($H15/AY15&gt;#REF!,$H15/AY15&lt;#REF!),"nmf ",$H15/AY15),"n/a ")</f>
+        <f>IFERROR($H15/AX15,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W15" s="16" t="str">
-        <f>IFERROR(IF(OR($H15/AZ15&gt;#REF!,$H15/AZ15&lt;#REF!),"nmf ",$H15/AZ15),"n/a ")</f>
+        <f>IFERROR($H15/AY15,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X15" s="16" t="str">
-        <f>IFERROR(IF(OR($H15/BA15&gt;#REF!,$H15/BA15&lt;#REF!),"nmf ",$H15/BA15),"n/a ")</f>
+        <f>IFERROR($H15/AZ15,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y15" s="16" t="str">
-        <f>IFERROR(IF(OR($H15/BC15&gt;#REF!,$H15/BC15&lt;#REF!),"nmf ",$H15/BC15),"n/a ")</f>
+        <f>IFERROR($H15/BB15,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z15" s="16" t="str">
-        <f>IFERROR(IF(OR($H15/BD15&gt;#REF!,$H15/BD15&lt;#REF!),"nmf ",$H15/BD15),"n/a ")</f>
+        <f>IFERROR($H15/BC15,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA15" s="16" t="str">
-        <f>IFERROR(IF(OR($H15/BE15&gt;#REF!,$H15/BE15&lt;#REF!),"nmf ",$H15/BE15),"n/a ")</f>
+        <f>IFERROR($H15/BD15,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB15" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="AC15" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="AD15" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="AE15" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AF15" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG15" s="33" t="str">
-        <f>IFERROR((BM15/AW15)-1,"n/a ")</f>
+        <f t="shared" si="7"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH15" s="33" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI15" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ15" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK15" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL15" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM15" s="72"/>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ15" s="83" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK15" s="83" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL15" s="72"/>
+      <c r="AN15" s="20" t="str" cm="1">
+        <f t="array" ref="AN15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO15" s="20" t="str" cm="1">
-        <f t="array" ref="AO15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP15" s="20" t="str" cm="1">
@@ -4523,12 +4549,12 @@
         <f t="array" ref="AQ15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR15" s="20" t="str" cm="1">
-        <f t="array" ref="AR15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS15" s="20" t="str" cm="1">
+        <f t="array" ref="AS15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT15" s="20" t="str" cm="1">
-        <f t="array" ref="AT15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU15" s="20" t="str" cm="1">
@@ -4539,8 +4565,8 @@
         <f t="array" ref="AV15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW15" s="20" t="str" cm="1">
-        <f t="array" ref="AW15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX15" s="13" t="str" cm="1">
+        <f t="array" ref="AX15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY15" s="13" t="str" cm="1">
@@ -4551,8 +4577,8 @@
         <f t="array" ref="AZ15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA15" s="13" t="str" cm="1">
-        <f t="array" ref="BA15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB15" s="13" t="str" cm="1">
+        <f t="array" ref="BB15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC15" s="13" t="str" cm="1">
@@ -4563,45 +4589,45 @@
         <f t="array" ref="BD15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE15" s="13" t="str" cm="1">
-        <f t="array" ref="BE15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG15" s="66" t="str" cm="1">
-        <f t="array" ref="BG15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF15" s="66" t="str" cm="1">
+        <f t="array" ref="BF15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG15" s="19" t="str" cm="1">
+        <f t="array" ref="BG15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH15" s="19" t="str" cm="1">
-        <f t="array" ref="BH15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI15" s="19" t="str" cm="1">
-        <f t="array" ref="BI15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ15" s="19" t="str" cm="1">
-        <f t="array" ref="BJ15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK15" s="37" t="e">
-        <f>+BI15-BJ15</f>
+        <f t="array" ref="BI15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ15" s="37" t="e">
+        <f>+BH15-BI15</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BL15" s="19" t="str" cm="1">
-        <f t="array" ref="BL15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK15" s="19" t="str" cm="1">
+        <f t="array" ref="BK15">IF($B15="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM15" s="20" t="str">
+        <f>IFERROR($AO15*$BR15,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN15" s="20" t="str">
-        <f>IFERROR($AP15*$BR15,"n/a")</f>
+        <f>IFERROR($AP15*BS15,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO15" s="20" t="str">
-        <f>IFERROR($AQ15*BS15,"n/a")</f>
+        <f>IFERROR($AQ15*$BT15,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP15" s="20" t="str">
-        <f>IFERROR($AR15*$BT15,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ15" s="44" t="str">
+        <f>IF($B15="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR15" s="44" t="str">
         <f>IF($B15="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B15,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -4629,27 +4655,27 @@
         <v/>
       </c>
       <c r="BZ15" s="62" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(IF(CD15/AO15&lt;0,"nmf ",CD15/AO15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA15" s="62" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(IF(CE15/AP15&lt;0,"nmf ",CE15/AP15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB15" s="62" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(IF(CF15/AQ15&lt;0,"nmf ",CF15/AQ15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD15" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f>IFERROR(BR15*AO15,"--")</f>
         <v>--</v>
       </c>
       <c r="CE15" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f>IFERROR(BS15*AP15,"--")</f>
         <v>--</v>
       </c>
       <c r="CF15" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f>IFERROR(BT15*AQ15,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -4687,23 +4713,22 @@
       <c r="AJ16" s="17"/>
       <c r="AK16" s="17"/>
       <c r="AL16" s="17"/>
-      <c r="AM16" s="17"/>
+      <c r="AN16" s="13"/>
       <c r="AO16" s="13"/>
       <c r="AP16" s="13"/>
       <c r="AQ16" s="13"/>
-      <c r="AR16" s="13"/>
+      <c r="AT16" s="20"/>
       <c r="AU16" s="20"/>
       <c r="AV16" s="20"/>
-      <c r="AW16" s="20"/>
+      <c r="AX16" s="13"/>
       <c r="AY16" s="13"/>
       <c r="AZ16" s="13"/>
-      <c r="BA16" s="13"/>
-      <c r="BG16" s="66"/>
+      <c r="BF16" s="66"/>
+      <c r="BG16" s="19"/>
       <c r="BH16" s="19"/>
       <c r="BI16" s="19"/>
       <c r="BJ16" s="19"/>
       <c r="BK16" s="19"/>
-      <c r="BL16" s="19"/>
       <c r="BR16" s="45"/>
       <c r="BS16" s="45"/>
       <c r="BT16" s="45"/>
@@ -4728,118 +4753,114 @@
       <c r="J17" s="25"/>
       <c r="K17" s="25"/>
       <c r="L17" s="35" t="str">
-        <f t="shared" ref="L17:AL17" si="45">IFERROR(AVERAGE(L10:L15),"n/a ")</f>
+        <f t="shared" ref="L17:AK17" si="20">IFERROR(AVERAGE(L10:L15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M17" s="35" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N17" s="26" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O17" s="35" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P17" s="35" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q17" s="26" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R17" s="26" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S17" s="26" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T17" s="36" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U17" s="36" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V17" s="26" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W17" s="26" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X17" s="26" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y17" s="26" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z17" s="26" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA17" s="26" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB17" s="36" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" ref="AB17" si="21">IFERROR(AVERAGE(AB10:AB15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AC17" s="36" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AD17" s="36" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AE17" s="36" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AF17" s="36" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" ref="AF17" si="22">IFERROR(AVERAGE(AF10:AF15),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG17" s="36" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH17" s="36" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI17" s="36" t="str">
-        <f t="shared" si="45"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ17" s="36" t="str">
-        <f t="shared" si="45"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK17" s="36" t="str">
-        <f t="shared" si="45"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL17" s="36" t="str">
-        <f t="shared" si="45"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM17" s="36"/>
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ17" s="84" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK17" s="84" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL17" s="36"/>
+      <c r="AT17" s="27"/>
       <c r="AU17" s="27"/>
       <c r="AV17" s="27"/>
-      <c r="AW17" s="27"/>
-      <c r="BG17" s="67"/>
+      <c r="BF17" s="67"/>
       <c r="BR17" s="45"/>
       <c r="BS17" s="45"/>
       <c r="BT17" s="45"/>
@@ -4857,10 +4878,10 @@
       <c r="J18" s="28"/>
       <c r="K18" s="28"/>
       <c r="L18" s="28"/>
+      <c r="AT18" s="27"/>
       <c r="AU18" s="27"/>
       <c r="AV18" s="27"/>
-      <c r="AW18" s="27"/>
-      <c r="BG18" s="67"/>
+      <c r="BF18" s="67"/>
       <c r="BR18" s="45"/>
       <c r="BS18" s="45"/>
       <c r="BT18" s="45"/>
@@ -4875,7 +4896,7 @@
     <row r="19" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="11"/>
       <c r="D19" s="71" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
@@ -4909,23 +4930,22 @@
       <c r="AJ19" s="17"/>
       <c r="AK19" s="17"/>
       <c r="AL19" s="17"/>
-      <c r="AM19" s="17"/>
+      <c r="AN19" s="13"/>
       <c r="AO19" s="13"/>
       <c r="AP19" s="13"/>
       <c r="AQ19" s="13"/>
-      <c r="AR19" s="13"/>
+      <c r="AT19" s="20"/>
       <c r="AU19" s="20"/>
       <c r="AV19" s="20"/>
-      <c r="AW19" s="20"/>
+      <c r="AX19" s="13"/>
       <c r="AY19" s="13"/>
       <c r="AZ19" s="13"/>
-      <c r="BA19" s="13"/>
-      <c r="BG19" s="66"/>
+      <c r="BF19" s="66"/>
+      <c r="BG19" s="19"/>
       <c r="BH19" s="19"/>
       <c r="BI19" s="19"/>
       <c r="BJ19" s="19"/>
       <c r="BK19" s="19"/>
-      <c r="BL19" s="19"/>
       <c r="BR19" s="45"/>
       <c r="BS19" s="45"/>
       <c r="BT19" s="45"/>
@@ -4964,116 +4984,116 @@
         <v/>
       </c>
       <c r="L20" s="16" t="str">
-        <f t="shared" ref="L20:O25" si="46">IFERROR(IF(OR($K20/AO20&gt;L$4,$K20/AO20&lt;L$3),"nmf ",$K20/AO20),"n/a ")</f>
+        <f>IFERROR(IF(OR($K20/AN20&gt;L$4,$K20/AN20&lt;L$3),"nmf ",$K20/AN20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M20" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K20/AO20&gt;M$4,$K20/AO20&lt;M$3),"nmf ",$K20/AO20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N20" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K20/AP20&gt;N$4,$K20/AP20&lt;N$3),"nmf ",$K20/AP20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O20" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K20/AQ20&gt;O$4,$K20/AQ20&lt;O$3),"nmf ",$K20/AQ20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P20" s="16" t="str">
-        <f t="shared" ref="P20:S25" si="47">IFERROR(IF(OR($K20/AT20&gt;P$4,$K20/AT20&lt;P$3),"nmf ",$K20/AT20),"n/a ")</f>
+        <f>IFERROR(IF(OR($K20/AS20&gt;P$4,$K20/AS20&lt;P$3),"nmf ",$K20/AS20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q20" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K20/AT20&gt;Q$4,$K20/AT20&lt;Q$3),"nmf ",$K20/AT20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R20" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K20/AU20&gt;R$4,$K20/AU20&lt;R$3),"nmf ",$K20/AU20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S20" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K20/AV20&gt;S$4,$K20/AV20&lt;S$3),"nmf ",$K20/AV20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T20" s="33" t="str">
-        <f t="shared" ref="T20:U25" si="48">IFERROR((AQ20/AP20)-1,"n/a ")</f>
+        <f t="shared" ref="T20:U25" si="23">IFERROR((AP20/AO20)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U20" s="33" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V20" s="16" t="str">
-        <f>IFERROR(IF(OR($H20/AY20&gt;#REF!,$H20/AY20&lt;#REF!),"nmf ",$H20/AY20),"n/a ")</f>
+        <f>IFERROR($H20/AX20,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W20" s="16" t="str">
-        <f>IFERROR(IF(OR($H20/AZ20&gt;#REF!,$H20/AZ20&lt;#REF!),"nmf ",$H20/AZ20),"n/a ")</f>
+        <f>IFERROR($H20/AY20,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X20" s="16" t="str">
-        <f>IFERROR(IF(OR($H20/BA20&gt;#REF!,$H20/BA20&lt;#REF!),"nmf ",$H20/BA20),"n/a ")</f>
+        <f>IFERROR($H20/AZ20,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y20" s="16" t="str">
-        <f>IFERROR(IF(OR($H20/BC20&gt;#REF!,$H20/BC20&lt;#REF!),"nmf ",$H20/BC20),"n/a ")</f>
+        <f>IFERROR($H20/BB20,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z20" s="16" t="str">
-        <f>IFERROR(IF(OR($H20/BD20&gt;#REF!,$H20/BD20&lt;#REF!),"nmf ",$H20/BD20),"n/a ")</f>
+        <f>IFERROR($H20/BC20,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA20" s="16" t="str">
-        <f>IFERROR(IF(OR($H20/BE20&gt;#REF!,$H20/BE20&lt;#REF!),"nmf ",$H20/BE20),"n/a ")</f>
+        <f>IFERROR($H20/BD20,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB20" s="33" t="str">
-        <f t="shared" ref="AB20:AB25" si="49">IFERROR((AS20/AR20)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f>IFERROR(IF(BQ20="--","n/a ",BQ20),"n/a ")</f>
+        <v/>
       </c>
       <c r="AC20" s="33" t="str">
-        <f t="shared" ref="AC20:AC25" si="50">IFERROR((AT20/AS20)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f>IFERROR(IF(BR20="--","n/a ",BR20),"n/a ")</f>
+        <v/>
       </c>
       <c r="AD20" s="33" t="str">
-        <f t="shared" ref="AD20:AD25" si="51">IFERROR((AU20/AT20)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" ref="AD20:AD25" si="24">IFERROR(IF(BS20="--","n/a ",BS20),"n/a ")</f>
+        <v/>
       </c>
       <c r="AE20" s="33" t="str">
-        <f t="shared" ref="AE20:AE25" si="52">IFERROR((AV20/AU20)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" ref="AE20:AE25" si="25">IFERROR(IF(BT20="--","n/a ",BT20),"n/a ")</f>
+        <v/>
       </c>
       <c r="AF20" s="33" t="str">
-        <f t="shared" ref="AF20:AF25" si="53">IFERROR((AW20/AV20)-1,"n/a ")</f>
+        <f>IFERROR((AS20/AN20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG20" s="33" t="str">
-        <f>IFERROR((BM20/AW20)-1,"n/a ")</f>
+        <f>IFERROR((AT20/AO20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH20" s="33" t="str">
-        <f t="shared" ref="AH20:AH25" si="54">IFERROR((BN20/BM20)-1,"n/a ")</f>
+        <f t="shared" ref="AH20:AH25" si="26">IFERROR((AU20/AP20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI20" s="33" t="str">
-        <f t="shared" ref="AI20:AI25" si="55">IFERROR((BO20/BN20)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ20" s="33" t="str">
-        <f t="shared" ref="AJ20:AJ25" si="56">IFERROR((BP20/BO20)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK20" s="33" t="str">
-        <f t="shared" ref="AK20:AK25" si="57">IFERROR((BQ20/BP20)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL20" s="33" t="str">
-        <f t="shared" ref="AL20:AL25" si="58">IFERROR((BR20/BQ20)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM20" s="72"/>
+        <f t="shared" ref="AI20:AI25" si="27">IFERROR((AV20/AQ20),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ20" s="83" t="str">
+        <f>IFERROR((BJ20/AT20),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK20" s="83" t="str">
+        <f>IFERROR((BJ20/AU20),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL20" s="72"/>
+      <c r="AN20" s="20" t="str" cm="1">
+        <f t="array" ref="AN20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO20" s="20" t="str" cm="1">
-        <f t="array" ref="AO20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP20" s="20" t="str" cm="1">
@@ -5084,12 +5104,12 @@
         <f t="array" ref="AQ20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR20" s="20" t="str" cm="1">
-        <f t="array" ref="AR20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS20" s="20" t="str" cm="1">
+        <f t="array" ref="AS20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT20" s="20" t="str" cm="1">
-        <f t="array" ref="AT20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU20" s="20" t="str" cm="1">
@@ -5100,8 +5120,8 @@
         <f t="array" ref="AV20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW20" s="20" t="str" cm="1">
-        <f t="array" ref="AW20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX20" s="13" t="str" cm="1">
+        <f t="array" ref="AX20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY20" s="13" t="str" cm="1">
@@ -5112,8 +5132,8 @@
         <f t="array" ref="AZ20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA20" s="13" t="str" cm="1">
-        <f t="array" ref="BA20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB20" s="13" t="str" cm="1">
+        <f t="array" ref="BB20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC20" s="13" t="str" cm="1">
@@ -5124,45 +5144,45 @@
         <f t="array" ref="BD20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE20" s="13" t="str" cm="1">
-        <f t="array" ref="BE20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG20" s="66" t="str" cm="1">
-        <f t="array" ref="BG20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF20" s="66" t="str" cm="1">
+        <f t="array" ref="BF20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG20" s="19" t="str" cm="1">
+        <f t="array" ref="BG20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH20" s="19" t="str" cm="1">
-        <f t="array" ref="BH20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI20" s="19" t="str" cm="1">
-        <f t="array" ref="BI20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ20" s="19" t="str" cm="1">
-        <f t="array" ref="BJ20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK20" s="37" t="e">
-        <f t="shared" ref="BK20:BK22" si="59">+BI20-BJ20</f>
+        <f t="array" ref="BI20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ20" s="37" t="e">
+        <f t="shared" ref="BJ20:BJ22" si="28">+BH20-BI20</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BL20" s="19" t="str" cm="1">
-        <f t="array" ref="BL20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK20" s="19" t="str" cm="1">
+        <f t="array" ref="BK20">IF($B20="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM20" s="20" t="str">
+        <f>IFERROR($AO20*$BR20,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN20" s="20" t="str">
-        <f>IFERROR($AP20*$BR20,"n/a")</f>
+        <f>IFERROR($AP20*BS20,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO20" s="20" t="str">
-        <f t="shared" ref="BO20:BO25" si="60">IFERROR($AQ20*BS20,"n/a")</f>
+        <f>IFERROR($AQ20*$BT20,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP20" s="20" t="str">
-        <f>IFERROR($AR20*$BT20,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ20" s="44" t="str">
+        <f>IF($B20="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR20" s="44" t="str">
         <f>IF($B20="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B20,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -5190,27 +5210,27 @@
         <v/>
       </c>
       <c r="BZ20" s="62" t="str">
-        <f t="shared" ref="BZ20:CB25" si="61">IFERROR(IF(CD20/AP20&lt;0,"nmf ",CD20/AP20),"n/a ")</f>
+        <f>IFERROR(IF(CD20/AO20&lt;0,"nmf ",CD20/AO20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA20" s="62" t="str">
-        <f t="shared" si="61"/>
+        <f>IFERROR(IF(CE20/AP20&lt;0,"nmf ",CE20/AP20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB20" s="62" t="str">
-        <f t="shared" si="61"/>
+        <f>IFERROR(IF(CF20/AQ20&lt;0,"nmf ",CF20/AQ20),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD20" s="20" t="str">
-        <f t="shared" ref="CD20:CF25" si="62">IFERROR(BR20*AP20,"--")</f>
+        <f>IFERROR(BR20*AO20,"--")</f>
         <v>--</v>
       </c>
       <c r="CE20" s="20" t="str">
-        <f t="shared" si="62"/>
+        <f>IFERROR(BS20*AP20,"--")</f>
         <v>--</v>
       </c>
       <c r="CF20" s="20" t="str">
-        <f t="shared" si="62"/>
+        <f>IFERROR(BT20*AQ20,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -5241,116 +5261,116 @@
         <v/>
       </c>
       <c r="L21" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K21/AN21&gt;L$4,$K21/AN21&lt;L$3),"nmf ",$K21/AN21),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M21" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K21/AO21&gt;M$4,$K21/AO21&lt;M$3),"nmf ",$K21/AO21),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N21" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K21/AP21&gt;N$4,$K21/AP21&lt;N$3),"nmf ",$K21/AP21),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O21" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K21/AQ21&gt;O$4,$K21/AQ21&lt;O$3),"nmf ",$K21/AQ21),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P21" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K21/AS21&gt;P$4,$K21/AS21&lt;P$3),"nmf ",$K21/AS21),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q21" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K21/AT21&gt;Q$4,$K21/AT21&lt;Q$3),"nmf ",$K21/AT21),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R21" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K21/AU21&gt;R$4,$K21/AU21&lt;R$3),"nmf ",$K21/AU21),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S21" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K21/AV21&gt;S$4,$K21/AV21&lt;S$3),"nmf ",$K21/AV21),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T21" s="33" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U21" s="33" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V21" s="16" t="str">
-        <f>IFERROR(IF(OR($H21/AY21&gt;#REF!,$H21/AY21&lt;#REF!),"nmf ",$H21/AY21),"n/a ")</f>
+        <f>IFERROR($H21/AX21,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W21" s="16" t="str">
-        <f>IFERROR(IF(OR($H21/AZ21&gt;#REF!,$H21/AZ21&lt;#REF!),"nmf ",$H21/AZ21),"n/a ")</f>
+        <f>IFERROR($H21/AY21,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X21" s="16" t="str">
-        <f>IFERROR(IF(OR($H21/BA21&gt;#REF!,$H21/BA21&lt;#REF!),"nmf ",$H21/BA21),"n/a ")</f>
+        <f>IFERROR($H21/AZ21,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y21" s="16" t="str">
-        <f>IFERROR(IF(OR($H21/BC21&gt;#REF!,$H21/BC21&lt;#REF!),"nmf ",$H21/BC21),"n/a ")</f>
+        <f>IFERROR($H21/BB21,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z21" s="16" t="str">
-        <f>IFERROR(IF(OR($H21/BD21&gt;#REF!,$H21/BD21&lt;#REF!),"nmf ",$H21/BD21),"n/a ")</f>
+        <f>IFERROR($H21/BC21,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA21" s="16" t="str">
-        <f>IFERROR(IF(OR($H21/BE21&gt;#REF!,$H21/BE21&lt;#REF!),"nmf ",$H21/BE21),"n/a ")</f>
+        <f>IFERROR($H21/BD21,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB21" s="33" t="str">
-        <f t="shared" si="49"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" ref="AB21:AC25" si="29">IFERROR(IF(BQ21="--","n/a ",BQ21),"n/a ")</f>
+        <v/>
       </c>
       <c r="AC21" s="33" t="str">
-        <f t="shared" si="50"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="29"/>
+        <v/>
       </c>
       <c r="AD21" s="33" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="24"/>
+        <v/>
       </c>
       <c r="AE21" s="33" t="str">
-        <f t="shared" si="52"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="25"/>
+        <v/>
       </c>
       <c r="AF21" s="33" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" ref="AF21:AG25" si="30">IFERROR((AS21/AN21),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG21" s="33" t="str">
-        <f>IFERROR((BM21/AW21)-1,"n/a ")</f>
+        <f t="shared" si="30"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH21" s="33" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI21" s="33" t="str">
-        <f t="shared" si="55"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ21" s="33" t="str">
-        <f t="shared" si="56"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK21" s="33" t="str">
-        <f t="shared" si="57"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL21" s="33" t="str">
-        <f t="shared" si="58"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM21" s="72"/>
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ21" s="83" t="str">
+        <f t="shared" ref="AJ21:AJ25" si="31">IFERROR((BJ21/AT21),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK21" s="83" t="str">
+        <f t="shared" ref="AK21:AK25" si="32">IFERROR((BJ21/AU21),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL21" s="72"/>
+      <c r="AN21" s="20" t="str" cm="1">
+        <f t="array" ref="AN21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO21" s="20" t="str" cm="1">
-        <f t="array" ref="AO21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP21" s="20" t="str" cm="1">
@@ -5361,12 +5381,12 @@
         <f t="array" ref="AQ21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR21" s="20" t="str" cm="1">
-        <f t="array" ref="AR21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS21" s="20" t="str" cm="1">
+        <f t="array" ref="AS21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT21" s="20" t="str" cm="1">
-        <f t="array" ref="AT21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU21" s="20" t="str" cm="1">
@@ -5377,8 +5397,8 @@
         <f t="array" ref="AV21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW21" s="20" t="str" cm="1">
-        <f t="array" ref="AW21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX21" s="13" t="str" cm="1">
+        <f t="array" ref="AX21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY21" s="13" t="str" cm="1">
@@ -5389,8 +5409,8 @@
         <f t="array" ref="AZ21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA21" s="13" t="str" cm="1">
-        <f t="array" ref="BA21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB21" s="13" t="str" cm="1">
+        <f t="array" ref="BB21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC21" s="13" t="str" cm="1">
@@ -5401,45 +5421,45 @@
         <f t="array" ref="BD21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE21" s="13" t="str" cm="1">
-        <f t="array" ref="BE21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG21" s="66" t="str" cm="1">
-        <f t="array" ref="BG21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF21" s="66" t="str" cm="1">
+        <f t="array" ref="BF21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG21" s="19" t="str" cm="1">
+        <f t="array" ref="BG21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH21" s="19" t="str" cm="1">
-        <f t="array" ref="BH21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI21" s="19" t="str" cm="1">
-        <f t="array" ref="BI21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ21" s="19" t="str" cm="1">
-        <f t="array" ref="BJ21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK21" s="37" t="e">
-        <f t="shared" si="59"/>
+        <f t="array" ref="BI21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ21" s="37" t="e">
+        <f t="shared" si="28"/>
         <v>#VALUE!</v>
       </c>
-      <c r="BL21" s="19" t="str" cm="1">
-        <f t="array" ref="BL21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK21" s="19" t="str" cm="1">
+        <f t="array" ref="BK21">IF($B21="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM21" s="20" t="str">
+        <f>IFERROR($AO21*$BR21,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN21" s="20" t="str">
-        <f>IFERROR($AP21*$BR21,"n/a")</f>
+        <f>IFERROR($AP21*BS21,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO21" s="20" t="str">
-        <f t="shared" si="60"/>
+        <f>IFERROR($AQ21*$BT21,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP21" s="20" t="str">
-        <f>IFERROR($AR21*$BT21,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ21" s="44" t="str">
+        <f>IF($B21="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR21" s="44" t="str">
         <f>IF($B21="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B21,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -5467,27 +5487,27 @@
         <v/>
       </c>
       <c r="BZ21" s="62" t="str">
-        <f t="shared" si="61"/>
+        <f>IFERROR(IF(CD21/AO21&lt;0,"nmf ",CD21/AO21),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA21" s="62" t="str">
-        <f t="shared" si="61"/>
+        <f>IFERROR(IF(CE21/AP21&lt;0,"nmf ",CE21/AP21),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB21" s="62" t="str">
-        <f t="shared" si="61"/>
+        <f>IFERROR(IF(CF21/AQ21&lt;0,"nmf ",CF21/AQ21),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD21" s="20" t="str">
-        <f t="shared" si="62"/>
+        <f>IFERROR(BR21*AO21,"--")</f>
         <v>--</v>
       </c>
       <c r="CE21" s="20" t="str">
-        <f t="shared" si="62"/>
+        <f>IFERROR(BS21*AP21,"--")</f>
         <v>--</v>
       </c>
       <c r="CF21" s="20" t="str">
-        <f t="shared" si="62"/>
+        <f>IFERROR(BT21*AQ21,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -5518,116 +5538,116 @@
         <v/>
       </c>
       <c r="L22" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K22/AN22&gt;L$4,$K22/AN22&lt;L$3),"nmf ",$K22/AN22),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M22" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K22/AO22&gt;M$4,$K22/AO22&lt;M$3),"nmf ",$K22/AO22),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N22" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K22/AP22&gt;N$4,$K22/AP22&lt;N$3),"nmf ",$K22/AP22),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O22" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K22/AQ22&gt;O$4,$K22/AQ22&lt;O$3),"nmf ",$K22/AQ22),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P22" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K22/AS22&gt;P$4,$K22/AS22&lt;P$3),"nmf ",$K22/AS22),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q22" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K22/AT22&gt;Q$4,$K22/AT22&lt;Q$3),"nmf ",$K22/AT22),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R22" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K22/AU22&gt;R$4,$K22/AU22&lt;R$3),"nmf ",$K22/AU22),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S22" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K22/AV22&gt;S$4,$K22/AV22&lt;S$3),"nmf ",$K22/AV22),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T22" s="33" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U22" s="33" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V22" s="16" t="str">
-        <f>IFERROR(IF(OR($H22/AY22&gt;#REF!,$H22/AY22&lt;#REF!),"nmf ",$H22/AY22),"n/a ")</f>
+        <f>IFERROR($H22/AX22,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W22" s="16" t="str">
-        <f>IFERROR(IF(OR($H22/AZ22&gt;#REF!,$H22/AZ22&lt;#REF!),"nmf ",$H22/AZ22),"n/a ")</f>
+        <f>IFERROR($H22/AY22,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X22" s="16" t="str">
-        <f>IFERROR(IF(OR($H22/BA22&gt;#REF!,$H22/BA22&lt;#REF!),"nmf ",$H22/BA22),"n/a ")</f>
+        <f>IFERROR($H22/AZ22,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y22" s="16" t="str">
-        <f>IFERROR(IF(OR($H22/BC22&gt;#REF!,$H22/BC22&lt;#REF!),"nmf ",$H22/BC22),"n/a ")</f>
+        <f>IFERROR($H22/BB22,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z22" s="16" t="str">
-        <f>IFERROR(IF(OR($H22/BD22&gt;#REF!,$H22/BD22&lt;#REF!),"nmf ",$H22/BD22),"n/a ")</f>
+        <f>IFERROR($H22/BC22,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA22" s="16" t="str">
-        <f>IFERROR(IF(OR($H22/BE22&gt;#REF!,$H22/BE22&lt;#REF!),"nmf ",$H22/BE22),"n/a ")</f>
+        <f>IFERROR($H22/BD22,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB22" s="33" t="str">
-        <f t="shared" si="49"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="29"/>
+        <v/>
       </c>
       <c r="AC22" s="33" t="str">
-        <f t="shared" si="50"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="29"/>
+        <v/>
       </c>
       <c r="AD22" s="33" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="24"/>
+        <v/>
       </c>
       <c r="AE22" s="33" t="str">
-        <f t="shared" si="52"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="25"/>
+        <v/>
       </c>
       <c r="AF22" s="33" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG22" s="33" t="str">
-        <f>IFERROR((BM22/AW22)-1,"n/a ")</f>
+        <f t="shared" si="30"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH22" s="33" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI22" s="33" t="str">
-        <f t="shared" si="55"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ22" s="33" t="str">
-        <f t="shared" si="56"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK22" s="33" t="str">
-        <f t="shared" si="57"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL22" s="33" t="str">
-        <f t="shared" si="58"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM22" s="72"/>
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ22" s="83" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK22" s="83" t="str">
+        <f t="shared" si="32"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL22" s="72"/>
+      <c r="AN22" s="20" t="str" cm="1">
+        <f t="array" ref="AN22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO22" s="20" t="str" cm="1">
-        <f t="array" ref="AO22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP22" s="20" t="str" cm="1">
@@ -5638,12 +5658,12 @@
         <f t="array" ref="AQ22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR22" s="20" t="str" cm="1">
-        <f t="array" ref="AR22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS22" s="20" t="str" cm="1">
+        <f t="array" ref="AS22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT22" s="20" t="str" cm="1">
-        <f t="array" ref="AT22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU22" s="20" t="str" cm="1">
@@ -5654,8 +5674,8 @@
         <f t="array" ref="AV22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW22" s="20" t="str" cm="1">
-        <f t="array" ref="AW22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX22" s="13" t="str" cm="1">
+        <f t="array" ref="AX22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY22" s="13" t="str" cm="1">
@@ -5666,8 +5686,8 @@
         <f t="array" ref="AZ22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA22" s="13" t="str" cm="1">
-        <f t="array" ref="BA22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB22" s="13" t="str" cm="1">
+        <f t="array" ref="BB22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC22" s="13" t="str" cm="1">
@@ -5678,45 +5698,45 @@
         <f t="array" ref="BD22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE22" s="13" t="str" cm="1">
-        <f t="array" ref="BE22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG22" s="66" t="str" cm="1">
-        <f t="array" ref="BG22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF22" s="66" t="str" cm="1">
+        <f t="array" ref="BF22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG22" s="19" t="str" cm="1">
+        <f t="array" ref="BG22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH22" s="19" t="str" cm="1">
-        <f t="array" ref="BH22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI22" s="19" t="str" cm="1">
-        <f t="array" ref="BI22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ22" s="19" t="str" cm="1">
-        <f t="array" ref="BJ22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK22" s="37" t="e">
-        <f t="shared" si="59"/>
+        <f t="array" ref="BI22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ22" s="37" t="e">
+        <f t="shared" si="28"/>
         <v>#VALUE!</v>
       </c>
-      <c r="BL22" s="19" t="str" cm="1">
-        <f t="array" ref="BL22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK22" s="19" t="str" cm="1">
+        <f t="array" ref="BK22">IF($B22="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM22" s="20" t="str">
+        <f>IFERROR($AO22*$BR22,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN22" s="20" t="str">
-        <f>IFERROR($AP22*$BR22,"n/a")</f>
+        <f>IFERROR($AP22*BS22,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO22" s="20" t="str">
-        <f t="shared" si="60"/>
+        <f>IFERROR($AQ22*$BT22,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP22" s="20" t="str">
-        <f>IFERROR($AR22*$BT22,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ22" s="44" t="str">
+        <f>IF($B22="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR22" s="44" t="str">
         <f>IF($B22="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B22,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -5744,27 +5764,27 @@
         <v/>
       </c>
       <c r="BZ22" s="62" t="str">
-        <f t="shared" si="61"/>
+        <f>IFERROR(IF(CD22/AO22&lt;0,"nmf ",CD22/AO22),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA22" s="62" t="str">
-        <f t="shared" si="61"/>
+        <f>IFERROR(IF(CE22/AP22&lt;0,"nmf ",CE22/AP22),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB22" s="62" t="str">
-        <f t="shared" si="61"/>
+        <f>IFERROR(IF(CF22/AQ22&lt;0,"nmf ",CF22/AQ22),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD22" s="20" t="str">
-        <f t="shared" si="62"/>
+        <f>IFERROR(BR22*AO22,"--")</f>
         <v>--</v>
       </c>
       <c r="CE22" s="20" t="str">
-        <f t="shared" si="62"/>
+        <f>IFERROR(BS22*AP22,"--")</f>
         <v>--</v>
       </c>
       <c r="CF22" s="20" t="str">
-        <f t="shared" si="62"/>
+        <f>IFERROR(BT22*AQ22,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -5795,116 +5815,116 @@
         <v/>
       </c>
       <c r="L23" s="16" t="str">
-        <f t="shared" ref="L23:L24" si="63">IFERROR(IF(OR($K23/AO23&gt;L$4,$K23/AO23&lt;L$3),"nmf ",$K23/AO23),"n/a ")</f>
+        <f>IFERROR(IF(OR($K23/AN23&gt;L$4,$K23/AN23&lt;L$3),"nmf ",$K23/AN23),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M23" s="16" t="str">
-        <f t="shared" ref="M23:M24" si="64">IFERROR(IF(OR($K23/AP23&gt;M$4,$K23/AP23&lt;M$3),"nmf ",$K23/AP23),"n/a ")</f>
+        <f>IFERROR(IF(OR($K23/AO23&gt;M$4,$K23/AO23&lt;M$3),"nmf ",$K23/AO23),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N23" s="16" t="str">
-        <f t="shared" ref="N23:N24" si="65">IFERROR(IF(OR($K23/AQ23&gt;N$4,$K23/AQ23&lt;N$3),"nmf ",$K23/AQ23),"n/a ")</f>
+        <f>IFERROR(IF(OR($K23/AP23&gt;N$4,$K23/AP23&lt;N$3),"nmf ",$K23/AP23),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O23" s="16" t="str">
-        <f t="shared" ref="O23:O24" si="66">IFERROR(IF(OR($K23/AR23&gt;O$4,$K23/AR23&lt;O$3),"nmf ",$K23/AR23),"n/a ")</f>
+        <f>IFERROR(IF(OR($K23/AQ23&gt;O$4,$K23/AQ23&lt;O$3),"nmf ",$K23/AQ23),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P23" s="16" t="str">
-        <f t="shared" ref="P23:P24" si="67">IFERROR(IF(OR($K23/AT23&gt;P$4,$K23/AT23&lt;P$3),"nmf ",$K23/AT23),"n/a ")</f>
+        <f>IFERROR(IF(OR($K23/AS23&gt;P$4,$K23/AS23&lt;P$3),"nmf ",$K23/AS23),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q23" s="16" t="str">
-        <f t="shared" ref="Q23:Q24" si="68">IFERROR(IF(OR($K23/AU23&gt;Q$4,$K23/AU23&lt;Q$3),"nmf ",$K23/AU23),"n/a ")</f>
+        <f>IFERROR(IF(OR($K23/AT23&gt;Q$4,$K23/AT23&lt;Q$3),"nmf ",$K23/AT23),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R23" s="16" t="str">
-        <f t="shared" ref="R23:R24" si="69">IFERROR(IF(OR($K23/AV23&gt;R$4,$K23/AV23&lt;R$3),"nmf ",$K23/AV23),"n/a ")</f>
+        <f>IFERROR(IF(OR($K23/AU23&gt;R$4,$K23/AU23&lt;R$3),"nmf ",$K23/AU23),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S23" s="16" t="str">
-        <f t="shared" ref="S23:S24" si="70">IFERROR(IF(OR($K23/AW23&gt;S$4,$K23/AW23&lt;S$3),"nmf ",$K23/AW23),"n/a ")</f>
+        <f>IFERROR(IF(OR($K23/AV23&gt;S$4,$K23/AV23&lt;S$3),"nmf ",$K23/AV23),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T23" s="33" t="str">
-        <f t="shared" ref="T23:T24" si="71">IFERROR((AQ23/AP23)-1,"n/a ")</f>
+        <f t="shared" ref="T23:T24" si="33">IFERROR((AP23/AO23)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U23" s="33" t="str">
-        <f t="shared" ref="U23:U24" si="72">IFERROR((AR23/AQ23)-1,"n/a ")</f>
+        <f t="shared" ref="U23:U24" si="34">IFERROR((AQ23/AP23)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V23" s="16" t="str">
-        <f>IFERROR(IF(OR($H23/AY23&gt;#REF!,$H23/AY23&lt;#REF!),"nmf ",$H23/AY23),"n/a ")</f>
+        <f>IFERROR($H23/AX23,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W23" s="16" t="str">
-        <f>IFERROR(IF(OR($H23/AZ23&gt;#REF!,$H23/AZ23&lt;#REF!),"nmf ",$H23/AZ23),"n/a ")</f>
+        <f>IFERROR($H23/AY23,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X23" s="16" t="str">
-        <f>IFERROR(IF(OR($H23/BA23&gt;#REF!,$H23/BA23&lt;#REF!),"nmf ",$H23/BA23),"n/a ")</f>
+        <f>IFERROR($H23/AZ23,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y23" s="16" t="str">
-        <f>IFERROR(IF(OR($H23/BC23&gt;#REF!,$H23/BC23&lt;#REF!),"nmf ",$H23/BC23),"n/a ")</f>
+        <f>IFERROR($H23/BB23,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z23" s="16" t="str">
-        <f>IFERROR(IF(OR($H23/BD23&gt;#REF!,$H23/BD23&lt;#REF!),"nmf ",$H23/BD23),"n/a ")</f>
+        <f>IFERROR($H23/BC23,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA23" s="16" t="str">
-        <f>IFERROR(IF(OR($H23/BE23&gt;#REF!,$H23/BE23&lt;#REF!),"nmf ",$H23/BE23),"n/a ")</f>
+        <f>IFERROR($H23/BD23,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB23" s="33" t="str">
-        <f t="shared" ref="AB23:AB24" si="73">IFERROR((AS23/AR23)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="29"/>
+        <v/>
       </c>
       <c r="AC23" s="33" t="str">
-        <f t="shared" ref="AC23:AC24" si="74">IFERROR((AT23/AS23)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="29"/>
+        <v/>
       </c>
       <c r="AD23" s="33" t="str">
-        <f t="shared" ref="AD23:AD24" si="75">IFERROR((AU23/AT23)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="24"/>
+        <v/>
       </c>
       <c r="AE23" s="33" t="str">
-        <f t="shared" ref="AE23:AE24" si="76">IFERROR((AV23/AU23)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="25"/>
+        <v/>
       </c>
       <c r="AF23" s="33" t="str">
-        <f t="shared" ref="AF23:AF24" si="77">IFERROR((AW23/AV23)-1,"n/a ")</f>
+        <f t="shared" si="30"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG23" s="33" t="str">
-        <f t="shared" ref="AG23:AG24" si="78">IFERROR((BM23/AW23)-1,"n/a ")</f>
+        <f t="shared" si="30"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH23" s="33" t="str">
-        <f t="shared" ref="AH23:AH24" si="79">IFERROR((BN23/BM23)-1,"n/a ")</f>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI23" s="33" t="str">
-        <f t="shared" ref="AI23:AI24" si="80">IFERROR((BO23/BN23)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ23" s="33" t="str">
-        <f t="shared" ref="AJ23:AJ24" si="81">IFERROR((BP23/BO23)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK23" s="33" t="str">
-        <f t="shared" ref="AK23:AK24" si="82">IFERROR((BQ23/BP23)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL23" s="33" t="str">
-        <f t="shared" ref="AL23:AL24" si="83">IFERROR((BR23/BQ23)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM23" s="72"/>
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ23" s="83" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK23" s="83" t="str">
+        <f t="shared" si="32"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL23" s="72"/>
+      <c r="AN23" s="20" t="str" cm="1">
+        <f t="array" ref="AN23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO23" s="20" t="str" cm="1">
-        <f t="array" ref="AO23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP23" s="20" t="str" cm="1">
@@ -5915,12 +5935,12 @@
         <f t="array" ref="AQ23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR23" s="20" t="str" cm="1">
-        <f t="array" ref="AR23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS23" s="20" t="str" cm="1">
+        <f t="array" ref="AS23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT23" s="20" t="str" cm="1">
-        <f t="array" ref="AT23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU23" s="20" t="str" cm="1">
@@ -5931,8 +5951,8 @@
         <f t="array" ref="AV23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW23" s="20" t="str" cm="1">
-        <f t="array" ref="AW23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX23" s="13" t="str" cm="1">
+        <f t="array" ref="AX23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY23" s="13" t="str" cm="1">
@@ -5943,8 +5963,8 @@
         <f t="array" ref="AZ23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA23" s="13" t="str" cm="1">
-        <f t="array" ref="BA23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB23" s="13" t="str" cm="1">
+        <f t="array" ref="BB23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC23" s="13" t="str" cm="1">
@@ -5955,45 +5975,45 @@
         <f t="array" ref="BD23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE23" s="13" t="str" cm="1">
-        <f t="array" ref="BE23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG23" s="66" t="str" cm="1">
-        <f t="array" ref="BG23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF23" s="66" t="str" cm="1">
+        <f t="array" ref="BF23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG23" s="19" t="str" cm="1">
+        <f t="array" ref="BG23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH23" s="19" t="str" cm="1">
-        <f t="array" ref="BH23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI23" s="19" t="str" cm="1">
-        <f t="array" ref="BI23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ23" s="19" t="str" cm="1">
-        <f t="array" ref="BJ23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK23" s="37" t="e">
-        <f t="shared" ref="BK23:BK24" si="84">+BI23-BJ23</f>
+        <f t="array" ref="BI23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ23" s="37" t="e">
+        <f t="shared" ref="BJ23:BJ24" si="35">+BH23-BI23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BL23" s="19" t="str" cm="1">
-        <f t="array" ref="BL23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK23" s="19" t="str" cm="1">
+        <f t="array" ref="BK23">IF($B23="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM23" s="20" t="str">
+        <f t="shared" ref="BM23:BM24" si="36">IFERROR($AO23*$BR23,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN23" s="20" t="str">
-        <f t="shared" ref="BN23:BN24" si="85">IFERROR($AP23*$BR23,"n/a")</f>
+        <f>IFERROR($AP23*BS23,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO23" s="20" t="str">
-        <f t="shared" ref="BO23:BO24" si="86">IFERROR($AQ23*BS23,"n/a")</f>
+        <f>IFERROR($AQ23*$BT23,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP23" s="20" t="str">
-        <f t="shared" ref="BP23:BP24" si="87">IFERROR($AR23*$BT23,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ23" s="44" t="str">
+        <f>IF($B23="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR23" s="44" t="str">
         <f>IF($B23="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B23,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -6021,27 +6041,27 @@
         <v/>
       </c>
       <c r="BZ23" s="62" t="str">
-        <f t="shared" ref="BZ23:BZ24" si="88">IFERROR(IF(CD23/AP23&lt;0,"nmf ",CD23/AP23),"n/a ")</f>
+        <f>IFERROR(IF(CD23/AO23&lt;0,"nmf ",CD23/AO23),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA23" s="62" t="str">
-        <f t="shared" ref="CA23:CA24" si="89">IFERROR(IF(CE23/AQ23&lt;0,"nmf ",CE23/AQ23),"n/a ")</f>
+        <f>IFERROR(IF(CE23/AP23&lt;0,"nmf ",CE23/AP23),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB23" s="62" t="str">
-        <f t="shared" ref="CB23:CB24" si="90">IFERROR(IF(CF23/AR23&lt;0,"nmf ",CF23/AR23),"n/a ")</f>
+        <f>IFERROR(IF(CF23/AQ23&lt;0,"nmf ",CF23/AQ23),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD23" s="20" t="str">
-        <f t="shared" ref="CD23:CD24" si="91">IFERROR(BR23*AP23,"--")</f>
+        <f>IFERROR(BR23*AO23,"--")</f>
         <v>--</v>
       </c>
       <c r="CE23" s="20" t="str">
-        <f t="shared" ref="CE23:CE24" si="92">IFERROR(BS23*AQ23,"--")</f>
+        <f>IFERROR(BS23*AP23,"--")</f>
         <v>--</v>
       </c>
       <c r="CF23" s="20" t="str">
-        <f t="shared" ref="CF23:CF24" si="93">IFERROR(BT23*AR23,"--")</f>
+        <f>IFERROR(BT23*AQ23,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -6072,116 +6092,116 @@
         <v/>
       </c>
       <c r="L24" s="16" t="str">
-        <f t="shared" si="63"/>
+        <f>IFERROR(IF(OR($K24/AN24&gt;L$4,$K24/AN24&lt;L$3),"nmf ",$K24/AN24),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M24" s="16" t="str">
-        <f t="shared" si="64"/>
+        <f>IFERROR(IF(OR($K24/AO24&gt;M$4,$K24/AO24&lt;M$3),"nmf ",$K24/AO24),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N24" s="16" t="str">
-        <f t="shared" si="65"/>
+        <f>IFERROR(IF(OR($K24/AP24&gt;N$4,$K24/AP24&lt;N$3),"nmf ",$K24/AP24),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O24" s="16" t="str">
-        <f t="shared" si="66"/>
+        <f>IFERROR(IF(OR($K24/AQ24&gt;O$4,$K24/AQ24&lt;O$3),"nmf ",$K24/AQ24),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P24" s="16" t="str">
-        <f t="shared" si="67"/>
+        <f>IFERROR(IF(OR($K24/AS24&gt;P$4,$K24/AS24&lt;P$3),"nmf ",$K24/AS24),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q24" s="16" t="str">
-        <f t="shared" si="68"/>
+        <f>IFERROR(IF(OR($K24/AT24&gt;Q$4,$K24/AT24&lt;Q$3),"nmf ",$K24/AT24),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R24" s="16" t="str">
-        <f t="shared" si="69"/>
+        <f>IFERROR(IF(OR($K24/AU24&gt;R$4,$K24/AU24&lt;R$3),"nmf ",$K24/AU24),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S24" s="16" t="str">
-        <f t="shared" si="70"/>
+        <f>IFERROR(IF(OR($K24/AV24&gt;S$4,$K24/AV24&lt;S$3),"nmf ",$K24/AV24),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T24" s="33" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="33"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U24" s="33" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="34"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V24" s="16" t="str">
-        <f>IFERROR(IF(OR($H24/AY24&gt;#REF!,$H24/AY24&lt;#REF!),"nmf ",$H24/AY24),"n/a ")</f>
+        <f>IFERROR($H24/AX24,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W24" s="16" t="str">
-        <f>IFERROR(IF(OR($H24/AZ24&gt;#REF!,$H24/AZ24&lt;#REF!),"nmf ",$H24/AZ24),"n/a ")</f>
+        <f>IFERROR($H24/AY24,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X24" s="16" t="str">
-        <f>IFERROR(IF(OR($H24/BA24&gt;#REF!,$H24/BA24&lt;#REF!),"nmf ",$H24/BA24),"n/a ")</f>
+        <f>IFERROR($H24/AZ24,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y24" s="16" t="str">
-        <f>IFERROR(IF(OR($H24/BC24&gt;#REF!,$H24/BC24&lt;#REF!),"nmf ",$H24/BC24),"n/a ")</f>
+        <f>IFERROR($H24/BB24,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z24" s="16" t="str">
-        <f>IFERROR(IF(OR($H24/BD24&gt;#REF!,$H24/BD24&lt;#REF!),"nmf ",$H24/BD24),"n/a ")</f>
+        <f>IFERROR($H24/BC24,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA24" s="16" t="str">
-        <f>IFERROR(IF(OR($H24/BE24&gt;#REF!,$H24/BE24&lt;#REF!),"nmf ",$H24/BE24),"n/a ")</f>
+        <f>IFERROR($H24/BD24,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB24" s="33" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="29"/>
+        <v/>
       </c>
       <c r="AC24" s="33" t="str">
-        <f t="shared" si="74"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="29"/>
+        <v/>
       </c>
       <c r="AD24" s="33" t="str">
-        <f t="shared" si="75"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="24"/>
+        <v/>
       </c>
       <c r="AE24" s="33" t="str">
-        <f t="shared" si="76"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="25"/>
+        <v/>
       </c>
       <c r="AF24" s="33" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG24" s="33" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH24" s="33" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI24" s="33" t="str">
-        <f t="shared" si="80"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ24" s="33" t="str">
-        <f t="shared" si="81"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK24" s="33" t="str">
-        <f t="shared" si="82"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL24" s="33" t="str">
-        <f t="shared" si="83"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM24" s="72"/>
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ24" s="83" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK24" s="83" t="str">
+        <f t="shared" si="32"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL24" s="72"/>
+      <c r="AN24" s="20" t="str" cm="1">
+        <f t="array" ref="AN24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO24" s="20" t="str" cm="1">
-        <f t="array" ref="AO24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP24" s="20" t="str" cm="1">
@@ -6192,12 +6212,12 @@
         <f t="array" ref="AQ24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR24" s="20" t="str" cm="1">
-        <f t="array" ref="AR24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS24" s="20" t="str" cm="1">
+        <f t="array" ref="AS24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT24" s="20" t="str" cm="1">
-        <f t="array" ref="AT24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU24" s="20" t="str" cm="1">
@@ -6208,8 +6228,8 @@
         <f t="array" ref="AV24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW24" s="20" t="str" cm="1">
-        <f t="array" ref="AW24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX24" s="13" t="str" cm="1">
+        <f t="array" ref="AX24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY24" s="13" t="str" cm="1">
@@ -6220,8 +6240,8 @@
         <f t="array" ref="AZ24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA24" s="13" t="str" cm="1">
-        <f t="array" ref="BA24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB24" s="13" t="str" cm="1">
+        <f t="array" ref="BB24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC24" s="13" t="str" cm="1">
@@ -6232,45 +6252,45 @@
         <f t="array" ref="BD24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE24" s="13" t="str" cm="1">
-        <f t="array" ref="BE24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG24" s="66" t="str" cm="1">
-        <f t="array" ref="BG24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF24" s="66" t="str" cm="1">
+        <f t="array" ref="BF24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG24" s="19" t="str" cm="1">
+        <f t="array" ref="BG24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH24" s="19" t="str" cm="1">
-        <f t="array" ref="BH24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI24" s="19" t="str" cm="1">
-        <f t="array" ref="BI24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ24" s="19" t="str" cm="1">
-        <f t="array" ref="BJ24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK24" s="37" t="e">
-        <f t="shared" si="84"/>
+        <f t="array" ref="BI24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ24" s="37" t="e">
+        <f t="shared" si="35"/>
         <v>#VALUE!</v>
       </c>
-      <c r="BL24" s="19" t="str" cm="1">
-        <f t="array" ref="BL24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK24" s="19" t="str" cm="1">
+        <f t="array" ref="BK24">IF($B24="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM24" s="20" t="str">
+        <f t="shared" si="36"/>
+        <v>n/a</v>
       </c>
       <c r="BN24" s="20" t="str">
-        <f t="shared" si="85"/>
+        <f>IFERROR($AP24*BS24,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO24" s="20" t="str">
-        <f t="shared" si="86"/>
+        <f>IFERROR($AQ24*$BT24,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP24" s="20" t="str">
-        <f t="shared" si="87"/>
-        <v>n/a</v>
+      <c r="BQ24" s="44" t="str">
+        <f>IF($B24="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR24" s="44" t="str">
         <f>IF($B24="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B24,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -6298,27 +6318,27 @@
         <v/>
       </c>
       <c r="BZ24" s="62" t="str">
-        <f t="shared" si="88"/>
+        <f>IFERROR(IF(CD24/AO24&lt;0,"nmf ",CD24/AO24),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA24" s="62" t="str">
-        <f t="shared" si="89"/>
+        <f>IFERROR(IF(CE24/AP24&lt;0,"nmf ",CE24/AP24),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB24" s="62" t="str">
-        <f t="shared" si="90"/>
+        <f>IFERROR(IF(CF24/AQ24&lt;0,"nmf ",CF24/AQ24),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD24" s="20" t="str">
-        <f t="shared" si="91"/>
+        <f>IFERROR(BR24*AO24,"--")</f>
         <v>--</v>
       </c>
       <c r="CE24" s="20" t="str">
-        <f t="shared" si="92"/>
+        <f>IFERROR(BS24*AP24,"--")</f>
         <v>--</v>
       </c>
       <c r="CF24" s="20" t="str">
-        <f t="shared" si="93"/>
+        <f>IFERROR(BT24*AQ24,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -6349,116 +6369,116 @@
         <v/>
       </c>
       <c r="L25" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K25/AN25&gt;L$4,$K25/AN25&lt;L$3),"nmf ",$K25/AN25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M25" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K25/AO25&gt;M$4,$K25/AO25&lt;M$3),"nmf ",$K25/AO25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N25" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K25/AP25&gt;N$4,$K25/AP25&lt;N$3),"nmf ",$K25/AP25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O25" s="16" t="str">
-        <f t="shared" si="46"/>
+        <f>IFERROR(IF(OR($K25/AQ25&gt;O$4,$K25/AQ25&lt;O$3),"nmf ",$K25/AQ25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P25" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K25/AS25&gt;P$4,$K25/AS25&lt;P$3),"nmf ",$K25/AS25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q25" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K25/AT25&gt;Q$4,$K25/AT25&lt;Q$3),"nmf ",$K25/AT25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R25" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K25/AU25&gt;R$4,$K25/AU25&lt;R$3),"nmf ",$K25/AU25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S25" s="16" t="str">
-        <f t="shared" si="47"/>
+        <f>IFERROR(IF(OR($K25/AV25&gt;S$4,$K25/AV25&lt;S$3),"nmf ",$K25/AV25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T25" s="33" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U25" s="33" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="23"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V25" s="16" t="str">
-        <f>IFERROR(IF(OR($H25/AY25&gt;#REF!,$H25/AY25&lt;#REF!),"nmf ",$H25/AY25),"n/a ")</f>
+        <f>IFERROR($H25/AX25,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W25" s="16" t="str">
-        <f>IFERROR(IF(OR($H25/AZ25&gt;#REF!,$H25/AZ25&lt;#REF!),"nmf ",$H25/AZ25),"n/a ")</f>
+        <f>IFERROR($H25/AY25,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X25" s="16" t="str">
-        <f>IFERROR(IF(OR($H25/BA25&gt;#REF!,$H25/BA25&lt;#REF!),"nmf ",$H25/BA25),"n/a ")</f>
+        <f>IFERROR($H25/AZ25,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y25" s="16" t="str">
-        <f>IFERROR(IF(OR($H25/BC25&gt;#REF!,$H25/BC25&lt;#REF!),"nmf ",$H25/BC25),"n/a ")</f>
+        <f>IFERROR($H25/BB25,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z25" s="16" t="str">
-        <f>IFERROR(IF(OR($H25/BD25&gt;#REF!,$H25/BD25&lt;#REF!),"nmf ",$H25/BD25),"n/a ")</f>
+        <f>IFERROR($H25/BC25,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA25" s="16" t="str">
-        <f>IFERROR(IF(OR($H25/BE25&gt;#REF!,$H25/BE25&lt;#REF!),"nmf ",$H25/BE25),"n/a ")</f>
+        <f>IFERROR($H25/BD25,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB25" s="33" t="str">
-        <f t="shared" si="49"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="29"/>
+        <v/>
       </c>
       <c r="AC25" s="33" t="str">
-        <f t="shared" si="50"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="29"/>
+        <v/>
       </c>
       <c r="AD25" s="33" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="24"/>
+        <v/>
       </c>
       <c r="AE25" s="33" t="str">
-        <f t="shared" si="52"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="25"/>
+        <v/>
       </c>
       <c r="AF25" s="33" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="30"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG25" s="33" t="str">
-        <f>IFERROR((BM25/AW25)-1,"n/a ")</f>
+        <f t="shared" si="30"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH25" s="33" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="26"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI25" s="33" t="str">
-        <f t="shared" si="55"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ25" s="33" t="str">
-        <f t="shared" si="56"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK25" s="33" t="str">
-        <f t="shared" si="57"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL25" s="33" t="str">
-        <f t="shared" si="58"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM25" s="72"/>
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ25" s="83" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK25" s="83" t="str">
+        <f t="shared" si="32"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL25" s="72"/>
+      <c r="AN25" s="20" t="str" cm="1">
+        <f t="array" ref="AN25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO25" s="20" t="str" cm="1">
-        <f t="array" ref="AO25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP25" s="20" t="str" cm="1">
@@ -6469,12 +6489,12 @@
         <f t="array" ref="AQ25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR25" s="20" t="str" cm="1">
-        <f t="array" ref="AR25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS25" s="20" t="str" cm="1">
+        <f t="array" ref="AS25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT25" s="20" t="str" cm="1">
-        <f t="array" ref="AT25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU25" s="20" t="str" cm="1">
@@ -6485,8 +6505,8 @@
         <f t="array" ref="AV25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW25" s="20" t="str" cm="1">
-        <f t="array" ref="AW25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX25" s="13" t="str" cm="1">
+        <f t="array" ref="AX25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY25" s="13" t="str" cm="1">
@@ -6497,8 +6517,8 @@
         <f t="array" ref="AZ25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA25" s="13" t="str" cm="1">
-        <f t="array" ref="BA25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB25" s="13" t="str" cm="1">
+        <f t="array" ref="BB25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC25" s="13" t="str" cm="1">
@@ -6509,45 +6529,45 @@
         <f t="array" ref="BD25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE25" s="13" t="str" cm="1">
-        <f t="array" ref="BE25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG25" s="66" t="str" cm="1">
-        <f t="array" ref="BG25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF25" s="66" t="str" cm="1">
+        <f t="array" ref="BF25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG25" s="19" t="str" cm="1">
+        <f t="array" ref="BG25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH25" s="19" t="str" cm="1">
-        <f t="array" ref="BH25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI25" s="19" t="str" cm="1">
-        <f t="array" ref="BI25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ25" s="19" t="str" cm="1">
-        <f t="array" ref="BJ25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK25" s="37" t="e">
-        <f>+BI25-BJ25</f>
+        <f t="array" ref="BI25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ25" s="37" t="e">
+        <f>+BH25-BI25</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BL25" s="19" t="str" cm="1">
-        <f t="array" ref="BL25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK25" s="19" t="str" cm="1">
+        <f t="array" ref="BK25">IF($B25="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM25" s="20" t="str">
+        <f>IFERROR($AO25*$BR25,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN25" s="20" t="str">
-        <f>IFERROR($AP25*$BR25,"n/a")</f>
+        <f>IFERROR($AP25*BS25,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO25" s="20" t="str">
-        <f t="shared" si="60"/>
+        <f>IFERROR($AQ25*$BT25,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP25" s="20" t="str">
-        <f>IFERROR($AR25*$BT25,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ25" s="44" t="str">
+        <f>IF($B25="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR25" s="44" t="str">
         <f>IF($B25="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B25,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -6575,27 +6595,27 @@
         <v/>
       </c>
       <c r="BZ25" s="62" t="str">
-        <f t="shared" si="61"/>
+        <f>IFERROR(IF(CD25/AO25&lt;0,"nmf ",CD25/AO25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA25" s="62" t="str">
-        <f t="shared" si="61"/>
+        <f>IFERROR(IF(CE25/AP25&lt;0,"nmf ",CE25/AP25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB25" s="62" t="str">
-        <f t="shared" si="61"/>
+        <f>IFERROR(IF(CF25/AQ25&lt;0,"nmf ",CF25/AQ25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD25" s="20" t="str">
-        <f t="shared" si="62"/>
+        <f>IFERROR(BR25*AO25,"--")</f>
         <v>--</v>
       </c>
       <c r="CE25" s="20" t="str">
-        <f t="shared" si="62"/>
+        <f>IFERROR(BS25*AP25,"--")</f>
         <v>--</v>
       </c>
       <c r="CF25" s="20" t="str">
-        <f t="shared" si="62"/>
+        <f>IFERROR(BT25*AQ25,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -6633,23 +6653,22 @@
       <c r="AJ26" s="17"/>
       <c r="AK26" s="17"/>
       <c r="AL26" s="17"/>
-      <c r="AM26" s="17"/>
-      <c r="AO26" s="19"/>
+      <c r="AN26" s="19"/>
+      <c r="AO26" s="13"/>
       <c r="AP26" s="13"/>
       <c r="AQ26" s="13"/>
-      <c r="AR26" s="13"/>
+      <c r="AT26" s="20"/>
       <c r="AU26" s="20"/>
       <c r="AV26" s="20"/>
-      <c r="AW26" s="20"/>
+      <c r="AX26" s="13"/>
       <c r="AY26" s="13"/>
       <c r="AZ26" s="13"/>
-      <c r="BA26" s="13"/>
+      <c r="BF26" s="19"/>
       <c r="BG26" s="19"/>
       <c r="BH26" s="19"/>
       <c r="BI26" s="19"/>
       <c r="BJ26" s="19"/>
       <c r="BK26" s="19"/>
-      <c r="BL26" s="19"/>
       <c r="BR26" s="45"/>
       <c r="BS26" s="45"/>
       <c r="BT26" s="45"/>
@@ -6690,98 +6709,94 @@
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P27" s="26" t="str">
-        <f t="shared" ref="P27" si="94">IFERROR(AVERAGE(P20:P25),"n/a ")</f>
+        <f t="shared" ref="P27" si="37">IFERROR(AVERAGE(P20:P25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q27" s="26" t="str">
-        <f t="shared" ref="Q27:AL27" si="95">IFERROR(AVERAGE(Q20:Q25),"n/a ")</f>
+        <f t="shared" ref="Q27:AK27" si="38">IFERROR(AVERAGE(Q20:Q25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R27" s="26" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S27" s="26" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T27" s="36" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U27" s="36" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V27" s="26" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W27" s="26" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X27" s="26" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y27" s="26" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z27" s="26" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA27" s="26" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB27" s="36" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" ref="AB27" si="39">IFERROR(AVERAGE(AB20:AB25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AC27" s="36" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AD27" s="36" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AE27" s="36" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AF27" s="36" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" ref="AF27" si="40">IFERROR(AVERAGE(AF20:AF25),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG27" s="36" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH27" s="36" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="38"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI27" s="36" t="str">
-        <f t="shared" si="95"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ27" s="36" t="str">
-        <f t="shared" si="95"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK27" s="36" t="str">
-        <f t="shared" si="95"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL27" s="36" t="str">
-        <f t="shared" si="95"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM27" s="36"/>
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ27" s="84" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK27" s="84" t="str">
+        <f t="shared" si="38"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL27" s="36"/>
       <c r="BR27" s="45"/>
       <c r="BS27" s="45"/>
       <c r="BT27" s="45"/>
@@ -6799,10 +6814,10 @@
       <c r="J28" s="28"/>
       <c r="K28" s="28"/>
       <c r="L28" s="28"/>
+      <c r="AT28" s="27"/>
       <c r="AU28" s="27"/>
       <c r="AV28" s="27"/>
-      <c r="AW28" s="27"/>
-      <c r="BG28" s="67"/>
+      <c r="BF28" s="67"/>
       <c r="BR28" s="45"/>
       <c r="BS28" s="45"/>
       <c r="BT28" s="45"/>
@@ -6817,7 +6832,7 @@
     <row r="29" spans="2:84" s="10" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="11"/>
       <c r="D29" s="71" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
@@ -6851,23 +6866,22 @@
       <c r="AJ29" s="17"/>
       <c r="AK29" s="17"/>
       <c r="AL29" s="17"/>
-      <c r="AM29" s="17"/>
+      <c r="AN29" s="13"/>
       <c r="AO29" s="13"/>
       <c r="AP29" s="13"/>
       <c r="AQ29" s="13"/>
-      <c r="AR29" s="13"/>
+      <c r="AT29" s="20"/>
       <c r="AU29" s="20"/>
       <c r="AV29" s="20"/>
-      <c r="AW29" s="20"/>
+      <c r="AX29" s="13"/>
       <c r="AY29" s="13"/>
       <c r="AZ29" s="13"/>
-      <c r="BA29" s="13"/>
-      <c r="BG29" s="66"/>
+      <c r="BF29" s="66"/>
+      <c r="BG29" s="19"/>
       <c r="BH29" s="19"/>
       <c r="BI29" s="19"/>
       <c r="BJ29" s="19"/>
       <c r="BK29" s="19"/>
-      <c r="BL29" s="19"/>
       <c r="BR29" s="45"/>
       <c r="BS29" s="45"/>
       <c r="BT29" s="45"/>
@@ -6906,116 +6920,116 @@
         <v/>
       </c>
       <c r="L30" s="16" t="str">
-        <f t="shared" ref="L30:L35" si="96">IFERROR(IF(OR($K30/AO30&gt;L$4,$K30/AO30&lt;L$3),"nmf ",$K30/AO30),"n/a ")</f>
+        <f>IFERROR(IF(OR($K30/AN30&gt;L$4,$K30/AN30&lt;L$3),"nmf ",$K30/AN30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M30" s="16" t="str">
-        <f t="shared" ref="M30:M35" si="97">IFERROR(IF(OR($K30/AP30&gt;M$4,$K30/AP30&lt;M$3),"nmf ",$K30/AP30),"n/a ")</f>
+        <f>IFERROR(IF(OR($K30/AO30&gt;M$4,$K30/AO30&lt;M$3),"nmf ",$K30/AO30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N30" s="16" t="str">
-        <f t="shared" ref="N30:N35" si="98">IFERROR(IF(OR($K30/AQ30&gt;N$4,$K30/AQ30&lt;N$3),"nmf ",$K30/AQ30),"n/a ")</f>
+        <f>IFERROR(IF(OR($K30/AP30&gt;N$4,$K30/AP30&lt;N$3),"nmf ",$K30/AP30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O30" s="16" t="str">
-        <f t="shared" ref="O30:O35" si="99">IFERROR(IF(OR($K30/AR30&gt;O$4,$K30/AR30&lt;O$3),"nmf ",$K30/AR30),"n/a ")</f>
+        <f>IFERROR(IF(OR($K30/AQ30&gt;O$4,$K30/AQ30&lt;O$3),"nmf ",$K30/AQ30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P30" s="16" t="str">
-        <f t="shared" ref="P30:P35" si="100">IFERROR(IF(OR($K30/AT30&gt;P$4,$K30/AT30&lt;P$3),"nmf ",$K30/AT30),"n/a ")</f>
+        <f>IFERROR(IF(OR($K30/AS30&gt;P$4,$K30/AS30&lt;P$3),"nmf ",$K30/AS30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q30" s="16" t="str">
-        <f t="shared" ref="Q30:Q35" si="101">IFERROR(IF(OR($K30/AU30&gt;Q$4,$K30/AU30&lt;Q$3),"nmf ",$K30/AU30),"n/a ")</f>
+        <f>IFERROR(IF(OR($K30/AT30&gt;Q$4,$K30/AT30&lt;Q$3),"nmf ",$K30/AT30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R30" s="16" t="str">
-        <f t="shared" ref="R30:R35" si="102">IFERROR(IF(OR($K30/AV30&gt;R$4,$K30/AV30&lt;R$3),"nmf ",$K30/AV30),"n/a ")</f>
+        <f>IFERROR(IF(OR($K30/AU30&gt;R$4,$K30/AU30&lt;R$3),"nmf ",$K30/AU30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S30" s="16" t="str">
-        <f t="shared" ref="S30:S35" si="103">IFERROR(IF(OR($K30/AW30&gt;S$4,$K30/AW30&lt;S$3),"nmf ",$K30/AW30),"n/a ")</f>
+        <f>IFERROR(IF(OR($K30/AV30&gt;S$4,$K30/AV30&lt;S$3),"nmf ",$K30/AV30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T30" s="33" t="str">
-        <f t="shared" ref="T30:T35" si="104">IFERROR((AQ30/AP30)-1,"n/a ")</f>
+        <f t="shared" ref="T30:T35" si="41">IFERROR((AP30/AO30)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U30" s="33" t="str">
-        <f t="shared" ref="U30:U35" si="105">IFERROR((AR30/AQ30)-1,"n/a ")</f>
+        <f t="shared" ref="U30:U35" si="42">IFERROR((AQ30/AP30)-1,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V30" s="16" t="str">
-        <f>IFERROR(IF(OR($H30/AY30&gt;#REF!,$H30/AY30&lt;#REF!),"nmf ",$H30/AY30),"n/a ")</f>
+        <f>IFERROR($H30/AX30,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W30" s="16" t="str">
-        <f>IFERROR(IF(OR($H30/AZ30&gt;#REF!,$H30/AZ30&lt;#REF!),"nmf ",$H30/AZ30),"n/a ")</f>
+        <f>IFERROR($H30/AY30,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X30" s="16" t="str">
-        <f>IFERROR(IF(OR($H30/BA30&gt;#REF!,$H30/BA30&lt;#REF!),"nmf ",$H30/BA30),"n/a ")</f>
+        <f>IFERROR($H30/AZ30,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y30" s="16" t="str">
-        <f>IFERROR(IF(OR($H30/BC30&gt;#REF!,$H30/BC30&lt;#REF!),"nmf ",$H30/BC30),"n/a ")</f>
+        <f>IFERROR($H30/BB30,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z30" s="16" t="str">
-        <f>IFERROR(IF(OR($H30/BD30&gt;#REF!,$H30/BD30&lt;#REF!),"nmf ",$H30/BD30),"n/a ")</f>
+        <f>IFERROR($H30/BC30,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA30" s="16" t="str">
-        <f>IFERROR(IF(OR($H30/BE30&gt;#REF!,$H30/BE30&lt;#REF!),"nmf ",$H30/BE30),"n/a ")</f>
+        <f>IFERROR($H30/BD30,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB30" s="33" t="str">
-        <f t="shared" ref="AB30:AB35" si="106">IFERROR((AS30/AR30)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f>IFERROR(IF(BQ30="--","n/a ",BQ30),"n/a ")</f>
+        <v/>
       </c>
       <c r="AC30" s="33" t="str">
-        <f t="shared" ref="AC30:AC35" si="107">IFERROR((AT30/AS30)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f>IFERROR(IF(BR30="--","n/a ",BR30),"n/a ")</f>
+        <v/>
       </c>
       <c r="AD30" s="33" t="str">
-        <f t="shared" ref="AD30:AD35" si="108">IFERROR((AU30/AT30)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" ref="AD30:AD35" si="43">IFERROR(IF(BS30="--","n/a ",BS30),"n/a ")</f>
+        <v/>
       </c>
       <c r="AE30" s="33" t="str">
-        <f t="shared" ref="AE30:AE35" si="109">IFERROR((AV30/AU30)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" ref="AE30:AE35" si="44">IFERROR(IF(BT30="--","n/a ",BT30),"n/a ")</f>
+        <v/>
       </c>
       <c r="AF30" s="33" t="str">
-        <f t="shared" ref="AF30:AF35" si="110">IFERROR((AW30/AV30)-1,"n/a ")</f>
+        <f>IFERROR((AS30/AN30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG30" s="33" t="str">
-        <f>IFERROR((BM30/AW30)-1,"n/a ")</f>
+        <f>IFERROR((AT30/AO30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH30" s="33" t="str">
-        <f t="shared" ref="AH30:AH35" si="111">IFERROR((BN30/BM30)-1,"n/a ")</f>
+        <f t="shared" ref="AH30:AH35" si="45">IFERROR((AU30/AP30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI30" s="33" t="str">
-        <f t="shared" ref="AI30:AI35" si="112">IFERROR((BO30/BN30)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ30" s="33" t="str">
-        <f t="shared" ref="AJ30:AJ35" si="113">IFERROR((BP30/BO30)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK30" s="33" t="str">
-        <f t="shared" ref="AK30:AK35" si="114">IFERROR((BQ30/BP30)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL30" s="33" t="str">
-        <f t="shared" ref="AL30:AL35" si="115">IFERROR((BR30/BQ30)-1,"n/a ")</f>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM30" s="72"/>
+        <f t="shared" ref="AI30:AI35" si="46">IFERROR((AV30/AQ30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ30" s="83" t="str">
+        <f>IFERROR((BJ30/AT30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK30" s="83" t="str">
+        <f>IFERROR((BJ30/AU30),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL30" s="72"/>
+      <c r="AN30" s="20" t="str" cm="1">
+        <f t="array" ref="AN30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO30" s="20" t="str" cm="1">
-        <f t="array" ref="AO30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP30" s="20" t="str" cm="1">
@@ -7026,12 +7040,12 @@
         <f t="array" ref="AQ30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR30" s="20" t="str" cm="1">
-        <f t="array" ref="AR30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS30" s="20" t="str" cm="1">
+        <f t="array" ref="AS30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT30" s="20" t="str" cm="1">
-        <f t="array" ref="AT30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU30" s="20" t="str" cm="1">
@@ -7042,8 +7056,8 @@
         <f t="array" ref="AV30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW30" s="20" t="str" cm="1">
-        <f t="array" ref="AW30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX30" s="13" t="str" cm="1">
+        <f t="array" ref="AX30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY30" s="13" t="str" cm="1">
@@ -7054,8 +7068,8 @@
         <f t="array" ref="AZ30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA30" s="13" t="str" cm="1">
-        <f t="array" ref="BA30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB30" s="13" t="str" cm="1">
+        <f t="array" ref="BB30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC30" s="13" t="str" cm="1">
@@ -7066,45 +7080,45 @@
         <f t="array" ref="BD30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE30" s="13" t="str" cm="1">
-        <f t="array" ref="BE30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG30" s="66" t="str" cm="1">
-        <f t="array" ref="BG30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF30" s="66" t="str" cm="1">
+        <f t="array" ref="BF30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG30" s="19" t="str" cm="1">
+        <f t="array" ref="BG30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH30" s="19" t="str" cm="1">
-        <f t="array" ref="BH30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI30" s="19" t="str" cm="1">
-        <f t="array" ref="BI30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ30" s="19" t="str" cm="1">
-        <f t="array" ref="BJ30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK30" s="37" t="e">
-        <f t="shared" ref="BK30:BK34" si="116">+BI30-BJ30</f>
+        <f t="array" ref="BI30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ30" s="37" t="e">
+        <f t="shared" ref="BJ30:BJ34" si="47">+BH30-BI30</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BL30" s="19" t="str" cm="1">
-        <f t="array" ref="BL30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK30" s="19" t="str" cm="1">
+        <f t="array" ref="BK30">IF($B30="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM30" s="20" t="str">
+        <f>IFERROR($AO30*$BR30,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN30" s="20" t="str">
-        <f>IFERROR($AP30*$BR30,"n/a")</f>
+        <f>IFERROR($AP30*BS30,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO30" s="20" t="str">
-        <f t="shared" ref="BO30:BO35" si="117">IFERROR($AQ30*BS30,"n/a")</f>
+        <f>IFERROR($AQ30*$BT30,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP30" s="20" t="str">
-        <f>IFERROR($AR30*$BT30,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ30" s="44" t="str">
+        <f>IF($B30="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR30" s="44" t="str">
         <f>IF($B30="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B30,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -7132,27 +7146,27 @@
         <v/>
       </c>
       <c r="BZ30" s="62" t="str">
-        <f t="shared" ref="BZ30:BZ35" si="118">IFERROR(IF(CD30/AP30&lt;0,"nmf ",CD30/AP30),"n/a ")</f>
+        <f>IFERROR(IF(CD30/AO30&lt;0,"nmf ",CD30/AO30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA30" s="62" t="str">
-        <f t="shared" ref="CA30:CA35" si="119">IFERROR(IF(CE30/AQ30&lt;0,"nmf ",CE30/AQ30),"n/a ")</f>
+        <f>IFERROR(IF(CE30/AP30&lt;0,"nmf ",CE30/AP30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB30" s="62" t="str">
-        <f t="shared" ref="CB30:CB35" si="120">IFERROR(IF(CF30/AR30&lt;0,"nmf ",CF30/AR30),"n/a ")</f>
+        <f>IFERROR(IF(CF30/AQ30&lt;0,"nmf ",CF30/AQ30),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD30" s="20" t="str">
-        <f t="shared" ref="CD30:CD35" si="121">IFERROR(BR30*AP30,"--")</f>
+        <f>IFERROR(BR30*AO30,"--")</f>
         <v>--</v>
       </c>
       <c r="CE30" s="20" t="str">
-        <f t="shared" ref="CE30:CE35" si="122">IFERROR(BS30*AQ30,"--")</f>
+        <f>IFERROR(BS30*AP30,"--")</f>
         <v>--</v>
       </c>
       <c r="CF30" s="20" t="str">
-        <f t="shared" ref="CF30:CF35" si="123">IFERROR(BT30*AR30,"--")</f>
+        <f>IFERROR(BT30*AQ30,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -7183,116 +7197,116 @@
         <v/>
       </c>
       <c r="L31" s="16" t="str">
-        <f t="shared" si="96"/>
+        <f>IFERROR(IF(OR($K31/AN31&gt;L$4,$K31/AN31&lt;L$3),"nmf ",$K31/AN31),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M31" s="16" t="str">
-        <f t="shared" si="97"/>
+        <f>IFERROR(IF(OR($K31/AO31&gt;M$4,$K31/AO31&lt;M$3),"nmf ",$K31/AO31),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N31" s="16" t="str">
-        <f t="shared" si="98"/>
+        <f>IFERROR(IF(OR($K31/AP31&gt;N$4,$K31/AP31&lt;N$3),"nmf ",$K31/AP31),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O31" s="16" t="str">
-        <f t="shared" si="99"/>
+        <f>IFERROR(IF(OR($K31/AQ31&gt;O$4,$K31/AQ31&lt;O$3),"nmf ",$K31/AQ31),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P31" s="16" t="str">
-        <f t="shared" si="100"/>
+        <f>IFERROR(IF(OR($K31/AS31&gt;P$4,$K31/AS31&lt;P$3),"nmf ",$K31/AS31),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q31" s="16" t="str">
-        <f t="shared" si="101"/>
+        <f>IFERROR(IF(OR($K31/AT31&gt;Q$4,$K31/AT31&lt;Q$3),"nmf ",$K31/AT31),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R31" s="16" t="str">
-        <f t="shared" si="102"/>
+        <f>IFERROR(IF(OR($K31/AU31&gt;R$4,$K31/AU31&lt;R$3),"nmf ",$K31/AU31),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S31" s="16" t="str">
-        <f t="shared" si="103"/>
+        <f>IFERROR(IF(OR($K31/AV31&gt;S$4,$K31/AV31&lt;S$3),"nmf ",$K31/AV31),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T31" s="33" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="41"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U31" s="33" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="42"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V31" s="16" t="str">
-        <f>IFERROR(IF(OR($H31/AY31&gt;#REF!,$H31/AY31&lt;#REF!),"nmf ",$H31/AY31),"n/a ")</f>
+        <f>IFERROR($H31/AX31,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W31" s="16" t="str">
-        <f>IFERROR(IF(OR($H31/AZ31&gt;#REF!,$H31/AZ31&lt;#REF!),"nmf ",$H31/AZ31),"n/a ")</f>
+        <f>IFERROR($H31/AY31,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X31" s="16" t="str">
-        <f>IFERROR(IF(OR($H31/BA31&gt;#REF!,$H31/BA31&lt;#REF!),"nmf ",$H31/BA31),"n/a ")</f>
+        <f>IFERROR($H31/AZ31,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y31" s="16" t="str">
-        <f>IFERROR(IF(OR($H31/BC31&gt;#REF!,$H31/BC31&lt;#REF!),"nmf ",$H31/BC31),"n/a ")</f>
+        <f>IFERROR($H31/BB31,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z31" s="16" t="str">
-        <f>IFERROR(IF(OR($H31/BD31&gt;#REF!,$H31/BD31&lt;#REF!),"nmf ",$H31/BD31),"n/a ")</f>
+        <f>IFERROR($H31/BC31,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA31" s="16" t="str">
-        <f>IFERROR(IF(OR($H31/BE31&gt;#REF!,$H31/BE31&lt;#REF!),"nmf ",$H31/BE31),"n/a ")</f>
+        <f>IFERROR($H31/BD31,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB31" s="33" t="str">
-        <f t="shared" si="106"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" ref="AB31:AC35" si="48">IFERROR(IF(BQ31="--","n/a ",BQ31),"n/a ")</f>
+        <v/>
       </c>
       <c r="AC31" s="33" t="str">
-        <f t="shared" si="107"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="48"/>
+        <v/>
       </c>
       <c r="AD31" s="33" t="str">
-        <f t="shared" si="108"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="43"/>
+        <v/>
       </c>
       <c r="AE31" s="33" t="str">
-        <f t="shared" si="109"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="44"/>
+        <v/>
       </c>
       <c r="AF31" s="33" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" ref="AF31:AG35" si="49">IFERROR((AS31/AN31),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG31" s="33" t="str">
-        <f>IFERROR((BM31/AW31)-1,"n/a ")</f>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH31" s="33" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI31" s="33" t="str">
-        <f t="shared" si="112"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ31" s="33" t="str">
-        <f t="shared" si="113"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK31" s="33" t="str">
-        <f t="shared" si="114"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL31" s="33" t="str">
-        <f t="shared" si="115"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM31" s="72"/>
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ31" s="83" t="str">
+        <f t="shared" ref="AJ31:AJ35" si="50">IFERROR((BJ31/AT31),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK31" s="83" t="str">
+        <f t="shared" ref="AK31:AK35" si="51">IFERROR((BJ31/AU31),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL31" s="72"/>
+      <c r="AN31" s="20" t="str" cm="1">
+        <f t="array" ref="AN31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO31" s="20" t="str" cm="1">
-        <f t="array" ref="AO31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP31" s="20" t="str" cm="1">
@@ -7303,12 +7317,12 @@
         <f t="array" ref="AQ31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR31" s="20" t="str" cm="1">
-        <f t="array" ref="AR31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS31" s="20" t="str" cm="1">
+        <f t="array" ref="AS31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT31" s="20" t="str" cm="1">
-        <f t="array" ref="AT31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU31" s="20" t="str" cm="1">
@@ -7319,8 +7333,8 @@
         <f t="array" ref="AV31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW31" s="20" t="str" cm="1">
-        <f t="array" ref="AW31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX31" s="13" t="str" cm="1">
+        <f t="array" ref="AX31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY31" s="13" t="str" cm="1">
@@ -7331,8 +7345,8 @@
         <f t="array" ref="AZ31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA31" s="13" t="str" cm="1">
-        <f t="array" ref="BA31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB31" s="13" t="str" cm="1">
+        <f t="array" ref="BB31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC31" s="13" t="str" cm="1">
@@ -7343,45 +7357,45 @@
         <f t="array" ref="BD31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE31" s="13" t="str" cm="1">
-        <f t="array" ref="BE31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG31" s="66" t="str" cm="1">
-        <f t="array" ref="BG31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF31" s="66" t="str" cm="1">
+        <f t="array" ref="BF31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG31" s="19" t="str" cm="1">
+        <f t="array" ref="BG31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH31" s="19" t="str" cm="1">
-        <f t="array" ref="BH31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI31" s="19" t="str" cm="1">
-        <f t="array" ref="BI31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ31" s="19" t="str" cm="1">
-        <f t="array" ref="BJ31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK31" s="37" t="e">
-        <f t="shared" si="116"/>
+        <f t="array" ref="BI31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ31" s="37" t="e">
+        <f t="shared" si="47"/>
         <v>#VALUE!</v>
       </c>
-      <c r="BL31" s="19" t="str" cm="1">
-        <f t="array" ref="BL31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK31" s="19" t="str" cm="1">
+        <f t="array" ref="BK31">IF($B31="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM31" s="20" t="str">
+        <f>IFERROR($AO31*$BR31,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN31" s="20" t="str">
-        <f>IFERROR($AP31*$BR31,"n/a")</f>
+        <f>IFERROR($AP31*BS31,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO31" s="20" t="str">
-        <f t="shared" si="117"/>
+        <f>IFERROR($AQ31*$BT31,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP31" s="20" t="str">
-        <f>IFERROR($AR31*$BT31,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ31" s="44" t="str">
+        <f>IF($B31="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR31" s="44" t="str">
         <f>IF($B31="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B31,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -7409,27 +7423,27 @@
         <v/>
       </c>
       <c r="BZ31" s="62" t="str">
-        <f t="shared" si="118"/>
+        <f>IFERROR(IF(CD31/AO31&lt;0,"nmf ",CD31/AO31),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA31" s="62" t="str">
-        <f t="shared" si="119"/>
+        <f>IFERROR(IF(CE31/AP31&lt;0,"nmf ",CE31/AP31),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB31" s="62" t="str">
-        <f t="shared" si="120"/>
+        <f>IFERROR(IF(CF31/AQ31&lt;0,"nmf ",CF31/AQ31),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD31" s="20" t="str">
-        <f t="shared" si="121"/>
+        <f>IFERROR(BR31*AO31,"--")</f>
         <v>--</v>
       </c>
       <c r="CE31" s="20" t="str">
-        <f t="shared" si="122"/>
+        <f>IFERROR(BS31*AP31,"--")</f>
         <v>--</v>
       </c>
       <c r="CF31" s="20" t="str">
-        <f t="shared" si="123"/>
+        <f>IFERROR(BT31*AQ31,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -7460,116 +7474,116 @@
         <v/>
       </c>
       <c r="L32" s="16" t="str">
-        <f t="shared" si="96"/>
+        <f>IFERROR(IF(OR($K32/AN32&gt;L$4,$K32/AN32&lt;L$3),"nmf ",$K32/AN32),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M32" s="16" t="str">
-        <f t="shared" si="97"/>
+        <f>IFERROR(IF(OR($K32/AO32&gt;M$4,$K32/AO32&lt;M$3),"nmf ",$K32/AO32),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N32" s="16" t="str">
-        <f t="shared" si="98"/>
+        <f>IFERROR(IF(OR($K32/AP32&gt;N$4,$K32/AP32&lt;N$3),"nmf ",$K32/AP32),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O32" s="16" t="str">
-        <f t="shared" si="99"/>
+        <f>IFERROR(IF(OR($K32/AQ32&gt;O$4,$K32/AQ32&lt;O$3),"nmf ",$K32/AQ32),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P32" s="16" t="str">
-        <f t="shared" si="100"/>
+        <f>IFERROR(IF(OR($K32/AS32&gt;P$4,$K32/AS32&lt;P$3),"nmf ",$K32/AS32),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q32" s="16" t="str">
-        <f t="shared" si="101"/>
+        <f>IFERROR(IF(OR($K32/AT32&gt;Q$4,$K32/AT32&lt;Q$3),"nmf ",$K32/AT32),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R32" s="16" t="str">
-        <f t="shared" si="102"/>
+        <f>IFERROR(IF(OR($K32/AU32&gt;R$4,$K32/AU32&lt;R$3),"nmf ",$K32/AU32),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S32" s="16" t="str">
-        <f t="shared" si="103"/>
+        <f>IFERROR(IF(OR($K32/AV32&gt;S$4,$K32/AV32&lt;S$3),"nmf ",$K32/AV32),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T32" s="33" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="41"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U32" s="33" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="42"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V32" s="16" t="str">
-        <f>IFERROR(IF(OR($H32/AY32&gt;#REF!,$H32/AY32&lt;#REF!),"nmf ",$H32/AY32),"n/a ")</f>
+        <f>IFERROR($H32/AX32,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W32" s="16" t="str">
-        <f>IFERROR(IF(OR($H32/AZ32&gt;#REF!,$H32/AZ32&lt;#REF!),"nmf ",$H32/AZ32),"n/a ")</f>
+        <f>IFERROR($H32/AY32,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X32" s="16" t="str">
-        <f>IFERROR(IF(OR($H32/BA32&gt;#REF!,$H32/BA32&lt;#REF!),"nmf ",$H32/BA32),"n/a ")</f>
+        <f>IFERROR($H32/AZ32,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y32" s="16" t="str">
-        <f>IFERROR(IF(OR($H32/BC32&gt;#REF!,$H32/BC32&lt;#REF!),"nmf ",$H32/BC32),"n/a ")</f>
+        <f>IFERROR($H32/BB32,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z32" s="16" t="str">
-        <f>IFERROR(IF(OR($H32/BD32&gt;#REF!,$H32/BD32&lt;#REF!),"nmf ",$H32/BD32),"n/a ")</f>
+        <f>IFERROR($H32/BC32,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA32" s="16" t="str">
-        <f>IFERROR(IF(OR($H32/BE32&gt;#REF!,$H32/BE32&lt;#REF!),"nmf ",$H32/BE32),"n/a ")</f>
+        <f>IFERROR($H32/BD32,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB32" s="33" t="str">
-        <f t="shared" si="106"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="48"/>
+        <v/>
       </c>
       <c r="AC32" s="33" t="str">
-        <f t="shared" si="107"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="48"/>
+        <v/>
       </c>
       <c r="AD32" s="33" t="str">
-        <f t="shared" si="108"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="43"/>
+        <v/>
       </c>
       <c r="AE32" s="33" t="str">
-        <f t="shared" si="109"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="44"/>
+        <v/>
       </c>
       <c r="AF32" s="33" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG32" s="33" t="str">
-        <f>IFERROR((BM32/AW32)-1,"n/a ")</f>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH32" s="33" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI32" s="33" t="str">
-        <f t="shared" si="112"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ32" s="33" t="str">
-        <f t="shared" si="113"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK32" s="33" t="str">
-        <f t="shared" si="114"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL32" s="33" t="str">
-        <f t="shared" si="115"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM32" s="72"/>
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ32" s="83" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK32" s="83" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL32" s="72"/>
+      <c r="AN32" s="20" t="str" cm="1">
+        <f t="array" ref="AN32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO32" s="20" t="str" cm="1">
-        <f t="array" ref="AO32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP32" s="20" t="str" cm="1">
@@ -7580,12 +7594,12 @@
         <f t="array" ref="AQ32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR32" s="20" t="str" cm="1">
-        <f t="array" ref="AR32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS32" s="20" t="str" cm="1">
+        <f t="array" ref="AS32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT32" s="20" t="str" cm="1">
-        <f t="array" ref="AT32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU32" s="20" t="str" cm="1">
@@ -7596,8 +7610,8 @@
         <f t="array" ref="AV32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW32" s="20" t="str" cm="1">
-        <f t="array" ref="AW32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX32" s="13" t="str" cm="1">
+        <f t="array" ref="AX32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY32" s="13" t="str" cm="1">
@@ -7608,8 +7622,8 @@
         <f t="array" ref="AZ32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA32" s="13" t="str" cm="1">
-        <f t="array" ref="BA32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB32" s="13" t="str" cm="1">
+        <f t="array" ref="BB32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC32" s="13" t="str" cm="1">
@@ -7620,45 +7634,45 @@
         <f t="array" ref="BD32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE32" s="13" t="str" cm="1">
-        <f t="array" ref="BE32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG32" s="66" t="str" cm="1">
-        <f t="array" ref="BG32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF32" s="66" t="str" cm="1">
+        <f t="array" ref="BF32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG32" s="19" t="str" cm="1">
+        <f t="array" ref="BG32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH32" s="19" t="str" cm="1">
-        <f t="array" ref="BH32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI32" s="19" t="str" cm="1">
-        <f t="array" ref="BI32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ32" s="19" t="str" cm="1">
-        <f t="array" ref="BJ32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK32" s="37" t="e">
-        <f t="shared" si="116"/>
+        <f t="array" ref="BI32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ32" s="37" t="e">
+        <f t="shared" si="47"/>
         <v>#VALUE!</v>
       </c>
-      <c r="BL32" s="19" t="str" cm="1">
-        <f t="array" ref="BL32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK32" s="19" t="str" cm="1">
+        <f t="array" ref="BK32">IF($B32="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM32" s="20" t="str">
+        <f>IFERROR($AO32*$BR32,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN32" s="20" t="str">
-        <f>IFERROR($AP32*$BR32,"n/a")</f>
+        <f>IFERROR($AP32*BS32,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO32" s="20" t="str">
-        <f t="shared" si="117"/>
+        <f>IFERROR($AQ32*$BT32,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP32" s="20" t="str">
-        <f>IFERROR($AR32*$BT32,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ32" s="44" t="str">
+        <f>IF($B32="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR32" s="44" t="str">
         <f>IF($B32="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B32,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -7686,27 +7700,27 @@
         <v/>
       </c>
       <c r="BZ32" s="62" t="str">
-        <f t="shared" si="118"/>
+        <f>IFERROR(IF(CD32/AO32&lt;0,"nmf ",CD32/AO32),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA32" s="62" t="str">
-        <f t="shared" si="119"/>
+        <f>IFERROR(IF(CE32/AP32&lt;0,"nmf ",CE32/AP32),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB32" s="62" t="str">
-        <f t="shared" si="120"/>
+        <f>IFERROR(IF(CF32/AQ32&lt;0,"nmf ",CF32/AQ32),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD32" s="20" t="str">
-        <f t="shared" si="121"/>
+        <f>IFERROR(BR32*AO32,"--")</f>
         <v>--</v>
       </c>
       <c r="CE32" s="20" t="str">
-        <f t="shared" si="122"/>
+        <f>IFERROR(BS32*AP32,"--")</f>
         <v>--</v>
       </c>
       <c r="CF32" s="20" t="str">
-        <f t="shared" si="123"/>
+        <f>IFERROR(BT32*AQ32,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -7737,116 +7751,116 @@
         <v/>
       </c>
       <c r="L33" s="16" t="str">
-        <f t="shared" si="96"/>
+        <f>IFERROR(IF(OR($K33/AN33&gt;L$4,$K33/AN33&lt;L$3),"nmf ",$K33/AN33),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M33" s="16" t="str">
-        <f t="shared" si="97"/>
+        <f>IFERROR(IF(OR($K33/AO33&gt;M$4,$K33/AO33&lt;M$3),"nmf ",$K33/AO33),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N33" s="16" t="str">
-        <f t="shared" si="98"/>
+        <f>IFERROR(IF(OR($K33/AP33&gt;N$4,$K33/AP33&lt;N$3),"nmf ",$K33/AP33),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O33" s="16" t="str">
-        <f t="shared" si="99"/>
+        <f>IFERROR(IF(OR($K33/AQ33&gt;O$4,$K33/AQ33&lt;O$3),"nmf ",$K33/AQ33),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P33" s="16" t="str">
-        <f t="shared" si="100"/>
+        <f>IFERROR(IF(OR($K33/AS33&gt;P$4,$K33/AS33&lt;P$3),"nmf ",$K33/AS33),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q33" s="16" t="str">
-        <f t="shared" si="101"/>
+        <f>IFERROR(IF(OR($K33/AT33&gt;Q$4,$K33/AT33&lt;Q$3),"nmf ",$K33/AT33),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R33" s="16" t="str">
-        <f t="shared" si="102"/>
+        <f>IFERROR(IF(OR($K33/AU33&gt;R$4,$K33/AU33&lt;R$3),"nmf ",$K33/AU33),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S33" s="16" t="str">
-        <f t="shared" si="103"/>
+        <f>IFERROR(IF(OR($K33/AV33&gt;S$4,$K33/AV33&lt;S$3),"nmf ",$K33/AV33),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T33" s="33" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="41"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U33" s="33" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="42"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V33" s="16" t="str">
-        <f>IFERROR(IF(OR($H33/AY33&gt;#REF!,$H33/AY33&lt;#REF!),"nmf ",$H33/AY33),"n/a ")</f>
+        <f>IFERROR($H33/AX33,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W33" s="16" t="str">
-        <f>IFERROR(IF(OR($H33/AZ33&gt;#REF!,$H33/AZ33&lt;#REF!),"nmf ",$H33/AZ33),"n/a ")</f>
+        <f>IFERROR($H33/AY33,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X33" s="16" t="str">
-        <f>IFERROR(IF(OR($H33/BA33&gt;#REF!,$H33/BA33&lt;#REF!),"nmf ",$H33/BA33),"n/a ")</f>
+        <f>IFERROR($H33/AZ33,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y33" s="16" t="str">
-        <f>IFERROR(IF(OR($H33/BC33&gt;#REF!,$H33/BC33&lt;#REF!),"nmf ",$H33/BC33),"n/a ")</f>
+        <f>IFERROR($H33/BB33,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z33" s="16" t="str">
-        <f>IFERROR(IF(OR($H33/BD33&gt;#REF!,$H33/BD33&lt;#REF!),"nmf ",$H33/BD33),"n/a ")</f>
+        <f>IFERROR($H33/BC33,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA33" s="16" t="str">
-        <f>IFERROR(IF(OR($H33/BE33&gt;#REF!,$H33/BE33&lt;#REF!),"nmf ",$H33/BE33),"n/a ")</f>
+        <f>IFERROR($H33/BD33,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB33" s="33" t="str">
-        <f t="shared" si="106"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="48"/>
+        <v/>
       </c>
       <c r="AC33" s="33" t="str">
-        <f t="shared" si="107"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="48"/>
+        <v/>
       </c>
       <c r="AD33" s="33" t="str">
-        <f t="shared" si="108"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="43"/>
+        <v/>
       </c>
       <c r="AE33" s="33" t="str">
-        <f t="shared" si="109"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="44"/>
+        <v/>
       </c>
       <c r="AF33" s="33" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG33" s="33" t="str">
-        <f t="shared" ref="AG33:AG34" si="124">IFERROR((BM33/AW33)-1,"n/a ")</f>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH33" s="33" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI33" s="33" t="str">
-        <f t="shared" si="112"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ33" s="33" t="str">
-        <f t="shared" si="113"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK33" s="33" t="str">
-        <f t="shared" si="114"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL33" s="33" t="str">
-        <f t="shared" si="115"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM33" s="72"/>
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ33" s="83" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK33" s="83" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL33" s="72"/>
+      <c r="AN33" s="20" t="str" cm="1">
+        <f t="array" ref="AN33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO33" s="20" t="str" cm="1">
-        <f t="array" ref="AO33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP33" s="20" t="str" cm="1">
@@ -7857,12 +7871,12 @@
         <f t="array" ref="AQ33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR33" s="20" t="str" cm="1">
-        <f t="array" ref="AR33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS33" s="20" t="str" cm="1">
+        <f t="array" ref="AS33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT33" s="20" t="str" cm="1">
-        <f t="array" ref="AT33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU33" s="20" t="str" cm="1">
@@ -7873,8 +7887,8 @@
         <f t="array" ref="AV33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW33" s="20" t="str" cm="1">
-        <f t="array" ref="AW33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX33" s="13" t="str" cm="1">
+        <f t="array" ref="AX33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY33" s="13" t="str" cm="1">
@@ -7885,8 +7899,8 @@
         <f t="array" ref="AZ33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA33" s="13" t="str" cm="1">
-        <f t="array" ref="BA33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB33" s="13" t="str" cm="1">
+        <f t="array" ref="BB33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC33" s="13" t="str" cm="1">
@@ -7897,45 +7911,45 @@
         <f t="array" ref="BD33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE33" s="13" t="str" cm="1">
-        <f t="array" ref="BE33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG33" s="66" t="str" cm="1">
-        <f t="array" ref="BG33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF33" s="66" t="str" cm="1">
+        <f t="array" ref="BF33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG33" s="19" t="str" cm="1">
+        <f t="array" ref="BG33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH33" s="19" t="str" cm="1">
-        <f t="array" ref="BH33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI33" s="19" t="str" cm="1">
-        <f t="array" ref="BI33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ33" s="19" t="str" cm="1">
-        <f t="array" ref="BJ33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK33" s="37" t="e">
-        <f t="shared" si="116"/>
+        <f t="array" ref="BI33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ33" s="37" t="e">
+        <f t="shared" si="47"/>
         <v>#VALUE!</v>
       </c>
-      <c r="BL33" s="19" t="str" cm="1">
-        <f t="array" ref="BL33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK33" s="19" t="str" cm="1">
+        <f t="array" ref="BK33">IF($B33="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM33" s="20" t="str">
+        <f t="shared" ref="BM33:BM34" si="52">IFERROR($AO33*$BR33,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN33" s="20" t="str">
-        <f t="shared" ref="BN33:BN34" si="125">IFERROR($AP33*$BR33,"n/a")</f>
+        <f>IFERROR($AP33*BS33,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO33" s="20" t="str">
-        <f t="shared" si="117"/>
+        <f>IFERROR($AQ33*$BT33,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP33" s="20" t="str">
-        <f t="shared" ref="BP33:BP34" si="126">IFERROR($AR33*$BT33,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ33" s="44" t="str">
+        <f>IF($B33="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR33" s="44" t="str">
         <f>IF($B33="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B33,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -7963,27 +7977,27 @@
         <v/>
       </c>
       <c r="BZ33" s="62" t="str">
-        <f t="shared" si="118"/>
+        <f>IFERROR(IF(CD33/AO33&lt;0,"nmf ",CD33/AO33),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA33" s="62" t="str">
-        <f t="shared" si="119"/>
+        <f>IFERROR(IF(CE33/AP33&lt;0,"nmf ",CE33/AP33),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB33" s="62" t="str">
-        <f t="shared" si="120"/>
+        <f>IFERROR(IF(CF33/AQ33&lt;0,"nmf ",CF33/AQ33),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD33" s="20" t="str">
-        <f t="shared" si="121"/>
+        <f>IFERROR(BR33*AO33,"--")</f>
         <v>--</v>
       </c>
       <c r="CE33" s="20" t="str">
-        <f t="shared" si="122"/>
+        <f>IFERROR(BS33*AP33,"--")</f>
         <v>--</v>
       </c>
       <c r="CF33" s="20" t="str">
-        <f t="shared" si="123"/>
+        <f>IFERROR(BT33*AQ33,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -8014,116 +8028,116 @@
         <v/>
       </c>
       <c r="L34" s="16" t="str">
-        <f t="shared" si="96"/>
+        <f>IFERROR(IF(OR($K34/AN34&gt;L$4,$K34/AN34&lt;L$3),"nmf ",$K34/AN34),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M34" s="16" t="str">
-        <f t="shared" si="97"/>
+        <f>IFERROR(IF(OR($K34/AO34&gt;M$4,$K34/AO34&lt;M$3),"nmf ",$K34/AO34),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N34" s="16" t="str">
-        <f t="shared" si="98"/>
+        <f>IFERROR(IF(OR($K34/AP34&gt;N$4,$K34/AP34&lt;N$3),"nmf ",$K34/AP34),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O34" s="16" t="str">
-        <f t="shared" si="99"/>
+        <f>IFERROR(IF(OR($K34/AQ34&gt;O$4,$K34/AQ34&lt;O$3),"nmf ",$K34/AQ34),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P34" s="16" t="str">
-        <f t="shared" si="100"/>
+        <f>IFERROR(IF(OR($K34/AS34&gt;P$4,$K34/AS34&lt;P$3),"nmf ",$K34/AS34),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q34" s="16" t="str">
-        <f t="shared" si="101"/>
+        <f>IFERROR(IF(OR($K34/AT34&gt;Q$4,$K34/AT34&lt;Q$3),"nmf ",$K34/AT34),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R34" s="16" t="str">
-        <f t="shared" si="102"/>
+        <f>IFERROR(IF(OR($K34/AU34&gt;R$4,$K34/AU34&lt;R$3),"nmf ",$K34/AU34),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S34" s="16" t="str">
-        <f t="shared" si="103"/>
+        <f>IFERROR(IF(OR($K34/AV34&gt;S$4,$K34/AV34&lt;S$3),"nmf ",$K34/AV34),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T34" s="33" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="41"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U34" s="33" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="42"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V34" s="16" t="str">
-        <f>IFERROR(IF(OR($H34/AY34&gt;#REF!,$H34/AY34&lt;#REF!),"nmf ",$H34/AY34),"n/a ")</f>
+        <f>IFERROR($H34/AX34,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W34" s="16" t="str">
-        <f>IFERROR(IF(OR($H34/AZ34&gt;#REF!,$H34/AZ34&lt;#REF!),"nmf ",$H34/AZ34),"n/a ")</f>
+        <f>IFERROR($H34/AY34,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X34" s="16" t="str">
-        <f>IFERROR(IF(OR($H34/BA34&gt;#REF!,$H34/BA34&lt;#REF!),"nmf ",$H34/BA34),"n/a ")</f>
+        <f>IFERROR($H34/AZ34,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y34" s="16" t="str">
-        <f>IFERROR(IF(OR($H34/BC34&gt;#REF!,$H34/BC34&lt;#REF!),"nmf ",$H34/BC34),"n/a ")</f>
+        <f>IFERROR($H34/BB34,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z34" s="16" t="str">
-        <f>IFERROR(IF(OR($H34/BD34&gt;#REF!,$H34/BD34&lt;#REF!),"nmf ",$H34/BD34),"n/a ")</f>
+        <f>IFERROR($H34/BC34,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA34" s="16" t="str">
-        <f>IFERROR(IF(OR($H34/BE34&gt;#REF!,$H34/BE34&lt;#REF!),"nmf ",$H34/BE34),"n/a ")</f>
+        <f>IFERROR($H34/BD34,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB34" s="33" t="str">
-        <f t="shared" si="106"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="48"/>
+        <v/>
       </c>
       <c r="AC34" s="33" t="str">
-        <f t="shared" si="107"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="48"/>
+        <v/>
       </c>
       <c r="AD34" s="33" t="str">
-        <f t="shared" si="108"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="43"/>
+        <v/>
       </c>
       <c r="AE34" s="33" t="str">
-        <f t="shared" si="109"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="44"/>
+        <v/>
       </c>
       <c r="AF34" s="33" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG34" s="33" t="str">
-        <f t="shared" si="124"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH34" s="33" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI34" s="33" t="str">
-        <f t="shared" si="112"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ34" s="33" t="str">
-        <f t="shared" si="113"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK34" s="33" t="str">
-        <f t="shared" si="114"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL34" s="33" t="str">
-        <f t="shared" si="115"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM34" s="72"/>
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ34" s="83" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK34" s="83" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL34" s="72"/>
+      <c r="AN34" s="20" t="str" cm="1">
+        <f t="array" ref="AN34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO34" s="20" t="str" cm="1">
-        <f t="array" ref="AO34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP34" s="20" t="str" cm="1">
@@ -8134,12 +8148,12 @@
         <f t="array" ref="AQ34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR34" s="20" t="str" cm="1">
-        <f t="array" ref="AR34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS34" s="20" t="str" cm="1">
+        <f t="array" ref="AS34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT34" s="20" t="str" cm="1">
-        <f t="array" ref="AT34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU34" s="20" t="str" cm="1">
@@ -8150,8 +8164,8 @@
         <f t="array" ref="AV34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW34" s="20" t="str" cm="1">
-        <f t="array" ref="AW34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX34" s="13" t="str" cm="1">
+        <f t="array" ref="AX34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY34" s="13" t="str" cm="1">
@@ -8162,8 +8176,8 @@
         <f t="array" ref="AZ34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA34" s="13" t="str" cm="1">
-        <f t="array" ref="BA34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB34" s="13" t="str" cm="1">
+        <f t="array" ref="BB34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC34" s="13" t="str" cm="1">
@@ -8174,45 +8188,45 @@
         <f t="array" ref="BD34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE34" s="13" t="str" cm="1">
-        <f t="array" ref="BE34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG34" s="66" t="str" cm="1">
-        <f t="array" ref="BG34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF34" s="66" t="str" cm="1">
+        <f t="array" ref="BF34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG34" s="19" t="str" cm="1">
+        <f t="array" ref="BG34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH34" s="19" t="str" cm="1">
-        <f t="array" ref="BH34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI34" s="19" t="str" cm="1">
-        <f t="array" ref="BI34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ34" s="19" t="str" cm="1">
-        <f t="array" ref="BJ34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK34" s="37" t="e">
-        <f t="shared" si="116"/>
+        <f t="array" ref="BI34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ34" s="37" t="e">
+        <f t="shared" si="47"/>
         <v>#VALUE!</v>
       </c>
-      <c r="BL34" s="19" t="str" cm="1">
-        <f t="array" ref="BL34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK34" s="19" t="str" cm="1">
+        <f t="array" ref="BK34">IF($B34="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM34" s="20" t="str">
+        <f t="shared" si="52"/>
+        <v>n/a</v>
       </c>
       <c r="BN34" s="20" t="str">
-        <f t="shared" si="125"/>
+        <f>IFERROR($AP34*BS34,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO34" s="20" t="str">
-        <f t="shared" si="117"/>
+        <f>IFERROR($AQ34*$BT34,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP34" s="20" t="str">
-        <f t="shared" si="126"/>
-        <v>n/a</v>
+      <c r="BQ34" s="44" t="str">
+        <f>IF($B34="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR34" s="44" t="str">
         <f>IF($B34="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B34,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -8240,27 +8254,27 @@
         <v/>
       </c>
       <c r="BZ34" s="62" t="str">
-        <f t="shared" si="118"/>
+        <f>IFERROR(IF(CD34/AO34&lt;0,"nmf ",CD34/AO34),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA34" s="62" t="str">
-        <f t="shared" si="119"/>
+        <f>IFERROR(IF(CE34/AP34&lt;0,"nmf ",CE34/AP34),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB34" s="62" t="str">
-        <f t="shared" si="120"/>
+        <f>IFERROR(IF(CF34/AQ34&lt;0,"nmf ",CF34/AQ34),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD34" s="20" t="str">
-        <f t="shared" si="121"/>
+        <f>IFERROR(BR34*AO34,"--")</f>
         <v>--</v>
       </c>
       <c r="CE34" s="20" t="str">
-        <f t="shared" si="122"/>
+        <f>IFERROR(BS34*AP34,"--")</f>
         <v>--</v>
       </c>
       <c r="CF34" s="20" t="str">
-        <f t="shared" si="123"/>
+        <f>IFERROR(BT34*AQ34,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -8291,116 +8305,116 @@
         <v/>
       </c>
       <c r="L35" s="16" t="str">
-        <f t="shared" si="96"/>
+        <f>IFERROR(IF(OR($K35/AN35&gt;L$4,$K35/AN35&lt;L$3),"nmf ",$K35/AN35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M35" s="16" t="str">
-        <f t="shared" si="97"/>
+        <f>IFERROR(IF(OR($K35/AO35&gt;M$4,$K35/AO35&lt;M$3),"nmf ",$K35/AO35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N35" s="16" t="str">
-        <f t="shared" si="98"/>
+        <f>IFERROR(IF(OR($K35/AP35&gt;N$4,$K35/AP35&lt;N$3),"nmf ",$K35/AP35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O35" s="16" t="str">
-        <f t="shared" si="99"/>
+        <f>IFERROR(IF(OR($K35/AQ35&gt;O$4,$K35/AQ35&lt;O$3),"nmf ",$K35/AQ35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P35" s="16" t="str">
-        <f t="shared" si="100"/>
+        <f>IFERROR(IF(OR($K35/AS35&gt;P$4,$K35/AS35&lt;P$3),"nmf ",$K35/AS35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q35" s="16" t="str">
-        <f t="shared" si="101"/>
+        <f>IFERROR(IF(OR($K35/AT35&gt;Q$4,$K35/AT35&lt;Q$3),"nmf ",$K35/AT35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R35" s="16" t="str">
-        <f t="shared" si="102"/>
+        <f>IFERROR(IF(OR($K35/AU35&gt;R$4,$K35/AU35&lt;R$3),"nmf ",$K35/AU35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S35" s="16" t="str">
-        <f t="shared" si="103"/>
+        <f>IFERROR(IF(OR($K35/AV35&gt;S$4,$K35/AV35&lt;S$3),"nmf ",$K35/AV35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T35" s="33" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="41"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U35" s="33" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="42"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V35" s="16" t="str">
-        <f>IFERROR(IF(OR($H35/AY35&gt;#REF!,$H35/AY35&lt;#REF!),"nmf ",$H35/AY35),"n/a ")</f>
+        <f>IFERROR($H35/AX35,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W35" s="16" t="str">
-        <f>IFERROR(IF(OR($H35/AZ35&gt;#REF!,$H35/AZ35&lt;#REF!),"nmf ",$H35/AZ35),"n/a ")</f>
+        <f>IFERROR($H35/AY35,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X35" s="16" t="str">
-        <f>IFERROR(IF(OR($H35/BA35&gt;#REF!,$H35/BA35&lt;#REF!),"nmf ",$H35/BA35),"n/a ")</f>
+        <f>IFERROR($H35/AZ35,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y35" s="16" t="str">
-        <f>IFERROR(IF(OR($H35/BC35&gt;#REF!,$H35/BC35&lt;#REF!),"nmf ",$H35/BC35),"n/a ")</f>
+        <f>IFERROR($H35/BB35,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z35" s="16" t="str">
-        <f>IFERROR(IF(OR($H35/BD35&gt;#REF!,$H35/BD35&lt;#REF!),"nmf ",$H35/BD35),"n/a ")</f>
+        <f>IFERROR($H35/BC35,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA35" s="16" t="str">
-        <f>IFERROR(IF(OR($H35/BE35&gt;#REF!,$H35/BE35&lt;#REF!),"nmf ",$H35/BE35),"n/a ")</f>
+        <f>IFERROR($H35/BD35,"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB35" s="33" t="str">
-        <f t="shared" si="106"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="48"/>
+        <v/>
       </c>
       <c r="AC35" s="33" t="str">
-        <f t="shared" si="107"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="48"/>
+        <v/>
       </c>
       <c r="AD35" s="33" t="str">
-        <f t="shared" si="108"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="43"/>
+        <v/>
       </c>
       <c r="AE35" s="33" t="str">
-        <f t="shared" si="109"/>
-        <v xml:space="preserve">n/a </v>
+        <f t="shared" si="44"/>
+        <v/>
       </c>
       <c r="AF35" s="33" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG35" s="33" t="str">
-        <f>IFERROR((BM35/AW35)-1,"n/a ")</f>
+        <f t="shared" si="49"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH35" s="33" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="45"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI35" s="33" t="str">
-        <f t="shared" si="112"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ35" s="33" t="str">
-        <f t="shared" si="113"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK35" s="33" t="str">
-        <f t="shared" si="114"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL35" s="33" t="str">
-        <f t="shared" si="115"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM35" s="72"/>
+        <f t="shared" si="46"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ35" s="83" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK35" s="83" t="str">
+        <f t="shared" si="51"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL35" s="72"/>
+      <c r="AN35" s="20" t="str" cm="1">
+        <f t="array" ref="AN35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_REV",AN$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
       <c r="AO35" s="20" t="str" cm="1">
-        <f t="array" ref="AO35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_REV",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AO35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_REV_EST",AO$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AP35" s="20" t="str" cm="1">
@@ -8411,12 +8425,12 @@
         <f t="array" ref="AQ35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_REV_EST",AQ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AR35" s="20" t="str" cm="1">
-        <f t="array" ref="AR35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_REV_EST",AR$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AS35" s="20" t="str" cm="1">
+        <f t="array" ref="AS35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EBITDA",AS$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AT35" s="20" t="str" cm="1">
-        <f t="array" ref="AT35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EBITDA",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="AT35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EBITDA_EST",AT$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="AU35" s="20" t="str" cm="1">
@@ -8427,8 +8441,8 @@
         <f t="array" ref="AV35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EBITDA_EST",AV$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
-      <c r="AW35" s="20" t="str" cm="1">
-        <f t="array" ref="AW35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EBITDA_EST",AW$7,$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+      <c r="AX35" s="13" t="str" cm="1">
+        <f t="array" ref="AX35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EPS_EST",AX$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="AY35" s="13" t="str" cm="1">
@@ -8439,8 +8453,8 @@
         <f t="array" ref="AZ35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EPS_EST",AZ$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BA35" s="13" t="str" cm="1">
-        <f t="array" ref="BA35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_EPS_EST",BA$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
+      <c r="BB35" s="13" t="str" cm="1">
+        <f t="array" ref="BB35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_CFPS_EST",BB$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
       <c r="BC35" s="13" t="str" cm="1">
@@ -8451,45 +8465,45 @@
         <f t="array" ref="BD35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_CFPS_EST",BD$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
         <v/>
       </c>
-      <c r="BE35" s="13" t="str" cm="1">
-        <f t="array" ref="BE35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_CFPS_EST",BE$7,$F$2,"Options:Curr="&amp;$F$3&amp;", NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BG35" s="66" t="str" cm="1">
-        <f t="array" ref="BG35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+      <c r="BF35" s="66" t="str" cm="1">
+        <f t="array" ref="BF35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_DIV_YIELD",WORKDAY($F$2+1,-1),"Options: NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BG35" s="19" t="str" cm="1">
+        <f t="array" ref="BG35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BH35" s="19" t="str" cm="1">
-        <f t="array" ref="BH35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <f t="array" ref="BH35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
         <v/>
       </c>
       <c r="BI35" s="19" t="str" cm="1">
-        <f t="array" ref="BI35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_TOTAL_DEBT","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BJ35" s="19" t="str" cm="1">
-        <f t="array" ref="BJ35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
-      </c>
-      <c r="BK35" s="37" t="e">
-        <f>+BI35-BJ35</f>
+        <f t="array" ref="BI35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_CASH_ST_INVEST","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BJ35" s="37" t="e">
+        <f>+BH35-BI35</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BL35" s="19" t="str" cm="1">
-        <f t="array" ref="BL35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
-        <v/>
+      <c r="BK35" s="19" t="str" cm="1">
+        <f t="array" ref="BK35">IF($B35="","",_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"IQ_TOTAL_EQUITY","FQ0",$F$2,"Options:Curr="&amp;$F$3&amp;", Mag=Millions, NA=--"))</f>
+        <v/>
+      </c>
+      <c r="BM35" s="20" t="str">
+        <f>IFERROR($AO35*$BR35,"n/a")</f>
+        <v>n/a</v>
       </c>
       <c r="BN35" s="20" t="str">
-        <f>IFERROR($AP35*$BR35,"n/a")</f>
+        <f>IFERROR($AP35*BS35,"n/a")</f>
         <v>n/a</v>
       </c>
       <c r="BO35" s="20" t="str">
-        <f t="shared" si="117"/>
+        <f>IFERROR($AQ35*$BT35,"n/a")</f>
         <v>n/a</v>
       </c>
-      <c r="BP35" s="20" t="str">
-        <f>IFERROR($AR35*$BT35,"n/a")</f>
-        <v>n/a</v>
+      <c r="BQ35" s="44" t="str">
+        <f>IF($B35="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_GROSS_MARGIN",BQ$7,$F$2,"Options: NA=--")/100,"--"))</f>
+        <v/>
       </c>
       <c r="BR35" s="44" t="str">
         <f>IF($B35="","",IFERROR(_xll.SNL.Clients.Office.Excel.Functions.SPG($B35,"SP_GROSS_MARGIN_EST",BR$7,$F$2,"Options: NA=--")/100,"--"))</f>
@@ -8517,27 +8531,27 @@
         <v/>
       </c>
       <c r="BZ35" s="62" t="str">
-        <f t="shared" si="118"/>
+        <f>IFERROR(IF(CD35/AO35&lt;0,"nmf ",CD35/AO35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CA35" s="62" t="str">
-        <f t="shared" si="119"/>
+        <f>IFERROR(IF(CE35/AP35&lt;0,"nmf ",CE35/AP35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CB35" s="62" t="str">
-        <f t="shared" si="120"/>
+        <f>IFERROR(IF(CF35/AQ35&lt;0,"nmf ",CF35/AQ35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="CD35" s="20" t="str">
-        <f t="shared" si="121"/>
+        <f>IFERROR(BR35*AO35,"--")</f>
         <v>--</v>
       </c>
       <c r="CE35" s="20" t="str">
-        <f t="shared" si="122"/>
+        <f>IFERROR(BS35*AP35,"--")</f>
         <v>--</v>
       </c>
       <c r="CF35" s="20" t="str">
-        <f t="shared" si="123"/>
+        <f>IFERROR(BT35*AQ35,"--")</f>
         <v>--</v>
       </c>
     </row>
@@ -8575,23 +8589,22 @@
       <c r="AJ36" s="17"/>
       <c r="AK36" s="17"/>
       <c r="AL36" s="17"/>
-      <c r="AM36" s="17"/>
-      <c r="AO36" s="19"/>
+      <c r="AN36" s="19"/>
+      <c r="AO36" s="13"/>
       <c r="AP36" s="13"/>
       <c r="AQ36" s="13"/>
-      <c r="AR36" s="13"/>
+      <c r="AT36" s="20"/>
       <c r="AU36" s="20"/>
       <c r="AV36" s="20"/>
-      <c r="AW36" s="20"/>
+      <c r="AX36" s="13"/>
       <c r="AY36" s="13"/>
       <c r="AZ36" s="13"/>
-      <c r="BA36" s="13"/>
+      <c r="BF36" s="19"/>
       <c r="BG36" s="19"/>
       <c r="BH36" s="19"/>
       <c r="BI36" s="19"/>
       <c r="BJ36" s="19"/>
       <c r="BK36" s="19"/>
-      <c r="BL36" s="19"/>
       <c r="BR36" s="45"/>
       <c r="BS36" s="45"/>
       <c r="BT36" s="45"/>
@@ -8632,98 +8645,94 @@
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P37" s="26" t="str">
-        <f t="shared" ref="P37:AL37" si="127">IFERROR(AVERAGE(P30:P35),"n/a ")</f>
+        <f t="shared" ref="P37:AK37" si="53">IFERROR(AVERAGE(P30:P35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q37" s="26" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R37" s="26" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S37" s="26" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T37" s="36" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U37" s="36" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="V37" s="26" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="W37" s="26" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="X37" s="26" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Y37" s="26" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Z37" s="26" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AA37" s="26" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AB37" s="36" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" ref="AB37" si="54">IFERROR(AVERAGE(AB30:AB35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AC37" s="36" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AD37" s="36" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AE37" s="36" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AF37" s="36" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" ref="AF37" si="55">IFERROR(AVERAGE(AF30:AF35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AG37" s="36" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AH37" s="36" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="53"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="AI37" s="36" t="str">
-        <f t="shared" si="127"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AJ37" s="36" t="str">
-        <f t="shared" si="127"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AK37" s="36" t="str">
-        <f t="shared" si="127"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AL37" s="36" t="str">
-        <f t="shared" si="127"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="AM37" s="36"/>
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ37" s="84" t="str">
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK37" s="84" t="str">
+        <f t="shared" si="53"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL37" s="36"/>
       <c r="BR37" s="45"/>
       <c r="BS37" s="45"/>
       <c r="BT37" s="45"/>
@@ -8772,7 +8781,6 @@
       <c r="AJ38" s="53"/>
       <c r="AK38" s="53"/>
       <c r="AL38" s="53"/>
-      <c r="AM38" s="53"/>
       <c r="BR38" s="45"/>
       <c r="BS38" s="45"/>
       <c r="BT38" s="45"/>
@@ -8801,110 +8809,106 @@
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M39" s="56" t="str">
-        <f t="shared" ref="M39:U39" si="128">IFERROR(AVERAGE(M10:M15,M20:M25,M30:M35),"n/a ")</f>
+        <f t="shared" ref="M39:U39" si="56">IFERROR(AVERAGE(M10:M15,M20:M25,M30:M35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N39" s="56" t="str">
-        <f t="shared" si="128"/>
+        <f t="shared" si="56"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O39" s="56" t="str">
-        <f t="shared" si="128"/>
+        <f t="shared" si="56"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P39" s="56" t="str">
-        <f t="shared" si="128"/>
+        <f t="shared" si="56"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q39" s="56" t="str">
-        <f t="shared" si="128"/>
+        <f t="shared" si="56"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R39" s="56" t="str">
-        <f t="shared" si="128"/>
+        <f t="shared" si="56"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S39" s="56" t="str">
-        <f t="shared" si="128"/>
+        <f t="shared" si="56"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T39" s="74" t="str">
-        <f t="shared" si="128"/>
+        <f t="shared" si="56"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U39" s="74" t="str">
-        <f t="shared" si="128"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="V39" s="56" t="e">
-        <f t="shared" ref="V39:AL39" si="129">AVERAGE(V10:V15,V20:V25)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W39" s="56" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X39" s="56" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y39" s="56" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z39" s="56" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA39" s="56" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB39" s="57" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC39" s="57" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD39" s="57" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE39" s="57" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF39" s="57" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG39" s="57" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH39" s="57" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI39" s="57" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ39" s="57" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK39" s="57" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL39" s="57" t="e">
-        <f t="shared" si="129"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM39" s="57"/>
+        <f t="shared" si="56"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V39" s="56" t="str">
+        <f t="shared" ref="V39:AK39" si="57">IFERROR(AVERAGE(V10:V15,V20:V25,V30:V35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W39" s="56" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X39" s="56" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y39" s="56" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z39" s="56" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA39" s="56" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB39" s="57" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC39" s="57" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD39" s="57" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE39" s="57" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF39" s="57" t="str">
+        <f t="shared" ref="AF39" si="58">IFERROR(AVERAGE(AF10:AF15,AF20:AF25,AF30:AF35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG39" s="57" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH39" s="57" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI39" s="57" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ39" s="85" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK39" s="85" t="str">
+        <f t="shared" si="57"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL39" s="57"/>
       <c r="BR39" s="46"/>
       <c r="BS39" s="46"/>
       <c r="BT39" s="46"/>
@@ -8919,7 +8923,7 @@
     <row r="40" spans="2:84" s="30" customFormat="1" ht="18" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B40" s="29"/>
       <c r="D40" s="50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E40" s="50"/>
       <c r="F40" s="50"/>
@@ -8929,114 +8933,110 @@
       <c r="J40" s="50"/>
       <c r="K40" s="50"/>
       <c r="L40" s="51">
-        <f t="shared" ref="L40:AL40" si="130">+IFERROR((SUM(L20:L25,L10:L15)-MAX(L10:L15,L20:L25)-MIN(L10:L15,L20:L25))/(COUNT(L20:L25,L10:L15)-2),"n/a ")</f>
+        <f t="shared" ref="L40:U40" si="59">+IFERROR((SUM(L20:L25,L10:L15)-MAX(L10:L15,L20:L25)-MIN(L10:L15,L20:L25))/(COUNT(L20:L25,L10:L15)-2),"n/a ")</f>
         <v>0</v>
       </c>
       <c r="M40" s="51">
-        <f t="shared" si="130"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="N40" s="51">
-        <f t="shared" si="130"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="O40" s="51">
-        <f t="shared" si="130"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="P40" s="51">
-        <f t="shared" si="130"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="Q40" s="51">
-        <f t="shared" si="130"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="R40" s="51">
-        <f t="shared" si="130"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="S40" s="51">
-        <f t="shared" si="130"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="T40" s="75">
-        <f t="shared" si="130"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="U40" s="75">
-        <f t="shared" si="130"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="V40" s="51">
-        <f t="shared" si="130"/>
+        <f t="shared" ref="V40:AK40" si="60">+IFERROR((SUM(V20:V25,V10:V15)-MAX(V10:V15,V20:V25)-MIN(V10:V15,V20:V25))/(COUNT(V20:V25,V10:V15)-2),"n/a ")</f>
         <v>0</v>
       </c>
       <c r="W40" s="51">
-        <f t="shared" si="130"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="X40" s="51">
-        <f t="shared" si="130"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="Y40" s="51">
-        <f t="shared" si="130"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="Z40" s="51">
-        <f t="shared" si="130"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AA40" s="51">
-        <f t="shared" si="130"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AB40" s="52">
-        <f t="shared" si="130"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AC40" s="52">
-        <f t="shared" si="130"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AD40" s="52">
-        <f t="shared" si="130"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AE40" s="52">
-        <f t="shared" si="130"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AF40" s="52">
-        <f t="shared" si="130"/>
+        <f t="shared" ref="AF40" si="61">+IFERROR((SUM(AF20:AF25,AF10:AF15)-MAX(AF10:AF15,AF20:AF25)-MIN(AF10:AF15,AF20:AF25))/(COUNT(AF20:AF25,AF10:AF15)-2),"n/a ")</f>
         <v>0</v>
       </c>
       <c r="AG40" s="52">
-        <f t="shared" si="130"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AH40" s="52">
-        <f t="shared" si="130"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AI40" s="52">
-        <f t="shared" si="130"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AJ40" s="52">
-        <f t="shared" si="130"/>
+      <c r="AJ40" s="86">
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AK40" s="52">
-        <f t="shared" si="130"/>
+      <c r="AK40" s="86">
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="AL40" s="52">
-        <f t="shared" si="130"/>
-        <v>0</v>
-      </c>
-      <c r="AM40" s="52"/>
+      <c r="AL40" s="52"/>
       <c r="BR40" s="46"/>
       <c r="BS40" s="46"/>
       <c r="BT40" s="46"/>
@@ -9051,7 +9051,7 @@
     <row r="41" spans="2:84" s="30" customFormat="1" ht="16.350000000000001" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="B41" s="29"/>
       <c r="D41" s="58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E41" s="58"/>
       <c r="F41" s="58"/>
@@ -9065,110 +9065,106 @@
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="M41" s="59" t="str">
-        <f t="shared" ref="M41:U41" si="131">IFERROR(MEDIAN(M20:M25,M10:M15,M30:M35),"n/a ")</f>
+        <f t="shared" ref="M41:U41" si="62">IFERROR(MEDIAN(M20:M25,M10:M15,M30:M35),"n/a ")</f>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="N41" s="59" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="62"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="O41" s="59" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="62"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="P41" s="59" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="62"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="Q41" s="59" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="62"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="R41" s="59" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="62"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="S41" s="59" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="62"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="T41" s="76" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="62"/>
         <v xml:space="preserve">n/a </v>
       </c>
       <c r="U41" s="76" t="str">
-        <f t="shared" si="131"/>
-        <v xml:space="preserve">n/a </v>
-      </c>
-      <c r="V41" s="59" t="e">
-        <f t="shared" ref="V41:AL41" si="132">+MEDIAN(V20:V25,V10:V15)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W41" s="59" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="X41" s="59" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y41" s="59" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z41" s="59" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA41" s="59" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB41" s="60" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC41" s="60" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD41" s="60" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE41" s="60" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF41" s="60" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG41" s="60" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH41" s="60" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI41" s="60" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ41" s="60" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="AK41" s="60" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="AL41" s="60" t="e">
-        <f t="shared" si="132"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="AM41" s="60"/>
+        <f t="shared" si="62"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="V41" s="59" t="str">
+        <f t="shared" ref="V41:AK41" si="63">IFERROR(MEDIAN(V20:V25,V10:V15,V30:V35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="W41" s="59" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="X41" s="59" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Y41" s="59" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="Z41" s="59" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AA41" s="59" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AB41" s="60" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AC41" s="60" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AD41" s="60" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AE41" s="60" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AF41" s="60" t="str">
+        <f t="shared" ref="AF41" si="64">IFERROR(MEDIAN(AF20:AF25,AF10:AF15,AF30:AF35),"n/a ")</f>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AG41" s="60" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AH41" s="60" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AI41" s="60" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AJ41" s="87" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AK41" s="87" t="str">
+        <f t="shared" si="63"/>
+        <v xml:space="preserve">n/a </v>
+      </c>
+      <c r="AL41" s="60"/>
       <c r="BR41" s="46"/>
       <c r="BS41" s="46"/>
       <c r="BT41" s="46"/>
@@ -9201,29 +9197,29 @@
     <sortCondition descending="1" ref="K10:K15"/>
   </sortState>
   <conditionalFormatting sqref="B10:B15">
-    <cfRule type="duplicateValues" dxfId="6" priority="59"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20:B25">
-    <cfRule type="duplicateValues" dxfId="5" priority="64"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30:B35">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:G15 G20:G25">
-    <cfRule type="expression" dxfId="3" priority="44">
+    <cfRule type="expression" dxfId="5" priority="46">
       <formula>I10="EUR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="45">
+    <cfRule type="expression" dxfId="4" priority="47">
       <formula>I10="CAD"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G30:G35">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>I30="EUR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>I30="CAD"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20:B25">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30:B35">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="19" fitToHeight="0" orientation="landscape" r:id="rId1"/>
